--- a/BOM_Projeto_Integrador.xlsx
+++ b/BOM_Projeto_Integrador.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Dados do Projeto" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lista de Compras'!$A$4:$H$188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lista de Compras'!$A$4:$H$187</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -574,7 +574,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Lista de materiais · gerada de 03_lista_materiais.md em 12/08/2026 22:07 · arquitetura 127 V CA → 24 V CC → 12 / 5 / 3,3 V</t>
+          <t>Lista de materiais · gerada de 03_lista_materiais.md em 13/08/2026 19:12 · arquitetura 127 V CA → 24 V CC → 12 / 5 / 3,3 V</t>
         </is>
       </c>
     </row>
@@ -888,22 +888,22 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>T1 — Módulo XL4016</t>
+          <t>⭐ Kit 2× Módulo LM2596 com display</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 kit</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Step-down 8 A / 300 W, CC+CV, Vin 8-40 V</t>
+          <t>Step-down 3 A, Vin até 40 V, saída ajustável, display LED vermelho de 3 dígitos integrado. Um módulo vira o T2, o outro vira o T3</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>12,0 V / 7,0 A</t>
+          <t>ver abaixo</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr"/>
@@ -919,22 +919,22 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>T2 — Módulo XL4015</t>
+          <t>→ T2 (poste P2, comando)</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Step-down 5 A, CC+CV (o do seu link)</t>
+          <t>1º módulo do kit — alimenta Arduino, Nextion, SD/RTC, lógica dos BTS, placa PI-1 e os LEDs da iluminação da maquete</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>5,10 V / 1,5 A</t>
+          <t>5,10 V</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
@@ -950,22 +950,22 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>T3 — Módulo XL4015</t>
+          <t>→ T3 (poste P3, auxiliares)</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Step-down 5 A, CC+CV (o do seu link)</t>
+          <t>2º módulo do kit — alimenta as fans internas e os coolers</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>12,0 V / 1,5 A</t>
+          <t>12,0 V</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr"/>
@@ -981,17 +981,17 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Dissipador de alumínio 40×40×20 mm</t>
+          <t>Kit LM2596 reserva</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1 kit</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Colado com fita térmica no CI e no diodo de cada módulo</t>
+          <t>Opcional mas recomendado. São os únicos conversores do projeto; queimar um na véspera sem reserva significa não apresentar</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -1012,17 +1012,17 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Fita térmica dupla face</t>
+          <t>Dissipador de alumínio ~20 × 15 × 10 mm</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Fixação dos dissipadores</t>
+          <t>⚠️ Obrigatório, colado no CI LM2596S de cada módulo. Sem ele o T3 passa dos 100 °C dentro do tubo — ver Doc 02 §2.8</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
@@ -1043,17 +1043,17 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Voltímetro digital 3 fios (0-100 V)</t>
+          <t>Fita térmica dupla face</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Leitor na frente do T2 e do T3. ⚠️ 3 fios (alimentação separada): o de 2 fios não lê 5,10 V de forma estável</t>
+          <t>Fixação dos dissipadores</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Voltímetro + amperímetro digital 3 fios</t>
+          <t>Acrílico transparente 1 mm</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 lâmina</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>Leitor na frente do T1 — mostra 12,0 V e a corrente da Peltier ao vivo</t>
+          <t>Janelas de visualização nos 3 tubos dos postes (~20 × 12 mm cada) — protege o display e mantém o visual fechado</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Acrílico 1 mm</t>
+          <t>Voltímetro + amperímetro digital 3 fios</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Janelinha de proteção dos 3 leitores</t>
+          <t>Único medidor comprado à parte — vai na caixa de derivação do P1, mostrando os 24,0 V do barramento e a corrente das Peltier ao vivo. Faixa: 0-100 V / 10 A</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>F1, F2, F3, F4, F5</t>
+          <t>F1, F2, F3 — entrada dos 3 ramais</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr"/>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Fusível mini automotivo 6 A</t>
+          <t>Fusível mini automotivo 10 A</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>F1 — ramal R1 (potência)</t>
+          <t>F1 — ramal R1 (potência 24 V, 6,0 A)</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr"/>
@@ -1210,17 +1210,17 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>3 usos + reservas</t>
+          <t>2 usos + 2 reservas</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>F2, F3 (ramais) e F4 (saída 5 V)</t>
+          <t>F2 (comando) e F3 (auxiliares)</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr"/>
@@ -1236,22 +1236,22 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Fusível mini automotivo 10 A</t>
+          <t>Terminal olhal M4 amarelo</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>1 uso + 1 reserva</t>
+          <t>Aterramento e barramento de 0 V</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>F5 — saída 12 V dos BTS</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr"/>
@@ -1261,61 +1261,33 @@
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Diodo Zener 5V6 / 5 W</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Crowbar de proteção do barramento 5 V</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>Saída do T2</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr"/>
-      <c r="G28" s="8" t="inlineStr"/>
-      <c r="H28" s="8">
-        <f>IF(C28*G28=0,"",C28*G28)</f>
-        <v/>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>M.1 — Base e estrutura</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Diodo Zener 13 V / 5 W</t>
+          <t>MDF 12 mm</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 chapa</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>Crowbar do barramento 12 V auxiliar</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>Saída do T3</t>
-        </is>
-      </c>
+          <t>1500 × 500 mm — tampo da base</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr"/>
       <c r="F29" s="11" t="inlineStr"/>
       <c r="G29" s="12" t="inlineStr"/>
       <c r="H29" s="12">
@@ -1325,28 +1297,24 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Diodo Zener 15 V / 5 W</t>
+          <t>MDF 15 mm</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Crowbar do barramento 12 V de potência</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>Saída do T1</t>
-        </is>
-      </c>
+          <t>Moldura perimetral 40 mm de altura (4 tiras)</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr"/>
       <c r="F30" s="7" t="inlineStr"/>
       <c r="G30" s="8" t="inlineStr"/>
       <c r="H30" s="8">
@@ -1356,28 +1324,24 @@
     </row>
     <row r="31">
       <c r="A31" s="9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Terminal olhal M4 amarelo</t>
+          <t>MDF 15 mm</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3 tiras</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>Aterramento e barramento de 0 V</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>Travessas de reforço 15 × 40 mm, com entalhe de 20 × 25 mm no centro</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr"/>
       <c r="F31" s="11" t="inlineStr"/>
       <c r="G31" s="12" t="inlineStr"/>
       <c r="H31" s="12">
@@ -1385,11 +1349,31 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>M.1 — Base e estrutura</t>
-        </is>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Pés de borracha antiderrapante</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Autoadesivos, Ø 25 mm — a base tem 1,5 m e pesa ~18 kg</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr"/>
+      <c r="F32" s="7" t="inlineStr"/>
+      <c r="G32" s="8" t="inlineStr"/>
+      <c r="H32" s="8">
+        <f>IF(C32*G32=0,"",C32*G32)</f>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -1398,17 +1382,17 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>MDF 12 mm</t>
+          <t>Conector circular GX16 8 pinos</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>1 chapa</t>
+          <t>1 par</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>1500 × 500 mm — tampo da base</t>
+          <t>Opcional — só na versão modular (união elétrica entre os 2 módulos)</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr"/>
@@ -1425,17 +1409,17 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>MDF 15 mm</t>
+          <t>Pinos-guia Ø 6 mm + buchas</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Moldura perimetral 40 mm de altura (4 tiras)</t>
+          <t>Opcional — alinhamento dos módulos</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr"/>
@@ -1452,17 +1436,17 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>MDF 15 mm</t>
+          <t>Alças de transporte</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>3 tiras</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>Travessas de reforço 15 × 40 mm, com entalhe de 20 × 25 mm no centro</t>
+          <t>Alça embutida de baú/case, laterais</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr"/>
@@ -1479,17 +1463,17 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Pés de borracha antiderrapante</t>
+          <t>Parafusos M5×20, M4×16, M3×12</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>kits</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Autoadesivos, Ø 25 mm — a base tem 1,5 m e pesa ~18 kg</t>
+          <t>Fixações gerais</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr"/>
@@ -1506,17 +1490,17 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Conector circular GX16 8 pinos</t>
+          <t>Insertos rosqueados M4/M5 p/ MDF</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>1 par</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>Opcional — só na versão modular (união elétrica entre os 2 módulos)</t>
+          <t>Evita espanar a rosca no MDF</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr"/>
@@ -1527,50 +1511,30 @@
         <v/>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Pinos-guia Ø 6 mm + buchas</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>Opcional — alinhamento dos módulos</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr"/>
-      <c r="F38" s="7" t="inlineStr"/>
-      <c r="G38" s="8" t="inlineStr"/>
-      <c r="H38" s="8">
-        <f>IF(C38*G38=0,"",C38*G38)</f>
-        <v/>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>M.2 — Subestação (caixa)</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Alças de transporte</t>
+          <t>MDF 9 mm ou acrílico opaco 4 mm</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Alça embutida de baú/case, laterais</t>
+          <t>Caixa 260 × 190 × 150 mm (L×P×A), frente voltada para a rua</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr"/>
@@ -1583,21 +1547,21 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Parafusos M5×20, M4×16, M3×12</t>
+          <t>Dobradiça pequena + fecho</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>kits</t>
+          <t>1 jogo</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Fixações gerais</t>
+          <t>Tampa de manutenção</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr"/>
@@ -1610,21 +1574,21 @@
     </row>
     <row r="41">
       <c r="A41" s="9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Insertos rosqueados M4/M5 p/ MDF</t>
+          <t>Tela metálica / alambrado miniatura</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Evita espanar a rosca no MDF</t>
+          <t>Cerca do pátio da subestação (tela de aço, malha 3 mm)</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr"/>
@@ -1635,11 +1599,31 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>M.2 — Subestação (caixa)</t>
-        </is>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Pedrisco / brita fina (aquário)</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>500 g</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>Piso do pátio da subestação — como nas subestações reais</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr"/>
+      <c r="F42" s="7" t="inlineStr"/>
+      <c r="G42" s="8" t="inlineStr"/>
+      <c r="H42" s="8">
+        <f>IF(C42*G42=0,"",C42*G42)</f>
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -1648,17 +1632,17 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>MDF 9 mm ou acrílico opaco 4 mm</t>
+          <t>Placa "PERIGO ALTA TENSÃO"</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>Caixa 260 × 190 × 150 mm (L×P×A), frente voltada para a rua</t>
+          <t>Impressa em papel adesivo, ~15 × 10 mm</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr"/>
@@ -1669,50 +1653,30 @@
         <v/>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>Dobradiça pequena + fecho</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>1 jogo</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>Tampa de manutenção</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr"/>
-      <c r="F44" s="7" t="inlineStr"/>
-      <c r="G44" s="8" t="inlineStr"/>
-      <c r="H44" s="8">
-        <f>IF(C44*G44=0,"",C44*G44)</f>
-        <v/>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>M.3 — Postes e linha de distribuição</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Tela metálica / alambrado miniatura</t>
+          <t>Tubo de alumínio Ø 8 mm</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,5 m</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>Cerca do pátio da subestação (tela de aço, malha 3 mm)</t>
+          <t>Cortar em 3 postes de 350 mm (300 mm visíveis + 50 mm de encaixe)</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr"/>
@@ -1725,21 +1689,21 @@
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Pedrisco / brita fina (aquário)</t>
+          <t>Barra chata de alumínio 12 × 2 mm</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>500 g</t>
+          <t>40 cm</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>Piso do pátio da subestação — como nas subestações reais</t>
+          <t>Cruzetas — 3 peças de 90 mm + 3 de 60 mm</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr"/>
@@ -1752,21 +1716,21 @@
     </row>
     <row r="47">
       <c r="A47" s="9" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Placa "PERIGO ALTA TENSÃO"</t>
+          <t>Fio rígido ENCAPADO 1,00 mm² VERMELHO ⬆</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 m</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>Impressa em papel adesivo, ~15 × 10 mm</t>
+          <t>Ramal R1 (potência, 6,0 A). ⚠️ Subiu de 0,75 para 1,00 mm² por causa da corrente das 2 Peltier. Nunca condutor nu — em CC qualquer ponte metálica é curto franco</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr"/>
@@ -1777,11 +1741,31 @@
         <v/>
       </c>
     </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>M.3 — Postes e linha de distribuição</t>
-        </is>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Fio rígido ENCAPADO 0,50 mm² MARROM</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>2 m</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>Ramal R2 (comando)</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr"/>
+      <c r="F48" s="7" t="inlineStr"/>
+      <c r="G48" s="8" t="inlineStr"/>
+      <c r="H48" s="8">
+        <f>IF(C48*G48=0,"",C48*G48)</f>
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -1790,17 +1774,17 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Tubo de alumínio Ø 8 mm</t>
+          <t>Fio rígido ENCAPADO 0,50 mm² CINZA</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>1,5 m</t>
+          <t>2 m</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Cortar em 3 postes de 350 mm (300 mm visíveis + 50 mm de encaixe)</t>
+          <t>Ramal R3 (auxiliares)</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr"/>
@@ -1817,17 +1801,17 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Barra chata de alumínio 12 × 2 mm</t>
+          <t>Fio rígido ENCAPADO 1,50 mm² AZUL CLARO ⬆</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>40 cm</t>
+          <t>2 m</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Cruzetas — 3 peças de 90 mm + 3 de 60 mm</t>
+          <t>Retorno comum 0 V — o "neutro" da linha, 40 mm abaixo da cruzeta. Subiu de 1,00 para 1,50 mm²: conduz a soma dos 3 ramais (6,9 A)</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr"/>
@@ -1844,17 +1828,17 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Fio rígido ENCAPADO 0,75 mm² VERMELHO</t>
+          <t>Contas/miçangas marrom ou branca Ø 6 mm</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>2 m</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>Ramal R1 (potência). ⚠️ Nunca condutor nu — em CC qualquer ponte metálica é curto franco</t>
+          <t>Isoladores de pino da cruzeta</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr"/>
@@ -1871,17 +1855,17 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Fio rígido ENCAPADO 0,50 mm² MARROM</t>
+          <t>Tubo de PVC Ø 50 mm</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>2 m</t>
+          <t>24 cm</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Ramal R2 (comando)</t>
+          <t>Corpos dos 3 postes — 8 cm cada: T2 (P2), T3 (P3) e a caixa de derivação (P1). Agora os três têm o mesmo diâmetro, porque o P1 deixou de ter conversor</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr"/>
@@ -1898,17 +1882,17 @@
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>Fio rígido ENCAPADO 0,50 mm² CINZA</t>
+          <t>Tampa/cap PVC Ø 50 mm</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>2 m</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>Ramal R3 (auxiliares)</t>
+          <t>Tampas dos 3 corpos</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr"/>
@@ -1925,17 +1909,17 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Fio rígido ENCAPADO 1,00 mm² AZUL CLARO</t>
+          <t>Cinta de alumínio 10 mm</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>2 m</t>
+          <t>1 m</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Retorno comum 0 V — o "neutro" da linha, 40 mm abaixo da cruzeta</t>
+          <t>Fixação dos transformadores e da caixa de derivação nos postes</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr"/>
@@ -1952,17 +1936,17 @@
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>Contas/miçangas marrom ou branca Ø 6 mm</t>
+          <t>Bornes de emenda pequenos (2 ou 3 vias)</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>Isoladores de pino da cruzeta</t>
+          <t>Dentro da caixa de derivação do P1 — ali os 24 V só se distribuem, não se transformam</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr"/>
@@ -1979,17 +1963,17 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Tubo de PVC Ø 63 mm</t>
+          <t>Flange/base de fixação dos postes</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>10 cm</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Corpo do transformador T1 (maior — comporta o XL4016 + cooler)</t>
+          <t>Podem ser feitas com sobra de MDF + insertos M4</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr"/>
@@ -2006,17 +1990,17 @@
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>Tubo de PVC Ø 50 mm</t>
+          <t>Etiquetas adesivas impressas</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>16 cm</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>Corpo dos transformadores T2 e T3</t>
+          <t>Identificação dos corpos: "P1 — DERIVAÇÃO 24 V", "T2 — 24/5 V", "T3 — 24/12 V"</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr"/>
@@ -2027,50 +2011,30 @@
         <v/>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>Tampa/cap PVC Ø 63 mm</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>Tampas do T1</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr"/>
-      <c r="F58" s="7" t="inlineStr"/>
-      <c r="G58" s="8" t="inlineStr"/>
-      <c r="H58" s="8">
-        <f>IF(C58*G58=0,"",C58*G58)</f>
-        <v/>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>M.4 — Rua e entrada da empresa (zona externa)</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>Tampa/cap PVC Ø 50 mm</t>
+          <t>Tinta spray cinza-asfalto escuro fosco</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>Tampas do T2 e T3</t>
+          <t>Pista da rua</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr"/>
@@ -2083,21 +2047,21 @@
     </row>
     <row r="60">
       <c r="A60" s="5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Cooler 30 mm 12 V</t>
+          <t>Tubo de alumínio Ø 5 mm</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>60 cm</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>Ventilação forçada dentro do T1 (dissipa ~10 W)</t>
+          <t>3 postes de iluminação pública de 180 mm — ⚠️ diferentes dos postes de distribuição</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr"/>
@@ -2110,11 +2074,11 @@
     </row>
     <row r="61">
       <c r="A61" s="9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>Cinta de alumínio 10 mm</t>
+          <t>Arame 1,5 mm</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
@@ -2124,7 +2088,7 @@
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>Fixação dos transformadores nos postes</t>
+          <t>Braço curvo das luminárias e estrutura do portão</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr"/>
@@ -2137,21 +2101,21 @@
     </row>
     <row r="62">
       <c r="A62" s="5" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Flange/base de fixação dos postes</t>
+          <t>LED 3 mm branco quente</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>Podem ser feitas com sobra de MDF + insertos M4</t>
+          <t>3 luminárias da rua + 1 na guarita. Alimentados em 5 V (BD-5V), com 220 Ω em série, sempre acesos. Vf ≈ 3,1 V</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr"/>
@@ -2162,11 +2126,31 @@
         <v/>
       </c>
     </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>M.4 — Rua e entrada da empresa (zona externa)</t>
-        </is>
+    <row r="63">
+      <c r="A63" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>Resistor 220 Ω 1/4 W</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>Limitador dos LEDs da rua — já contabilizado na lista L.4, não compre de novo. ⚠️ Valor dimensionado para 5 V: (5 − 3,1)/220 = 8,6 mA. Monte cada um dentro da base do poste, com termorretrátil</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr"/>
+      <c r="F63" s="11" t="inlineStr"/>
+      <c r="G63" s="12" t="inlineStr"/>
+      <c r="H63" s="12">
+        <f>IF(C63*G63=0,"",C63*G63)</f>
+        <v/>
       </c>
     </row>
     <row r="64">
@@ -2175,17 +2159,17 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Tinta spray cinza-asfalto escuro fosco</t>
+          <t>Carro de passeio miniatura 1:50</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>Pista da rua</t>
+          <t>~88 mm. Se só achar 1:64 (68 mm), pode usar — mas não misture escalas</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr"/>
@@ -2202,17 +2186,17 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Tubo de alumínio Ø 5 mm</t>
+          <t>Caminhão / van 1:50</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>60 cm</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>3 postes de iluminação pública de 180 mm — ⚠️ diferentes dos postes de distribuição</t>
+          <t>~150 mm, entrando pelo portão</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr"/>
@@ -2229,17 +2213,17 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Arame 1,5 mm</t>
+          <t>Tira de MDF 3 mm</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>1 m</t>
+          <t>1,5 m</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>Braço curvo das luminárias e estrutura do portão</t>
+          <t>Meio-fio (guia), 4 mm de altura, pintado de branco</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr"/>
@@ -2256,17 +2240,17 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>LED 3 mm branco quente</t>
+          <t>Fita branca 2 mm ou caneta posca branca</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>3 luminárias da rua + 1 na guarita</t>
+          <t>Faixa central tracejada, faixa de bordo e faixa de pedestres</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr"/>
@@ -2283,17 +2267,17 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Resistor 2,2 kΩ 1/4 W</t>
+          <t>MDF 4 mm</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>Limitador dos LEDs (24 V)</t>
+          <t>Muro da empresa: 50 mm de altura × 290 mm, em X = 640</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr"/>
@@ -2310,17 +2294,17 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>Carro de passeio miniatura 1:50</t>
+          <t>MDF 4 mm</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>~88 mm. Se só achar 1:64 (68 mm), pode usar — mas não misture escalas</t>
+          <t>Guarita 45 × 45 × 55 mm, com janela recortada</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr"/>
@@ -2337,7 +2321,7 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Caminhão / van 1:50</t>
+          <t>Tinta azul industrial</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -2347,7 +2331,7 @@
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>~150 mm, entrando pelo portão</t>
+          <t>Portão corrediço</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr"/>
@@ -2364,17 +2348,17 @@
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>Tira de MDF 3 mm</t>
+          <t>Árvores de maquete</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>1,5 m</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>Meio-fio (guia), 4 mm de altura, pintado de branco</t>
+          <t>Escala 1:50, na calçada da frente</t>
         </is>
       </c>
       <c r="E71" s="10" t="inlineStr"/>
@@ -2391,17 +2375,17 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Fita branca 2 mm ou caneta posca branca</t>
+          <t>Placas de trânsito miniatura</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>Faixa central tracejada, faixa de bordo e faixa de pedestres</t>
+          <t>"PARE" e "VELOCIDADE MÁXIMA 10 km/h"</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr"/>
@@ -2418,17 +2402,17 @@
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>MDF 4 mm</t>
+          <t>Lixeira urbana + abrigo de ônibus</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 cada</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>Muro da empresa: 50 mm de altura × 290 mm, em X = 640</t>
+          <t>Opcional — enriquece a cena</t>
         </is>
       </c>
       <c r="E73" s="10" t="inlineStr"/>
@@ -2439,50 +2423,30 @@
         <v/>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>MDF 4 mm</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>Guarita 45 × 45 × 55 mm, com janela recortada</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr"/>
-      <c r="F74" s="7" t="inlineStr"/>
-      <c r="G74" s="8" t="inlineStr"/>
-      <c r="H74" s="8">
-        <f>IF(C74*G74=0,"",C74*G74)</f>
-        <v/>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>M.5 — Chão de fábrica (cenografia)</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="9" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>Tinta azul industrial</t>
+          <t>Tinta spray cinza claro fosco</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>Portão corrediço</t>
+          <t>Piso industrial (epóxi)</t>
         </is>
       </c>
       <c r="E75" s="10" t="inlineStr"/>
@@ -2495,21 +2459,21 @@
     </row>
     <row r="76">
       <c r="A76" s="5" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Árvores de maquete</t>
+          <t>Tinta spray preto fosco</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>Escala 1:50, na calçada da frente</t>
+          <t>Estruturas e acabamento</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr"/>
@@ -2522,21 +2486,21 @@
     </row>
     <row r="77">
       <c r="A77" s="9" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>Placas de trânsito miniatura</t>
+          <t>Verniz fosco spray</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>"PARE" e "VELOCIDADE MÁXIMA 10 km/h"</t>
+          <t>Proteção final do piso pintado</t>
         </is>
       </c>
       <c r="E77" s="10" t="inlineStr"/>
@@ -2549,21 +2513,21 @@
     </row>
     <row r="78">
       <c r="A78" s="5" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Lixeira urbana + abrigo de ônibus</t>
+          <t>Fita adesiva amarela 10 mm</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>1 cada</t>
+          <t>1 rolo</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>Opcional — enriquece a cena</t>
+          <t>Demarcação de corredores e áreas</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr"/>
@@ -2574,11 +2538,31 @@
         <v/>
       </c>
     </row>
-    <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>M.5 — Chão de fábrica (cenografia)</t>
-        </is>
+    <row r="79">
+      <c r="A79" s="9" t="n">
+        <v>67</v>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>Fita zebrada amarelo/preto 20 mm</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>1 rolo</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>Faixa de segurança em frente ao painel (exigência NR-10 — zona de trabalho)</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="inlineStr"/>
+      <c r="F79" s="11" t="inlineStr"/>
+      <c r="G79" s="12" t="inlineStr"/>
+      <c r="H79" s="12">
+        <f>IF(C79*G79=0,"",C79*G79)</f>
+        <v/>
       </c>
     </row>
     <row r="80">
@@ -2587,17 +2571,17 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Tinta spray cinza claro fosco</t>
+          <t>Fita adesiva verde 10 mm</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 rolo</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>Piso industrial (epóxi)</t>
+          <t>Rota de fuga</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr"/>
@@ -2614,17 +2598,17 @@
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>Tinta spray preto fosco</t>
+          <t>Figuras de maquete escala 1:50</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>Estruturas e acabamento</t>
+          <t>(4 na fábrica, 3 na rua, 3 reservas) Pessoas com EPI (loja de maquetaria/arquitetura)</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr"/>
@@ -2641,17 +2625,17 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>Verniz fosco spray</t>
+          <t>Miniaturas: empilhadeira, pallets, tambores</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>Proteção final do piso pintado</t>
+          <t>Ambientação do chão de fábrica</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr"/>
@@ -2668,17 +2652,17 @@
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>Fita adesiva amarela 10 mm</t>
+          <t>Extintor miniatura + placa</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>1 rolo</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>Demarcação de corredores e áreas</t>
+          <t>Sinalização de segurança</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr"/>
@@ -2695,17 +2679,17 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>Fita zebrada amarelo/preto 20 mm</t>
+          <t>Placas de sinalização impressas</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>1 rolo</t>
+          <t>1 folha</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>Faixa de segurança em frente ao painel (exigência NR-10 — zona de trabalho)</t>
+          <t>"RISCO ELÉTRICO", "USO OBRIGATÓRIO DE EPI", "SAÍDA" — papel adesivo</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr"/>
@@ -2722,17 +2706,17 @@
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>Fita adesiva verde 10 mm</t>
+          <t>Eletrocalha / perfilado aéreo</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>1 rolo</t>
+          <t>60 cm</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>Rota de fuga</t>
+          <t>Canaleta de acrílico ou perfil U de alumínio — leva os cabos do painel à câmara por cima, como na indústria</t>
         </is>
       </c>
       <c r="E85" s="10" t="inlineStr"/>
@@ -2749,17 +2733,17 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Figuras de maquete escala 1:50</t>
+          <t>Suportes/mãos-francesas da eletrocalha</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>(4 na fábrica, 3 na rua, 3 reservas) Pessoas com EPI (loja de maquetaria/arquitetura)</t>
+          <t>Cantoneira de alumínio</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr"/>
@@ -2776,7 +2760,7 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>Miniaturas: empilhadeira, pallets, tambores</t>
+          <t>EVA ou MDF 6 mm</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
@@ -2786,7 +2770,7 @@
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>Ambientação do chão de fábrica</t>
+          <t>Bases de máquinas fictícias e plataformas</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr"/>
@@ -2797,50 +2781,30 @@
         <v/>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="5" t="n">
-        <v>76</v>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>Extintor miniatura + placa</t>
-        </is>
-      </c>
-      <c r="C88" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>Sinalização de segurança</t>
-        </is>
-      </c>
-      <c r="E88" s="6" t="inlineStr"/>
-      <c r="F88" s="7" t="inlineStr"/>
-      <c r="G88" s="8" t="inlineStr"/>
-      <c r="H88" s="8">
-        <f>IF(C88*G88=0,"",C88*G88)</f>
-        <v/>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>C.2 — Isolamento térmico</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="9" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>Placas de sinalização impressas</t>
+          <t>XPS 30 mm (poliestireno extrudado)</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>1 folha</t>
+          <t>1 m²</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>"RISCO ELÉTRICO", "USO OBRIGATÓRIO DE EPI", "SAÍDA" — papel adesivo</t>
+          <t>Isolante principal — k ≈ 0,033 W/m·K. 30 mm, não 20 mm (ver Doc 12)</t>
         </is>
       </c>
       <c r="E89" s="10" t="inlineStr"/>
@@ -2853,21 +2817,21 @@
     </row>
     <row r="90">
       <c r="A90" s="5" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Eletrocalha / perfilado aéreo</t>
+          <t>Fita adesiva de alumínio 50 mm</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>60 cm</t>
+          <t>1 rolo</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>Canaleta de acrílico ou perfil U de alumínio — leva os cabos do painel à câmara por cima, como na indústria</t>
+          <t>⚠️ Barreira de vapor — obrigatória em todas as juntas do XPS, pelo lado externo (quente)</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr"/>
@@ -2880,21 +2844,21 @@
     </row>
     <row r="91">
       <c r="A91" s="9" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>Suportes/mãos-francesas da eletrocalha</t>
+          <t>Manta elastomérica autoadesiva 6 mm</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1 m²</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>Cantoneira de alumínio</t>
+          <t>Tipo Armaflex — cantos, arestas e ao redor das passagens de cabo</t>
         </is>
       </c>
       <c r="E91" s="10" t="inlineStr"/>
@@ -2907,21 +2871,21 @@
     </row>
     <row r="92">
       <c r="A92" s="5" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>EVA ou MDF 6 mm</t>
+          <t>Espuma expansiva PU (mini)</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>Bases de máquinas fictícias e plataformas</t>
+          <t>Selagem de passagens de cabo e dreno</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr"/>
@@ -2935,27 +2899,27 @@
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>C.2 — Isolamento térmico</t>
+          <t>C.3 — Vedação, porta e dreno</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>XPS 30 mm (poliestireno extrudado)</t>
+          <t>Perfil EPDM tubular autoadesivo 9 × 6 mm</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>1 m²</t>
+          <t>2 m</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>Isolante principal — k ≈ 0,033 W/m·K. 30 mm, não 20 mm (ver Doc 12)</t>
+          <t>Vedação da porta — perfil tubular comprime muito melhor que o chato de 5 mm</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr"/>
@@ -2968,21 +2932,21 @@
     </row>
     <row r="95">
       <c r="A95" s="9" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>Fita adesiva de alumínio 50 mm</t>
+          <t>Dobradiça piano de alumínio</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>1 rolo</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>⚠️ Barreira de vapor — obrigatória em todas as juntas do XPS, pelo lado externo (quente)</t>
+          <t>250 mm (cortar de uma barra de 75 cm)</t>
         </is>
       </c>
       <c r="E95" s="10" t="inlineStr"/>
@@ -2995,21 +2959,21 @@
     </row>
     <row r="96">
       <c r="A96" s="5" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>Manta elastomérica autoadesiva 6 mm</t>
+          <t>Fecho de pressão (borboleta) inox</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>1 m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>Tipo Armaflex — cantos, arestas e ao redor das passagens de cabo</t>
+          <t>Comprime a vedação — tipo fecho de baú</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr"/>
@@ -3022,11 +2986,11 @@
     </row>
     <row r="97">
       <c r="A97" s="9" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>Espuma expansiva PU (mini)</t>
+          <t>Puxador de câmara fria (miniatura)</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
@@ -3036,7 +3000,7 @@
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>Selagem de passagens de cabo e dreno</t>
+          <t>Estética — pode ser um puxador de móvel pequeno</t>
         </is>
       </c>
       <c r="E97" s="10" t="inlineStr"/>
@@ -3047,11 +3011,31 @@
         <v/>
       </c>
     </row>
-    <row r="98" ht="22" customHeight="1">
-      <c r="A98" s="4" t="inlineStr">
-        <is>
-          <t>C.3 — Vedação, porta e dreno</t>
-        </is>
+    <row r="98">
+      <c r="A98" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>Cola S-320 Sinteglas</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>250 ml</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>Colagem de acrílico por capilaridade</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr"/>
+      <c r="F98" s="7" t="inlineStr"/>
+      <c r="G98" s="8" t="inlineStr"/>
+      <c r="H98" s="8">
+        <f>IF(C98*G98=0,"",C98*G98)</f>
+        <v/>
       </c>
     </row>
     <row r="99">
@@ -3060,17 +3044,17 @@
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>Perfil EPDM tubular autoadesivo 9 × 6 mm</t>
+          <t>Silicone neutro transparente</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>2 m</t>
+          <t>1 tubo</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>Vedação da porta — perfil tubular comprime muito melhor que o chato de 5 mm</t>
+          <t>Vedação de juntas (⚠️ neutro, o acético ataca o acrílico)</t>
         </is>
       </c>
       <c r="E99" s="10" t="inlineStr"/>
@@ -3087,7 +3071,7 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>Dobradiça piano de alumínio</t>
+          <t>Bandeja de alumínio</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
@@ -3097,7 +3081,7 @@
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>250 mm (cortar de uma barra de 75 cm)</t>
+          <t>~190 × 90 mm — coleta de condensado</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr"/>
@@ -3114,17 +3098,17 @@
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>Fecho de pressão (borboleta) inox</t>
+          <t>Tubo de silicone Ø 6 mm</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40 cm</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>Comprime a vedação — tipo fecho de baú</t>
+          <t>Dreno até o recipiente externo</t>
         </is>
       </c>
       <c r="E101" s="10" t="inlineStr"/>
@@ -3141,17 +3125,17 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Puxador de câmara fria (miniatura)</t>
+          <t>Sílica gel indicadora</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3 sachês</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>Estética — pode ser um puxador de móvel pequeno</t>
+          <t>2 na câmara + 1 dentro da câmara de ar da porta dupla</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr"/>
@@ -3168,17 +3152,17 @@
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>Cola S-320 Sinteglas</t>
+          <t>Recipiente coletor de condensado</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>250 ml</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>Colagem de acrílico por capilaridade</t>
+          <t>Frasco pequeno, embutido na maquete</t>
         </is>
       </c>
       <c r="E103" s="10" t="inlineStr"/>
@@ -3189,40 +3173,20 @@
         <v/>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>Silicone neutro transparente</t>
-        </is>
-      </c>
-      <c r="C104" s="5" t="inlineStr">
-        <is>
-          <t>1 tubo</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>Vedação de juntas (⚠️ neutro, o acético ataca o acrílico)</t>
-        </is>
-      </c>
-      <c r="E104" s="6" t="inlineStr"/>
-      <c r="F104" s="7" t="inlineStr"/>
-      <c r="G104" s="8" t="inlineStr"/>
-      <c r="H104" s="8">
-        <f>IF(C104*G104=0,"",C104*G104)</f>
-        <v/>
+    <row r="104" ht="22" customHeight="1">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>⚡ CAMADA 2 — PAINEL DE COMANDO</t>
+        </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>Bandeja de alumínio</t>
+          <t>Caixa de comando ou MDF</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
@@ -3232,7 +3196,7 @@
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>~190 × 90 mm — coleta de condensado</t>
+          <t>400 × 500 × 200 mm — comprada pronta ou feita em MDF 15 mm</t>
         </is>
       </c>
       <c r="E105" s="10" t="inlineStr"/>
@@ -3245,21 +3209,21 @@
     </row>
     <row r="106">
       <c r="A106" s="5" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>Tubo de silicone Ø 6 mm</t>
+          <t>Porta do painel</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>40 cm</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>Dreno até o recipiente externo</t>
+          <t>MDF 12 mm ou acrílico fumê 5 mm (fica bonito ver os LEDs)</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr"/>
@@ -3272,21 +3236,21 @@
     </row>
     <row r="107">
       <c r="A107" s="9" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>Sílica gel indicadora</t>
+          <t>Trilho DIN 35 mm</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>3 sachês</t>
+          <t>1,5 m</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>2 na câmara + 1 dentro da câmara de ar da porta dupla</t>
+          <t>Aço galvanizado — 3 trilhos de ~360 mm</t>
         </is>
       </c>
       <c r="E107" s="10" t="inlineStr"/>
@@ -3299,21 +3263,21 @@
     </row>
     <row r="108">
       <c r="A108" s="5" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>Recipiente coletor de condensado</t>
+          <t>Canaleta perfurada 30 × 30 mm</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2 m</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>Frasco pequeno, embutido na maquete</t>
+          <t>Com tampa — organização profissional dos cabos</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr"/>
@@ -3324,11 +3288,31 @@
         <v/>
       </c>
     </row>
-    <row r="109" ht="22" customHeight="1">
-      <c r="A109" s="4" t="inlineStr">
-        <is>
-          <t>⚡ CAMADA 2 — PAINEL DE COMANDO</t>
-        </is>
+    <row r="109">
+      <c r="A109" s="9" t="n">
+        <v>94</v>
+      </c>
+      <c r="B109" s="10" t="inlineStr">
+        <is>
+          <t>Bloco de distribuição DIN — 1 entrada 4 mm² + 4 saídas</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D109" s="10" t="inlineStr">
+        <is>
+          <t>BD-POT — 24 V de potência comutados pelo KA2 → BTS #1, BTS #2 e reservas. ⚠️ Cai com a emergência</t>
+        </is>
+      </c>
+      <c r="E109" s="10" t="inlineStr"/>
+      <c r="F109" s="11" t="inlineStr"/>
+      <c r="G109" s="12" t="inlineStr"/>
+      <c r="H109" s="12">
+        <f>IF(C109*G109=0,"",C109*G109)</f>
+        <v/>
       </c>
     </row>
     <row r="110">
@@ -3337,17 +3321,17 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Caixa de comando ou MDF</t>
+          <t>Bloco de distribuição DIN — 1 entrada 2,5 mm² + 4 saídas</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>400 × 500 × 200 mm — comprada pronta ou feita em MDF 15 mm</t>
+          <t>BD-AUX (12 V auxiliar, do T3) e BD-24V (24 V permanentes: DNLCB30/ESP32, cadeia de comando e o positivo comum dos 4 sinaleiros). ⚠️ Não confundir com o BD-POT — este não cai com a emergência, é o que mantém a supervisão viva para publicar o evento por MQTT</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr"/>
@@ -3364,7 +3348,7 @@
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>Porta do painel</t>
+          <t>Bloco de distribuição DIN — 1 entrada 2,5 mm² + 6 saídas</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
@@ -3374,7 +3358,7 @@
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>MDF 12 mm ou acrílico fumê 5 mm (fica bonito ver os LEDs)</t>
+          <t>BD-5V — Arduino, Nextion, SD/RTC, lógica dos 2 BTS, LEDs</t>
         </is>
       </c>
       <c r="E111" s="10" t="inlineStr"/>
@@ -3391,17 +3375,17 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>Trilho DIN 35 mm</t>
+          <t>Bloco de distribuição DIN — 1 entrada 10 mm² + 8 saídas</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>1,5 m</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>Aço galvanizado — 3 trilhos de ~360 mm</t>
+          <t>BD-0V — ⭐ o star ground do projeto. Todos os retornos convergem aqui</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr"/>
@@ -3418,17 +3402,17 @@
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>Canaleta perfurada 30 × 30 mm</t>
+          <t>Bornes DIN parafuso 2,5 mm²</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>2 m</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>Com tampa — organização profissional dos cabos</t>
+          <t>Passagem e reservas</t>
         </is>
       </c>
       <c r="E113" s="10" t="inlineStr"/>
@@ -3445,17 +3429,17 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>Bloco de distribuição DIN — 1 entrada 4 mm² + 4 saídas</t>
+          <t>Separadores/tampas de borne</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>BD-POT — 12 V de potência → BTS #1, BTS #2 e reservas</t>
+          <t>Acabamento das réguas</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr"/>
@@ -3472,17 +3456,17 @@
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>Bloco de distribuição DIN — 1 entrada 2,5 mm² + 4 saídas</t>
+          <t>Alternativa mais barata: bornes comuns + ponte de interligação (pente)</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>BD-AUX (12 V auxiliar) e BD-24V (24 V)</t>
+          <t>Funciona igual aos blocos, custa menos, menos prático para alterar depois</t>
         </is>
       </c>
       <c r="E115" s="10" t="inlineStr"/>
@@ -3499,17 +3483,17 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>Bloco de distribuição DIN — 1 entrada 2,5 mm² + 6 saídas</t>
+          <t>Identificadores de borne e de cabo</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 kit</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>BD-5V — Arduino, Nextion, SD/RTC, lógica dos 2 BTS, LEDs</t>
+          <t>Anilhas numeradas — exigido em painel industrial</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr"/>
@@ -3526,17 +3510,17 @@
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>Bloco de distribuição DIN — 1 entrada 10 mm² + 8 saídas</t>
+          <t>Trava-fim de trilho DIN</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>BD-0V — ⭐ o star ground do projeto. Todos os retornos convergem aqui</t>
+          <t>Impede os componentes de deslizarem</t>
         </is>
       </c>
       <c r="E117" s="10" t="inlineStr"/>
@@ -3553,17 +3537,17 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Bornes DIN parafuso 2,5 mm²</t>
+          <t>Botão de Emergência cogumelo 22 mm</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>Passagem e reservas</t>
+          <t>Com trava (girar p/ destravar) — 2 blocos NF (1 para o comando 24 V, 1 para a leitura do Arduino)</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr"/>
@@ -3580,17 +3564,17 @@
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>Separadores/tampas de borne</t>
+          <t>Botão START 22 mm</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>Acabamento das réguas</t>
+          <t>Verde, momentâneo — 1 bloco NA (só informa o Arduino)</t>
         </is>
       </c>
       <c r="E119" s="10" t="inlineStr"/>
@@ -3607,17 +3591,17 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>Alternativa mais barata: bornes comuns + ponte de interligação (pente)</t>
+          <t>Botão STOP 22 mm</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>Funciona igual aos blocos, custa menos, menos prático para alterar depois</t>
+          <t>Vermelho, momentâneo — 1 NF (corta o KA2 em 24 V) + 1 NA (avisa o Arduino)</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr"/>
@@ -3634,17 +3618,17 @@
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>Identificadores de borne e de cabo</t>
+          <t>Botão REARME 22 mm</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>1 kit</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>Anilhas numeradas — exigido em painel industrial</t>
+          <t>AZUL, momentâneo — 1 bloco NA. Refaz o selo do KA1 após a emergência. Buscar botão pulsador azul 22mm</t>
         </is>
       </c>
       <c r="E121" s="10" t="inlineStr"/>
@@ -3661,17 +3645,17 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>Trava-fim de trilho DIN</t>
+          <t>Blocos de contato 22 mm avulsos</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>Impede os componentes de deslizarem</t>
+          <t>3 NF + 1 NA: emergência (2 NF), STOP (1 NF + 1 NA). Ver Doc 31 §31.3</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr"/>
@@ -3688,7 +3672,7 @@
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>Botão de Emergência cogumelo 22 mm</t>
+          <t>Chave seccionadora 24 V no painel</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
@@ -3698,7 +3682,7 @@
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>Com trava (girar p/ destravar) — 2 blocos NF (1 para o comando 24 V, 1 para a leitura do Arduino)</t>
+          <t>Rotativa 2 posições 22 mm — chave geral local da máquina</t>
         </is>
       </c>
       <c r="E123" s="10" t="inlineStr"/>
@@ -3715,17 +3699,17 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>Botão START 22 mm</t>
+          <t>Sinaleiros LED 22 mm 24 V</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>Verde, momentâneo — 1 bloco NA (só informa o Arduino)</t>
+          <t>Verde (RUN), Azul (COOL), Amarelo (HEAT), Vermelho (FAULT). ⚠️ 24 V confirmado — acionados pelo ULN2803 da placa PI-1, alimentados pelo BD-24V permanente (o vermelho de FALHA precisa continuar aceso com a emergência acionada). ~20 mA cada, resistor interno já incluso</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr"/>
@@ -3742,17 +3726,17 @@
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>Botão STOP 22 mm</t>
+          <t>Prensa-cabo PG9</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>Vermelho, momentâneo — 1 NF (corta o KA2 em 24 V) + 1 NA (avisa o Arduino)</t>
+          <t>Entrada 24 V de potência (vindo do P1) · saída de potência para a câmara · saída de sinais</t>
         </is>
       </c>
       <c r="E125" s="10" t="inlineStr"/>
@@ -3769,17 +3753,17 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>Botão REARME 22 mm</t>
+          <t>Prensa-cabo PG7</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>AZUL, momentâneo — 1 bloco NA. Refaz o selo do KA1 após a emergência. Buscar botão pulsador azul 22mm</t>
+          <t>Entrada 5 V (do T2) e entrada 12 V auxiliar + 24 V (do T3)</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr"/>
@@ -3796,17 +3780,17 @@
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>Blocos de contato 22 mm avulsos</t>
+          <t>Bolsa porta-documentos p/ porta</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>3 NF + 1 NA: emergência (2 NF), STOP (1 NF + 1 NA). Ver Doc 31 §31.3</t>
+          <t>Guarda o diagrama elétrico — padrão em painel industrial</t>
         </is>
       </c>
       <c r="E127" s="10" t="inlineStr"/>
@@ -3817,50 +3801,30 @@
         <v/>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="5" t="n">
-        <v>113</v>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>Chave seccionadora 24 V no painel</t>
-        </is>
-      </c>
-      <c r="C128" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr">
-        <is>
-          <t>Rotativa 2 posições 22 mm — chave geral local da máquina</t>
-        </is>
-      </c>
-      <c r="E128" s="6" t="inlineStr"/>
-      <c r="F128" s="7" t="inlineStr"/>
-      <c r="G128" s="8" t="inlineStr"/>
-      <c r="H128" s="8">
-        <f>IF(C128*G128=0,"",C128*G128)</f>
-        <v/>
+    <row r="128" ht="22" customHeight="1">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>L.1 — Controle e interface</t>
+        </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="9" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>Sinaleiros LED 22 mm 24 V</t>
+          <t>Arduino Mega 2560 R3</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>Verde (RUN), Azul (COOL), Amarelo (HEAT), Vermelho (FAULT)</t>
+          <t>ATmega2560, 54 GPIO, 4 UARTs</t>
         </is>
       </c>
       <c r="E129" s="10" t="inlineStr"/>
@@ -3873,21 +3837,21 @@
     </row>
     <row r="130">
       <c r="A130" s="5" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>Prensa-cabo PG9</t>
+          <t>Shield de expansão Mega (bornes parafuso)</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>Entrada 12 V potência · saída de potência · saída de sinais</t>
+          <t>Sensor Shield V2.0</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr"/>
@@ -3900,21 +3864,21 @@
     </row>
     <row r="131">
       <c r="A131" s="9" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>Prensa-cabo PG7</t>
+          <t>Suporte DIN para Arduino Mega</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>Entrada 5 V (do T2) e entrada 12 V auxiliar + 24 V (do T3)</t>
+          <t>Ou SPCI4/adaptador</t>
         </is>
       </c>
       <c r="E131" s="10" t="inlineStr"/>
@@ -3927,11 +3891,11 @@
     </row>
     <row r="132">
       <c r="A132" s="5" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>Bolsa porta-documentos p/ porta</t>
+          <t>Tela Nextion Basic 3.2"</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
@@ -3941,7 +3905,7 @@
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>Guarda o diagrama elétrico — padrão em painel industrial</t>
+          <t>NX4024T032, 400×240, TTL 5 V</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr"/>
@@ -3952,11 +3916,31 @@
         <v/>
       </c>
     </row>
-    <row r="133" ht="22" customHeight="1">
-      <c r="A133" s="4" t="inlineStr">
-        <is>
-          <t>L.1 — Controle e interface</t>
-        </is>
+    <row r="133">
+      <c r="A133" s="9" t="n">
+        <v>117</v>
+      </c>
+      <c r="B133" s="10" t="inlineStr">
+        <is>
+          <t>ESP32-WROOM-32U</t>
+        </is>
+      </c>
+      <c r="C133" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D133" s="10" t="inlineStr">
+        <is>
+          <t>30 pinos, conector de antena IPEX</t>
+        </is>
+      </c>
+      <c r="E133" s="10" t="inlineStr"/>
+      <c r="F133" s="11" t="inlineStr"/>
+      <c r="G133" s="12" t="inlineStr"/>
+      <c r="H133" s="12">
+        <f>IF(C133*G133=0,"",C133*G133)</f>
+        <v/>
       </c>
     </row>
     <row r="134">
@@ -3965,7 +3949,7 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>Arduino Mega 2560 R3</t>
+          <t>DNLCB30 — base DIN para ESP32</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
@@ -3975,7 +3959,7 @@
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>ATmega2560, 54 GPIO, 4 UARTs</t>
+          <t>Entrada 7–35 V (alimentada direto do barramento 24 V), conversão 3,3 ↔ 5 V automática. Não inclui o ESP32</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr"/>
@@ -3992,7 +3976,7 @@
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>Shield de expansão Mega (bornes parafuso)</t>
+          <t>Pigtail IPEX (u.FL) → SMA macho, 20–30 cm</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
@@ -4002,7 +3986,7 @@
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>Sensor Shield V2.0</t>
+          <t>Liga o ESP32 ao conector de painel</t>
         </is>
       </c>
       <c r="E135" s="10" t="inlineStr"/>
@@ -4019,7 +4003,7 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>Suporte DIN para Arduino Mega</t>
+          <t>Conector SMA fêmea de painel (bulkhead)</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
@@ -4029,7 +4013,7 @@
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>Ou SPCI4/adaptador</t>
+          <t>Rosca de painel Ø 6,5 mm, com porca e arruela de pressão. ⚠️ Nunca passar o coaxial por prensa-cabo</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr"/>
@@ -4046,7 +4030,7 @@
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>Tela Nextion Basic 3.2"</t>
+          <t>Antena 2,4 GHz SMA macho 3 dBi articulável</t>
         </is>
       </c>
       <c r="C137" s="9" t="inlineStr">
@@ -4056,7 +4040,7 @@
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>NX4024T032, 400×240, TTL 5 V</t>
+          <t>Rosqueada por fora, na lateral direita, parte alta do painel</t>
         </is>
       </c>
       <c r="E137" s="10" t="inlineStr"/>
@@ -4073,7 +4057,7 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>ESP32-WROOM-32U</t>
+          <t>Módulo Micro SD (SPI)</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
@@ -4083,7 +4067,7 @@
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>30 pinos, conector de antena IPEX</t>
+          <t>5 V, com regulador e level shifter</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr"/>
@@ -4100,7 +4084,7 @@
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>DNLCB30 — base DIN para ESP32</t>
+          <t>Cartão Micro SD</t>
         </is>
       </c>
       <c r="C139" s="9" t="inlineStr">
@@ -4110,7 +4094,7 @@
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>Entrada 7–35 V (alimentada direto do barramento 24 V), conversão 3,3 ↔ 5 V automática. Não inclui o ESP32</t>
+          <t>8–16 GB, Classe 10</t>
         </is>
       </c>
       <c r="E139" s="10" t="inlineStr"/>
@@ -4127,7 +4111,7 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>Pigtail IPEX (u.FL) → SMA macho, 20–30 cm</t>
+          <t>Módulo RTC DS3231</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
@@ -4137,7 +4121,7 @@
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>Liga o ESP32 ao conector de painel</t>
+          <t>I²C, ±2 ppm</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr"/>
@@ -4154,7 +4138,7 @@
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>Conector SMA fêmea de painel (bulkhead)</t>
+          <t>Bateria CR2032</t>
         </is>
       </c>
       <c r="C141" s="9" t="inlineStr">
@@ -4164,7 +4148,7 @@
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>Rosca de painel Ø 6,5 mm, com porca e arruela de pressão. ⚠️ Nunca passar o coaxial por prensa-cabo</t>
+          <t>Backup do RTC</t>
         </is>
       </c>
       <c r="E141" s="10" t="inlineStr"/>
@@ -4175,50 +4159,30 @@
         <v/>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="5" t="n">
-        <v>126</v>
-      </c>
-      <c r="B142" s="6" t="inlineStr">
-        <is>
-          <t>Antena 2,4 GHz SMA macho 3 dBi articulável</t>
-        </is>
-      </c>
-      <c r="C142" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D142" s="6" t="inlineStr">
-        <is>
-          <t>Rosqueada por fora, na lateral direita, parte alta do painel</t>
-        </is>
-      </c>
-      <c r="E142" s="6" t="inlineStr"/>
-      <c r="F142" s="7" t="inlineStr"/>
-      <c r="G142" s="8" t="inlineStr"/>
-      <c r="H142" s="8">
-        <f>IF(C142*G142=0,"",C142*G142)</f>
-        <v/>
+    <row r="142" ht="22" customHeight="1">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>L.2 — Potência e acionamento</t>
+        </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="9" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>Módulo Micro SD (SPI)</t>
+          <t>Driver ponte-H BTS7960</t>
         </is>
       </c>
       <c r="C143" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>5 V, com regulador e level shifter</t>
+          <t>43 A, pino IS de diagnóstico</t>
         </is>
       </c>
       <c r="E143" s="10" t="inlineStr"/>
@@ -4231,21 +4195,21 @@
     </row>
     <row r="144">
       <c r="A144" s="5" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>Cartão Micro SD</t>
+          <t>Suporte SPCI4 trilho DIN</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>8–16 GB, Classe 10</t>
+          <t>Fixa PCI 100 × 79 mm</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr"/>
@@ -4258,11 +4222,11 @@
     </row>
     <row r="145">
       <c r="A145" s="9" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>Módulo RTC DS3231</t>
+          <t>Cooler 40 mm 12 V</t>
         </is>
       </c>
       <c r="C145" s="9" t="inlineStr">
@@ -4272,7 +4236,7 @@
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t>I²C, ±2 ppm</t>
+          <t>Refrigeração dos BTS</t>
         </is>
       </c>
       <c r="E145" s="10" t="inlineStr"/>
@@ -4285,11 +4249,11 @@
     </row>
     <row r="146">
       <c r="A146" s="5" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>Bateria CR2032</t>
+          <t>KA1 — Relé de interface 24 Vcc, 2 contatos</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
@@ -4299,7 +4263,7 @@
       </c>
       <c r="D146" s="6" t="inlineStr">
         <is>
-          <t>Backup do RTC</t>
+          <t>Faz o selo (habilitação) e alimenta a bobina do KA2. Conduz só miliampères — 6 A basta. Buscar relé de interface 24vdc 2 contatos din. Premium: Finder 55.32.9.024.0040</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr"/>
@@ -4310,11 +4274,31 @@
         <v/>
       </c>
     </row>
-    <row r="147" ht="22" customHeight="1">
-      <c r="A147" s="4" t="inlineStr">
-        <is>
-          <t>L.2 — Potência e acionamento</t>
-        </is>
+    <row r="147">
+      <c r="A147" s="9" t="n">
+        <v>130</v>
+      </c>
+      <c r="B147" s="10" t="inlineStr">
+        <is>
+          <t>KA2 — Relé de interface 24 Vcc, contato ≥ 10 A</t>
+        </is>
+      </c>
+      <c r="C147" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D147" s="10" t="inlineStr">
+        <is>
+          <t>É ele que chaveia os 24 V / 6,0 A de potência dos BTS. ⚠️ Confirme os 10 A no anúncio — a maioria dos slim é de 6 A — e confirme que a corrente é declarada em DC: muito relé de 10 A/250 VAC cai para 5 A ou menos em 24 Vcc, porque corrente contínua não tem passagem por zero e o arco custa mais a extinguir. Buscar relé de interface 24vdc 10a trilho din. Premium: Finder 46.61.9.024.0040 + base 95.05 (16 A)</t>
+        </is>
+      </c>
+      <c r="E147" s="10" t="inlineStr"/>
+      <c r="F147" s="11" t="inlineStr"/>
+      <c r="G147" s="12" t="inlineStr"/>
+      <c r="H147" s="12">
+        <f>IF(C147*G147=0,"",C147*G147)</f>
+        <v/>
       </c>
     </row>
     <row r="148">
@@ -4323,17 +4307,17 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>Driver ponte-H BTS7960</t>
+          <t>Resistor 10 kΩ 1/4 W</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>43 A, pino IS de diagnóstico</t>
+          <t>Pull-down em cada R_EN dos BTS7960 (2) + reservas. ⚠️ Garante que pino solto = driver desligado — ficou ainda mais crítico com os 24 V permanentes na entrada dos BTS</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr"/>
@@ -4350,7 +4334,7 @@
       </c>
       <c r="B149" s="10" t="inlineStr">
         <is>
-          <t>Suporte SPCI4 trilho DIN</t>
+          <t>Resistor 22 kΩ 1/4 W ⬆</t>
         </is>
       </c>
       <c r="C149" s="9" t="inlineStr">
@@ -4360,7 +4344,7 @@
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>Fixa PCI 100 × 79 mm</t>
+          <t>Braço superior do divisor de realimentação de tensão para o pino D25</t>
         </is>
       </c>
       <c r="E149" s="10" t="inlineStr"/>
@@ -4377,17 +4361,17 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>Cooler 40 mm 12 V</t>
+          <t>Resistor 4,7 kΩ 1/4 W</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>Refrigeração dos BTS</t>
+          <t>Braço inferior do mesmo divisor</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr"/>
@@ -4398,50 +4382,30 @@
         <v/>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="9" t="n">
-        <v>134</v>
-      </c>
-      <c r="B151" s="10" t="inlineStr">
-        <is>
-          <t>KA1 — Relé de interface 24 Vcc, 2 contatos</t>
-        </is>
-      </c>
-      <c r="C151" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D151" s="10" t="inlineStr">
-        <is>
-          <t>Faz o selo (habilitação) e alimenta a bobina do KA2. Conduz só miliampères — 6 A basta. Buscar relé de interface 24vdc 2 contatos din. Premium: Finder 55.32.9.024.0040</t>
-        </is>
-      </c>
-      <c r="E151" s="10" t="inlineStr"/>
-      <c r="F151" s="11" t="inlineStr"/>
-      <c r="G151" s="12" t="inlineStr"/>
-      <c r="H151" s="12">
-        <f>IF(C151*G151=0,"",C151*G151)</f>
-        <v/>
+    <row r="151" ht="22" customHeight="1">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>L.3 — Atuadores térmicos e ventilação</t>
+        </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>KA2 — Relé de interface 24 Vcc, contato ≥ 10 A</t>
+          <t>Pastilha Peltier TEC1-12706</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>É ele que chaveia os 12 V / 6,3 A dos BTS. ⚠️ Confirme os 10 A no anúncio — a maioria dos slim é de 6 A. Buscar relé de interface 24vdc 10a trilho din. Premium: Finder 46.61.9.024.0040 + base 95.05 (16 A)</t>
+          <t>12 V / ~6 A / 60 W cada. 2 em uso, ligadas EM SÉRIE (24 V / 6,0 A / 144 W) + 1 reserva. ⚠️ Comprar do mesmo lote/vendedor — em série as duas conduzem a mesma corrente, e pastilhas descasadas trabalham desequilibradas</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr"/>
@@ -4454,21 +4418,21 @@
     </row>
     <row r="153">
       <c r="A153" s="9" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>Resistor 10 kΩ 1/4 W</t>
+          <t>Aquecedor PTC cerâmico 24 V / 60 W</t>
         </is>
       </c>
       <c r="C153" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>Pull-down em cada R_EN dos BTS7960 (2) + divisor de realimentação (1) + reserva. ⚠️ Garante que pino solto = driver desligado</t>
+          <t>Com aletas, versão de 24 V (2,5 A) para ligar direto no barramento. 60 W, não 100 W — equilibra as duas potências. ⚠️ Menos comum que o de 12 V: comprar cedo, no Lote A. Buscar também como aquecedor ar quente ptc 24v (incubadora / impressora 3D)</t>
         </is>
       </c>
       <c r="E153" s="10" t="inlineStr"/>
@@ -4481,11 +4445,11 @@
     </row>
     <row r="154">
       <c r="A154" s="5" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>Resistor 4,7 kΩ 1/4 W</t>
+          <t>Dissipador + cooler 80 mm p/ lado quente da Peltier</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
@@ -4495,7 +4459,7 @@
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
-          <t>Divisor de realimentação do 12 V para o pino D25</t>
+          <t>Um para cada pastilha. ⚠️ 3 fios (com sinal de RPM) nos dois — o firmware monitora os dois tacômetros e bloqueia a refrigeração se qualquer um parar</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr"/>
@@ -4508,21 +4472,21 @@
     </row>
     <row r="155">
       <c r="A155" s="9" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>Diodo 1N4007</t>
+          <t>Pasta térmica</t>
         </is>
       </c>
       <c r="C155" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>Proteção geral e reservas (o relé de interface já traz o roda-livre interno)</t>
+          <t>Seringa 5 g — dá para os 2 conjuntos</t>
         </is>
       </c>
       <c r="E155" s="10" t="inlineStr"/>
@@ -4533,11 +4497,31 @@
         <v/>
       </c>
     </row>
-    <row r="156" ht="22" customHeight="1">
-      <c r="A156" s="4" t="inlineStr">
-        <is>
-          <t>L.3 — Atuadores térmicos e ventilação</t>
-        </is>
+    <row r="156">
+      <c r="A156" s="5" t="n">
+        <v>138</v>
+      </c>
+      <c r="B156" s="6" t="inlineStr">
+        <is>
+          <t>Fan 60 × 60 mm 12 V</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t>Internas — lado PTC (1 sopra ↑, 1 sopra ↓)</t>
+        </is>
+      </c>
+      <c r="E156" s="6" t="inlineStr"/>
+      <c r="F156" s="7" t="inlineStr"/>
+      <c r="G156" s="8" t="inlineStr"/>
+      <c r="H156" s="8">
+        <f>IF(C156*G156=0,"",C156*G156)</f>
+        <v/>
       </c>
     </row>
     <row r="157">
@@ -4546,17 +4530,17 @@
       </c>
       <c r="B157" s="10" t="inlineStr">
         <is>
-          <t>Pastilha Peltier TEC1-12706</t>
+          <t>Fan 40 × 40 mm 12 V</t>
         </is>
       </c>
       <c r="C157" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>12 V, ~6 A, 60 W (+1 reserva é sábio)</t>
+          <t>Internas — lado Peltier (1 sopra ↓, 1 sopra ↑)</t>
         </is>
       </c>
       <c r="E157" s="10" t="inlineStr"/>
@@ -4567,40 +4551,20 @@
         <v/>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="5" t="n">
-        <v>140</v>
-      </c>
-      <c r="B158" s="6" t="inlineStr">
-        <is>
-          <t>Aquecedor PTC cerâmico 12 V 60 W</t>
-        </is>
-      </c>
-      <c r="C158" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D158" s="6" t="inlineStr">
-        <is>
-          <t>Com aletas. 60 W, não 100 W — equilibra as duas potências e alivia o T1</t>
-        </is>
-      </c>
-      <c r="E158" s="6" t="inlineStr"/>
-      <c r="F158" s="7" t="inlineStr"/>
-      <c r="G158" s="8" t="inlineStr"/>
-      <c r="H158" s="8">
-        <f>IF(C158*G158=0,"",C158*G158)</f>
-        <v/>
+    <row r="158" ht="22" customHeight="1">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>L.4 — Sensores</t>
+        </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="9" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B159" s="10" t="inlineStr">
         <is>
-          <t>Dissipador + cooler 80 mm p/ lado quente da Peltier</t>
+          <t>Sensor DS18B20 à prova d'água</t>
         </is>
       </c>
       <c r="C159" s="9" t="inlineStr">
@@ -4610,7 +4574,7 @@
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>3 fios (com sinal de RPM) — obrigatório para a proteção</t>
+          <t>1-Wire, ±0,5 °C — centro da câmara</t>
         </is>
       </c>
       <c r="E159" s="10" t="inlineStr"/>
@@ -4623,21 +4587,21 @@
     </row>
     <row r="160">
       <c r="A160" s="5" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>Pasta térmica</t>
+          <t>Resistor 4,7 kΩ 1/4 W</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>Seringa 5 g</t>
+          <t>Pull-up do barramento 1-Wire</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr"/>
@@ -4650,21 +4614,21 @@
     </row>
     <row r="161">
       <c r="A161" s="9" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B161" s="10" t="inlineStr">
         <is>
-          <t>Fan 60 × 60 mm 12 V</t>
+          <t>Sensor AM2315C</t>
         </is>
       </c>
       <c r="C161" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D161" s="10" t="inlineStr">
         <is>
-          <t>Internas — lado PTC (1 sopra ↑, 1 sopra ↓)</t>
+          <t>I²C, umidade + temperatura, carcaça selada</t>
         </is>
       </c>
       <c r="E161" s="10" t="inlineStr"/>
@@ -4677,21 +4641,21 @@
     </row>
     <row r="162">
       <c r="A162" s="5" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>Fan 40 × 40 mm 12 V</t>
+          <t>Capacitor cerâmico 100 nF</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>Internas — lado Peltier (1 sopra ↓, 1 sopra ↑)</t>
+          <t>Filtro dos pinos IS dos BTS (2) + filtro do divisor D25 (1) + reservas</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr"/>
@@ -4702,57 +4666,57 @@
         <v/>
       </c>
     </row>
-    <row r="163" ht="22" customHeight="1">
-      <c r="A163" s="4" t="inlineStr">
-        <is>
-          <t>L.4 — Sensores</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="5" t="n">
-        <v>145</v>
-      </c>
-      <c r="B164" s="6" t="inlineStr">
-        <is>
-          <t>Sensor DS18B20 à prova d'água</t>
-        </is>
-      </c>
-      <c r="C164" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D164" s="6" t="inlineStr">
-        <is>
-          <t>1-Wire, ±0,5 °C — centro da câmara</t>
-        </is>
-      </c>
-      <c r="E164" s="6" t="inlineStr"/>
-      <c r="F164" s="7" t="inlineStr"/>
-      <c r="G164" s="8" t="inlineStr"/>
-      <c r="H164" s="8">
-        <f>IF(C164*G164=0,"",C164*G164)</f>
-        <v/>
+    <row r="163">
+      <c r="A163" s="9" t="n">
+        <v>144</v>
+      </c>
+      <c r="B163" s="10" t="inlineStr">
+        <is>
+          <t>Resistor 220 Ω 1/4 W</t>
+        </is>
+      </c>
+      <c r="C163" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D163" s="10" t="inlineStr">
+        <is>
+          <t>4 usos + 2 reservas — série dos LEDs brancos da iluminação da maquete (5 V). ⚠️ Não são mais dos sinaleiros do painel, que agora são de 24 V</t>
+        </is>
+      </c>
+      <c r="E163" s="10" t="inlineStr"/>
+      <c r="F163" s="11" t="inlineStr"/>
+      <c r="G163" s="12" t="inlineStr"/>
+      <c r="H163" s="12">
+        <f>IF(C163*G163=0,"",C163*G163)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" ht="22" customHeight="1">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>L.5 — Placa de Interface PI-1 (onde os componentes discretos moram)</t>
+        </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="9" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B165" s="10" t="inlineStr">
         <is>
-          <t>Resistor 4,7 kΩ 1/4 W</t>
+          <t>Placa ilhada (padrão furos isolados)</t>
         </is>
       </c>
       <c r="C165" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>Pull-up do barramento 1-Wire</t>
+          <t>~5 × 7 cm. ⚠️ Ilhada, não de barramento — na de barramento você acaba tendo que cortar trilha, e é dali que saem os curtos difíceis de achar</t>
         </is>
       </c>
       <c r="E165" s="10" t="inlineStr"/>
@@ -4765,11 +4729,11 @@
     </row>
     <row r="166">
       <c r="A166" s="5" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>Sensor AM2315C</t>
+          <t>Caixa modular para trilho DIN — 3 módulos (52,5 mm)</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
@@ -4779,7 +4743,7 @@
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>I²C, umidade + temperatura, carcaça selada</t>
+          <t>Invólucro da PI-1. Cabe no espaço livre do trilho 3, ao lado do Arduino. Buscar caixa para trilho din 3m modular</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr"/>
@@ -4792,21 +4756,21 @@
     </row>
     <row r="167">
       <c r="A167" s="9" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B167" s="10" t="inlineStr">
         <is>
-          <t>Capacitor cerâmico 100 nF</t>
+          <t>Borne KF350 / KRE passo 3,5 mm — 10 vias</t>
         </is>
       </c>
       <c r="C167" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D167" s="10" t="inlineStr">
         <is>
-          <t>Filtro dos pinos IS dos BTS</t>
+          <t>Um borne superior (lado Arduino) e um inferior (lado campo). Passo de 3,5 mm porque todos os cabos são de 0,25 mm²</t>
         </is>
       </c>
       <c r="E167" s="10" t="inlineStr"/>
@@ -4819,21 +4783,21 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>Resistor 220 Ω 1/4 W</t>
+          <t>CI ULN2803A (DIP 18 pinos)</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>Série dos LEDs de sinalização</t>
+          <t>Driver dos 4 sinaleiros de 24 V — 8 canais Darlington, 500 mA/50 V, com diodos de proteção internos. 1 uso + 1 reserva (o CI é barato e é o único ponto onde 24 V encosta na lógica)</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr"/>
@@ -4844,11 +4808,31 @@
         <v/>
       </c>
     </row>
-    <row r="169" ht="22" customHeight="1">
-      <c r="A169" s="4" t="inlineStr">
-        <is>
-          <t>🔧 CAMADA 3 — CABOS E ACESSÓRIOS</t>
-        </is>
+    <row r="169">
+      <c r="A169" s="9" t="n">
+        <v>149</v>
+      </c>
+      <c r="B169" s="10" t="inlineStr">
+        <is>
+          <t>Soquete DIP 18 pinos</t>
+        </is>
+      </c>
+      <c r="C169" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D169" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ Solde o soquete, não o CI. Permite trocar o chip sem dessoldar nada</t>
+        </is>
+      </c>
+      <c r="E169" s="10" t="inlineStr"/>
+      <c r="F169" s="11" t="inlineStr"/>
+      <c r="G169" s="12" t="inlineStr"/>
+      <c r="H169" s="12">
+        <f>IF(C169*G169=0,"",C169*G169)</f>
+        <v/>
       </c>
     </row>
     <row r="170">
@@ -4857,24 +4841,20 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>Cabo flexível 1,5 mm² preto</t>
+          <t>Fio rígido 0,25 mm² para interligação</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>3 m</t>
+          <t>1 m</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
         <is>
-          <t>750 V</t>
-        </is>
-      </c>
-      <c r="E170" s="6" t="inlineStr">
-        <is>
-          <t>Retorno geral 0 V e 12 V de potência</t>
-        </is>
-      </c>
+          <t>Ligações por baixo da placa. ⚠️ Não usar "sobra de perna" de componente em trecho longo — oxida e não é isolada</t>
+        </is>
+      </c>
+      <c r="E170" s="6" t="inlineStr"/>
       <c r="F170" s="7" t="inlineStr"/>
       <c r="G170" s="8" t="inlineStr"/>
       <c r="H170" s="8">
@@ -4888,24 +4868,20 @@
       </c>
       <c r="B171" s="10" t="inlineStr">
         <is>
-          <t>Cabo flexível 1,5 mm² vermelho</t>
+          <t>Verniz spray para PCI (ou esmalte incolor)</t>
         </is>
       </c>
       <c r="C171" s="9" t="inlineStr">
         <is>
-          <t>2 m</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D171" s="10" t="inlineStr">
         <is>
-          <t>750 V</t>
-        </is>
-      </c>
-      <c r="E171" s="10" t="inlineStr">
-        <is>
-          <t>12 V de potência (BTS)</t>
-        </is>
-      </c>
+          <t>Proteção do lado da solda contra umidade e oxidação</t>
+        </is>
+      </c>
+      <c r="E171" s="10" t="inlineStr"/>
       <c r="F171" s="11" t="inlineStr"/>
       <c r="G171" s="12" t="inlineStr"/>
       <c r="H171" s="12">
@@ -4919,24 +4895,20 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>Cabo flexível 0,75 mm² vermelho/preto</t>
+          <t>Termorretrátil Ø 2 mm</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>3 m</t>
+          <t>30 cm</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>750 V</t>
-        </is>
-      </c>
-      <c r="E172" s="6" t="inlineStr">
-        <is>
-          <t>Barramento 24 V (trechos internos)</t>
-        </is>
-      </c>
+          <t>Isolação dos 2 resistores de 10 kΩ soldados nos BTS7960</t>
+        </is>
+      </c>
+      <c r="E172" s="6" t="inlineStr"/>
       <c r="F172" s="7" t="inlineStr"/>
       <c r="G172" s="8" t="inlineStr"/>
       <c r="H172" s="8">
@@ -4950,24 +4922,20 @@
       </c>
       <c r="B173" s="10" t="inlineStr">
         <is>
-          <t>Cabo flexível 0,5 mm² (5 cores)</t>
+          <t>Etiqueta impressa em papel adesivo</t>
         </is>
       </c>
       <c r="C173" s="9" t="inlineStr">
         <is>
-          <t>10 m</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D173" s="10" t="inlineStr">
         <is>
-          <t>750 V</t>
-        </is>
-      </c>
-      <c r="E173" s="10" t="inlineStr">
-        <is>
-          <t>5 V, 12 V auxiliar</t>
-        </is>
-      </c>
+          <t>Identificação das 20 vias na frente da caixa — é o que torna a placa auditável</t>
+        </is>
+      </c>
+      <c r="E173" s="10" t="inlineStr"/>
       <c r="F173" s="11" t="inlineStr"/>
       <c r="G173" s="12" t="inlineStr"/>
       <c r="H173" s="12">
@@ -4975,59 +4943,35 @@
         <v/>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="5" t="n">
-        <v>154</v>
-      </c>
-      <c r="B174" s="6" t="inlineStr">
-        <is>
-          <t>Cabo flexível 0,25 mm² (8 cores)</t>
-        </is>
-      </c>
-      <c r="C174" s="5" t="inlineStr">
-        <is>
-          <t>15 m</t>
-        </is>
-      </c>
-      <c r="D174" s="6" t="inlineStr">
-        <is>
-          <t>Sinais</t>
-        </is>
-      </c>
-      <c r="E174" s="6" t="inlineStr">
-        <is>
-          <t>Sensores, botões, comunicação</t>
-        </is>
-      </c>
-      <c r="F174" s="7" t="inlineStr"/>
-      <c r="G174" s="8" t="inlineStr"/>
-      <c r="H174" s="8">
-        <f>IF(C174*G174=0,"",C174*G174)</f>
-        <v/>
+    <row r="174" ht="22" customHeight="1">
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t>🔧 CAMADA 3 — CABOS E ACESSÓRIOS</t>
+        </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="9" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B175" s="10" t="inlineStr">
         <is>
-          <t>Cabo par trançado blindado 2×0,25 mm²</t>
+          <t>Cabo flexível 1,5 mm² preto</t>
         </is>
       </c>
       <c r="C175" s="9" t="inlineStr">
         <is>
-          <t>2 m</t>
+          <t>3 m</t>
         </is>
       </c>
       <c r="D175" s="10" t="inlineStr">
         <is>
-          <t>Blindado, malha aterrada em um ponto</t>
+          <t>750 V</t>
         </is>
       </c>
       <c r="E175" s="10" t="inlineStr">
         <is>
-          <t>I²C e 1-Wire (trecho câmara → painel)</t>
+          <t>Retorno geral 0 V (6,9 A — soma dos 3 ramais)</t>
         </is>
       </c>
       <c r="F175" s="11" t="inlineStr"/>
@@ -5039,26 +4983,26 @@
     </row>
     <row r="176">
       <c r="A176" s="5" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>Terminal tubular (ilhós) 0,25 / 0,5 / 1,5 mm²</t>
+          <t>Cabo flexível 1,5 mm² vermelho</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>1 kit</t>
+          <t>2 m</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>Com colarinho colorido</t>
+          <t>750 V</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>Obrigatório em todo borne parafuso</t>
+          <t>24 V de potência — P1 → painel → BTS (6,0 A)</t>
         </is>
       </c>
       <c r="F176" s="7" t="inlineStr"/>
@@ -5070,26 +5014,26 @@
     </row>
     <row r="177">
       <c r="A177" s="9" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B177" s="10" t="inlineStr">
         <is>
-          <t>Alicate de crimpar terminal tubular</t>
+          <t>Cabo flexível 0,75 mm² vermelho/preto</t>
         </is>
       </c>
       <c r="C177" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3 m</t>
         </is>
       </c>
       <c r="D177" s="10" t="inlineStr">
         <is>
-          <t>Tipo quadrado/hexagonal</t>
+          <t>750 V</t>
         </is>
       </c>
       <c r="E177" s="10" t="inlineStr">
         <is>
-          <t>Ferramenta</t>
+          <t>Barramento 24 V (trechos internos) e saída de 12 V do T3 (1,0 A)</t>
         </is>
       </c>
       <c r="F177" s="11" t="inlineStr"/>
@@ -5101,26 +5045,26 @@
     </row>
     <row r="178">
       <c r="A178" s="5" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>Terminal olhal M4</t>
+          <t>Cabo flexível 0,5 mm² (5 cores)</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 m</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr">
         <is>
-          <t>Amarelo/vermelho</t>
+          <t>750 V</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
         <is>
-          <t>Aterramento</t>
+          <t>5 V e derivações do 12 V auxiliar</t>
         </is>
       </c>
       <c r="F178" s="7" t="inlineStr"/>
@@ -5132,26 +5076,26 @@
     </row>
     <row r="179">
       <c r="A179" s="9" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>Espaguete termorretrátil (kit)</t>
+          <t>Cabo flexível 0,25 mm² (8 cores)</t>
         </is>
       </c>
       <c r="C179" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15 m</t>
         </is>
       </c>
       <c r="D179" s="10" t="inlineStr">
         <is>
-          <t>Diversas bitolas</t>
+          <t>Sinais</t>
         </is>
       </c>
       <c r="E179" s="10" t="inlineStr">
         <is>
-          <t>Isolação de emendas</t>
+          <t>Sensores, botões, comunicação</t>
         </is>
       </c>
       <c r="F179" s="11" t="inlineStr"/>
@@ -5163,26 +5107,26 @@
     </row>
     <row r="180">
       <c r="A180" s="5" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>Abraçadeiras de nylon 100 mm</t>
+          <t>Cabo par trançado blindado 2×0,25 mm²</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2 m</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Blindado, malha aterrada em um ponto</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
         <is>
-          <t>Amarração</t>
+          <t>I²C e 1-Wire (trecho câmara → painel)</t>
         </is>
       </c>
       <c r="F180" s="7" t="inlineStr"/>
@@ -5194,11 +5138,11 @@
     </row>
     <row r="181">
       <c r="A181" s="9" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B181" s="10" t="inlineStr">
         <is>
-          <t>Anilhas de identificação de cabo</t>
+          <t>Terminal tubular (ilhós) 0,25 / 0,5 / 1,5 mm²</t>
         </is>
       </c>
       <c r="C181" s="9" t="inlineStr">
@@ -5208,12 +5152,12 @@
       </c>
       <c r="D181" s="10" t="inlineStr">
         <is>
-          <t>Numeradas 0–9</t>
+          <t>Com colarinho colorido</t>
         </is>
       </c>
       <c r="E181" s="10" t="inlineStr">
         <is>
-          <t>Identificação (norma de painel)</t>
+          <t>Obrigatório em todo borne parafuso</t>
         </is>
       </c>
       <c r="F181" s="11" t="inlineStr"/>
@@ -5225,26 +5169,26 @@
     </row>
     <row r="182">
       <c r="A182" s="5" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>Espiral organizador Ø 8 mm</t>
+          <t>Alicate de crimpar terminal tubular</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>2 m</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Tipo quadrado/hexagonal</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>Chicote painel → câmara</t>
+          <t>Ferramenta</t>
         </is>
       </c>
       <c r="F182" s="7" t="inlineStr"/>
@@ -5254,11 +5198,35 @@
         <v/>
       </c>
     </row>
-    <row r="183" ht="22" customHeight="1">
-      <c r="A183" s="4" t="inlineStr">
-        <is>
-          <t>⚠️ Itens que NÃO existem mais nesta versão</t>
-        </is>
+    <row r="183">
+      <c r="A183" s="9" t="n">
+        <v>162</v>
+      </c>
+      <c r="B183" s="10" t="inlineStr">
+        <is>
+          <t>Terminal olhal M4</t>
+        </is>
+      </c>
+      <c r="C183" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D183" s="10" t="inlineStr">
+        <is>
+          <t>Amarelo/vermelho</t>
+        </is>
+      </c>
+      <c r="E183" s="10" t="inlineStr">
+        <is>
+          <t>Aterramento</t>
+        </is>
+      </c>
+      <c r="F183" s="11" t="inlineStr"/>
+      <c r="G183" s="12" t="inlineStr"/>
+      <c r="H183" s="12">
+        <f>IF(C183*G183=0,"",C183*G183)</f>
+        <v/>
       </c>
     </row>
     <row r="184">
@@ -5267,12 +5235,24 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>Fonte ATX 500 W</t>
-        </is>
-      </c>
-      <c r="C184" s="5" t="inlineStr"/>
-      <c r="D184" s="6" t="inlineStr"/>
-      <c r="E184" s="6" t="inlineStr"/>
+          <t>Espaguete termorretrátil (kit)</t>
+        </is>
+      </c>
+      <c r="C184" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D184" s="6" t="inlineStr">
+        <is>
+          <t>Diversas bitolas</t>
+        </is>
+      </c>
+      <c r="E184" s="6" t="inlineStr">
+        <is>
+          <t>Isolação de emendas</t>
+        </is>
+      </c>
       <c r="F184" s="7" t="inlineStr"/>
       <c r="G184" s="8" t="inlineStr"/>
       <c r="H184" s="8">
@@ -5286,12 +5266,24 @@
       </c>
       <c r="B185" s="10" t="inlineStr">
         <is>
-          <t>Jumper PS_ON (verde-preto)</t>
-        </is>
-      </c>
-      <c r="C185" s="9" t="inlineStr"/>
-      <c r="D185" s="10" t="inlineStr"/>
-      <c r="E185" s="10" t="inlineStr"/>
+          <t>Abraçadeiras de nylon 100 mm</t>
+        </is>
+      </c>
+      <c r="C185" s="9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D185" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E185" s="10" t="inlineStr">
+        <is>
+          <t>Amarração</t>
+        </is>
+      </c>
       <c r="F185" s="11" t="inlineStr"/>
       <c r="G185" s="12" t="inlineStr"/>
       <c r="H185" s="12">
@@ -5305,12 +5297,24 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>Acrílico preto 3 mm (cobertura)</t>
-        </is>
-      </c>
-      <c r="C186" s="5" t="inlineStr"/>
-      <c r="D186" s="6" t="inlineStr"/>
-      <c r="E186" s="6" t="inlineStr"/>
+          <t>Anilhas de identificação de cabo</t>
+        </is>
+      </c>
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>1 kit</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr">
+        <is>
+          <t>Numeradas 0–9</t>
+        </is>
+      </c>
+      <c r="E186" s="6" t="inlineStr">
+        <is>
+          <t>Identificação (norma de painel)</t>
+        </is>
+      </c>
       <c r="F186" s="7" t="inlineStr"/>
       <c r="G186" s="8" t="inlineStr"/>
       <c r="H186" s="8">
@@ -5324,12 +5328,24 @@
       </c>
       <c r="B187" s="10" t="inlineStr">
         <is>
-          <t>Porta simples de acrílico 10 mm</t>
-        </is>
-      </c>
-      <c r="C187" s="9" t="inlineStr"/>
-      <c r="D187" s="10" t="inlineStr"/>
-      <c r="E187" s="10" t="inlineStr"/>
+          <t>Espiral organizador Ø 8 mm</t>
+        </is>
+      </c>
+      <c r="C187" s="9" t="inlineStr">
+        <is>
+          <t>2 m</t>
+        </is>
+      </c>
+      <c r="D187" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E187" s="10" t="inlineStr">
+        <is>
+          <t>Chicote painel → câmara</t>
+        </is>
+      </c>
       <c r="F187" s="11" t="inlineStr"/>
       <c r="G187" s="12" t="inlineStr"/>
       <c r="H187" s="12">
@@ -5337,58 +5353,39 @@
         <v/>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="5" t="n">
-        <v>167</v>
-      </c>
-      <c r="B188" s="6" t="inlineStr">
-        <is>
-          <t>XPS 20 mm</t>
-        </is>
-      </c>
-      <c r="C188" s="5" t="inlineStr"/>
-      <c r="D188" s="6" t="inlineStr"/>
-      <c r="E188" s="6" t="inlineStr"/>
-      <c r="F188" s="7" t="inlineStr"/>
-      <c r="G188" s="8" t="inlineStr"/>
-      <c r="H188" s="8">
-        <f>IF(C188*G188=0,"",C188*G188)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="190">
-      <c r="F190" s="13" t="inlineStr">
+    <row r="189">
+      <c r="F189" s="13" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="H190" s="14">
-        <f>SUM(H5:H188)</f>
+      <c r="H189" s="14">
+        <f>SUM(H5:H187)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H188"/>
+  <autoFilter ref="A4:H187"/>
   <mergeCells count="19">
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A98:H98"/>
-    <mergeCell ref="A169:H169"/>
+    <mergeCell ref="A142:H142"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A79:H79"/>
-    <mergeCell ref="A183:H183"/>
-    <mergeCell ref="A133:H133"/>
-    <mergeCell ref="A163:H163"/>
+    <mergeCell ref="A88:H88"/>
+    <mergeCell ref="A174:H174"/>
+    <mergeCell ref="A128:H128"/>
+    <mergeCell ref="A164:H164"/>
+    <mergeCell ref="A158:H158"/>
+    <mergeCell ref="A74:H74"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A104:H104"/>
+    <mergeCell ref="A151:H151"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A109:H109"/>
-    <mergeCell ref="A147:H147"/>
-    <mergeCell ref="A156:H156"/>
-    <mergeCell ref="A63:H63"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A44:H44"/>
     <mergeCell ref="A93:H93"/>
+    <mergeCell ref="A58:H58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5584,7 +5581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -5601,180 +5598,288 @@
     <row r="3">
       <c r="A3" s="19" t="inlineStr">
         <is>
-          <t>Tensão de entrada</t>
+          <t>Arquitetura de energia</t>
         </is>
       </c>
       <c r="B3" s="20" t="inlineStr">
         <is>
-          <t>127 V CA</t>
+          <t>Potência em 24 V — carga térmica sem conversor</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
-          <t>Barramento de distribuição</t>
+          <t>Tensão de entrada</t>
         </is>
       </c>
       <c r="B4" s="22" t="inlineStr">
         <is>
-          <t>24 V CC (SELV)</t>
+          <t>127 V CA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>Potência instalada (fonte)</t>
+          <t>Barramento de distribuição</t>
         </is>
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>240 W · 10 A</t>
+          <t>24 V CC (SELV)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="21" t="inlineStr">
         <is>
-          <t>Consumo calculado</t>
+          <t>Potência instalada (fonte)</t>
         </is>
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>≈ 101 W · 4,2 A @ 24 V</t>
+          <t>240 W · 10 A</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>Corrente CA de entrada</t>
+          <t>Consumo calculado</t>
         </is>
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>1,44 A</t>
+          <t>≈ 166 W · 6,9 A @ 24 V</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="21" t="inlineStr">
         <is>
-          <t>Queda de tensão na linha dos postes</t>
+          <t>Folga da fonte</t>
         </is>
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>0,17 V (0,71 %)</t>
+          <t>1,44× (44 %) — a fonte de 150 W NÃO atende</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t>Tensões derivadas</t>
+          <t>Corrente CA de entrada</t>
         </is>
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>12,0 V potência · 12,0 V auxiliar · 5,10 V comando · 3,3 V ESP32</t>
+          <t>2,37 A</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="21" t="inlineStr">
         <is>
-          <t>Níveis de proteção</t>
+          <t>Queda de tensão na linha dos postes</t>
         </is>
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>9 (do disjuntor ao intertravamento por software)</t>
+          <t>0,21 V (0,86 %)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>Volume útil da câmara</t>
+          <t>Conversores</t>
         </is>
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>5,0 litros (200 × 100 × 250 mm)</t>
+          <t>2 × LM2596 com display (T2 e T3) · P1 é derivação direta</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="21" t="inlineStr">
         <is>
-          <t>Carga térmica calculada</t>
+          <t>Tensões derivadas</t>
         </is>
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>≈ 9,5 W</t>
+          <t>24,0 V potência (direto) · 12,0 V auxiliar · 5,10 V comando · 3,3 V ESP32</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>Capacidade da Peltier a ΔT = 20 K</t>
+          <t>Fusíveis dos ramais</t>
         </is>
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>≈ 30 W (margem de 3,2×)</t>
+          <t>F1 = 10 A · F2 = 2 A · F3 = 2 A (sem F4/F5, sem crowbar)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="21" t="inlineStr">
         <is>
-          <t>Isolamento</t>
+          <t>Níveis de proteção</t>
         </is>
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>XPS 30 mm + barreira de vapor · U = 0,86 W/m²·K</t>
+          <t>5 (do disjuntor ao intertravamento por software)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>Porta</t>
+          <t>Volume útil da câmara</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>Dupla · U = 2,42 W/m²·K (não condensa)</t>
+          <t>5,0 litros (200 × 100 × 250 mm)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="21" t="inlineStr">
         <is>
-          <t>Base da maquete</t>
+          <t>Carga térmica calculada</t>
         </is>
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>900 × 500 mm · escala cenográfica 1:50</t>
+          <t>≈ 9,5 W</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="19" t="inlineStr">
         <is>
+          <t>Refrigeração</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>2 × TEC1-12706 EM SÉRIE · 24 V · 6,0 A · 144 W</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>Capacidade das Peltier a ΔT = 20 K</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>≈ 60 W (margem de 6,3×)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>Dissipação no lado quente</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>≈ 200 W — 2 conjuntos dissipador + cooler 80 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>Aquecimento</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>PTC cerâmico de 24 V · 60 W · 2,5 A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>Isolamento</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>XPS 30 mm + barreira de vapor · U = 0,86 W/m²·K</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>Porta</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>Dupla · U = 2,42 W/m²·K (não condensa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>Base da maquete</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>1500 × 500 mm · escala cenográfica 1:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
           <t>Painel</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>400 × 500 × 200 mm · 3 trilhos DIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>Componentes discretos</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>6 + 1 CI ULN2803 na PI-1 · 2 nos BTS7960 · 4 nos postes da maquete</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Sinalização</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>4 sinaleiros 22 mm de 24 V (via ULN2803) · 4 LEDs brancos de 5 V na maquete</t>
         </is>
       </c>
     </row>

--- a/BOM_Projeto_Integrador.xlsx
+++ b/BOM_Projeto_Integrador.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Dados do Projeto" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lista de Compras'!$A$4:$H$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lista de Compras'!$A$4:$J$197</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,6 +47,11 @@
       <b val="1"/>
       <color rgb="001D3557"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <sz val="9"/>
+      <u val="single"/>
     </font>
     <font>
       <b val="1"/>
@@ -124,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -144,6 +149,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -156,31 +164,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -551,17 +562,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H189"/>
+  <dimension ref="A1:J199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -574,7 +587,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Lista de materiais · gerada de 03_lista_materiais.md em 13/08/2026 19:12 · arquitetura 127 V CA → 24 V CC → 12 / 5 / 3,3 V</t>
+          <t>Lista de materiais · gerada de 03_lista_materiais.md em 13/08/2026 23:11 · arquitetura 127 V CA → 24 V CC → 12 / 5 / 3,3 V</t>
         </is>
       </c>
     </row>
@@ -601,20 +614,30 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Observação / busca</t>
+          <t>Observação</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Link de compra</t>
+          <t>🔎 Buscar no Mercado Livre</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>🔎 Buscar na Amazon</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Link escolhido (cole aqui)</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>Preço unit. (R$)</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Total (R$)</t>
         </is>
@@ -651,41 +674,57 @@
           <t>fonte chaveada 24v 10a 240w</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8">
-        <f>IF(C6*G6=0,"",C6*G6)</f>
+      <c r="F6" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fonte-chaveada-24v-10a-240w","🔎 fonte chaveada 24v 10a 240w")</f>
+        <v/>
+      </c>
+      <c r="G6" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fonte+chaveada+24v+10a+240w","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H6" s="8" t="inlineStr"/>
+      <c r="I6" s="9" t="inlineStr"/>
+      <c r="J6" s="9">
+        <f>IF(C6*I6=0,"",C6*I6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="n">
+      <c r="A7" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Disjuntor DIN 2P 6 A curva C</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Bipolar, 6 A, curva C (por causa do inrush da fonte), 3 kA</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>disjuntor bipolar 6a curva c din</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr"/>
-      <c r="G7" s="12" t="inlineStr"/>
-      <c r="H7" s="12">
-        <f>IF(C7*G7=0,"",C7*G7)</f>
+      <c r="F7" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/disjuntor-bipolar-6a-curva-c-din","🔎 disjuntor bipolar 6a curva c")</f>
+        <v/>
+      </c>
+      <c r="G7" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=disjuntor+bipolar+6a+curva+c+din","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H7" s="13" t="inlineStr"/>
+      <c r="I7" s="14" t="inlineStr"/>
+      <c r="J7" s="14">
+        <f>IF(C7*I7=0,"",C7*I7)</f>
         <v/>
       </c>
     </row>
@@ -713,41 +752,57 @@
           <t>chave seletora 2 posicoes 22mm</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr"/>
-      <c r="G8" s="8" t="inlineStr"/>
-      <c r="H8" s="8">
-        <f>IF(C8*G8=0,"",C8*G8)</f>
+      <c r="F8" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/chave-seletora-2-posicoes-22mm","🔎 chave seletora 2 posicoes 22")</f>
+        <v/>
+      </c>
+      <c r="G8" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=chave+seletora+2+posicoes+22mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H8" s="8" t="inlineStr"/>
+      <c r="I8" s="9" t="inlineStr"/>
+      <c r="J8" s="9">
+        <f>IF(C8*I8=0,"",C8*I8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n">
+      <c r="A9" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Cabo PP 3×1,5 mm² + plugue</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>1,5 m</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Cabo de entrada AC com plugue 2P+T 10 A</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>cabo pp 3x1,5 com plugue</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr"/>
-      <c r="G9" s="12" t="inlineStr"/>
-      <c r="H9" s="12">
-        <f>IF(C9*G9=0,"",C9*G9)</f>
+      <c r="F9" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-pp-3x1-5-com-plugue","🔎 cabo pp 3x1,5 com plugue")</f>
+        <v/>
+      </c>
+      <c r="G9" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+pp+3x1%2C5+com+plugue","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H9" s="13" t="inlineStr"/>
+      <c r="I9" s="14" t="inlineStr"/>
+      <c r="J9" s="14">
+        <f>IF(C9*I9=0,"",C9*I9)</f>
         <v/>
       </c>
     </row>
@@ -775,41 +830,57 @@
           <t>prensa cabo pg9</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr"/>
-      <c r="G10" s="8" t="inlineStr"/>
-      <c r="H10" s="8">
-        <f>IF(C10*G10=0,"",C10*G10)</f>
+      <c r="F10" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/prensa-cabo-pg9","🔎 prensa cabo pg9")</f>
+        <v/>
+      </c>
+      <c r="G10" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=prensa+cabo+pg9","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H10" s="8" t="inlineStr"/>
+      <c r="I10" s="9" t="inlineStr"/>
+      <c r="J10" s="9">
+        <f>IF(C10*I10=0,"",C10*I10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n">
+      <c r="A11" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Borne DIN 4 mm²</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Distribuição 24 V e 0 V na subestação</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>borne trilho din 4mm parafuso</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr"/>
-      <c r="G11" s="12" t="inlineStr"/>
-      <c r="H11" s="12">
-        <f>IF(C11*G11=0,"",C11*G11)</f>
+      <c r="F11" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/borne-trilho-din-4mm-parafuso","🔎 borne trilho din 4mm parafus")</f>
+        <v/>
+      </c>
+      <c r="G11" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=borne+trilho+din+4mm+parafuso","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H11" s="13" t="inlineStr"/>
+      <c r="I11" s="14" t="inlineStr"/>
+      <c r="J11" s="14">
+        <f>IF(C11*I11=0,"",C11*I11)</f>
         <v/>
       </c>
     </row>
@@ -837,41 +908,57 @@
           <t>cooler 60mm 24v</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr"/>
-      <c r="G12" s="8" t="inlineStr"/>
-      <c r="H12" s="8">
-        <f>IF(C12*G12=0,"",C12*G12)</f>
+      <c r="F12" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cooler-60mm-24v","🔎 cooler 60mm 24v")</f>
+        <v/>
+      </c>
+      <c r="G12" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cooler+60mm+24v","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H12" s="8" t="inlineStr"/>
+      <c r="I12" s="9" t="inlineStr"/>
+      <c r="J12" s="9">
+        <f>IF(C12*I12=0,"",C12*I12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="n">
+      <c r="A13" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Grade + filtro 60 mm</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Veneziana de entrada de ar da subestação</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>grade cooler 60mm com filtro</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr"/>
-      <c r="G13" s="12" t="inlineStr"/>
-      <c r="H13" s="12">
-        <f>IF(C13*G13=0,"",C13*G13)</f>
+      <c r="F13" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/grade-cooler-60mm-com-filtro","🔎 grade cooler 60mm com filtro")</f>
+        <v/>
+      </c>
+      <c r="G13" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=grade+cooler+60mm+com+filtro","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H13" s="13" t="inlineStr"/>
+      <c r="I13" s="14" t="inlineStr"/>
+      <c r="J13" s="14">
+        <f>IF(C13*I13=0,"",C13*I13)</f>
         <v/>
       </c>
     </row>
@@ -883,33 +970,45 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="n">
+      <c r="A15" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>⭐ Kit 2× Módulo LM2596 com display</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>1 kit</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Step-down 3 A, Vin até 40 V, saída ajustável, display LED vermelho de 3 dígitos integrado. Um módulo vira o T2, o outro vira o T3</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>ver abaixo</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr"/>
-      <c r="G15" s="12" t="inlineStr"/>
-      <c r="H15" s="12">
-        <f>IF(C15*G15=0,"",C15*G15)</f>
+      <c r="F15" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/kit-2-modulo-lm2596-display","🔎 kit 2 modulo lm2596 display")</f>
+        <v/>
+      </c>
+      <c r="G15" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=kit+2+modulo+lm2596+display","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>Mercado Livre</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr"/>
+      <c r="J15" s="14">
+        <f>IF(C15*I15=0,"",C15*I15)</f>
         <v/>
       </c>
     </row>
@@ -937,41 +1036,45 @@
           <t>5,10 V</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr"/>
+      <c r="F16" s="8" t="inlineStr"/>
       <c r="G16" s="8" t="inlineStr"/>
-      <c r="H16" s="8">
-        <f>IF(C16*G16=0,"",C16*G16)</f>
+      <c r="H16" s="8" t="inlineStr"/>
+      <c r="I16" s="9" t="inlineStr"/>
+      <c r="J16" s="9">
+        <f>IF(C16*I16=0,"",C16*I16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="n">
+      <c r="A17" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>→ T3 (poste P3, auxiliares)</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>2º módulo do kit — alimenta as fans internas e os coolers</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>12,0 V</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr"/>
-      <c r="G17" s="12" t="inlineStr"/>
-      <c r="H17" s="12">
-        <f>IF(C17*G17=0,"",C17*G17)</f>
+      <c r="F17" s="13" t="inlineStr"/>
+      <c r="G17" s="13" t="inlineStr"/>
+      <c r="H17" s="13" t="inlineStr"/>
+      <c r="I17" s="14" t="inlineStr"/>
+      <c r="J17" s="14">
+        <f>IF(C17*I17=0,"",C17*I17)</f>
         <v/>
       </c>
     </row>
@@ -999,41 +1102,57 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr"/>
-      <c r="G18" s="8" t="inlineStr"/>
-      <c r="H18" s="8">
-        <f>IF(C18*G18=0,"",C18*G18)</f>
+      <c r="F18" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/kit-lm2596-reserva","🔎 kit lm2596 reserva")</f>
+        <v/>
+      </c>
+      <c r="G18" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=kit+lm2596+reserva","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H18" s="8" t="inlineStr"/>
+      <c r="I18" s="9" t="inlineStr"/>
+      <c r="J18" s="9">
+        <f>IF(C18*I18=0,"",C18*I18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="n">
+      <c r="A19" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Dissipador de alumínio ~20 × 15 × 10 mm</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>⚠️ Obrigatório, colado no CI LM2596S de cada módulo. Sem ele o T3 passa dos 100 °C dentro do tubo — ver Doc 02 §2.8</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr"/>
-      <c r="G19" s="12" t="inlineStr"/>
-      <c r="H19" s="12">
-        <f>IF(C19*G19=0,"",C19*G19)</f>
+      <c r="F19" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/dissipador-aluminio-20-15-10-mm","🔎 dissipador aluminio 20 15 10")</f>
+        <v/>
+      </c>
+      <c r="G19" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=dissipador+aluminio+20+15+10+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H19" s="13" t="inlineStr"/>
+      <c r="I19" s="14" t="inlineStr"/>
+      <c r="J19" s="14">
+        <f>IF(C19*I19=0,"",C19*I19)</f>
         <v/>
       </c>
     </row>
@@ -1061,41 +1180,57 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="8" t="inlineStr"/>
-      <c r="H20" s="8">
-        <f>IF(C20*G20=0,"",C20*G20)</f>
+      <c r="F20" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-termica-dupla-face","🔎 fita termica dupla face")</f>
+        <v/>
+      </c>
+      <c r="G20" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+termica+dupla+face","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H20" s="8" t="inlineStr"/>
+      <c r="I20" s="9" t="inlineStr"/>
+      <c r="J20" s="9">
+        <f>IF(C20*I20=0,"",C20*I20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="n">
+      <c r="A21" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Acrílico transparente 1 mm</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>1 lâmina</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Janelas de visualização nos 3 tubos dos postes (~20 × 12 mm cada) — protege o display e mantém o visual fechado</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr"/>
-      <c r="G21" s="12" t="inlineStr"/>
-      <c r="H21" s="12">
-        <f>IF(C21*G21=0,"",C21*G21)</f>
+      <c r="F21" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/acrilico-transparente-1-mm","🔎 acrilico transparente 1 mm")</f>
+        <v/>
+      </c>
+      <c r="G21" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=acrilico+transparente+1+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H21" s="13" t="inlineStr"/>
+      <c r="I21" s="14" t="inlineStr"/>
+      <c r="J21" s="14">
+        <f>IF(C21*I21=0,"",C21*I21)</f>
         <v/>
       </c>
     </row>
@@ -1123,10 +1258,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr"/>
-      <c r="G22" s="8" t="inlineStr"/>
-      <c r="H22" s="8">
-        <f>IF(C22*G22=0,"",C22*G22)</f>
+      <c r="F22" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/voltimetro-amperimetro-digital-3-fios","🔎 voltimetro amperimetro digit")</f>
+        <v/>
+      </c>
+      <c r="G22" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=voltimetro+amperimetro+digital+3+fios","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H22" s="8" t="inlineStr"/>
+      <c r="I22" s="9" t="inlineStr"/>
+      <c r="J22" s="9">
+        <f>IF(C22*I22=0,"",C22*I22)</f>
         <v/>
       </c>
     </row>
@@ -1161,41 +1304,57 @@
           <t>F1, F2, F3 — entrada dos 3 ramais</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr"/>
-      <c r="G24" s="8" t="inlineStr"/>
-      <c r="H24" s="8">
-        <f>IF(C24*G24=0,"",C24*G24)</f>
+      <c r="F24" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/porta-fusivel-mini-automotivo-din","🔎 porta fusivel mini automotiv")</f>
+        <v/>
+      </c>
+      <c r="G24" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=porta+fusivel+mini+automotivo+din","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H24" s="8" t="inlineStr"/>
+      <c r="I24" s="9" t="inlineStr"/>
+      <c r="J24" s="9">
+        <f>IF(C24*I24=0,"",C24*I24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="n">
+      <c r="A25" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Fusível mini automotivo 10 A</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>1 uso + 1 reserva</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>F1 — ramal R1 (potência 24 V, 6,0 A)</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr"/>
-      <c r="G25" s="12" t="inlineStr"/>
-      <c r="H25" s="12">
-        <f>IF(C25*G25=0,"",C25*G25)</f>
+      <c r="F25" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fusivel-mini-automotivo-10","🔎 fusivel mini automotivo 10")</f>
+        <v/>
+      </c>
+      <c r="G25" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fusivel+mini+automotivo+10","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H25" s="13" t="inlineStr"/>
+      <c r="I25" s="14" t="inlineStr"/>
+      <c r="J25" s="14">
+        <f>IF(C25*I25=0,"",C25*I25)</f>
         <v/>
       </c>
     </row>
@@ -1223,41 +1382,57 @@
           <t>F2 (comando) e F3 (auxiliares)</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr"/>
-      <c r="G26" s="8" t="inlineStr"/>
-      <c r="H26" s="8">
-        <f>IF(C26*G26=0,"",C26*G26)</f>
+      <c r="F26" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fusivel-mini-automotivo-2","🔎 fusivel mini automotivo 2")</f>
+        <v/>
+      </c>
+      <c r="G26" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fusivel+mini+automotivo+2","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H26" s="8" t="inlineStr"/>
+      <c r="I26" s="9" t="inlineStr"/>
+      <c r="J26" s="9">
+        <f>IF(C26*I26=0,"",C26*I26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="n">
+      <c r="A27" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>Terminal olhal M4 amarelo</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>Aterramento e barramento de 0 V</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr"/>
-      <c r="G27" s="12" t="inlineStr"/>
-      <c r="H27" s="12">
-        <f>IF(C27*G27=0,"",C27*G27)</f>
+      <c r="F27" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/terminal-olhal-m4-amarelo","🔎 terminal olhal m4 amarelo")</f>
+        <v/>
+      </c>
+      <c r="G27" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=terminal+olhal+m4+amarelo","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H27" s="13" t="inlineStr"/>
+      <c r="I27" s="14" t="inlineStr"/>
+      <c r="J27" s="14">
+        <f>IF(C27*I27=0,"",C27*I27)</f>
         <v/>
       </c>
     </row>
@@ -1269,29 +1444,37 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="n">
+      <c r="A29" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>MDF 12 mm</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>1 chapa</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>1500 × 500 mm — tampo da base</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr"/>
-      <c r="F29" s="11" t="inlineStr"/>
-      <c r="G29" s="12" t="inlineStr"/>
-      <c r="H29" s="12">
-        <f>IF(C29*G29=0,"",C29*G29)</f>
+      <c r="E29" s="11" t="inlineStr"/>
+      <c r="F29" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/mdf-12-mm","🔎 mdf 12 mm")</f>
+        <v/>
+      </c>
+      <c r="G29" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=mdf+12+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H29" s="13" t="inlineStr"/>
+      <c r="I29" s="14" t="inlineStr"/>
+      <c r="J29" s="14">
+        <f>IF(C29*I29=0,"",C29*I29)</f>
         <v/>
       </c>
     </row>
@@ -1315,37 +1498,53 @@
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr"/>
-      <c r="F30" s="7" t="inlineStr"/>
-      <c r="G30" s="8" t="inlineStr"/>
-      <c r="H30" s="8">
-        <f>IF(C30*G30=0,"",C30*G30)</f>
+      <c r="F30" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/mdf-15-mm","🔎 mdf 15 mm")</f>
+        <v/>
+      </c>
+      <c r="G30" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=mdf+15+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H30" s="8" t="inlineStr"/>
+      <c r="I30" s="9" t="inlineStr"/>
+      <c r="J30" s="9">
+        <f>IF(C30*I30=0,"",C30*I30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="n">
+      <c r="A31" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>MDF 15 mm</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>3 tiras</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>Travessas de reforço 15 × 40 mm, com entalhe de 20 × 25 mm no centro</t>
         </is>
       </c>
-      <c r="E31" s="10" t="inlineStr"/>
-      <c r="F31" s="11" t="inlineStr"/>
-      <c r="G31" s="12" t="inlineStr"/>
-      <c r="H31" s="12">
-        <f>IF(C31*G31=0,"",C31*G31)</f>
+      <c r="E31" s="11" t="inlineStr"/>
+      <c r="F31" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/mdf-15-mm","🔎 mdf 15 mm")</f>
+        <v/>
+      </c>
+      <c r="G31" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=mdf+15+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H31" s="13" t="inlineStr"/>
+      <c r="I31" s="14" t="inlineStr"/>
+      <c r="J31" s="14">
+        <f>IF(C31*I31=0,"",C31*I31)</f>
         <v/>
       </c>
     </row>
@@ -1369,37 +1568,53 @@
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="7" t="inlineStr"/>
-      <c r="G32" s="8" t="inlineStr"/>
-      <c r="H32" s="8">
-        <f>IF(C32*G32=0,"",C32*G32)</f>
+      <c r="F32" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/pes-borracha-antiderrapante","🔎 pes borracha antiderrapante")</f>
+        <v/>
+      </c>
+      <c r="G32" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=pes+borracha+antiderrapante","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H32" s="8" t="inlineStr"/>
+      <c r="I32" s="9" t="inlineStr"/>
+      <c r="J32" s="9">
+        <f>IF(C32*I32=0,"",C32*I32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="n">
+      <c r="A33" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>Conector circular GX16 8 pinos</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>1 par</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>Opcional — só na versão modular (união elétrica entre os 2 módulos)</t>
         </is>
       </c>
-      <c r="E33" s="10" t="inlineStr"/>
-      <c r="F33" s="11" t="inlineStr"/>
-      <c r="G33" s="12" t="inlineStr"/>
-      <c r="H33" s="12">
-        <f>IF(C33*G33=0,"",C33*G33)</f>
+      <c r="E33" s="11" t="inlineStr"/>
+      <c r="F33" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/conector-circular-gx16-8-pinos","🔎 conector circular gx16 8 pin")</f>
+        <v/>
+      </c>
+      <c r="G33" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=conector+circular+gx16+8+pinos","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H33" s="13" t="inlineStr"/>
+      <c r="I33" s="14" t="inlineStr"/>
+      <c r="J33" s="14">
+        <f>IF(C33*I33=0,"",C33*I33)</f>
         <v/>
       </c>
     </row>
@@ -1423,37 +1638,53 @@
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr"/>
-      <c r="F34" s="7" t="inlineStr"/>
-      <c r="G34" s="8" t="inlineStr"/>
-      <c r="H34" s="8">
-        <f>IF(C34*G34=0,"",C34*G34)</f>
+      <c r="F34" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/pinos-guia-6-mm-buchas","🔎 pinos guia 6 mm buchas")</f>
+        <v/>
+      </c>
+      <c r="G34" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=pinos+guia+6+mm+buchas","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H34" s="8" t="inlineStr"/>
+      <c r="I34" s="9" t="inlineStr"/>
+      <c r="J34" s="9">
+        <f>IF(C34*I34=0,"",C34*I34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="n">
+      <c r="A35" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>Alças de transporte</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>Alça embutida de baú/case, laterais</t>
         </is>
       </c>
-      <c r="E35" s="10" t="inlineStr"/>
-      <c r="F35" s="11" t="inlineStr"/>
-      <c r="G35" s="12" t="inlineStr"/>
-      <c r="H35" s="12">
-        <f>IF(C35*G35=0,"",C35*G35)</f>
+      <c r="E35" s="11" t="inlineStr"/>
+      <c r="F35" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/alcas-transporte","🔎 alcas transporte")</f>
+        <v/>
+      </c>
+      <c r="G35" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=alcas+transporte","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H35" s="13" t="inlineStr"/>
+      <c r="I35" s="14" t="inlineStr"/>
+      <c r="J35" s="14">
+        <f>IF(C35*I35=0,"",C35*I35)</f>
         <v/>
       </c>
     </row>
@@ -1477,37 +1708,53 @@
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr"/>
-      <c r="F36" s="7" t="inlineStr"/>
-      <c r="G36" s="8" t="inlineStr"/>
-      <c r="H36" s="8">
-        <f>IF(C36*G36=0,"",C36*G36)</f>
+      <c r="F36" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/parafusos-m5-20-m4-16-m3-12","🔎 parafusos m5 20, m4 16, m3 1")</f>
+        <v/>
+      </c>
+      <c r="G36" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=parafusos+m5+20%2C+m4+16%2C+m3+12","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H36" s="8" t="inlineStr"/>
+      <c r="I36" s="9" t="inlineStr"/>
+      <c r="J36" s="9">
+        <f>IF(C36*I36=0,"",C36*I36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="n">
+      <c r="A37" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>Insertos rosqueados M4/M5 p/ MDF</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D37" s="11" t="inlineStr">
         <is>
           <t>Evita espanar a rosca no MDF</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr"/>
-      <c r="F37" s="11" t="inlineStr"/>
-      <c r="G37" s="12" t="inlineStr"/>
-      <c r="H37" s="12">
-        <f>IF(C37*G37=0,"",C37*G37)</f>
+      <c r="E37" s="11" t="inlineStr"/>
+      <c r="F37" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/insertos-rosqueados-m4-m5-p-mdf","🔎 insertos rosqueados m4 m5 p ")</f>
+        <v/>
+      </c>
+      <c r="G37" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=insertos+rosqueados+m4+m5+p+mdf","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H37" s="13" t="inlineStr"/>
+      <c r="I37" s="14" t="inlineStr"/>
+      <c r="J37" s="14">
+        <f>IF(C37*I37=0,"",C37*I37)</f>
         <v/>
       </c>
     </row>
@@ -1519,29 +1766,37 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="n">
+      <c r="A39" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>MDF 9 mm ou acrílico opaco 4 mm</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>Caixa 260 × 190 × 150 mm (L×P×A), frente voltada para a rua</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr"/>
-      <c r="F39" s="11" t="inlineStr"/>
-      <c r="G39" s="12" t="inlineStr"/>
-      <c r="H39" s="12">
-        <f>IF(C39*G39=0,"",C39*G39)</f>
+      <c r="E39" s="11" t="inlineStr"/>
+      <c r="F39" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/mdf-9-mm-acrilico-opaco-4-mm","🔎 mdf 9 mm acrilico opaco 4 mm")</f>
+        <v/>
+      </c>
+      <c r="G39" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=mdf+9+mm+acrilico+opaco+4+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H39" s="13" t="inlineStr"/>
+      <c r="I39" s="14" t="inlineStr"/>
+      <c r="J39" s="14">
+        <f>IF(C39*I39=0,"",C39*I39)</f>
         <v/>
       </c>
     </row>
@@ -1565,37 +1820,53 @@
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr"/>
-      <c r="F40" s="7" t="inlineStr"/>
-      <c r="G40" s="8" t="inlineStr"/>
-      <c r="H40" s="8">
-        <f>IF(C40*G40=0,"",C40*G40)</f>
+      <c r="F40" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/dobradica-pequena-fecho","🔎 dobradica pequena fecho")</f>
+        <v/>
+      </c>
+      <c r="G40" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=dobradica+pequena+fecho","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H40" s="8" t="inlineStr"/>
+      <c r="I40" s="9" t="inlineStr"/>
+      <c r="J40" s="9">
+        <f>IF(C40*I40=0,"",C40*I40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="n">
+      <c r="A41" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>Tela metálica / alambrado miniatura</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D41" s="11" t="inlineStr">
         <is>
           <t>Cerca do pátio da subestação (tela de aço, malha 3 mm)</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr"/>
-      <c r="F41" s="11" t="inlineStr"/>
-      <c r="G41" s="12" t="inlineStr"/>
-      <c r="H41" s="12">
-        <f>IF(C41*G41=0,"",C41*G41)</f>
+      <c r="E41" s="11" t="inlineStr"/>
+      <c r="F41" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tela-metalica-alambrado-miniatura","🔎 tela metalica alambrado mini")</f>
+        <v/>
+      </c>
+      <c r="G41" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tela+metalica+alambrado+miniatura","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H41" s="13" t="inlineStr"/>
+      <c r="I41" s="14" t="inlineStr"/>
+      <c r="J41" s="14">
+        <f>IF(C41*I41=0,"",C41*I41)</f>
         <v/>
       </c>
     </row>
@@ -1619,37 +1890,53 @@
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr"/>
-      <c r="F42" s="7" t="inlineStr"/>
-      <c r="G42" s="8" t="inlineStr"/>
-      <c r="H42" s="8">
-        <f>IF(C42*G42=0,"",C42*G42)</f>
+      <c r="F42" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/pedrisco-brita-fina","🔎 pedrisco brita fina")</f>
+        <v/>
+      </c>
+      <c r="G42" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=pedrisco+brita+fina","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H42" s="8" t="inlineStr"/>
+      <c r="I42" s="9" t="inlineStr"/>
+      <c r="J42" s="9">
+        <f>IF(C42*I42=0,"",C42*I42)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="n">
+      <c r="A43" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="B43" s="10" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>Placa "PERIGO ALTA TENSÃO"</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D43" s="10" t="inlineStr">
+      <c r="D43" s="11" t="inlineStr">
         <is>
           <t>Impressa em papel adesivo, ~15 × 10 mm</t>
         </is>
       </c>
-      <c r="E43" s="10" t="inlineStr"/>
-      <c r="F43" s="11" t="inlineStr"/>
-      <c r="G43" s="12" t="inlineStr"/>
-      <c r="H43" s="12">
-        <f>IF(C43*G43=0,"",C43*G43)</f>
+      <c r="E43" s="11" t="inlineStr"/>
+      <c r="F43" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/placa-perigo-alta-tensao","🔎 placa perigo alta tensao")</f>
+        <v/>
+      </c>
+      <c r="G43" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=placa+perigo+alta+tensao","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H43" s="13" t="inlineStr"/>
+      <c r="I43" s="14" t="inlineStr"/>
+      <c r="J43" s="14">
+        <f>IF(C43*I43=0,"",C43*I43)</f>
         <v/>
       </c>
     </row>
@@ -1661,29 +1948,37 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="n">
+      <c r="A45" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="B45" s="10" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>Tubo de alumínio Ø 8 mm</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>1,5 m</t>
         </is>
       </c>
-      <c r="D45" s="10" t="inlineStr">
+      <c r="D45" s="11" t="inlineStr">
         <is>
           <t>Cortar em 3 postes de 350 mm (300 mm visíveis + 50 mm de encaixe)</t>
         </is>
       </c>
-      <c r="E45" s="10" t="inlineStr"/>
-      <c r="F45" s="11" t="inlineStr"/>
-      <c r="G45" s="12" t="inlineStr"/>
-      <c r="H45" s="12">
-        <f>IF(C45*G45=0,"",C45*G45)</f>
+      <c r="E45" s="11" t="inlineStr"/>
+      <c r="F45" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tubo-aluminio-8-mm","🔎 tubo aluminio 8 mm")</f>
+        <v/>
+      </c>
+      <c r="G45" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tubo+aluminio+8+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H45" s="13" t="inlineStr"/>
+      <c r="I45" s="14" t="inlineStr"/>
+      <c r="J45" s="14">
+        <f>IF(C45*I45=0,"",C45*I45)</f>
         <v/>
       </c>
     </row>
@@ -1707,37 +2002,53 @@
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr"/>
-      <c r="F46" s="7" t="inlineStr"/>
-      <c r="G46" s="8" t="inlineStr"/>
-      <c r="H46" s="8">
-        <f>IF(C46*G46=0,"",C46*G46)</f>
+      <c r="F46" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/barra-chata-aluminio-12-2-mm","🔎 barra chata aluminio 12 2 mm")</f>
+        <v/>
+      </c>
+      <c r="G46" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=barra+chata+aluminio+12+2+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H46" s="8" t="inlineStr"/>
+      <c r="I46" s="9" t="inlineStr"/>
+      <c r="J46" s="9">
+        <f>IF(C46*I46=0,"",C46*I46)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="n">
+      <c r="A47" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="B47" s="10" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>Fio rígido ENCAPADO 1,00 mm² VERMELHO ⬆</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C47" s="10" t="inlineStr">
         <is>
           <t>2 m</t>
         </is>
       </c>
-      <c r="D47" s="10" t="inlineStr">
+      <c r="D47" s="11" t="inlineStr">
         <is>
           <t>Ramal R1 (potência, 6,0 A). ⚠️ Subiu de 0,75 para 1,00 mm² por causa da corrente das 2 Peltier. Nunca condutor nu — em CC qualquer ponte metálica é curto franco</t>
         </is>
       </c>
-      <c r="E47" s="10" t="inlineStr"/>
-      <c r="F47" s="11" t="inlineStr"/>
-      <c r="G47" s="12" t="inlineStr"/>
-      <c r="H47" s="12">
-        <f>IF(C47*G47=0,"",C47*G47)</f>
+      <c r="E47" s="11" t="inlineStr"/>
+      <c r="F47" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-rigido-encapado-1-00-mm-vermelho","🔎 fio rigido encapado 1,00 mm ")</f>
+        <v/>
+      </c>
+      <c r="G47" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+rigido+encapado+1%2C00+mm+vermelho","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H47" s="13" t="inlineStr"/>
+      <c r="I47" s="14" t="inlineStr"/>
+      <c r="J47" s="14">
+        <f>IF(C47*I47=0,"",C47*I47)</f>
         <v/>
       </c>
     </row>
@@ -1761,37 +2072,53 @@
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr"/>
-      <c r="F48" s="7" t="inlineStr"/>
-      <c r="G48" s="8" t="inlineStr"/>
-      <c r="H48" s="8">
-        <f>IF(C48*G48=0,"",C48*G48)</f>
+      <c r="F48" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-rigido-encapado-0-50-mm-marrom","🔎 fio rigido encapado 0,50 mm ")</f>
+        <v/>
+      </c>
+      <c r="G48" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+rigido+encapado+0%2C50+mm+marrom","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H48" s="8" t="inlineStr"/>
+      <c r="I48" s="9" t="inlineStr"/>
+      <c r="J48" s="9">
+        <f>IF(C48*I48=0,"",C48*I48)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="n">
+      <c r="A49" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="B49" s="10" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>Fio rígido ENCAPADO 0,50 mm² CINZA</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C49" s="10" t="inlineStr">
         <is>
           <t>2 m</t>
         </is>
       </c>
-      <c r="D49" s="10" t="inlineStr">
+      <c r="D49" s="11" t="inlineStr">
         <is>
           <t>Ramal R3 (auxiliares)</t>
         </is>
       </c>
-      <c r="E49" s="10" t="inlineStr"/>
-      <c r="F49" s="11" t="inlineStr"/>
-      <c r="G49" s="12" t="inlineStr"/>
-      <c r="H49" s="12">
-        <f>IF(C49*G49=0,"",C49*G49)</f>
+      <c r="E49" s="11" t="inlineStr"/>
+      <c r="F49" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-rigido-encapado-0-50-mm-cinza","🔎 fio rigido encapado 0,50 mm ")</f>
+        <v/>
+      </c>
+      <c r="G49" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+rigido+encapado+0%2C50+mm+cinza","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H49" s="13" t="inlineStr"/>
+      <c r="I49" s="14" t="inlineStr"/>
+      <c r="J49" s="14">
+        <f>IF(C49*I49=0,"",C49*I49)</f>
         <v/>
       </c>
     </row>
@@ -1815,37 +2142,53 @@
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr"/>
-      <c r="F50" s="7" t="inlineStr"/>
-      <c r="G50" s="8" t="inlineStr"/>
-      <c r="H50" s="8">
-        <f>IF(C50*G50=0,"",C50*G50)</f>
+      <c r="F50" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-rigido-encapado-1-50-mm-azul-claro","🔎 fio rigido encapado 1,50 mm ")</f>
+        <v/>
+      </c>
+      <c r="G50" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+rigido+encapado+1%2C50+mm+azul+claro","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H50" s="8" t="inlineStr"/>
+      <c r="I50" s="9" t="inlineStr"/>
+      <c r="J50" s="9">
+        <f>IF(C50*I50=0,"",C50*I50)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="n">
+      <c r="A51" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="B51" s="10" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>Contas/miçangas marrom ou branca Ø 6 mm</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D51" s="10" t="inlineStr">
+      <c r="D51" s="11" t="inlineStr">
         <is>
           <t>Isoladores de pino da cruzeta</t>
         </is>
       </c>
-      <c r="E51" s="10" t="inlineStr"/>
-      <c r="F51" s="11" t="inlineStr"/>
-      <c r="G51" s="12" t="inlineStr"/>
-      <c r="H51" s="12">
-        <f>IF(C51*G51=0,"",C51*G51)</f>
+      <c r="E51" s="11" t="inlineStr"/>
+      <c r="F51" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/contas-micangas-marrom-branca-6-mm","🔎 contas micangas marrom branc")</f>
+        <v/>
+      </c>
+      <c r="G51" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=contas+micangas+marrom+branca+6+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H51" s="13" t="inlineStr"/>
+      <c r="I51" s="14" t="inlineStr"/>
+      <c r="J51" s="14">
+        <f>IF(C51*I51=0,"",C51*I51)</f>
         <v/>
       </c>
     </row>
@@ -1869,37 +2212,53 @@
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr"/>
-      <c r="F52" s="7" t="inlineStr"/>
-      <c r="G52" s="8" t="inlineStr"/>
-      <c r="H52" s="8">
-        <f>IF(C52*G52=0,"",C52*G52)</f>
+      <c r="F52" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tubo-pvc-50-mm","🔎 tubo pvc 50 mm")</f>
+        <v/>
+      </c>
+      <c r="G52" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tubo+pvc+50+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H52" s="8" t="inlineStr"/>
+      <c r="I52" s="9" t="inlineStr"/>
+      <c r="J52" s="9">
+        <f>IF(C52*I52=0,"",C52*I52)</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="n">
+      <c r="A53" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="B53" s="10" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>Tampa/cap PVC Ø 50 mm</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
+      <c r="C53" s="10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D53" s="10" t="inlineStr">
+      <c r="D53" s="11" t="inlineStr">
         <is>
           <t>Tampas dos 3 corpos</t>
         </is>
       </c>
-      <c r="E53" s="10" t="inlineStr"/>
-      <c r="F53" s="11" t="inlineStr"/>
-      <c r="G53" s="12" t="inlineStr"/>
-      <c r="H53" s="12">
-        <f>IF(C53*G53=0,"",C53*G53)</f>
+      <c r="E53" s="11" t="inlineStr"/>
+      <c r="F53" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tampa-cap-pvc-50-mm","🔎 tampa cap pvc 50 mm")</f>
+        <v/>
+      </c>
+      <c r="G53" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tampa+cap+pvc+50+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H53" s="13" t="inlineStr"/>
+      <c r="I53" s="14" t="inlineStr"/>
+      <c r="J53" s="14">
+        <f>IF(C53*I53=0,"",C53*I53)</f>
         <v/>
       </c>
     </row>
@@ -1923,37 +2282,53 @@
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr"/>
-      <c r="F54" s="7" t="inlineStr"/>
-      <c r="G54" s="8" t="inlineStr"/>
-      <c r="H54" s="8">
-        <f>IF(C54*G54=0,"",C54*G54)</f>
+      <c r="F54" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cinta-aluminio-10-mm","🔎 cinta aluminio 10 mm")</f>
+        <v/>
+      </c>
+      <c r="G54" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cinta+aluminio+10+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H54" s="8" t="inlineStr"/>
+      <c r="I54" s="9" t="inlineStr"/>
+      <c r="J54" s="9">
+        <f>IF(C54*I54=0,"",C54*I54)</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="n">
+      <c r="A55" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="B55" s="10" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>Bornes de emenda pequenos (2 ou 3 vias)</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D55" s="10" t="inlineStr">
+      <c r="D55" s="11" t="inlineStr">
         <is>
           <t>Dentro da caixa de derivação do P1 — ali os 24 V só se distribuem, não se transformam</t>
         </is>
       </c>
-      <c r="E55" s="10" t="inlineStr"/>
-      <c r="F55" s="11" t="inlineStr"/>
-      <c r="G55" s="12" t="inlineStr"/>
-      <c r="H55" s="12">
-        <f>IF(C55*G55=0,"",C55*G55)</f>
+      <c r="E55" s="11" t="inlineStr"/>
+      <c r="F55" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/bornes-emenda-pequenos","🔎 bornes emenda pequenos")</f>
+        <v/>
+      </c>
+      <c r="G55" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=bornes+emenda+pequenos","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H55" s="13" t="inlineStr"/>
+      <c r="I55" s="14" t="inlineStr"/>
+      <c r="J55" s="14">
+        <f>IF(C55*I55=0,"",C55*I55)</f>
         <v/>
       </c>
     </row>
@@ -1977,37 +2352,53 @@
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr"/>
-      <c r="F56" s="7" t="inlineStr"/>
-      <c r="G56" s="8" t="inlineStr"/>
-      <c r="H56" s="8">
-        <f>IF(C56*G56=0,"",C56*G56)</f>
+      <c r="F56" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/flange-base-fixacao-postes","🔎 flange base fixacao postes")</f>
+        <v/>
+      </c>
+      <c r="G56" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=flange+base+fixacao+postes","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H56" s="8" t="inlineStr"/>
+      <c r="I56" s="9" t="inlineStr"/>
+      <c r="J56" s="9">
+        <f>IF(C56*I56=0,"",C56*I56)</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="n">
+      <c r="A57" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="B57" s="10" t="inlineStr">
+      <c r="B57" s="11" t="inlineStr">
         <is>
           <t>Etiquetas adesivas impressas</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C57" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D57" s="10" t="inlineStr">
+      <c r="D57" s="11" t="inlineStr">
         <is>
           <t>Identificação dos corpos: "P1 — DERIVAÇÃO 24 V", "T2 — 24/5 V", "T3 — 24/12 V"</t>
         </is>
       </c>
-      <c r="E57" s="10" t="inlineStr"/>
-      <c r="F57" s="11" t="inlineStr"/>
-      <c r="G57" s="12" t="inlineStr"/>
-      <c r="H57" s="12">
-        <f>IF(C57*G57=0,"",C57*G57)</f>
+      <c r="E57" s="11" t="inlineStr"/>
+      <c r="F57" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/etiquetas-adesivas-impressas","🔎 etiquetas adesivas impressas")</f>
+        <v/>
+      </c>
+      <c r="G57" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=etiquetas+adesivas+impressas","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H57" s="13" t="inlineStr"/>
+      <c r="I57" s="14" t="inlineStr"/>
+      <c r="J57" s="14">
+        <f>IF(C57*I57=0,"",C57*I57)</f>
         <v/>
       </c>
     </row>
@@ -2019,29 +2410,37 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="n">
+      <c r="A59" s="10" t="n">
         <v>48</v>
       </c>
-      <c r="B59" s="10" t="inlineStr">
+      <c r="B59" s="11" t="inlineStr">
         <is>
           <t>Tinta spray cinza-asfalto escuro fosco</t>
         </is>
       </c>
-      <c r="C59" s="9" t="inlineStr">
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D59" s="10" t="inlineStr">
+      <c r="D59" s="11" t="inlineStr">
         <is>
           <t>Pista da rua</t>
         </is>
       </c>
-      <c r="E59" s="10" t="inlineStr"/>
-      <c r="F59" s="11" t="inlineStr"/>
-      <c r="G59" s="12" t="inlineStr"/>
-      <c r="H59" s="12">
-        <f>IF(C59*G59=0,"",C59*G59)</f>
+      <c r="E59" s="11" t="inlineStr"/>
+      <c r="F59" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tinta-spray-cinza-asfalto-escuro-fosco","🔎 tinta spray cinza asfalto es")</f>
+        <v/>
+      </c>
+      <c r="G59" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tinta+spray+cinza+asfalto+escuro+fosco","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H59" s="13" t="inlineStr"/>
+      <c r="I59" s="14" t="inlineStr"/>
+      <c r="J59" s="14">
+        <f>IF(C59*I59=0,"",C59*I59)</f>
         <v/>
       </c>
     </row>
@@ -2065,37 +2464,53 @@
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr"/>
-      <c r="F60" s="7" t="inlineStr"/>
-      <c r="G60" s="8" t="inlineStr"/>
-      <c r="H60" s="8">
-        <f>IF(C60*G60=0,"",C60*G60)</f>
+      <c r="F60" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tubo-aluminio-5-mm","🔎 tubo aluminio 5 mm")</f>
+        <v/>
+      </c>
+      <c r="G60" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tubo+aluminio+5+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H60" s="8" t="inlineStr"/>
+      <c r="I60" s="9" t="inlineStr"/>
+      <c r="J60" s="9">
+        <f>IF(C60*I60=0,"",C60*I60)</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="n">
+      <c r="A61" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="B61" s="10" t="inlineStr">
+      <c r="B61" s="11" t="inlineStr">
         <is>
           <t>Arame 1,5 mm</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C61" s="10" t="inlineStr">
         <is>
           <t>1 m</t>
         </is>
       </c>
-      <c r="D61" s="10" t="inlineStr">
+      <c r="D61" s="11" t="inlineStr">
         <is>
           <t>Braço curvo das luminárias e estrutura do portão</t>
         </is>
       </c>
-      <c r="E61" s="10" t="inlineStr"/>
-      <c r="F61" s="11" t="inlineStr"/>
-      <c r="G61" s="12" t="inlineStr"/>
-      <c r="H61" s="12">
-        <f>IF(C61*G61=0,"",C61*G61)</f>
+      <c r="E61" s="11" t="inlineStr"/>
+      <c r="F61" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/arame-1-5-mm","🔎 arame 1,5 mm")</f>
+        <v/>
+      </c>
+      <c r="G61" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=arame+1%2C5+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H61" s="13" t="inlineStr"/>
+      <c r="I61" s="14" t="inlineStr"/>
+      <c r="J61" s="14">
+        <f>IF(C61*I61=0,"",C61*I61)</f>
         <v/>
       </c>
     </row>
@@ -2119,37 +2534,53 @@
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr"/>
-      <c r="F62" s="7" t="inlineStr"/>
-      <c r="G62" s="8" t="inlineStr"/>
-      <c r="H62" s="8">
-        <f>IF(C62*G62=0,"",C62*G62)</f>
+      <c r="F62" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/led-3-mm-branco-quente","🔎 led 3 mm branco quente")</f>
+        <v/>
+      </c>
+      <c r="G62" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=led+3+mm+branco+quente","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H62" s="8" t="inlineStr"/>
+      <c r="I62" s="9" t="inlineStr"/>
+      <c r="J62" s="9">
+        <f>IF(C62*I62=0,"",C62*I62)</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="9" t="n">
+      <c r="A63" s="10" t="n">
         <v>52</v>
       </c>
-      <c r="B63" s="10" t="inlineStr">
+      <c r="B63" s="11" t="inlineStr">
         <is>
           <t>Resistor 220 Ω 1/4 W</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D63" s="10" t="inlineStr">
+      <c r="D63" s="11" t="inlineStr">
         <is>
           <t>Limitador dos LEDs da rua — já contabilizado na lista L.4, não compre de novo. ⚠️ Valor dimensionado para 5 V: (5 − 3,1)/220 = 8,6 mA. Monte cada um dentro da base do poste, com termorretrátil</t>
         </is>
       </c>
-      <c r="E63" s="10" t="inlineStr"/>
-      <c r="F63" s="11" t="inlineStr"/>
-      <c r="G63" s="12" t="inlineStr"/>
-      <c r="H63" s="12">
-        <f>IF(C63*G63=0,"",C63*G63)</f>
+      <c r="E63" s="11" t="inlineStr"/>
+      <c r="F63" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-220-1-4-w","🔎 resistor 220 1 4 w")</f>
+        <v/>
+      </c>
+      <c r="G63" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+220+1+4+w","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H63" s="13" t="inlineStr"/>
+      <c r="I63" s="14" t="inlineStr"/>
+      <c r="J63" s="14">
+        <f>IF(C63*I63=0,"",C63*I63)</f>
         <v/>
       </c>
     </row>
@@ -2173,37 +2604,53 @@
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr"/>
-      <c r="F64" s="7" t="inlineStr"/>
-      <c r="G64" s="8" t="inlineStr"/>
-      <c r="H64" s="8">
-        <f>IF(C64*G64=0,"",C64*G64)</f>
+      <c r="F64" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/carro-passeio-miniatura-1-50","🔎 carro passeio miniatura 1 50")</f>
+        <v/>
+      </c>
+      <c r="G64" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=carro+passeio+miniatura+1+50","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H64" s="8" t="inlineStr"/>
+      <c r="I64" s="9" t="inlineStr"/>
+      <c r="J64" s="9">
+        <f>IF(C64*I64=0,"",C64*I64)</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="9" t="n">
+      <c r="A65" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="B65" s="10" t="inlineStr">
+      <c r="B65" s="11" t="inlineStr">
         <is>
           <t>Caminhão / van 1:50</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C65" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D65" s="10" t="inlineStr">
+      <c r="D65" s="11" t="inlineStr">
         <is>
           <t>~150 mm, entrando pelo portão</t>
         </is>
       </c>
-      <c r="E65" s="10" t="inlineStr"/>
-      <c r="F65" s="11" t="inlineStr"/>
-      <c r="G65" s="12" t="inlineStr"/>
-      <c r="H65" s="12">
-        <f>IF(C65*G65=0,"",C65*G65)</f>
+      <c r="E65" s="11" t="inlineStr"/>
+      <c r="F65" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/caminhao-van-1-50","🔎 caminhao van 1 50")</f>
+        <v/>
+      </c>
+      <c r="G65" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=caminhao+van+1+50","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H65" s="13" t="inlineStr"/>
+      <c r="I65" s="14" t="inlineStr"/>
+      <c r="J65" s="14">
+        <f>IF(C65*I65=0,"",C65*I65)</f>
         <v/>
       </c>
     </row>
@@ -2227,37 +2674,53 @@
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr"/>
-      <c r="F66" s="7" t="inlineStr"/>
-      <c r="G66" s="8" t="inlineStr"/>
-      <c r="H66" s="8">
-        <f>IF(C66*G66=0,"",C66*G66)</f>
+      <c r="F66" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tira-mdf-3-mm","🔎 tira mdf 3 mm")</f>
+        <v/>
+      </c>
+      <c r="G66" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tira+mdf+3+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H66" s="8" t="inlineStr"/>
+      <c r="I66" s="9" t="inlineStr"/>
+      <c r="J66" s="9">
+        <f>IF(C66*I66=0,"",C66*I66)</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="9" t="n">
+      <c r="A67" s="10" t="n">
         <v>56</v>
       </c>
-      <c r="B67" s="10" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>Fita branca 2 mm ou caneta posca branca</t>
         </is>
       </c>
-      <c r="C67" s="9" t="inlineStr">
+      <c r="C67" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D67" s="10" t="inlineStr">
+      <c r="D67" s="11" t="inlineStr">
         <is>
           <t>Faixa central tracejada, faixa de bordo e faixa de pedestres</t>
         </is>
       </c>
-      <c r="E67" s="10" t="inlineStr"/>
-      <c r="F67" s="11" t="inlineStr"/>
-      <c r="G67" s="12" t="inlineStr"/>
-      <c r="H67" s="12">
-        <f>IF(C67*G67=0,"",C67*G67)</f>
+      <c r="E67" s="11" t="inlineStr"/>
+      <c r="F67" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-branca-2-mm-caneta-posca-branca","🔎 fita branca 2 mm caneta posc")</f>
+        <v/>
+      </c>
+      <c r="G67" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+branca+2+mm+caneta+posca+branca","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H67" s="13" t="inlineStr"/>
+      <c r="I67" s="14" t="inlineStr"/>
+      <c r="J67" s="14">
+        <f>IF(C67*I67=0,"",C67*I67)</f>
         <v/>
       </c>
     </row>
@@ -2281,37 +2744,53 @@
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr"/>
-      <c r="F68" s="7" t="inlineStr"/>
-      <c r="G68" s="8" t="inlineStr"/>
-      <c r="H68" s="8">
-        <f>IF(C68*G68=0,"",C68*G68)</f>
+      <c r="F68" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/mdf-4-mm","🔎 mdf 4 mm")</f>
+        <v/>
+      </c>
+      <c r="G68" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=mdf+4+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H68" s="8" t="inlineStr"/>
+      <c r="I68" s="9" t="inlineStr"/>
+      <c r="J68" s="9">
+        <f>IF(C68*I68=0,"",C68*I68)</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="9" t="n">
+      <c r="A69" s="10" t="n">
         <v>58</v>
       </c>
-      <c r="B69" s="10" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>MDF 4 mm</t>
         </is>
       </c>
-      <c r="C69" s="9" t="inlineStr">
+      <c r="C69" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D69" s="10" t="inlineStr">
+      <c r="D69" s="11" t="inlineStr">
         <is>
           <t>Guarita 45 × 45 × 55 mm, com janela recortada</t>
         </is>
       </c>
-      <c r="E69" s="10" t="inlineStr"/>
-      <c r="F69" s="11" t="inlineStr"/>
-      <c r="G69" s="12" t="inlineStr"/>
-      <c r="H69" s="12">
-        <f>IF(C69*G69=0,"",C69*G69)</f>
+      <c r="E69" s="11" t="inlineStr"/>
+      <c r="F69" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/mdf-4-mm","🔎 mdf 4 mm")</f>
+        <v/>
+      </c>
+      <c r="G69" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=mdf+4+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H69" s="13" t="inlineStr"/>
+      <c r="I69" s="14" t="inlineStr"/>
+      <c r="J69" s="14">
+        <f>IF(C69*I69=0,"",C69*I69)</f>
         <v/>
       </c>
     </row>
@@ -2335,37 +2814,53 @@
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr"/>
-      <c r="F70" s="7" t="inlineStr"/>
-      <c r="G70" s="8" t="inlineStr"/>
-      <c r="H70" s="8">
-        <f>IF(C70*G70=0,"",C70*G70)</f>
+      <c r="F70" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tinta-azul-industrial","🔎 tinta azul industrial")</f>
+        <v/>
+      </c>
+      <c r="G70" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tinta+azul+industrial","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H70" s="8" t="inlineStr"/>
+      <c r="I70" s="9" t="inlineStr"/>
+      <c r="J70" s="9">
+        <f>IF(C70*I70=0,"",C70*I70)</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="9" t="n">
+      <c r="A71" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="B71" s="10" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>Árvores de maquete</t>
         </is>
       </c>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="C71" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D71" s="10" t="inlineStr">
+      <c r="D71" s="11" t="inlineStr">
         <is>
           <t>Escala 1:50, na calçada da frente</t>
         </is>
       </c>
-      <c r="E71" s="10" t="inlineStr"/>
-      <c r="F71" s="11" t="inlineStr"/>
-      <c r="G71" s="12" t="inlineStr"/>
-      <c r="H71" s="12">
-        <f>IF(C71*G71=0,"",C71*G71)</f>
+      <c r="E71" s="11" t="inlineStr"/>
+      <c r="F71" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/arvores-maquete","🔎 arvores maquete")</f>
+        <v/>
+      </c>
+      <c r="G71" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=arvores+maquete","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H71" s="13" t="inlineStr"/>
+      <c r="I71" s="14" t="inlineStr"/>
+      <c r="J71" s="14">
+        <f>IF(C71*I71=0,"",C71*I71)</f>
         <v/>
       </c>
     </row>
@@ -2389,37 +2884,53 @@
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr"/>
-      <c r="F72" s="7" t="inlineStr"/>
-      <c r="G72" s="8" t="inlineStr"/>
-      <c r="H72" s="8">
-        <f>IF(C72*G72=0,"",C72*G72)</f>
+      <c r="F72" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/placas-transito-miniatura","🔎 placas transito miniatura")</f>
+        <v/>
+      </c>
+      <c r="G72" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=placas+transito+miniatura","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H72" s="8" t="inlineStr"/>
+      <c r="I72" s="9" t="inlineStr"/>
+      <c r="J72" s="9">
+        <f>IF(C72*I72=0,"",C72*I72)</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="9" t="n">
+      <c r="A73" s="10" t="n">
         <v>62</v>
       </c>
-      <c r="B73" s="10" t="inlineStr">
+      <c r="B73" s="11" t="inlineStr">
         <is>
           <t>Lixeira urbana + abrigo de ônibus</t>
         </is>
       </c>
-      <c r="C73" s="9" t="inlineStr">
+      <c r="C73" s="10" t="inlineStr">
         <is>
           <t>1 cada</t>
         </is>
       </c>
-      <c r="D73" s="10" t="inlineStr">
+      <c r="D73" s="11" t="inlineStr">
         <is>
           <t>Opcional — enriquece a cena</t>
         </is>
       </c>
-      <c r="E73" s="10" t="inlineStr"/>
-      <c r="F73" s="11" t="inlineStr"/>
-      <c r="G73" s="12" t="inlineStr"/>
-      <c r="H73" s="12">
-        <f>IF(C73*G73=0,"",C73*G73)</f>
+      <c r="E73" s="11" t="inlineStr"/>
+      <c r="F73" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/lixeira-urbana-abrigo-onibus","🔎 lixeira urbana abrigo onibus")</f>
+        <v/>
+      </c>
+      <c r="G73" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=lixeira+urbana+abrigo+onibus","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H73" s="13" t="inlineStr"/>
+      <c r="I73" s="14" t="inlineStr"/>
+      <c r="J73" s="14">
+        <f>IF(C73*I73=0,"",C73*I73)</f>
         <v/>
       </c>
     </row>
@@ -2431,29 +2942,37 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="9" t="n">
+      <c r="A75" s="10" t="n">
         <v>63</v>
       </c>
-      <c r="B75" s="10" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
         <is>
           <t>Tinta spray cinza claro fosco</t>
         </is>
       </c>
-      <c r="C75" s="9" t="inlineStr">
+      <c r="C75" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D75" s="10" t="inlineStr">
+      <c r="D75" s="11" t="inlineStr">
         <is>
           <t>Piso industrial (epóxi)</t>
         </is>
       </c>
-      <c r="E75" s="10" t="inlineStr"/>
-      <c r="F75" s="11" t="inlineStr"/>
-      <c r="G75" s="12" t="inlineStr"/>
-      <c r="H75" s="12">
-        <f>IF(C75*G75=0,"",C75*G75)</f>
+      <c r="E75" s="11" t="inlineStr"/>
+      <c r="F75" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tinta-spray-cinza-claro-fosco","🔎 tinta spray cinza claro fosc")</f>
+        <v/>
+      </c>
+      <c r="G75" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tinta+spray+cinza+claro+fosco","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H75" s="13" t="inlineStr"/>
+      <c r="I75" s="14" t="inlineStr"/>
+      <c r="J75" s="14">
+        <f>IF(C75*I75=0,"",C75*I75)</f>
         <v/>
       </c>
     </row>
@@ -2477,37 +2996,53 @@
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr"/>
-      <c r="F76" s="7" t="inlineStr"/>
-      <c r="G76" s="8" t="inlineStr"/>
-      <c r="H76" s="8">
-        <f>IF(C76*G76=0,"",C76*G76)</f>
+      <c r="F76" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tinta-spray-preto-fosco","🔎 tinta spray preto fosco")</f>
+        <v/>
+      </c>
+      <c r="G76" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tinta+spray+preto+fosco","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H76" s="8" t="inlineStr"/>
+      <c r="I76" s="9" t="inlineStr"/>
+      <c r="J76" s="9">
+        <f>IF(C76*I76=0,"",C76*I76)</f>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="9" t="n">
+      <c r="A77" s="10" t="n">
         <v>65</v>
       </c>
-      <c r="B77" s="10" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>Verniz fosco spray</t>
         </is>
       </c>
-      <c r="C77" s="9" t="inlineStr">
+      <c r="C77" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D77" s="10" t="inlineStr">
+      <c r="D77" s="11" t="inlineStr">
         <is>
           <t>Proteção final do piso pintado</t>
         </is>
       </c>
-      <c r="E77" s="10" t="inlineStr"/>
-      <c r="F77" s="11" t="inlineStr"/>
-      <c r="G77" s="12" t="inlineStr"/>
-      <c r="H77" s="12">
-        <f>IF(C77*G77=0,"",C77*G77)</f>
+      <c r="E77" s="11" t="inlineStr"/>
+      <c r="F77" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/verniz-fosco-spray","🔎 verniz fosco spray")</f>
+        <v/>
+      </c>
+      <c r="G77" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=verniz+fosco+spray","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H77" s="13" t="inlineStr"/>
+      <c r="I77" s="14" t="inlineStr"/>
+      <c r="J77" s="14">
+        <f>IF(C77*I77=0,"",C77*I77)</f>
         <v/>
       </c>
     </row>
@@ -2531,37 +3066,53 @@
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr"/>
-      <c r="F78" s="7" t="inlineStr"/>
-      <c r="G78" s="8" t="inlineStr"/>
-      <c r="H78" s="8">
-        <f>IF(C78*G78=0,"",C78*G78)</f>
+      <c r="F78" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-adesiva-amarela-10-mm","🔎 fita adesiva amarela 10 mm")</f>
+        <v/>
+      </c>
+      <c r="G78" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+adesiva+amarela+10+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H78" s="8" t="inlineStr"/>
+      <c r="I78" s="9" t="inlineStr"/>
+      <c r="J78" s="9">
+        <f>IF(C78*I78=0,"",C78*I78)</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="9" t="n">
+      <c r="A79" s="10" t="n">
         <v>67</v>
       </c>
-      <c r="B79" s="10" t="inlineStr">
+      <c r="B79" s="11" t="inlineStr">
         <is>
           <t>Fita zebrada amarelo/preto 20 mm</t>
         </is>
       </c>
-      <c r="C79" s="9" t="inlineStr">
+      <c r="C79" s="10" t="inlineStr">
         <is>
           <t>1 rolo</t>
         </is>
       </c>
-      <c r="D79" s="10" t="inlineStr">
+      <c r="D79" s="11" t="inlineStr">
         <is>
           <t>Faixa de segurança em frente ao painel (exigência NR-10 — zona de trabalho)</t>
         </is>
       </c>
-      <c r="E79" s="10" t="inlineStr"/>
-      <c r="F79" s="11" t="inlineStr"/>
-      <c r="G79" s="12" t="inlineStr"/>
-      <c r="H79" s="12">
-        <f>IF(C79*G79=0,"",C79*G79)</f>
+      <c r="E79" s="11" t="inlineStr"/>
+      <c r="F79" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-zebrada-amarelo-preto-20-mm","🔎 fita zebrada amarelo preto 2")</f>
+        <v/>
+      </c>
+      <c r="G79" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+zebrada+amarelo+preto+20+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H79" s="13" t="inlineStr"/>
+      <c r="I79" s="14" t="inlineStr"/>
+      <c r="J79" s="14">
+        <f>IF(C79*I79=0,"",C79*I79)</f>
         <v/>
       </c>
     </row>
@@ -2585,37 +3136,53 @@
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr"/>
-      <c r="F80" s="7" t="inlineStr"/>
-      <c r="G80" s="8" t="inlineStr"/>
-      <c r="H80" s="8">
-        <f>IF(C80*G80=0,"",C80*G80)</f>
+      <c r="F80" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-adesiva-verde-10-mm","🔎 fita adesiva verde 10 mm")</f>
+        <v/>
+      </c>
+      <c r="G80" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+adesiva+verde+10+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H80" s="8" t="inlineStr"/>
+      <c r="I80" s="9" t="inlineStr"/>
+      <c r="J80" s="9">
+        <f>IF(C80*I80=0,"",C80*I80)</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="9" t="n">
+      <c r="A81" s="10" t="n">
         <v>69</v>
       </c>
-      <c r="B81" s="10" t="inlineStr">
+      <c r="B81" s="11" t="inlineStr">
         <is>
           <t>Figuras de maquete escala 1:50</t>
         </is>
       </c>
-      <c r="C81" s="9" t="inlineStr">
+      <c r="C81" s="10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D81" s="10" t="inlineStr">
+      <c r="D81" s="11" t="inlineStr">
         <is>
           <t>(4 na fábrica, 3 na rua, 3 reservas) Pessoas com EPI (loja de maquetaria/arquitetura)</t>
         </is>
       </c>
-      <c r="E81" s="10" t="inlineStr"/>
-      <c r="F81" s="11" t="inlineStr"/>
-      <c r="G81" s="12" t="inlineStr"/>
-      <c r="H81" s="12">
-        <f>IF(C81*G81=0,"",C81*G81)</f>
+      <c r="E81" s="11" t="inlineStr"/>
+      <c r="F81" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/figuras-maquete-escala-1-50","🔎 figuras maquete escala 1 50")</f>
+        <v/>
+      </c>
+      <c r="G81" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=figuras+maquete+escala+1+50","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H81" s="13" t="inlineStr"/>
+      <c r="I81" s="14" t="inlineStr"/>
+      <c r="J81" s="14">
+        <f>IF(C81*I81=0,"",C81*I81)</f>
         <v/>
       </c>
     </row>
@@ -2639,37 +3206,53 @@
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr"/>
-      <c r="F82" s="7" t="inlineStr"/>
-      <c r="G82" s="8" t="inlineStr"/>
-      <c r="H82" s="8">
-        <f>IF(C82*G82=0,"",C82*G82)</f>
+      <c r="F82" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/miniaturas-empilhadeira-pallets-tambores","🔎 miniaturas empilhadeira, pal")</f>
+        <v/>
+      </c>
+      <c r="G82" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=miniaturas+empilhadeira%2C+pallets%2C+tambores","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H82" s="8" t="inlineStr"/>
+      <c r="I82" s="9" t="inlineStr"/>
+      <c r="J82" s="9">
+        <f>IF(C82*I82=0,"",C82*I82)</f>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="9" t="n">
+      <c r="A83" s="10" t="n">
         <v>71</v>
       </c>
-      <c r="B83" s="10" t="inlineStr">
+      <c r="B83" s="11" t="inlineStr">
         <is>
           <t>Extintor miniatura + placa</t>
         </is>
       </c>
-      <c r="C83" s="9" t="inlineStr">
+      <c r="C83" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D83" s="10" t="inlineStr">
+      <c r="D83" s="11" t="inlineStr">
         <is>
           <t>Sinalização de segurança</t>
         </is>
       </c>
-      <c r="E83" s="10" t="inlineStr"/>
-      <c r="F83" s="11" t="inlineStr"/>
-      <c r="G83" s="12" t="inlineStr"/>
-      <c r="H83" s="12">
-        <f>IF(C83*G83=0,"",C83*G83)</f>
+      <c r="E83" s="11" t="inlineStr"/>
+      <c r="F83" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/extintor-miniatura-placa","🔎 extintor miniatura placa")</f>
+        <v/>
+      </c>
+      <c r="G83" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=extintor+miniatura+placa","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H83" s="13" t="inlineStr"/>
+      <c r="I83" s="14" t="inlineStr"/>
+      <c r="J83" s="14">
+        <f>IF(C83*I83=0,"",C83*I83)</f>
         <v/>
       </c>
     </row>
@@ -2693,37 +3276,53 @@
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr"/>
-      <c r="F84" s="7" t="inlineStr"/>
-      <c r="G84" s="8" t="inlineStr"/>
-      <c r="H84" s="8">
-        <f>IF(C84*G84=0,"",C84*G84)</f>
+      <c r="F84" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/placas-sinalizacao-impressas","🔎 placas sinalizacao impressas")</f>
+        <v/>
+      </c>
+      <c r="G84" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=placas+sinalizacao+impressas","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H84" s="8" t="inlineStr"/>
+      <c r="I84" s="9" t="inlineStr"/>
+      <c r="J84" s="9">
+        <f>IF(C84*I84=0,"",C84*I84)</f>
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="9" t="n">
+      <c r="A85" s="10" t="n">
         <v>73</v>
       </c>
-      <c r="B85" s="10" t="inlineStr">
+      <c r="B85" s="11" t="inlineStr">
         <is>
           <t>Eletrocalha / perfilado aéreo</t>
         </is>
       </c>
-      <c r="C85" s="9" t="inlineStr">
+      <c r="C85" s="10" t="inlineStr">
         <is>
           <t>60 cm</t>
         </is>
       </c>
-      <c r="D85" s="10" t="inlineStr">
+      <c r="D85" s="11" t="inlineStr">
         <is>
           <t>Canaleta de acrílico ou perfil U de alumínio — leva os cabos do painel à câmara por cima, como na indústria</t>
         </is>
       </c>
-      <c r="E85" s="10" t="inlineStr"/>
-      <c r="F85" s="11" t="inlineStr"/>
-      <c r="G85" s="12" t="inlineStr"/>
-      <c r="H85" s="12">
-        <f>IF(C85*G85=0,"",C85*G85)</f>
+      <c r="E85" s="11" t="inlineStr"/>
+      <c r="F85" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/eletrocalha-perfilado-aereo","🔎 eletrocalha perfilado aereo")</f>
+        <v/>
+      </c>
+      <c r="G85" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=eletrocalha+perfilado+aereo","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H85" s="13" t="inlineStr"/>
+      <c r="I85" s="14" t="inlineStr"/>
+      <c r="J85" s="14">
+        <f>IF(C85*I85=0,"",C85*I85)</f>
         <v/>
       </c>
     </row>
@@ -2747,37 +3346,53 @@
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr"/>
-      <c r="F86" s="7" t="inlineStr"/>
-      <c r="G86" s="8" t="inlineStr"/>
-      <c r="H86" s="8">
-        <f>IF(C86*G86=0,"",C86*G86)</f>
+      <c r="F86" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/suportes-maos-francesas-eletrocalha","🔎 suportes maos francesas elet")</f>
+        <v/>
+      </c>
+      <c r="G86" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=suportes+maos+francesas+eletrocalha","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H86" s="8" t="inlineStr"/>
+      <c r="I86" s="9" t="inlineStr"/>
+      <c r="J86" s="9">
+        <f>IF(C86*I86=0,"",C86*I86)</f>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="9" t="n">
+      <c r="A87" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="B87" s="10" t="inlineStr">
+      <c r="B87" s="11" t="inlineStr">
         <is>
           <t>EVA ou MDF 6 mm</t>
         </is>
       </c>
-      <c r="C87" s="9" t="inlineStr">
+      <c r="C87" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D87" s="10" t="inlineStr">
+      <c r="D87" s="11" t="inlineStr">
         <is>
           <t>Bases de máquinas fictícias e plataformas</t>
         </is>
       </c>
-      <c r="E87" s="10" t="inlineStr"/>
-      <c r="F87" s="11" t="inlineStr"/>
-      <c r="G87" s="12" t="inlineStr"/>
-      <c r="H87" s="12">
-        <f>IF(C87*G87=0,"",C87*G87)</f>
+      <c r="E87" s="11" t="inlineStr"/>
+      <c r="F87" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/eva-mdf-6-mm","🔎 eva mdf 6 mm")</f>
+        <v/>
+      </c>
+      <c r="G87" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=eva+mdf+6+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H87" s="13" t="inlineStr"/>
+      <c r="I87" s="14" t="inlineStr"/>
+      <c r="J87" s="14">
+        <f>IF(C87*I87=0,"",C87*I87)</f>
         <v/>
       </c>
     </row>
@@ -2789,29 +3404,37 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="9" t="n">
+      <c r="A89" s="10" t="n">
         <v>76</v>
       </c>
-      <c r="B89" s="10" t="inlineStr">
+      <c r="B89" s="11" t="inlineStr">
         <is>
           <t>XPS 30 mm (poliestireno extrudado)</t>
         </is>
       </c>
-      <c r="C89" s="9" t="inlineStr">
+      <c r="C89" s="10" t="inlineStr">
         <is>
           <t>1 m²</t>
         </is>
       </c>
-      <c r="D89" s="10" t="inlineStr">
+      <c r="D89" s="11" t="inlineStr">
         <is>
           <t>Isolante principal — k ≈ 0,033 W/m·K. 30 mm, não 20 mm (ver Doc 12)</t>
         </is>
       </c>
-      <c r="E89" s="10" t="inlineStr"/>
-      <c r="F89" s="11" t="inlineStr"/>
-      <c r="G89" s="12" t="inlineStr"/>
-      <c r="H89" s="12">
-        <f>IF(C89*G89=0,"",C89*G89)</f>
+      <c r="E89" s="11" t="inlineStr"/>
+      <c r="F89" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/xps-30-mm","🔎 xps 30 mm")</f>
+        <v/>
+      </c>
+      <c r="G89" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=xps+30+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H89" s="13" t="inlineStr"/>
+      <c r="I89" s="14" t="inlineStr"/>
+      <c r="J89" s="14">
+        <f>IF(C89*I89=0,"",C89*I89)</f>
         <v/>
       </c>
     </row>
@@ -2835,37 +3458,53 @@
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr"/>
-      <c r="F90" s="7" t="inlineStr"/>
-      <c r="G90" s="8" t="inlineStr"/>
-      <c r="H90" s="8">
-        <f>IF(C90*G90=0,"",C90*G90)</f>
+      <c r="F90" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-adesiva-aluminio-50-mm","🔎 fita adesiva aluminio 50 mm")</f>
+        <v/>
+      </c>
+      <c r="G90" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+adesiva+aluminio+50+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H90" s="8" t="inlineStr"/>
+      <c r="I90" s="9" t="inlineStr"/>
+      <c r="J90" s="9">
+        <f>IF(C90*I90=0,"",C90*I90)</f>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="9" t="n">
+      <c r="A91" s="10" t="n">
         <v>78</v>
       </c>
-      <c r="B91" s="10" t="inlineStr">
+      <c r="B91" s="11" t="inlineStr">
         <is>
           <t>Manta elastomérica autoadesiva 6 mm</t>
         </is>
       </c>
-      <c r="C91" s="9" t="inlineStr">
+      <c r="C91" s="10" t="inlineStr">
         <is>
           <t>1 m²</t>
         </is>
       </c>
-      <c r="D91" s="10" t="inlineStr">
+      <c r="D91" s="11" t="inlineStr">
         <is>
           <t>Tipo Armaflex — cantos, arestas e ao redor das passagens de cabo</t>
         </is>
       </c>
-      <c r="E91" s="10" t="inlineStr"/>
-      <c r="F91" s="11" t="inlineStr"/>
-      <c r="G91" s="12" t="inlineStr"/>
-      <c r="H91" s="12">
-        <f>IF(C91*G91=0,"",C91*G91)</f>
+      <c r="E91" s="11" t="inlineStr"/>
+      <c r="F91" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/manta-elastomerica-autoadesiva-6-mm","🔎 manta elastomerica autoadesi")</f>
+        <v/>
+      </c>
+      <c r="G91" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=manta+elastomerica+autoadesiva+6+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H91" s="13" t="inlineStr"/>
+      <c r="I91" s="14" t="inlineStr"/>
+      <c r="J91" s="14">
+        <f>IF(C91*I91=0,"",C91*I91)</f>
         <v/>
       </c>
     </row>
@@ -2889,10 +3528,18 @@
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr"/>
-      <c r="F92" s="7" t="inlineStr"/>
-      <c r="G92" s="8" t="inlineStr"/>
-      <c r="H92" s="8">
-        <f>IF(C92*G92=0,"",C92*G92)</f>
+      <c r="F92" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/espuma-expansiva-pu","🔎 espuma expansiva pu")</f>
+        <v/>
+      </c>
+      <c r="G92" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=espuma+expansiva+pu","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H92" s="8" t="inlineStr"/>
+      <c r="I92" s="9" t="inlineStr"/>
+      <c r="J92" s="9">
+        <f>IF(C92*I92=0,"",C92*I92)</f>
         <v/>
       </c>
     </row>
@@ -2923,37 +3570,53 @@
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr"/>
-      <c r="F94" s="7" t="inlineStr"/>
-      <c r="G94" s="8" t="inlineStr"/>
-      <c r="H94" s="8">
-        <f>IF(C94*G94=0,"",C94*G94)</f>
+      <c r="F94" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/perfil-epdm-tubular-autoadesivo-9-6-mm","🔎 perfil epdm tubular autoades")</f>
+        <v/>
+      </c>
+      <c r="G94" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=perfil+epdm+tubular+autoadesivo+9+6+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H94" s="8" t="inlineStr"/>
+      <c r="I94" s="9" t="inlineStr"/>
+      <c r="J94" s="9">
+        <f>IF(C94*I94=0,"",C94*I94)</f>
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="9" t="n">
+      <c r="A95" s="10" t="n">
         <v>81</v>
       </c>
-      <c r="B95" s="10" t="inlineStr">
+      <c r="B95" s="11" t="inlineStr">
         <is>
           <t>Dobradiça piano de alumínio</t>
         </is>
       </c>
-      <c r="C95" s="9" t="inlineStr">
+      <c r="C95" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D95" s="10" t="inlineStr">
+      <c r="D95" s="11" t="inlineStr">
         <is>
           <t>250 mm (cortar de uma barra de 75 cm)</t>
         </is>
       </c>
-      <c r="E95" s="10" t="inlineStr"/>
-      <c r="F95" s="11" t="inlineStr"/>
-      <c r="G95" s="12" t="inlineStr"/>
-      <c r="H95" s="12">
-        <f>IF(C95*G95=0,"",C95*G95)</f>
+      <c r="E95" s="11" t="inlineStr"/>
+      <c r="F95" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/dobradica-piano-aluminio","🔎 dobradica piano aluminio")</f>
+        <v/>
+      </c>
+      <c r="G95" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=dobradica+piano+aluminio","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H95" s="13" t="inlineStr"/>
+      <c r="I95" s="14" t="inlineStr"/>
+      <c r="J95" s="14">
+        <f>IF(C95*I95=0,"",C95*I95)</f>
         <v/>
       </c>
     </row>
@@ -2977,37 +3640,53 @@
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr"/>
-      <c r="F96" s="7" t="inlineStr"/>
-      <c r="G96" s="8" t="inlineStr"/>
-      <c r="H96" s="8">
-        <f>IF(C96*G96=0,"",C96*G96)</f>
+      <c r="F96" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fecho-pressao-inox","🔎 fecho pressao inox")</f>
+        <v/>
+      </c>
+      <c r="G96" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fecho+pressao+inox","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H96" s="8" t="inlineStr"/>
+      <c r="I96" s="9" t="inlineStr"/>
+      <c r="J96" s="9">
+        <f>IF(C96*I96=0,"",C96*I96)</f>
         <v/>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="9" t="n">
+      <c r="A97" s="10" t="n">
         <v>83</v>
       </c>
-      <c r="B97" s="10" t="inlineStr">
+      <c r="B97" s="11" t="inlineStr">
         <is>
           <t>Puxador de câmara fria (miniatura)</t>
         </is>
       </c>
-      <c r="C97" s="9" t="inlineStr">
+      <c r="C97" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D97" s="10" t="inlineStr">
+      <c r="D97" s="11" t="inlineStr">
         <is>
           <t>Estética — pode ser um puxador de móvel pequeno</t>
         </is>
       </c>
-      <c r="E97" s="10" t="inlineStr"/>
-      <c r="F97" s="11" t="inlineStr"/>
-      <c r="G97" s="12" t="inlineStr"/>
-      <c r="H97" s="12">
-        <f>IF(C97*G97=0,"",C97*G97)</f>
+      <c r="E97" s="11" t="inlineStr"/>
+      <c r="F97" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/puxador-camara-fria","🔎 puxador camara fria")</f>
+        <v/>
+      </c>
+      <c r="G97" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=puxador+camara+fria","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H97" s="13" t="inlineStr"/>
+      <c r="I97" s="14" t="inlineStr"/>
+      <c r="J97" s="14">
+        <f>IF(C97*I97=0,"",C97*I97)</f>
         <v/>
       </c>
     </row>
@@ -3031,37 +3710,53 @@
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr"/>
-      <c r="F98" s="7" t="inlineStr"/>
-      <c r="G98" s="8" t="inlineStr"/>
-      <c r="H98" s="8">
-        <f>IF(C98*G98=0,"",C98*G98)</f>
+      <c r="F98" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cola-s-320-sinteglas","🔎 cola s 320 sinteglas")</f>
+        <v/>
+      </c>
+      <c r="G98" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cola+s+320+sinteglas","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H98" s="8" t="inlineStr"/>
+      <c r="I98" s="9" t="inlineStr"/>
+      <c r="J98" s="9">
+        <f>IF(C98*I98=0,"",C98*I98)</f>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="9" t="n">
+      <c r="A99" s="10" t="n">
         <v>85</v>
       </c>
-      <c r="B99" s="10" t="inlineStr">
+      <c r="B99" s="11" t="inlineStr">
         <is>
           <t>Silicone neutro transparente</t>
         </is>
       </c>
-      <c r="C99" s="9" t="inlineStr">
+      <c r="C99" s="10" t="inlineStr">
         <is>
           <t>1 tubo</t>
         </is>
       </c>
-      <c r="D99" s="10" t="inlineStr">
+      <c r="D99" s="11" t="inlineStr">
         <is>
           <t>Vedação de juntas (⚠️ neutro, o acético ataca o acrílico)</t>
         </is>
       </c>
-      <c r="E99" s="10" t="inlineStr"/>
-      <c r="F99" s="11" t="inlineStr"/>
-      <c r="G99" s="12" t="inlineStr"/>
-      <c r="H99" s="12">
-        <f>IF(C99*G99=0,"",C99*G99)</f>
+      <c r="E99" s="11" t="inlineStr"/>
+      <c r="F99" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/silicone-neutro-transparente","🔎 silicone neutro transparente")</f>
+        <v/>
+      </c>
+      <c r="G99" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=silicone+neutro+transparente","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H99" s="13" t="inlineStr"/>
+      <c r="I99" s="14" t="inlineStr"/>
+      <c r="J99" s="14">
+        <f>IF(C99*I99=0,"",C99*I99)</f>
         <v/>
       </c>
     </row>
@@ -3085,37 +3780,53 @@
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr"/>
-      <c r="F100" s="7" t="inlineStr"/>
-      <c r="G100" s="8" t="inlineStr"/>
-      <c r="H100" s="8">
-        <f>IF(C100*G100=0,"",C100*G100)</f>
+      <c r="F100" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/bandeja-aluminio","🔎 bandeja aluminio")</f>
+        <v/>
+      </c>
+      <c r="G100" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=bandeja+aluminio","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H100" s="8" t="inlineStr"/>
+      <c r="I100" s="9" t="inlineStr"/>
+      <c r="J100" s="9">
+        <f>IF(C100*I100=0,"",C100*I100)</f>
         <v/>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="9" t="n">
+      <c r="A101" s="10" t="n">
         <v>87</v>
       </c>
-      <c r="B101" s="10" t="inlineStr">
+      <c r="B101" s="11" t="inlineStr">
         <is>
           <t>Tubo de silicone Ø 6 mm</t>
         </is>
       </c>
-      <c r="C101" s="9" t="inlineStr">
+      <c r="C101" s="10" t="inlineStr">
         <is>
           <t>40 cm</t>
         </is>
       </c>
-      <c r="D101" s="10" t="inlineStr">
+      <c r="D101" s="11" t="inlineStr">
         <is>
           <t>Dreno até o recipiente externo</t>
         </is>
       </c>
-      <c r="E101" s="10" t="inlineStr"/>
-      <c r="F101" s="11" t="inlineStr"/>
-      <c r="G101" s="12" t="inlineStr"/>
-      <c r="H101" s="12">
-        <f>IF(C101*G101=0,"",C101*G101)</f>
+      <c r="E101" s="11" t="inlineStr"/>
+      <c r="F101" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tubo-silicone-6-mm","🔎 tubo silicone 6 mm")</f>
+        <v/>
+      </c>
+      <c r="G101" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tubo+silicone+6+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H101" s="13" t="inlineStr"/>
+      <c r="I101" s="14" t="inlineStr"/>
+      <c r="J101" s="14">
+        <f>IF(C101*I101=0,"",C101*I101)</f>
         <v/>
       </c>
     </row>
@@ -3139,37 +3850,53 @@
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr"/>
-      <c r="F102" s="7" t="inlineStr"/>
-      <c r="G102" s="8" t="inlineStr"/>
-      <c r="H102" s="8">
-        <f>IF(C102*G102=0,"",C102*G102)</f>
+      <c r="F102" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/silica-gel-indicadora","🔎 silica gel indicadora")</f>
+        <v/>
+      </c>
+      <c r="G102" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=silica+gel+indicadora","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H102" s="8" t="inlineStr"/>
+      <c r="I102" s="9" t="inlineStr"/>
+      <c r="J102" s="9">
+        <f>IF(C102*I102=0,"",C102*I102)</f>
         <v/>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="9" t="n">
+      <c r="A103" s="10" t="n">
         <v>89</v>
       </c>
-      <c r="B103" s="10" t="inlineStr">
+      <c r="B103" s="11" t="inlineStr">
         <is>
           <t>Recipiente coletor de condensado</t>
         </is>
       </c>
-      <c r="C103" s="9" t="inlineStr">
+      <c r="C103" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D103" s="10" t="inlineStr">
+      <c r="D103" s="11" t="inlineStr">
         <is>
           <t>Frasco pequeno, embutido na maquete</t>
         </is>
       </c>
-      <c r="E103" s="10" t="inlineStr"/>
-      <c r="F103" s="11" t="inlineStr"/>
-      <c r="G103" s="12" t="inlineStr"/>
-      <c r="H103" s="12">
-        <f>IF(C103*G103=0,"",C103*G103)</f>
+      <c r="E103" s="11" t="inlineStr"/>
+      <c r="F103" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/recipiente-coletor-condensado","🔎 recipiente coletor condensad")</f>
+        <v/>
+      </c>
+      <c r="G103" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=recipiente+coletor+condensado","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H103" s="13" t="inlineStr"/>
+      <c r="I103" s="14" t="inlineStr"/>
+      <c r="J103" s="14">
+        <f>IF(C103*I103=0,"",C103*I103)</f>
         <v/>
       </c>
     </row>
@@ -3181,29 +3908,37 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="9" t="n">
+      <c r="A105" s="10" t="n">
         <v>90</v>
       </c>
-      <c r="B105" s="10" t="inlineStr">
+      <c r="B105" s="11" t="inlineStr">
         <is>
           <t>Caixa de comando ou MDF</t>
         </is>
       </c>
-      <c r="C105" s="9" t="inlineStr">
+      <c r="C105" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D105" s="10" t="inlineStr">
+      <c r="D105" s="11" t="inlineStr">
         <is>
           <t>400 × 500 × 200 mm — comprada pronta ou feita em MDF 15 mm</t>
         </is>
       </c>
-      <c r="E105" s="10" t="inlineStr"/>
-      <c r="F105" s="11" t="inlineStr"/>
-      <c r="G105" s="12" t="inlineStr"/>
-      <c r="H105" s="12">
-        <f>IF(C105*G105=0,"",C105*G105)</f>
+      <c r="E105" s="11" t="inlineStr"/>
+      <c r="F105" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/caixa-comando-mdf","🔎 caixa comando mdf")</f>
+        <v/>
+      </c>
+      <c r="G105" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=caixa+comando+mdf","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H105" s="13" t="inlineStr"/>
+      <c r="I105" s="14" t="inlineStr"/>
+      <c r="J105" s="14">
+        <f>IF(C105*I105=0,"",C105*I105)</f>
         <v/>
       </c>
     </row>
@@ -3227,37 +3962,53 @@
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr"/>
-      <c r="F106" s="7" t="inlineStr"/>
-      <c r="G106" s="8" t="inlineStr"/>
-      <c r="H106" s="8">
-        <f>IF(C106*G106=0,"",C106*G106)</f>
+      <c r="F106" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/porta-painel","🔎 porta painel")</f>
+        <v/>
+      </c>
+      <c r="G106" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=porta+painel","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H106" s="8" t="inlineStr"/>
+      <c r="I106" s="9" t="inlineStr"/>
+      <c r="J106" s="9">
+        <f>IF(C106*I106=0,"",C106*I106)</f>
         <v/>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="9" t="n">
+      <c r="A107" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="B107" s="10" t="inlineStr">
+      <c r="B107" s="11" t="inlineStr">
         <is>
           <t>Trilho DIN 35 mm</t>
         </is>
       </c>
-      <c r="C107" s="9" t="inlineStr">
+      <c r="C107" s="10" t="inlineStr">
         <is>
           <t>1,5 m</t>
         </is>
       </c>
-      <c r="D107" s="10" t="inlineStr">
+      <c r="D107" s="11" t="inlineStr">
         <is>
           <t>Aço galvanizado — 3 trilhos de ~360 mm</t>
         </is>
       </c>
-      <c r="E107" s="10" t="inlineStr"/>
-      <c r="F107" s="11" t="inlineStr"/>
-      <c r="G107" s="12" t="inlineStr"/>
-      <c r="H107" s="12">
-        <f>IF(C107*G107=0,"",C107*G107)</f>
+      <c r="E107" s="11" t="inlineStr"/>
+      <c r="F107" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/trilho-din-35-mm","🔎 trilho din 35 mm")</f>
+        <v/>
+      </c>
+      <c r="G107" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=trilho+din+35+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H107" s="13" t="inlineStr"/>
+      <c r="I107" s="14" t="inlineStr"/>
+      <c r="J107" s="14">
+        <f>IF(C107*I107=0,"",C107*I107)</f>
         <v/>
       </c>
     </row>
@@ -3281,37 +4032,53 @@
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr"/>
-      <c r="F108" s="7" t="inlineStr"/>
-      <c r="G108" s="8" t="inlineStr"/>
-      <c r="H108" s="8">
-        <f>IF(C108*G108=0,"",C108*G108)</f>
+      <c r="F108" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/canaleta-perfurada-30-30-mm","🔎 canaleta perfurada 30 30 mm")</f>
+        <v/>
+      </c>
+      <c r="G108" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=canaleta+perfurada+30+30+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H108" s="8" t="inlineStr"/>
+      <c r="I108" s="9" t="inlineStr"/>
+      <c r="J108" s="9">
+        <f>IF(C108*I108=0,"",C108*I108)</f>
         <v/>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="9" t="n">
+      <c r="A109" s="10" t="n">
         <v>94</v>
       </c>
-      <c r="B109" s="10" t="inlineStr">
+      <c r="B109" s="11" t="inlineStr">
         <is>
           <t>Bloco de distribuição DIN — 1 entrada 4 mm² + 4 saídas</t>
         </is>
       </c>
-      <c r="C109" s="9" t="inlineStr">
+      <c r="C109" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D109" s="10" t="inlineStr">
+      <c r="D109" s="11" t="inlineStr">
         <is>
           <t>BD-POT — 24 V de potência comutados pelo KA2 → BTS #1, BTS #2 e reservas. ⚠️ Cai com a emergência</t>
         </is>
       </c>
-      <c r="E109" s="10" t="inlineStr"/>
-      <c r="F109" s="11" t="inlineStr"/>
-      <c r="G109" s="12" t="inlineStr"/>
-      <c r="H109" s="12">
-        <f>IF(C109*G109=0,"",C109*G109)</f>
+      <c r="E109" s="11" t="inlineStr"/>
+      <c r="F109" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/bloco-distribuicao-din","🔎 bloco distribuicao din")</f>
+        <v/>
+      </c>
+      <c r="G109" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=bloco+distribuicao+din","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H109" s="13" t="inlineStr"/>
+      <c r="I109" s="14" t="inlineStr"/>
+      <c r="J109" s="14">
+        <f>IF(C109*I109=0,"",C109*I109)</f>
         <v/>
       </c>
     </row>
@@ -3335,37 +4102,53 @@
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr"/>
-      <c r="F110" s="7" t="inlineStr"/>
-      <c r="G110" s="8" t="inlineStr"/>
-      <c r="H110" s="8">
-        <f>IF(C110*G110=0,"",C110*G110)</f>
+      <c r="F110" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/bloco-distribuicao-din","🔎 bloco distribuicao din")</f>
+        <v/>
+      </c>
+      <c r="G110" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=bloco+distribuicao+din","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H110" s="8" t="inlineStr"/>
+      <c r="I110" s="9" t="inlineStr"/>
+      <c r="J110" s="9">
+        <f>IF(C110*I110=0,"",C110*I110)</f>
         <v/>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="9" t="n">
+      <c r="A111" s="10" t="n">
         <v>96</v>
       </c>
-      <c r="B111" s="10" t="inlineStr">
+      <c r="B111" s="11" t="inlineStr">
         <is>
           <t>Bloco de distribuição DIN — 1 entrada 2,5 mm² + 6 saídas</t>
         </is>
       </c>
-      <c r="C111" s="9" t="inlineStr">
+      <c r="C111" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D111" s="10" t="inlineStr">
+      <c r="D111" s="11" t="inlineStr">
         <is>
           <t>BD-5V — Arduino, Nextion, SD/RTC, lógica dos 2 BTS, LEDs</t>
         </is>
       </c>
-      <c r="E111" s="10" t="inlineStr"/>
-      <c r="F111" s="11" t="inlineStr"/>
-      <c r="G111" s="12" t="inlineStr"/>
-      <c r="H111" s="12">
-        <f>IF(C111*G111=0,"",C111*G111)</f>
+      <c r="E111" s="11" t="inlineStr"/>
+      <c r="F111" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/bloco-distribuicao-din","🔎 bloco distribuicao din")</f>
+        <v/>
+      </c>
+      <c r="G111" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=bloco+distribuicao+din","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H111" s="13" t="inlineStr"/>
+      <c r="I111" s="14" t="inlineStr"/>
+      <c r="J111" s="14">
+        <f>IF(C111*I111=0,"",C111*I111)</f>
         <v/>
       </c>
     </row>
@@ -3389,37 +4172,53 @@
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr"/>
-      <c r="F112" s="7" t="inlineStr"/>
-      <c r="G112" s="8" t="inlineStr"/>
-      <c r="H112" s="8">
-        <f>IF(C112*G112=0,"",C112*G112)</f>
+      <c r="F112" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/bloco-distribuicao-din","🔎 bloco distribuicao din")</f>
+        <v/>
+      </c>
+      <c r="G112" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=bloco+distribuicao+din","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H112" s="8" t="inlineStr"/>
+      <c r="I112" s="9" t="inlineStr"/>
+      <c r="J112" s="9">
+        <f>IF(C112*I112=0,"",C112*I112)</f>
         <v/>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="9" t="n">
+      <c r="A113" s="10" t="n">
         <v>98</v>
       </c>
-      <c r="B113" s="10" t="inlineStr">
+      <c r="B113" s="11" t="inlineStr">
         <is>
           <t>Bornes DIN parafuso 2,5 mm²</t>
         </is>
       </c>
-      <c r="C113" s="9" t="inlineStr">
+      <c r="C113" s="10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D113" s="10" t="inlineStr">
+      <c r="D113" s="11" t="inlineStr">
         <is>
           <t>Passagem e reservas</t>
         </is>
       </c>
-      <c r="E113" s="10" t="inlineStr"/>
-      <c r="F113" s="11" t="inlineStr"/>
-      <c r="G113" s="12" t="inlineStr"/>
-      <c r="H113" s="12">
-        <f>IF(C113*G113=0,"",C113*G113)</f>
+      <c r="E113" s="11" t="inlineStr"/>
+      <c r="F113" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/bornes-din-parafuso-2-5-mm","🔎 bornes din parafuso 2,5 mm")</f>
+        <v/>
+      </c>
+      <c r="G113" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=bornes+din+parafuso+2%2C5+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H113" s="13" t="inlineStr"/>
+      <c r="I113" s="14" t="inlineStr"/>
+      <c r="J113" s="14">
+        <f>IF(C113*I113=0,"",C113*I113)</f>
         <v/>
       </c>
     </row>
@@ -3443,37 +4242,53 @@
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr"/>
-      <c r="F114" s="7" t="inlineStr"/>
-      <c r="G114" s="8" t="inlineStr"/>
-      <c r="H114" s="8">
-        <f>IF(C114*G114=0,"",C114*G114)</f>
+      <c r="F114" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/separadores-tampas-borne","🔎 separadores tampas borne")</f>
+        <v/>
+      </c>
+      <c r="G114" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=separadores+tampas+borne","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H114" s="8" t="inlineStr"/>
+      <c r="I114" s="9" t="inlineStr"/>
+      <c r="J114" s="9">
+        <f>IF(C114*I114=0,"",C114*I114)</f>
         <v/>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="9" t="n">
+      <c r="A115" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="B115" s="10" t="inlineStr">
+      <c r="B115" s="11" t="inlineStr">
         <is>
           <t>Alternativa mais barata: bornes comuns + ponte de interligação (pente)</t>
         </is>
       </c>
-      <c r="C115" s="9" t="inlineStr">
+      <c r="C115" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D115" s="10" t="inlineStr">
+      <c r="D115" s="11" t="inlineStr">
         <is>
           <t>Funciona igual aos blocos, custa menos, menos prático para alterar depois</t>
         </is>
       </c>
-      <c r="E115" s="10" t="inlineStr"/>
-      <c r="F115" s="11" t="inlineStr"/>
-      <c r="G115" s="12" t="inlineStr"/>
-      <c r="H115" s="12">
-        <f>IF(C115*G115=0,"",C115*G115)</f>
+      <c r="E115" s="11" t="inlineStr"/>
+      <c r="F115" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/alternativa-mais-barata-bornes-comuns-ponte-interligacao","🔎 alternativa mais barata born")</f>
+        <v/>
+      </c>
+      <c r="G115" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=alternativa+mais+barata+bornes+comuns+ponte+interligacao","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H115" s="13" t="inlineStr"/>
+      <c r="I115" s="14" t="inlineStr"/>
+      <c r="J115" s="14">
+        <f>IF(C115*I115=0,"",C115*I115)</f>
         <v/>
       </c>
     </row>
@@ -3497,37 +4312,53 @@
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr"/>
-      <c r="F116" s="7" t="inlineStr"/>
-      <c r="G116" s="8" t="inlineStr"/>
-      <c r="H116" s="8">
-        <f>IF(C116*G116=0,"",C116*G116)</f>
+      <c r="F116" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/identificadores-borne-cabo","🔎 identificadores borne cabo")</f>
+        <v/>
+      </c>
+      <c r="G116" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=identificadores+borne+cabo","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H116" s="8" t="inlineStr"/>
+      <c r="I116" s="9" t="inlineStr"/>
+      <c r="J116" s="9">
+        <f>IF(C116*I116=0,"",C116*I116)</f>
         <v/>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="9" t="n">
+      <c r="A117" s="10" t="n">
         <v>102</v>
       </c>
-      <c r="B117" s="10" t="inlineStr">
+      <c r="B117" s="11" t="inlineStr">
         <is>
           <t>Trava-fim de trilho DIN</t>
         </is>
       </c>
-      <c r="C117" s="9" t="inlineStr">
+      <c r="C117" s="10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D117" s="10" t="inlineStr">
+      <c r="D117" s="11" t="inlineStr">
         <is>
           <t>Impede os componentes de deslizarem</t>
         </is>
       </c>
-      <c r="E117" s="10" t="inlineStr"/>
-      <c r="F117" s="11" t="inlineStr"/>
-      <c r="G117" s="12" t="inlineStr"/>
-      <c r="H117" s="12">
-        <f>IF(C117*G117=0,"",C117*G117)</f>
+      <c r="E117" s="11" t="inlineStr"/>
+      <c r="F117" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/trava-fim-trilho-din","🔎 trava fim trilho din")</f>
+        <v/>
+      </c>
+      <c r="G117" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=trava+fim+trilho+din","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H117" s="13" t="inlineStr"/>
+      <c r="I117" s="14" t="inlineStr"/>
+      <c r="J117" s="14">
+        <f>IF(C117*I117=0,"",C117*I117)</f>
         <v/>
       </c>
     </row>
@@ -3551,37 +4382,53 @@
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr"/>
-      <c r="F118" s="7" t="inlineStr"/>
-      <c r="G118" s="8" t="inlineStr"/>
-      <c r="H118" s="8">
-        <f>IF(C118*G118=0,"",C118*G118)</f>
+      <c r="F118" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/botao-emergencia-cogumelo-22-mm","🔎 botao emergencia cogumelo 22")</f>
+        <v/>
+      </c>
+      <c r="G118" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=botao+emergencia+cogumelo+22+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H118" s="8" t="inlineStr"/>
+      <c r="I118" s="9" t="inlineStr"/>
+      <c r="J118" s="9">
+        <f>IF(C118*I118=0,"",C118*I118)</f>
         <v/>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="9" t="n">
+      <c r="A119" s="10" t="n">
         <v>104</v>
       </c>
-      <c r="B119" s="10" t="inlineStr">
+      <c r="B119" s="11" t="inlineStr">
         <is>
           <t>Botão START 22 mm</t>
         </is>
       </c>
-      <c r="C119" s="9" t="inlineStr">
+      <c r="C119" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D119" s="10" t="inlineStr">
+      <c r="D119" s="11" t="inlineStr">
         <is>
           <t>Verde, momentâneo — 1 bloco NA (só informa o Arduino)</t>
         </is>
       </c>
-      <c r="E119" s="10" t="inlineStr"/>
-      <c r="F119" s="11" t="inlineStr"/>
-      <c r="G119" s="12" t="inlineStr"/>
-      <c r="H119" s="12">
-        <f>IF(C119*G119=0,"",C119*G119)</f>
+      <c r="E119" s="11" t="inlineStr"/>
+      <c r="F119" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/botao-start-22-mm","🔎 botao start 22 mm")</f>
+        <v/>
+      </c>
+      <c r="G119" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=botao+start+22+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H119" s="13" t="inlineStr"/>
+      <c r="I119" s="14" t="inlineStr"/>
+      <c r="J119" s="14">
+        <f>IF(C119*I119=0,"",C119*I119)</f>
         <v/>
       </c>
     </row>
@@ -3605,37 +4452,53 @@
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr"/>
-      <c r="F120" s="7" t="inlineStr"/>
-      <c r="G120" s="8" t="inlineStr"/>
-      <c r="H120" s="8">
-        <f>IF(C120*G120=0,"",C120*G120)</f>
+      <c r="F120" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/botao-stop-22-mm","🔎 botao stop 22 mm")</f>
+        <v/>
+      </c>
+      <c r="G120" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=botao+stop+22+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H120" s="8" t="inlineStr"/>
+      <c r="I120" s="9" t="inlineStr"/>
+      <c r="J120" s="9">
+        <f>IF(C120*I120=0,"",C120*I120)</f>
         <v/>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="9" t="n">
+      <c r="A121" s="10" t="n">
         <v>106</v>
       </c>
-      <c r="B121" s="10" t="inlineStr">
+      <c r="B121" s="11" t="inlineStr">
         <is>
           <t>Botão REARME 22 mm</t>
         </is>
       </c>
-      <c r="C121" s="9" t="inlineStr">
+      <c r="C121" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D121" s="10" t="inlineStr">
+      <c r="D121" s="11" t="inlineStr">
         <is>
           <t>AZUL, momentâneo — 1 bloco NA. Refaz o selo do KA1 após a emergência. Buscar botão pulsador azul 22mm</t>
         </is>
       </c>
-      <c r="E121" s="10" t="inlineStr"/>
-      <c r="F121" s="11" t="inlineStr"/>
-      <c r="G121" s="12" t="inlineStr"/>
-      <c r="H121" s="12">
-        <f>IF(C121*G121=0,"",C121*G121)</f>
+      <c r="E121" s="11" t="inlineStr"/>
+      <c r="F121" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/botao-rearme-22-mm","🔎 botao rearme 22 mm")</f>
+        <v/>
+      </c>
+      <c r="G121" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=botao+rearme+22+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H121" s="13" t="inlineStr"/>
+      <c r="I121" s="14" t="inlineStr"/>
+      <c r="J121" s="14">
+        <f>IF(C121*I121=0,"",C121*I121)</f>
         <v/>
       </c>
     </row>
@@ -3659,37 +4522,53 @@
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr"/>
-      <c r="F122" s="7" t="inlineStr"/>
-      <c r="G122" s="8" t="inlineStr"/>
-      <c r="H122" s="8">
-        <f>IF(C122*G122=0,"",C122*G122)</f>
+      <c r="F122" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/blocos-contato-22-mm-avulsos","🔎 blocos contato 22 mm avulsos")</f>
+        <v/>
+      </c>
+      <c r="G122" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=blocos+contato+22+mm+avulsos","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H122" s="8" t="inlineStr"/>
+      <c r="I122" s="9" t="inlineStr"/>
+      <c r="J122" s="9">
+        <f>IF(C122*I122=0,"",C122*I122)</f>
         <v/>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="9" t="n">
+      <c r="A123" s="10" t="n">
         <v>108</v>
       </c>
-      <c r="B123" s="10" t="inlineStr">
+      <c r="B123" s="11" t="inlineStr">
         <is>
           <t>Chave seccionadora 24 V no painel</t>
         </is>
       </c>
-      <c r="C123" s="9" t="inlineStr">
+      <c r="C123" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D123" s="10" t="inlineStr">
+      <c r="D123" s="11" t="inlineStr">
         <is>
           <t>Rotativa 2 posições 22 mm — chave geral local da máquina</t>
         </is>
       </c>
-      <c r="E123" s="10" t="inlineStr"/>
-      <c r="F123" s="11" t="inlineStr"/>
-      <c r="G123" s="12" t="inlineStr"/>
-      <c r="H123" s="12">
-        <f>IF(C123*G123=0,"",C123*G123)</f>
+      <c r="E123" s="11" t="inlineStr"/>
+      <c r="F123" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/chave-seccionadora-24-v-painel","🔎 chave seccionadora 24 v pain")</f>
+        <v/>
+      </c>
+      <c r="G123" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=chave+seccionadora+24+v+painel","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H123" s="13" t="inlineStr"/>
+      <c r="I123" s="14" t="inlineStr"/>
+      <c r="J123" s="14">
+        <f>IF(C123*I123=0,"",C123*I123)</f>
         <v/>
       </c>
     </row>
@@ -3713,37 +4592,53 @@
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr"/>
-      <c r="F124" s="7" t="inlineStr"/>
-      <c r="G124" s="8" t="inlineStr"/>
-      <c r="H124" s="8">
-        <f>IF(C124*G124=0,"",C124*G124)</f>
+      <c r="F124" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/sinaleiros-led-22-mm-24-v","🔎 sinaleiros led 22 mm 24 v")</f>
+        <v/>
+      </c>
+      <c r="G124" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=sinaleiros+led+22+mm+24+v","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H124" s="8" t="inlineStr"/>
+      <c r="I124" s="9" t="inlineStr"/>
+      <c r="J124" s="9">
+        <f>IF(C124*I124=0,"",C124*I124)</f>
         <v/>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="9" t="n">
+      <c r="A125" s="10" t="n">
         <v>110</v>
       </c>
-      <c r="B125" s="10" t="inlineStr">
+      <c r="B125" s="11" t="inlineStr">
         <is>
           <t>Prensa-cabo PG9</t>
         </is>
       </c>
-      <c r="C125" s="9" t="inlineStr">
+      <c r="C125" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D125" s="10" t="inlineStr">
+      <c r="D125" s="11" t="inlineStr">
         <is>
           <t>Entrada 24 V de potência (vindo do P1) · saída de potência para a câmara · saída de sinais</t>
         </is>
       </c>
-      <c r="E125" s="10" t="inlineStr"/>
-      <c r="F125" s="11" t="inlineStr"/>
-      <c r="G125" s="12" t="inlineStr"/>
-      <c r="H125" s="12">
-        <f>IF(C125*G125=0,"",C125*G125)</f>
+      <c r="E125" s="11" t="inlineStr"/>
+      <c r="F125" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/prensa-cabo-pg9","🔎 prensa cabo pg9")</f>
+        <v/>
+      </c>
+      <c r="G125" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=prensa+cabo+pg9","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H125" s="13" t="inlineStr"/>
+      <c r="I125" s="14" t="inlineStr"/>
+      <c r="J125" s="14">
+        <f>IF(C125*I125=0,"",C125*I125)</f>
         <v/>
       </c>
     </row>
@@ -3767,37 +4662,53 @@
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr"/>
-      <c r="F126" s="7" t="inlineStr"/>
-      <c r="G126" s="8" t="inlineStr"/>
-      <c r="H126" s="8">
-        <f>IF(C126*G126=0,"",C126*G126)</f>
+      <c r="F126" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/prensa-cabo-pg7","🔎 prensa cabo pg7")</f>
+        <v/>
+      </c>
+      <c r="G126" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=prensa+cabo+pg7","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H126" s="8" t="inlineStr"/>
+      <c r="I126" s="9" t="inlineStr"/>
+      <c r="J126" s="9">
+        <f>IF(C126*I126=0,"",C126*I126)</f>
         <v/>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="9" t="n">
+      <c r="A127" s="10" t="n">
         <v>112</v>
       </c>
-      <c r="B127" s="10" t="inlineStr">
+      <c r="B127" s="11" t="inlineStr">
         <is>
           <t>Bolsa porta-documentos p/ porta</t>
         </is>
       </c>
-      <c r="C127" s="9" t="inlineStr">
+      <c r="C127" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D127" s="10" t="inlineStr">
+      <c r="D127" s="11" t="inlineStr">
         <is>
           <t>Guarda o diagrama elétrico — padrão em painel industrial</t>
         </is>
       </c>
-      <c r="E127" s="10" t="inlineStr"/>
-      <c r="F127" s="11" t="inlineStr"/>
-      <c r="G127" s="12" t="inlineStr"/>
-      <c r="H127" s="12">
-        <f>IF(C127*G127=0,"",C127*G127)</f>
+      <c r="E127" s="11" t="inlineStr"/>
+      <c r="F127" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/bolsa-porta-documentos-p-porta","🔎 bolsa porta documentos p por")</f>
+        <v/>
+      </c>
+      <c r="G127" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=bolsa+porta+documentos+p+porta","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H127" s="13" t="inlineStr"/>
+      <c r="I127" s="14" t="inlineStr"/>
+      <c r="J127" s="14">
+        <f>IF(C127*I127=0,"",C127*I127)</f>
         <v/>
       </c>
     </row>
@@ -3809,29 +4720,37 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="9" t="n">
+      <c r="A129" s="10" t="n">
         <v>113</v>
       </c>
-      <c r="B129" s="10" t="inlineStr">
+      <c r="B129" s="11" t="inlineStr">
         <is>
           <t>Arduino Mega 2560 R3</t>
         </is>
       </c>
-      <c r="C129" s="9" t="inlineStr">
+      <c r="C129" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D129" s="10" t="inlineStr">
+      <c r="D129" s="11" t="inlineStr">
         <is>
           <t>ATmega2560, 54 GPIO, 4 UARTs</t>
         </is>
       </c>
-      <c r="E129" s="10" t="inlineStr"/>
-      <c r="F129" s="11" t="inlineStr"/>
-      <c r="G129" s="12" t="inlineStr"/>
-      <c r="H129" s="12">
-        <f>IF(C129*G129=0,"",C129*G129)</f>
+      <c r="E129" s="11" t="inlineStr"/>
+      <c r="F129" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/arduino-mega-2560-r3","🔎 arduino mega 2560 r3")</f>
+        <v/>
+      </c>
+      <c r="G129" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=arduino+mega+2560+r3","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H129" s="13" t="inlineStr"/>
+      <c r="I129" s="14" t="inlineStr"/>
+      <c r="J129" s="14">
+        <f>IF(C129*I129=0,"",C129*I129)</f>
         <v/>
       </c>
     </row>
@@ -3855,37 +4774,53 @@
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr"/>
-      <c r="F130" s="7" t="inlineStr"/>
-      <c r="G130" s="8" t="inlineStr"/>
-      <c r="H130" s="8">
-        <f>IF(C130*G130=0,"",C130*G130)</f>
+      <c r="F130" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/shield-expansao-mega","🔎 shield expansao mega")</f>
+        <v/>
+      </c>
+      <c r="G130" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=shield+expansao+mega","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H130" s="8" t="inlineStr"/>
+      <c r="I130" s="9" t="inlineStr"/>
+      <c r="J130" s="9">
+        <f>IF(C130*I130=0,"",C130*I130)</f>
         <v/>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="9" t="n">
+      <c r="A131" s="10" t="n">
         <v>115</v>
       </c>
-      <c r="B131" s="10" t="inlineStr">
+      <c r="B131" s="11" t="inlineStr">
         <is>
           <t>Suporte DIN para Arduino Mega</t>
         </is>
       </c>
-      <c r="C131" s="9" t="inlineStr">
+      <c r="C131" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D131" s="10" t="inlineStr">
+      <c r="D131" s="11" t="inlineStr">
         <is>
           <t>Ou SPCI4/adaptador</t>
         </is>
       </c>
-      <c r="E131" s="10" t="inlineStr"/>
-      <c r="F131" s="11" t="inlineStr"/>
-      <c r="G131" s="12" t="inlineStr"/>
-      <c r="H131" s="12">
-        <f>IF(C131*G131=0,"",C131*G131)</f>
+      <c r="E131" s="11" t="inlineStr"/>
+      <c r="F131" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/suporte-din-arduino-mega","🔎 suporte din arduino mega")</f>
+        <v/>
+      </c>
+      <c r="G131" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=suporte+din+arduino+mega","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H131" s="13" t="inlineStr"/>
+      <c r="I131" s="14" t="inlineStr"/>
+      <c r="J131" s="14">
+        <f>IF(C131*I131=0,"",C131*I131)</f>
         <v/>
       </c>
     </row>
@@ -3909,37 +4844,53 @@
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr"/>
-      <c r="F132" s="7" t="inlineStr"/>
-      <c r="G132" s="8" t="inlineStr"/>
-      <c r="H132" s="8">
-        <f>IF(C132*G132=0,"",C132*G132)</f>
+      <c r="F132" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tela-nextion-basic-3-2","🔎 tela nextion basic 3 2")</f>
+        <v/>
+      </c>
+      <c r="G132" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tela+nextion+basic+3+2","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H132" s="8" t="inlineStr"/>
+      <c r="I132" s="9" t="inlineStr"/>
+      <c r="J132" s="9">
+        <f>IF(C132*I132=0,"",C132*I132)</f>
         <v/>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="9" t="n">
+      <c r="A133" s="10" t="n">
         <v>117</v>
       </c>
-      <c r="B133" s="10" t="inlineStr">
+      <c r="B133" s="11" t="inlineStr">
         <is>
           <t>ESP32-WROOM-32U</t>
         </is>
       </c>
-      <c r="C133" s="9" t="inlineStr">
+      <c r="C133" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D133" s="10" t="inlineStr">
+      <c r="D133" s="11" t="inlineStr">
         <is>
           <t>30 pinos, conector de antena IPEX</t>
         </is>
       </c>
-      <c r="E133" s="10" t="inlineStr"/>
-      <c r="F133" s="11" t="inlineStr"/>
-      <c r="G133" s="12" t="inlineStr"/>
-      <c r="H133" s="12">
-        <f>IF(C133*G133=0,"",C133*G133)</f>
+      <c r="E133" s="11" t="inlineStr"/>
+      <c r="F133" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/esp32-wroom-32u","🔎 esp32 wroom 32u")</f>
+        <v/>
+      </c>
+      <c r="G133" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=esp32+wroom+32u","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H133" s="13" t="inlineStr"/>
+      <c r="I133" s="14" t="inlineStr"/>
+      <c r="J133" s="14">
+        <f>IF(C133*I133=0,"",C133*I133)</f>
         <v/>
       </c>
     </row>
@@ -3963,37 +4914,53 @@
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr"/>
-      <c r="F134" s="7" t="inlineStr"/>
-      <c r="G134" s="8" t="inlineStr"/>
-      <c r="H134" s="8">
-        <f>IF(C134*G134=0,"",C134*G134)</f>
+      <c r="F134" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/dnlcb30-base-din-esp32","🔎 dnlcb30 base din esp32")</f>
+        <v/>
+      </c>
+      <c r="G134" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=dnlcb30+base+din+esp32","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H134" s="8" t="inlineStr"/>
+      <c r="I134" s="9" t="inlineStr"/>
+      <c r="J134" s="9">
+        <f>IF(C134*I134=0,"",C134*I134)</f>
         <v/>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="9" t="n">
+      <c r="A135" s="10" t="n">
         <v>119</v>
       </c>
-      <c r="B135" s="10" t="inlineStr">
+      <c r="B135" s="11" t="inlineStr">
         <is>
           <t>Pigtail IPEX (u.FL) → SMA macho, 20–30 cm</t>
         </is>
       </c>
-      <c r="C135" s="9" t="inlineStr">
+      <c r="C135" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D135" s="10" t="inlineStr">
+      <c r="D135" s="11" t="inlineStr">
         <is>
           <t>Liga o ESP32 ao conector de painel</t>
         </is>
       </c>
-      <c r="E135" s="10" t="inlineStr"/>
-      <c r="F135" s="11" t="inlineStr"/>
-      <c r="G135" s="12" t="inlineStr"/>
-      <c r="H135" s="12">
-        <f>IF(C135*G135=0,"",C135*G135)</f>
+      <c r="E135" s="11" t="inlineStr"/>
+      <c r="F135" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/pigtail-ipex-sma-macho-20-30-cm","🔎 pigtail ipex sma macho, 20 3")</f>
+        <v/>
+      </c>
+      <c r="G135" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=pigtail+ipex+sma+macho%2C+20+30+cm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H135" s="13" t="inlineStr"/>
+      <c r="I135" s="14" t="inlineStr"/>
+      <c r="J135" s="14">
+        <f>IF(C135*I135=0,"",C135*I135)</f>
         <v/>
       </c>
     </row>
@@ -4017,37 +4984,53 @@
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr"/>
-      <c r="F136" s="7" t="inlineStr"/>
-      <c r="G136" s="8" t="inlineStr"/>
-      <c r="H136" s="8">
-        <f>IF(C136*G136=0,"",C136*G136)</f>
+      <c r="F136" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/conector-sma-femea-painel","🔎 conector sma femea painel")</f>
+        <v/>
+      </c>
+      <c r="G136" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=conector+sma+femea+painel","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H136" s="8" t="inlineStr"/>
+      <c r="I136" s="9" t="inlineStr"/>
+      <c r="J136" s="9">
+        <f>IF(C136*I136=0,"",C136*I136)</f>
         <v/>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="9" t="n">
+      <c r="A137" s="10" t="n">
         <v>121</v>
       </c>
-      <c r="B137" s="10" t="inlineStr">
+      <c r="B137" s="11" t="inlineStr">
         <is>
           <t>Antena 2,4 GHz SMA macho 3 dBi articulável</t>
         </is>
       </c>
-      <c r="C137" s="9" t="inlineStr">
+      <c r="C137" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D137" s="10" t="inlineStr">
+      <c r="D137" s="11" t="inlineStr">
         <is>
           <t>Rosqueada por fora, na lateral direita, parte alta do painel</t>
         </is>
       </c>
-      <c r="E137" s="10" t="inlineStr"/>
-      <c r="F137" s="11" t="inlineStr"/>
-      <c r="G137" s="12" t="inlineStr"/>
-      <c r="H137" s="12">
-        <f>IF(C137*G137=0,"",C137*G137)</f>
+      <c r="E137" s="11" t="inlineStr"/>
+      <c r="F137" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/antena-2-4-ghz-sma-macho-3-dbi","🔎 antena 2,4 ghz sma macho 3 d")</f>
+        <v/>
+      </c>
+      <c r="G137" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=antena+2%2C4+ghz+sma+macho+3+dbi","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H137" s="13" t="inlineStr"/>
+      <c r="I137" s="14" t="inlineStr"/>
+      <c r="J137" s="14">
+        <f>IF(C137*I137=0,"",C137*I137)</f>
         <v/>
       </c>
     </row>
@@ -4071,37 +5054,53 @@
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr"/>
-      <c r="F138" s="7" t="inlineStr"/>
-      <c r="G138" s="8" t="inlineStr"/>
-      <c r="H138" s="8">
-        <f>IF(C138*G138=0,"",C138*G138)</f>
+      <c r="F138" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/modulo-micro-sd","🔎 modulo micro sd")</f>
+        <v/>
+      </c>
+      <c r="G138" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=modulo+micro+sd","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H138" s="8" t="inlineStr"/>
+      <c r="I138" s="9" t="inlineStr"/>
+      <c r="J138" s="9">
+        <f>IF(C138*I138=0,"",C138*I138)</f>
         <v/>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="9" t="n">
+      <c r="A139" s="10" t="n">
         <v>123</v>
       </c>
-      <c r="B139" s="10" t="inlineStr">
+      <c r="B139" s="11" t="inlineStr">
         <is>
           <t>Cartão Micro SD</t>
         </is>
       </c>
-      <c r="C139" s="9" t="inlineStr">
+      <c r="C139" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D139" s="10" t="inlineStr">
+      <c r="D139" s="11" t="inlineStr">
         <is>
           <t>8–16 GB, Classe 10</t>
         </is>
       </c>
-      <c r="E139" s="10" t="inlineStr"/>
-      <c r="F139" s="11" t="inlineStr"/>
-      <c r="G139" s="12" t="inlineStr"/>
-      <c r="H139" s="12">
-        <f>IF(C139*G139=0,"",C139*G139)</f>
+      <c r="E139" s="11" t="inlineStr"/>
+      <c r="F139" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cartao-micro-sd","🔎 cartao micro sd")</f>
+        <v/>
+      </c>
+      <c r="G139" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cartao+micro+sd","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H139" s="13" t="inlineStr"/>
+      <c r="I139" s="14" t="inlineStr"/>
+      <c r="J139" s="14">
+        <f>IF(C139*I139=0,"",C139*I139)</f>
         <v/>
       </c>
     </row>
@@ -4125,37 +5124,53 @@
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr"/>
-      <c r="F140" s="7" t="inlineStr"/>
-      <c r="G140" s="8" t="inlineStr"/>
-      <c r="H140" s="8">
-        <f>IF(C140*G140=0,"",C140*G140)</f>
+      <c r="F140" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/modulo-rtc-ds3231","🔎 modulo rtc ds3231")</f>
+        <v/>
+      </c>
+      <c r="G140" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=modulo+rtc+ds3231","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H140" s="8" t="inlineStr"/>
+      <c r="I140" s="9" t="inlineStr"/>
+      <c r="J140" s="9">
+        <f>IF(C140*I140=0,"",C140*I140)</f>
         <v/>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="9" t="n">
+      <c r="A141" s="10" t="n">
         <v>125</v>
       </c>
-      <c r="B141" s="10" t="inlineStr">
+      <c r="B141" s="11" t="inlineStr">
         <is>
           <t>Bateria CR2032</t>
         </is>
       </c>
-      <c r="C141" s="9" t="inlineStr">
+      <c r="C141" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D141" s="10" t="inlineStr">
+      <c r="D141" s="11" t="inlineStr">
         <is>
           <t>Backup do RTC</t>
         </is>
       </c>
-      <c r="E141" s="10" t="inlineStr"/>
-      <c r="F141" s="11" t="inlineStr"/>
-      <c r="G141" s="12" t="inlineStr"/>
-      <c r="H141" s="12">
-        <f>IF(C141*G141=0,"",C141*G141)</f>
+      <c r="E141" s="11" t="inlineStr"/>
+      <c r="F141" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/bateria-cr2032","🔎 bateria cr2032")</f>
+        <v/>
+      </c>
+      <c r="G141" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=bateria+cr2032","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H141" s="13" t="inlineStr"/>
+      <c r="I141" s="14" t="inlineStr"/>
+      <c r="J141" s="14">
+        <f>IF(C141*I141=0,"",C141*I141)</f>
         <v/>
       </c>
     </row>
@@ -4167,29 +5182,37 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="9" t="n">
+      <c r="A143" s="10" t="n">
         <v>126</v>
       </c>
-      <c r="B143" s="10" t="inlineStr">
+      <c r="B143" s="11" t="inlineStr">
         <is>
           <t>Driver ponte-H BTS7960</t>
         </is>
       </c>
-      <c r="C143" s="9" t="inlineStr">
+      <c r="C143" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D143" s="10" t="inlineStr">
+      <c r="D143" s="11" t="inlineStr">
         <is>
           <t>43 A, pino IS de diagnóstico</t>
         </is>
       </c>
-      <c r="E143" s="10" t="inlineStr"/>
-      <c r="F143" s="11" t="inlineStr"/>
-      <c r="G143" s="12" t="inlineStr"/>
-      <c r="H143" s="12">
-        <f>IF(C143*G143=0,"",C143*G143)</f>
+      <c r="E143" s="11" t="inlineStr"/>
+      <c r="F143" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/driver-ponte-h-bts7960","🔎 driver ponte h bts7960")</f>
+        <v/>
+      </c>
+      <c r="G143" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=driver+ponte+h+bts7960","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H143" s="13" t="inlineStr"/>
+      <c r="I143" s="14" t="inlineStr"/>
+      <c r="J143" s="14">
+        <f>IF(C143*I143=0,"",C143*I143)</f>
         <v/>
       </c>
     </row>
@@ -4213,37 +5236,53 @@
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr"/>
-      <c r="F144" s="7" t="inlineStr"/>
-      <c r="G144" s="8" t="inlineStr"/>
-      <c r="H144" s="8">
-        <f>IF(C144*G144=0,"",C144*G144)</f>
+      <c r="F144" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/suporte-spci4-trilho-din","🔎 suporte spci4 trilho din")</f>
+        <v/>
+      </c>
+      <c r="G144" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=suporte+spci4+trilho+din","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H144" s="8" t="inlineStr"/>
+      <c r="I144" s="9" t="inlineStr"/>
+      <c r="J144" s="9">
+        <f>IF(C144*I144=0,"",C144*I144)</f>
         <v/>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="9" t="n">
+      <c r="A145" s="10" t="n">
         <v>128</v>
       </c>
-      <c r="B145" s="10" t="inlineStr">
+      <c r="B145" s="11" t="inlineStr">
         <is>
           <t>Cooler 40 mm 12 V</t>
         </is>
       </c>
-      <c r="C145" s="9" t="inlineStr">
+      <c r="C145" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D145" s="10" t="inlineStr">
+      <c r="D145" s="11" t="inlineStr">
         <is>
           <t>Refrigeração dos BTS</t>
         </is>
       </c>
-      <c r="E145" s="10" t="inlineStr"/>
-      <c r="F145" s="11" t="inlineStr"/>
-      <c r="G145" s="12" t="inlineStr"/>
-      <c r="H145" s="12">
-        <f>IF(C145*G145=0,"",C145*G145)</f>
+      <c r="E145" s="11" t="inlineStr"/>
+      <c r="F145" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cooler-40-mm-12-v","🔎 cooler 40 mm 12 v")</f>
+        <v/>
+      </c>
+      <c r="G145" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cooler+40+mm+12+v","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H145" s="13" t="inlineStr"/>
+      <c r="I145" s="14" t="inlineStr"/>
+      <c r="J145" s="14">
+        <f>IF(C145*I145=0,"",C145*I145)</f>
         <v/>
       </c>
     </row>
@@ -4267,37 +5306,53 @@
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr"/>
-      <c r="F146" s="7" t="inlineStr"/>
-      <c r="G146" s="8" t="inlineStr"/>
-      <c r="H146" s="8">
-        <f>IF(C146*G146=0,"",C146*G146)</f>
+      <c r="F146" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/rele-interface-24-vcc-2-contatos","🔎 rele interface 24 vcc, 2 con")</f>
+        <v/>
+      </c>
+      <c r="G146" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=rele+interface+24+vcc%2C+2+contatos","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H146" s="8" t="inlineStr"/>
+      <c r="I146" s="9" t="inlineStr"/>
+      <c r="J146" s="9">
+        <f>IF(C146*I146=0,"",C146*I146)</f>
         <v/>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="9" t="n">
+      <c r="A147" s="10" t="n">
         <v>130</v>
       </c>
-      <c r="B147" s="10" t="inlineStr">
+      <c r="B147" s="11" t="inlineStr">
         <is>
           <t>KA2 — Relé de interface 24 Vcc, contato ≥ 10 A</t>
         </is>
       </c>
-      <c r="C147" s="9" t="inlineStr">
+      <c r="C147" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D147" s="10" t="inlineStr">
+      <c r="D147" s="11" t="inlineStr">
         <is>
           <t>É ele que chaveia os 24 V / 6,0 A de potência dos BTS. ⚠️ Confirme os 10 A no anúncio — a maioria dos slim é de 6 A — e confirme que a corrente é declarada em DC: muito relé de 10 A/250 VAC cai para 5 A ou menos em 24 Vcc, porque corrente contínua não tem passagem por zero e o arco custa mais a extinguir. Buscar relé de interface 24vdc 10a trilho din. Premium: Finder 46.61.9.024.0040 + base 95.05 (16 A)</t>
         </is>
       </c>
-      <c r="E147" s="10" t="inlineStr"/>
-      <c r="F147" s="11" t="inlineStr"/>
-      <c r="G147" s="12" t="inlineStr"/>
-      <c r="H147" s="12">
-        <f>IF(C147*G147=0,"",C147*G147)</f>
+      <c r="E147" s="11" t="inlineStr"/>
+      <c r="F147" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/rele-interface-24-vcc-contato-10","🔎 rele interface 24 vcc, conta")</f>
+        <v/>
+      </c>
+      <c r="G147" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=rele+interface+24+vcc%2C+contato+10","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H147" s="13" t="inlineStr"/>
+      <c r="I147" s="14" t="inlineStr"/>
+      <c r="J147" s="14">
+        <f>IF(C147*I147=0,"",C147*I147)</f>
         <v/>
       </c>
     </row>
@@ -4321,37 +5376,53 @@
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr"/>
-      <c r="F148" s="7" t="inlineStr"/>
-      <c r="G148" s="8" t="inlineStr"/>
-      <c r="H148" s="8">
-        <f>IF(C148*G148=0,"",C148*G148)</f>
+      <c r="F148" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-10-k-1-4-w","🔎 resistor 10 k 1 4 w")</f>
+        <v/>
+      </c>
+      <c r="G148" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+10+k+1+4+w","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H148" s="8" t="inlineStr"/>
+      <c r="I148" s="9" t="inlineStr"/>
+      <c r="J148" s="9">
+        <f>IF(C148*I148=0,"",C148*I148)</f>
         <v/>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="9" t="n">
+      <c r="A149" s="10" t="n">
         <v>132</v>
       </c>
-      <c r="B149" s="10" t="inlineStr">
+      <c r="B149" s="11" t="inlineStr">
         <is>
           <t>Resistor 22 kΩ 1/4 W ⬆</t>
         </is>
       </c>
-      <c r="C149" s="9" t="inlineStr">
+      <c r="C149" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D149" s="10" t="inlineStr">
+      <c r="D149" s="11" t="inlineStr">
         <is>
           <t>Braço superior do divisor de realimentação de tensão para o pino D25</t>
         </is>
       </c>
-      <c r="E149" s="10" t="inlineStr"/>
-      <c r="F149" s="11" t="inlineStr"/>
-      <c r="G149" s="12" t="inlineStr"/>
-      <c r="H149" s="12">
-        <f>IF(C149*G149=0,"",C149*G149)</f>
+      <c r="E149" s="11" t="inlineStr"/>
+      <c r="F149" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-22-k-1-4-w","🔎 resistor 22 k 1 4 w")</f>
+        <v/>
+      </c>
+      <c r="G149" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+22+k+1+4+w","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H149" s="13" t="inlineStr"/>
+      <c r="I149" s="14" t="inlineStr"/>
+      <c r="J149" s="14">
+        <f>IF(C149*I149=0,"",C149*I149)</f>
         <v/>
       </c>
     </row>
@@ -4375,10 +5446,18 @@
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr"/>
-      <c r="F150" s="7" t="inlineStr"/>
-      <c r="G150" s="8" t="inlineStr"/>
-      <c r="H150" s="8">
-        <f>IF(C150*G150=0,"",C150*G150)</f>
+      <c r="F150" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-4-7-k-1-4-w","🔎 resistor 4,7 k 1 4 w")</f>
+        <v/>
+      </c>
+      <c r="G150" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+4%2C7+k+1+4+w","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H150" s="8" t="inlineStr"/>
+      <c r="I150" s="9" t="inlineStr"/>
+      <c r="J150" s="9">
+        <f>IF(C150*I150=0,"",C150*I150)</f>
         <v/>
       </c>
     </row>
@@ -4409,37 +5488,53 @@
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr"/>
-      <c r="F152" s="7" t="inlineStr"/>
-      <c r="G152" s="8" t="inlineStr"/>
-      <c r="H152" s="8">
-        <f>IF(C152*G152=0,"",C152*G152)</f>
+      <c r="F152" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/pastilha-peltier-tec1-12706","🔎 pastilha peltier tec1 12706")</f>
+        <v/>
+      </c>
+      <c r="G152" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=pastilha+peltier+tec1+12706","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H152" s="8" t="inlineStr"/>
+      <c r="I152" s="9" t="inlineStr"/>
+      <c r="J152" s="9">
+        <f>IF(C152*I152=0,"",C152*I152)</f>
         <v/>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="9" t="n">
+      <c r="A153" s="10" t="n">
         <v>135</v>
       </c>
-      <c r="B153" s="10" t="inlineStr">
-        <is>
-          <t>Aquecedor PTC cerâmico 24 V / 60 W</t>
-        </is>
-      </c>
-      <c r="C153" s="9" t="inlineStr">
+      <c r="B153" s="11" t="inlineStr">
+        <is>
+          <t>Aquecedor PTC cerâmico 24 V / 80 W</t>
+        </is>
+      </c>
+      <c r="C153" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D153" s="10" t="inlineStr">
-        <is>
-          <t>Com aletas, versão de 24 V (2,5 A) para ligar direto no barramento. 60 W, não 100 W — equilibra as duas potências. ⚠️ Menos comum que o de 12 V: comprar cedo, no Lote A. Buscar também como aquecedor ar quente ptc 24v (incubadora / impressora 3D)</t>
-        </is>
-      </c>
-      <c r="E153" s="10" t="inlineStr"/>
-      <c r="F153" s="11" t="inlineStr"/>
-      <c r="G153" s="12" t="inlineStr"/>
-      <c r="H153" s="12">
-        <f>IF(C153*G153=0,"",C153*G153)</f>
+      <c r="D153" s="11" t="inlineStr">
+        <is>
+          <t>Com aletas e ventilador, versão de 24 V (~3,3 A) para ligar direto no barramento. ⚠️ 60 W não existe no mercado brasileiro — as versões reais são 80 W, 100 W e 150 W. Use a de 80 W: fica bem equilibrada contra os ~60 W de capacidade de refrigeração das 2 Peltier, e mantém a corrente em 3,3 A (metade da Peltier). A de 150 W passaria a ser o pior caso do ramal (6,25 A) e desequilibra o controle. Buscar aquecedor ptc 24v ventilador</t>
+        </is>
+      </c>
+      <c r="E153" s="11" t="inlineStr"/>
+      <c r="F153" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/aquecedor-ptc-ceramico-24-v-80-w","🔎 aquecedor ptc ceramico 24 v ")</f>
+        <v/>
+      </c>
+      <c r="G153" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=aquecedor+ptc+ceramico+24+v+80+w","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H153" s="13" t="inlineStr"/>
+      <c r="I153" s="14" t="inlineStr"/>
+      <c r="J153" s="14">
+        <f>IF(C153*I153=0,"",C153*I153)</f>
         <v/>
       </c>
     </row>
@@ -4463,37 +5558,53 @@
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr"/>
-      <c r="F154" s="7" t="inlineStr"/>
-      <c r="G154" s="8" t="inlineStr"/>
-      <c r="H154" s="8">
-        <f>IF(C154*G154=0,"",C154*G154)</f>
+      <c r="F154" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/dissipador-cooler-80-mm-p-lado-quente","🔎 dissipador cooler 80 mm p la")</f>
+        <v/>
+      </c>
+      <c r="G154" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=dissipador+cooler+80+mm+p+lado+quente","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H154" s="8" t="inlineStr"/>
+      <c r="I154" s="9" t="inlineStr"/>
+      <c r="J154" s="9">
+        <f>IF(C154*I154=0,"",C154*I154)</f>
         <v/>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="9" t="n">
+      <c r="A155" s="10" t="n">
         <v>137</v>
       </c>
-      <c r="B155" s="10" t="inlineStr">
+      <c r="B155" s="11" t="inlineStr">
         <is>
           <t>Pasta térmica</t>
         </is>
       </c>
-      <c r="C155" s="9" t="inlineStr">
+      <c r="C155" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D155" s="10" t="inlineStr">
+      <c r="D155" s="11" t="inlineStr">
         <is>
           <t>Seringa 5 g — dá para os 2 conjuntos</t>
         </is>
       </c>
-      <c r="E155" s="10" t="inlineStr"/>
-      <c r="F155" s="11" t="inlineStr"/>
-      <c r="G155" s="12" t="inlineStr"/>
-      <c r="H155" s="12">
-        <f>IF(C155*G155=0,"",C155*G155)</f>
+      <c r="E155" s="11" t="inlineStr"/>
+      <c r="F155" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/pasta-termica","🔎 pasta termica")</f>
+        <v/>
+      </c>
+      <c r="G155" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=pasta+termica","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H155" s="13" t="inlineStr"/>
+      <c r="I155" s="14" t="inlineStr"/>
+      <c r="J155" s="14">
+        <f>IF(C155*I155=0,"",C155*I155)</f>
         <v/>
       </c>
     </row>
@@ -4517,37 +5628,53 @@
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr"/>
-      <c r="F156" s="7" t="inlineStr"/>
-      <c r="G156" s="8" t="inlineStr"/>
-      <c r="H156" s="8">
-        <f>IF(C156*G156=0,"",C156*G156)</f>
+      <c r="F156" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fan-60-60-mm-12-v","🔎 fan 60 60 mm 12 v")</f>
+        <v/>
+      </c>
+      <c r="G156" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fan+60+60+mm+12+v","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H156" s="8" t="inlineStr"/>
+      <c r="I156" s="9" t="inlineStr"/>
+      <c r="J156" s="9">
+        <f>IF(C156*I156=0,"",C156*I156)</f>
         <v/>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="9" t="n">
+      <c r="A157" s="10" t="n">
         <v>139</v>
       </c>
-      <c r="B157" s="10" t="inlineStr">
+      <c r="B157" s="11" t="inlineStr">
         <is>
           <t>Fan 40 × 40 mm 12 V</t>
         </is>
       </c>
-      <c r="C157" s="9" t="inlineStr">
+      <c r="C157" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D157" s="10" t="inlineStr">
+      <c r="D157" s="11" t="inlineStr">
         <is>
           <t>Internas — lado Peltier (1 sopra ↓, 1 sopra ↑)</t>
         </is>
       </c>
-      <c r="E157" s="10" t="inlineStr"/>
-      <c r="F157" s="11" t="inlineStr"/>
-      <c r="G157" s="12" t="inlineStr"/>
-      <c r="H157" s="12">
-        <f>IF(C157*G157=0,"",C157*G157)</f>
+      <c r="E157" s="11" t="inlineStr"/>
+      <c r="F157" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fan-40-40-mm-12-v","🔎 fan 40 40 mm 12 v")</f>
+        <v/>
+      </c>
+      <c r="G157" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fan+40+40+mm+12+v","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H157" s="13" t="inlineStr"/>
+      <c r="I157" s="14" t="inlineStr"/>
+      <c r="J157" s="14">
+        <f>IF(C157*I157=0,"",C157*I157)</f>
         <v/>
       </c>
     </row>
@@ -4559,29 +5686,37 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="9" t="n">
+      <c r="A159" s="10" t="n">
         <v>140</v>
       </c>
-      <c r="B159" s="10" t="inlineStr">
+      <c r="B159" s="11" t="inlineStr">
         <is>
           <t>Sensor DS18B20 à prova d'água</t>
         </is>
       </c>
-      <c r="C159" s="9" t="inlineStr">
+      <c r="C159" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D159" s="10" t="inlineStr">
+      <c r="D159" s="11" t="inlineStr">
         <is>
           <t>1-Wire, ±0,5 °C — centro da câmara</t>
         </is>
       </c>
-      <c r="E159" s="10" t="inlineStr"/>
-      <c r="F159" s="11" t="inlineStr"/>
-      <c r="G159" s="12" t="inlineStr"/>
-      <c r="H159" s="12">
-        <f>IF(C159*G159=0,"",C159*G159)</f>
+      <c r="E159" s="11" t="inlineStr"/>
+      <c r="F159" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/sensor-ds18b20-prova-d-agua","🔎 sensor ds18b20 prova d agua")</f>
+        <v/>
+      </c>
+      <c r="G159" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=sensor+ds18b20+prova+d+agua","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H159" s="13" t="inlineStr"/>
+      <c r="I159" s="14" t="inlineStr"/>
+      <c r="J159" s="14">
+        <f>IF(C159*I159=0,"",C159*I159)</f>
         <v/>
       </c>
     </row>
@@ -4605,37 +5740,53 @@
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr"/>
-      <c r="F160" s="7" t="inlineStr"/>
-      <c r="G160" s="8" t="inlineStr"/>
-      <c r="H160" s="8">
-        <f>IF(C160*G160=0,"",C160*G160)</f>
+      <c r="F160" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-4-7-k-1-4-w","🔎 resistor 4,7 k 1 4 w")</f>
+        <v/>
+      </c>
+      <c r="G160" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+4%2C7+k+1+4+w","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H160" s="8" t="inlineStr"/>
+      <c r="I160" s="9" t="inlineStr"/>
+      <c r="J160" s="9">
+        <f>IF(C160*I160=0,"",C160*I160)</f>
         <v/>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="9" t="n">
+      <c r="A161" s="10" t="n">
         <v>142</v>
       </c>
-      <c r="B161" s="10" t="inlineStr">
+      <c r="B161" s="11" t="inlineStr">
         <is>
           <t>Sensor AM2315C</t>
         </is>
       </c>
-      <c r="C161" s="9" t="inlineStr">
+      <c r="C161" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D161" s="10" t="inlineStr">
+      <c r="D161" s="11" t="inlineStr">
         <is>
           <t>I²C, umidade + temperatura, carcaça selada</t>
         </is>
       </c>
-      <c r="E161" s="10" t="inlineStr"/>
-      <c r="F161" s="11" t="inlineStr"/>
-      <c r="G161" s="12" t="inlineStr"/>
-      <c r="H161" s="12">
-        <f>IF(C161*G161=0,"",C161*G161)</f>
+      <c r="E161" s="11" t="inlineStr"/>
+      <c r="F161" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/sensor-am2315c","🔎 sensor am2315c")</f>
+        <v/>
+      </c>
+      <c r="G161" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=sensor+am2315c","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H161" s="13" t="inlineStr"/>
+      <c r="I161" s="14" t="inlineStr"/>
+      <c r="J161" s="14">
+        <f>IF(C161*I161=0,"",C161*I161)</f>
         <v/>
       </c>
     </row>
@@ -4659,71 +5810,95 @@
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr"/>
-      <c r="F162" s="7" t="inlineStr"/>
-      <c r="G162" s="8" t="inlineStr"/>
-      <c r="H162" s="8">
-        <f>IF(C162*G162=0,"",C162*G162)</f>
+      <c r="F162" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/capacitor-ceramico-100-nf","🔎 capacitor ceramico 100 nf")</f>
+        <v/>
+      </c>
+      <c r="G162" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=capacitor+ceramico+100+nf","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H162" s="8" t="inlineStr"/>
+      <c r="I162" s="9" t="inlineStr"/>
+      <c r="J162" s="9">
+        <f>IF(C162*I162=0,"",C162*I162)</f>
         <v/>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="9" t="n">
+      <c r="A163" s="10" t="n">
         <v>144</v>
       </c>
-      <c r="B163" s="10" t="inlineStr">
+      <c r="B163" s="11" t="inlineStr">
         <is>
           <t>Resistor 220 Ω 1/4 W</t>
         </is>
       </c>
-      <c r="C163" s="9" t="inlineStr">
+      <c r="C163" s="10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D163" s="10" t="inlineStr">
+      <c r="D163" s="11" t="inlineStr">
         <is>
           <t>4 usos + 2 reservas — série dos LEDs brancos da iluminação da maquete (5 V). ⚠️ Não são mais dos sinaleiros do painel, que agora são de 24 V</t>
         </is>
       </c>
-      <c r="E163" s="10" t="inlineStr"/>
-      <c r="F163" s="11" t="inlineStr"/>
-      <c r="G163" s="12" t="inlineStr"/>
-      <c r="H163" s="12">
-        <f>IF(C163*G163=0,"",C163*G163)</f>
+      <c r="E163" s="11" t="inlineStr"/>
+      <c r="F163" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-220-1-4-w","🔎 resistor 220 1 4 w")</f>
+        <v/>
+      </c>
+      <c r="G163" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+220+1+4+w","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H163" s="13" t="inlineStr"/>
+      <c r="I163" s="14" t="inlineStr"/>
+      <c r="J163" s="14">
+        <f>IF(C163*I163=0,"",C163*I163)</f>
         <v/>
       </c>
     </row>
     <row r="164" ht="22" customHeight="1">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>L.5 — Placa de Interface PI-1 (onde os componentes discretos moram)</t>
+          <t>L.4b — Posições de ensaio (dispositivos sob teste)</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="9" t="n">
+      <c r="A165" s="10" t="n">
         <v>145</v>
       </c>
-      <c r="B165" s="10" t="inlineStr">
-        <is>
-          <t>Placa ilhada (padrão furos isolados)</t>
-        </is>
-      </c>
-      <c r="C165" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D165" s="10" t="inlineStr">
-        <is>
-          <t>~5 × 7 cm. ⚠️ Ilhada, não de barramento — na de barramento você acaba tendo que cortar trilha, e é dali que saem os curtos difíceis de achar</t>
-        </is>
-      </c>
-      <c r="E165" s="10" t="inlineStr"/>
-      <c r="F165" s="11" t="inlineStr"/>
-      <c r="G165" s="12" t="inlineStr"/>
-      <c r="H165" s="12">
-        <f>IF(C165*G165=0,"",C165*G165)</f>
+      <c r="B165" s="11" t="inlineStr">
+        <is>
+          <t>Sensor INA219 (módulo I²C)</t>
+        </is>
+      </c>
+      <c r="C165" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D165" s="11" t="inlineStr">
+        <is>
+          <t>Mede tensão e corrente, ±3,2 A. ⚠️ 4 endereços selecionáveis (0x40/0x41/0x44/0x45) — um por posição, todos no mesmo par de fios</t>
+        </is>
+      </c>
+      <c r="E165" s="11" t="inlineStr"/>
+      <c r="F165" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/sensor-ina219","🔎 sensor ina219")</f>
+        <v/>
+      </c>
+      <c r="G165" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=sensor+ina219","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H165" s="13" t="inlineStr"/>
+      <c r="I165" s="14" t="inlineStr"/>
+      <c r="J165" s="14">
+        <f>IF(C165*I165=0,"",C165*I165)</f>
         <v/>
       </c>
     </row>
@@ -4733,51 +5908,67 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>Caixa modular para trilho DIN — 3 módulos (52,5 mm)</t>
+          <t>Porta-fusível mini automotivo DIN</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>Invólucro da PI-1. Cabe no espaço livre do trilho 3, ao lado do Arduino. Buscar caixa para trilho din 3m modular</t>
+          <t>F-P1 a F-P4 — proteção individual de cada posição de ensaio</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr"/>
-      <c r="F166" s="7" t="inlineStr"/>
-      <c r="G166" s="8" t="inlineStr"/>
-      <c r="H166" s="8">
-        <f>IF(C166*G166=0,"",C166*G166)</f>
+      <c r="F166" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/porta-fusivel-mini-automotivo-din","🔎 porta fusivel mini automotiv")</f>
+        <v/>
+      </c>
+      <c r="G166" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=porta+fusivel+mini+automotivo+din","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H166" s="8" t="inlineStr"/>
+      <c r="I166" s="9" t="inlineStr"/>
+      <c r="J166" s="9">
+        <f>IF(C166*I166=0,"",C166*I166)</f>
         <v/>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="9" t="n">
+      <c r="A167" s="10" t="n">
         <v>147</v>
       </c>
-      <c r="B167" s="10" t="inlineStr">
-        <is>
-          <t>Borne KF350 / KRE passo 3,5 mm — 10 vias</t>
-        </is>
-      </c>
-      <c r="C167" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D167" s="10" t="inlineStr">
-        <is>
-          <t>Um borne superior (lado Arduino) e um inferior (lado campo). Passo de 3,5 mm porque todos os cabos são de 0,25 mm²</t>
-        </is>
-      </c>
-      <c r="E167" s="10" t="inlineStr"/>
-      <c r="F167" s="11" t="inlineStr"/>
-      <c r="G167" s="12" t="inlineStr"/>
-      <c r="H167" s="12">
-        <f>IF(C167*G167=0,"",C167*G167)</f>
+      <c r="B167" s="11" t="inlineStr">
+        <is>
+          <t>Fusível mini automotivo 500 mA</t>
+        </is>
+      </c>
+      <c r="C167" s="10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D167" s="11" t="inlineStr">
+        <is>
+          <t>4 usos + 4 reservas</t>
+        </is>
+      </c>
+      <c r="E167" s="11" t="inlineStr"/>
+      <c r="F167" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fusivel-mini-automotivo-500-ma","🔎 fusivel mini automotivo 500 ")</f>
+        <v/>
+      </c>
+      <c r="G167" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fusivel+mini+automotivo+500+ma","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H167" s="13" t="inlineStr"/>
+      <c r="I167" s="14" t="inlineStr"/>
+      <c r="J167" s="14">
+        <f>IF(C167*I167=0,"",C167*I167)</f>
         <v/>
       </c>
     </row>
@@ -4787,51 +5978,67 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>CI ULN2803A (DIP 18 pinos)</t>
+          <t>Placa ilhada pequena</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>Driver dos 4 sinaleiros de 24 V — 8 canais Darlington, 500 mA/50 V, com diodos de proteção internos. 1 uso + 1 reserva (o CI é barato e é o único ponto onde 24 V encosta na lógica)</t>
+          <t>~30 × 40 mm — corpo de cada placa simuladora de dispositivo</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr"/>
-      <c r="F168" s="7" t="inlineStr"/>
-      <c r="G168" s="8" t="inlineStr"/>
-      <c r="H168" s="8">
-        <f>IF(C168*G168=0,"",C168*G168)</f>
+      <c r="F168" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/placa-ilhada-pequena","🔎 placa ilhada pequena")</f>
+        <v/>
+      </c>
+      <c r="G168" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=placa+ilhada+pequena","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H168" s="8" t="inlineStr"/>
+      <c r="I168" s="9" t="inlineStr"/>
+      <c r="J168" s="9">
+        <f>IF(C168*I168=0,"",C168*I168)</f>
         <v/>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="9" t="n">
+      <c r="A169" s="10" t="n">
         <v>149</v>
       </c>
-      <c r="B169" s="10" t="inlineStr">
-        <is>
-          <t>Soquete DIP 18 pinos</t>
-        </is>
-      </c>
-      <c r="C169" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D169" s="10" t="inlineStr">
-        <is>
-          <t>⚠️ Solde o soquete, não o CI. Permite trocar o chip sem dessoldar nada</t>
-        </is>
-      </c>
-      <c r="E169" s="10" t="inlineStr"/>
-      <c r="F169" s="11" t="inlineStr"/>
-      <c r="G169" s="12" t="inlineStr"/>
-      <c r="H169" s="12">
-        <f>IF(C169*G169=0,"",C169*G169)</f>
+      <c r="B169" s="11" t="inlineStr">
+        <is>
+          <t>Resistor 220 Ω / 5 W</t>
+        </is>
+      </c>
+      <c r="C169" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D169" s="11" t="inlineStr">
+        <is>
+          <t>Carga térmica de cada simulador (~3 W). ⚠️ 5 W, não 1/4 W</t>
+        </is>
+      </c>
+      <c r="E169" s="11" t="inlineStr"/>
+      <c r="F169" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-220-5-w","🔎 resistor 220 5 w")</f>
+        <v/>
+      </c>
+      <c r="G169" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+220+5+w","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H169" s="13" t="inlineStr"/>
+      <c r="I169" s="14" t="inlineStr"/>
+      <c r="J169" s="14">
+        <f>IF(C169*I169=0,"",C169*I169)</f>
         <v/>
       </c>
     </row>
@@ -4841,51 +6048,67 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>Fio rígido 0,25 mm² para interligação</t>
+          <t>Resistor 1,2 kΩ 1/4 W</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>1 m</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
         <is>
-          <t>Ligações por baixo da placa. ⚠️ Não usar "sobra de perna" de componente em trecho longo — oxida e não é isolada</t>
+          <t>Limitador do LED indicador de cada posição</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr"/>
-      <c r="F170" s="7" t="inlineStr"/>
-      <c r="G170" s="8" t="inlineStr"/>
-      <c r="H170" s="8">
-        <f>IF(C170*G170=0,"",C170*G170)</f>
+      <c r="F170" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-1-2-k-1-4-w","🔎 resistor 1,2 k 1 4 w")</f>
+        <v/>
+      </c>
+      <c r="G170" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+1%2C2+k+1+4+w","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H170" s="8" t="inlineStr"/>
+      <c r="I170" s="9" t="inlineStr"/>
+      <c r="J170" s="9">
+        <f>IF(C170*I170=0,"",C170*I170)</f>
         <v/>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="9" t="n">
+      <c r="A171" s="10" t="n">
         <v>151</v>
       </c>
-      <c r="B171" s="10" t="inlineStr">
-        <is>
-          <t>Verniz spray para PCI (ou esmalte incolor)</t>
-        </is>
-      </c>
-      <c r="C171" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D171" s="10" t="inlineStr">
-        <is>
-          <t>Proteção do lado da solda contra umidade e oxidação</t>
-        </is>
-      </c>
-      <c r="E171" s="10" t="inlineStr"/>
-      <c r="F171" s="11" t="inlineStr"/>
-      <c r="G171" s="12" t="inlineStr"/>
-      <c r="H171" s="12">
-        <f>IF(C171*G171=0,"",C171*G171)</f>
+      <c r="B171" s="11" t="inlineStr">
+        <is>
+          <t>LED 5 mm difuso</t>
+        </is>
+      </c>
+      <c r="C171" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D171" s="11" t="inlineStr">
+        <is>
+          <t>Indica "posição viva", visível pela porta da câmara</t>
+        </is>
+      </c>
+      <c r="E171" s="11" t="inlineStr"/>
+      <c r="F171" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/led-5-mm-difuso","🔎 led 5 mm difuso")</f>
+        <v/>
+      </c>
+      <c r="G171" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=led+5+mm+difuso","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H171" s="13" t="inlineStr"/>
+      <c r="I171" s="14" t="inlineStr"/>
+      <c r="J171" s="14">
+        <f>IF(C171*I171=0,"",C171*I171)</f>
         <v/>
       </c>
     </row>
@@ -4895,89 +6118,109 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>Termorretrátil Ø 2 mm</t>
+          <t>Micro-chave ou jumper</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>30 cm</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>Isolação dos 2 resistores de 10 kΩ soldados nos BTS7960</t>
+          <t>⭐ Simula a falha do dispositivo — é o que permite demonstrar a detecção ao vivo na apresentação</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr"/>
-      <c r="F172" s="7" t="inlineStr"/>
-      <c r="G172" s="8" t="inlineStr"/>
-      <c r="H172" s="8">
-        <f>IF(C172*G172=0,"",C172*G172)</f>
+      <c r="F172" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/micro-chave-jumper","🔎 micro chave jumper")</f>
+        <v/>
+      </c>
+      <c r="G172" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=micro+chave+jumper","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H172" s="8" t="inlineStr"/>
+      <c r="I172" s="9" t="inlineStr"/>
+      <c r="J172" s="9">
+        <f>IF(C172*I172=0,"",C172*I172)</f>
         <v/>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="9" t="n">
+      <c r="A173" s="10" t="n">
         <v>153</v>
       </c>
-      <c r="B173" s="10" t="inlineStr">
-        <is>
-          <t>Etiqueta impressa em papel adesivo</t>
-        </is>
-      </c>
-      <c r="C173" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D173" s="10" t="inlineStr">
-        <is>
-          <t>Identificação das 20 vias na frente da caixa — é o que torna a placa auditável</t>
-        </is>
-      </c>
-      <c r="E173" s="10" t="inlineStr"/>
-      <c r="F173" s="11" t="inlineStr"/>
-      <c r="G173" s="12" t="inlineStr"/>
-      <c r="H173" s="12">
-        <f>IF(C173*G173=0,"",C173*G173)</f>
+      <c r="B173" s="11" t="inlineStr">
+        <is>
+          <t>Borne DIN 2,5 mm²</t>
+        </is>
+      </c>
+      <c r="C173" s="10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D173" s="11" t="inlineStr">
+        <is>
+          <t>Entrada e saída de cada posição</t>
+        </is>
+      </c>
+      <c r="E173" s="11" t="inlineStr"/>
+      <c r="F173" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/borne-din-2-5-mm","🔎 borne din 2,5 mm")</f>
+        <v/>
+      </c>
+      <c r="G173" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=borne+din+2%2C5+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H173" s="13" t="inlineStr"/>
+      <c r="I173" s="14" t="inlineStr"/>
+      <c r="J173" s="14">
+        <f>IF(C173*I173=0,"",C173*I173)</f>
         <v/>
       </c>
     </row>
     <row r="174" ht="22" customHeight="1">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>🔧 CAMADA 3 — CABOS E ACESSÓRIOS</t>
+          <t>L.5 — Placa de Interface PI-1 (onde os componentes discretos moram)</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="9" t="n">
+      <c r="A175" s="10" t="n">
         <v>154</v>
       </c>
-      <c r="B175" s="10" t="inlineStr">
-        <is>
-          <t>Cabo flexível 1,5 mm² preto</t>
-        </is>
-      </c>
-      <c r="C175" s="9" t="inlineStr">
-        <is>
-          <t>3 m</t>
-        </is>
-      </c>
-      <c r="D175" s="10" t="inlineStr">
-        <is>
-          <t>750 V</t>
-        </is>
-      </c>
-      <c r="E175" s="10" t="inlineStr">
-        <is>
-          <t>Retorno geral 0 V (6,9 A — soma dos 3 ramais)</t>
-        </is>
-      </c>
-      <c r="F175" s="11" t="inlineStr"/>
-      <c r="G175" s="12" t="inlineStr"/>
-      <c r="H175" s="12">
-        <f>IF(C175*G175=0,"",C175*G175)</f>
+      <c r="B175" s="11" t="inlineStr">
+        <is>
+          <t>Placa ilhada (padrão furos isolados)</t>
+        </is>
+      </c>
+      <c r="C175" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D175" s="11" t="inlineStr">
+        <is>
+          <t>~5 × 7 cm. ⚠️ Ilhada, não de barramento — na de barramento você acaba tendo que cortar trilha, e é dali que saem os curtos difíceis de achar</t>
+        </is>
+      </c>
+      <c r="E175" s="11" t="inlineStr"/>
+      <c r="F175" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/placa-ilhada","🔎 placa ilhada")</f>
+        <v/>
+      </c>
+      <c r="G175" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=placa+ilhada","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H175" s="13" t="inlineStr"/>
+      <c r="I175" s="14" t="inlineStr"/>
+      <c r="J175" s="14">
+        <f>IF(C175*I175=0,"",C175*I175)</f>
         <v/>
       </c>
     </row>
@@ -4987,59 +6230,67 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>Cabo flexível 1,5 mm² vermelho</t>
+          <t>Caixa modular para trilho DIN — 3 módulos (52,5 mm)</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>2 m</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>750 V</t>
-        </is>
-      </c>
-      <c r="E176" s="6" t="inlineStr">
-        <is>
-          <t>24 V de potência — P1 → painel → BTS (6,0 A)</t>
-        </is>
-      </c>
-      <c r="F176" s="7" t="inlineStr"/>
-      <c r="G176" s="8" t="inlineStr"/>
-      <c r="H176" s="8">
-        <f>IF(C176*G176=0,"",C176*G176)</f>
+          <t>Invólucro da PI-1. Cabe no espaço livre do trilho 3, ao lado do Arduino. Buscar caixa para trilho din 3m modular</t>
+        </is>
+      </c>
+      <c r="E176" s="6" t="inlineStr"/>
+      <c r="F176" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/caixa-modular-trilho-din","🔎 caixa modular trilho din")</f>
+        <v/>
+      </c>
+      <c r="G176" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=caixa+modular+trilho+din","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H176" s="8" t="inlineStr"/>
+      <c r="I176" s="9" t="inlineStr"/>
+      <c r="J176" s="9">
+        <f>IF(C176*I176=0,"",C176*I176)</f>
         <v/>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="9" t="n">
+      <c r="A177" s="10" t="n">
         <v>156</v>
       </c>
-      <c r="B177" s="10" t="inlineStr">
-        <is>
-          <t>Cabo flexível 0,75 mm² vermelho/preto</t>
-        </is>
-      </c>
-      <c r="C177" s="9" t="inlineStr">
-        <is>
-          <t>3 m</t>
-        </is>
-      </c>
-      <c r="D177" s="10" t="inlineStr">
-        <is>
-          <t>750 V</t>
-        </is>
-      </c>
-      <c r="E177" s="10" t="inlineStr">
-        <is>
-          <t>Barramento 24 V (trechos internos) e saída de 12 V do T3 (1,0 A)</t>
-        </is>
-      </c>
-      <c r="F177" s="11" t="inlineStr"/>
-      <c r="G177" s="12" t="inlineStr"/>
-      <c r="H177" s="12">
-        <f>IF(C177*G177=0,"",C177*G177)</f>
+      <c r="B177" s="11" t="inlineStr">
+        <is>
+          <t>Borne KF350 / KRE passo 3,5 mm — 10 vias</t>
+        </is>
+      </c>
+      <c r="C177" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D177" s="11" t="inlineStr">
+        <is>
+          <t>Um borne superior (lado Arduino) e um inferior (lado campo). Passo de 3,5 mm porque todos os cabos são de 0,25 mm²</t>
+        </is>
+      </c>
+      <c r="E177" s="11" t="inlineStr"/>
+      <c r="F177" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/borne-kf350-kre-passo-3-5-mm","🔎 borne kf350 kre passo 3,5 mm")</f>
+        <v/>
+      </c>
+      <c r="G177" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=borne+kf350+kre+passo+3%2C5+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H177" s="13" t="inlineStr"/>
+      <c r="I177" s="14" t="inlineStr"/>
+      <c r="J177" s="14">
+        <f>IF(C177*I177=0,"",C177*I177)</f>
         <v/>
       </c>
     </row>
@@ -5049,59 +6300,67 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>Cabo flexível 0,5 mm² (5 cores)</t>
+          <t>CI ULN2803A (DIP 18 pinos)</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>10 m</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr">
         <is>
-          <t>750 V</t>
-        </is>
-      </c>
-      <c r="E178" s="6" t="inlineStr">
-        <is>
-          <t>5 V e derivações do 12 V auxiliar</t>
-        </is>
-      </c>
-      <c r="F178" s="7" t="inlineStr"/>
-      <c r="G178" s="8" t="inlineStr"/>
-      <c r="H178" s="8">
-        <f>IF(C178*G178=0,"",C178*G178)</f>
+          <t>Driver dos 4 sinaleiros de 24 V — 8 canais Darlington, 500 mA/50 V, com diodos de proteção internos. 1 uso + 1 reserva (o CI é barato e é o único ponto onde 24 V encosta na lógica)</t>
+        </is>
+      </c>
+      <c r="E178" s="6" t="inlineStr"/>
+      <c r="F178" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/ci-uln2803a","🔎 ci uln2803a")</f>
+        <v/>
+      </c>
+      <c r="G178" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=ci+uln2803a","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H178" s="8" t="inlineStr"/>
+      <c r="I178" s="9" t="inlineStr"/>
+      <c r="J178" s="9">
+        <f>IF(C178*I178=0,"",C178*I178)</f>
         <v/>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="9" t="n">
+      <c r="A179" s="10" t="n">
         <v>158</v>
       </c>
-      <c r="B179" s="10" t="inlineStr">
-        <is>
-          <t>Cabo flexível 0,25 mm² (8 cores)</t>
-        </is>
-      </c>
-      <c r="C179" s="9" t="inlineStr">
-        <is>
-          <t>15 m</t>
-        </is>
-      </c>
-      <c r="D179" s="10" t="inlineStr">
-        <is>
-          <t>Sinais</t>
-        </is>
-      </c>
-      <c r="E179" s="10" t="inlineStr">
-        <is>
-          <t>Sensores, botões, comunicação</t>
-        </is>
-      </c>
-      <c r="F179" s="11" t="inlineStr"/>
-      <c r="G179" s="12" t="inlineStr"/>
-      <c r="H179" s="12">
-        <f>IF(C179*G179=0,"",C179*G179)</f>
+      <c r="B179" s="11" t="inlineStr">
+        <is>
+          <t>Soquete DIP 18 pinos</t>
+        </is>
+      </c>
+      <c r="C179" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D179" s="11" t="inlineStr">
+        <is>
+          <t>⚠️ Solde o soquete, não o CI. Permite trocar o chip sem dessoldar nada</t>
+        </is>
+      </c>
+      <c r="E179" s="11" t="inlineStr"/>
+      <c r="F179" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/soquete-dip-18-pinos","🔎 soquete dip 18 pinos")</f>
+        <v/>
+      </c>
+      <c r="G179" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=soquete+dip+18+pinos","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H179" s="13" t="inlineStr"/>
+      <c r="I179" s="14" t="inlineStr"/>
+      <c r="J179" s="14">
+        <f>IF(C179*I179=0,"",C179*I179)</f>
         <v/>
       </c>
     </row>
@@ -5111,59 +6370,67 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>Cabo par trançado blindado 2×0,25 mm²</t>
+          <t>Fio rígido 0,25 mm² para interligação</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>2 m</t>
+          <t>1 m</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr">
         <is>
-          <t>Blindado, malha aterrada em um ponto</t>
-        </is>
-      </c>
-      <c r="E180" s="6" t="inlineStr">
-        <is>
-          <t>I²C e 1-Wire (trecho câmara → painel)</t>
-        </is>
-      </c>
-      <c r="F180" s="7" t="inlineStr"/>
-      <c r="G180" s="8" t="inlineStr"/>
-      <c r="H180" s="8">
-        <f>IF(C180*G180=0,"",C180*G180)</f>
+          <t>Ligações por baixo da placa. ⚠️ Não usar "sobra de perna" de componente em trecho longo — oxida e não é isolada</t>
+        </is>
+      </c>
+      <c r="E180" s="6" t="inlineStr"/>
+      <c r="F180" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-rigido-0-25-mm-interligacao","🔎 fio rigido 0,25 mm interliga")</f>
+        <v/>
+      </c>
+      <c r="G180" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+rigido+0%2C25+mm+interligacao","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H180" s="8" t="inlineStr"/>
+      <c r="I180" s="9" t="inlineStr"/>
+      <c r="J180" s="9">
+        <f>IF(C180*I180=0,"",C180*I180)</f>
         <v/>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="9" t="n">
+      <c r="A181" s="10" t="n">
         <v>160</v>
       </c>
-      <c r="B181" s="10" t="inlineStr">
-        <is>
-          <t>Terminal tubular (ilhós) 0,25 / 0,5 / 1,5 mm²</t>
-        </is>
-      </c>
-      <c r="C181" s="9" t="inlineStr">
-        <is>
-          <t>1 kit</t>
-        </is>
-      </c>
-      <c r="D181" s="10" t="inlineStr">
-        <is>
-          <t>Com colarinho colorido</t>
-        </is>
-      </c>
-      <c r="E181" s="10" t="inlineStr">
-        <is>
-          <t>Obrigatório em todo borne parafuso</t>
-        </is>
-      </c>
-      <c r="F181" s="11" t="inlineStr"/>
-      <c r="G181" s="12" t="inlineStr"/>
-      <c r="H181" s="12">
-        <f>IF(C181*G181=0,"",C181*G181)</f>
+      <c r="B181" s="11" t="inlineStr">
+        <is>
+          <t>Verniz spray para PCI (ou esmalte incolor)</t>
+        </is>
+      </c>
+      <c r="C181" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D181" s="11" t="inlineStr">
+        <is>
+          <t>Proteção do lado da solda contra umidade e oxidação</t>
+        </is>
+      </c>
+      <c r="E181" s="11" t="inlineStr"/>
+      <c r="F181" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/verniz-spray-pci","🔎 verniz spray pci")</f>
+        <v/>
+      </c>
+      <c r="G181" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=verniz+spray+pci","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H181" s="13" t="inlineStr"/>
+      <c r="I181" s="14" t="inlineStr"/>
+      <c r="J181" s="14">
+        <f>IF(C181*I181=0,"",C181*I181)</f>
         <v/>
       </c>
     </row>
@@ -5173,219 +6440,618 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>Alicate de crimpar terminal tubular</t>
+          <t>Termorretrátil Ø 2 mm</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
+          <t>30 cm</t>
+        </is>
+      </c>
+      <c r="D182" s="6" t="inlineStr">
+        <is>
+          <t>Isolação dos 2 resistores de 10 kΩ soldados nos BTS7960</t>
+        </is>
+      </c>
+      <c r="E182" s="6" t="inlineStr"/>
+      <c r="F182" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/termorretratil-2-mm","🔎 termorretratil 2 mm")</f>
+        <v/>
+      </c>
+      <c r="G182" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=termorretratil+2+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H182" s="8" t="inlineStr"/>
+      <c r="I182" s="9" t="inlineStr"/>
+      <c r="J182" s="9">
+        <f>IF(C182*I182=0,"",C182*I182)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="10" t="n">
+        <v>162</v>
+      </c>
+      <c r="B183" s="11" t="inlineStr">
+        <is>
+          <t>Etiqueta impressa em papel adesivo</t>
+        </is>
+      </c>
+      <c r="C183" s="10" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D182" s="6" t="inlineStr">
-        <is>
-          <t>Tipo quadrado/hexagonal</t>
-        </is>
-      </c>
-      <c r="E182" s="6" t="inlineStr">
-        <is>
-          <t>Ferramenta</t>
-        </is>
-      </c>
-      <c r="F182" s="7" t="inlineStr"/>
-      <c r="G182" s="8" t="inlineStr"/>
-      <c r="H182" s="8">
-        <f>IF(C182*G182=0,"",C182*G182)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="9" t="n">
-        <v>162</v>
-      </c>
-      <c r="B183" s="10" t="inlineStr">
-        <is>
-          <t>Terminal olhal M4</t>
-        </is>
-      </c>
-      <c r="C183" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D183" s="10" t="inlineStr">
-        <is>
-          <t>Amarelo/vermelho</t>
-        </is>
-      </c>
-      <c r="E183" s="10" t="inlineStr">
-        <is>
-          <t>Aterramento</t>
-        </is>
-      </c>
-      <c r="F183" s="11" t="inlineStr"/>
-      <c r="G183" s="12" t="inlineStr"/>
-      <c r="H183" s="12">
-        <f>IF(C183*G183=0,"",C183*G183)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="5" t="n">
+      <c r="D183" s="11" t="inlineStr">
+        <is>
+          <t>Identificação das 20 vias na frente da caixa — é o que torna a placa auditável</t>
+        </is>
+      </c>
+      <c r="E183" s="11" t="inlineStr"/>
+      <c r="F183" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/etiqueta-impressa-papel-adesivo","🔎 etiqueta impressa papel ades")</f>
+        <v/>
+      </c>
+      <c r="G183" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=etiqueta+impressa+papel+adesivo","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H183" s="13" t="inlineStr"/>
+      <c r="I183" s="14" t="inlineStr"/>
+      <c r="J183" s="14">
+        <f>IF(C183*I183=0,"",C183*I183)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184" ht="22" customHeight="1">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>🔧 CAMADA 3 — CABOS E ACESSÓRIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="10" t="n">
         <v>163</v>
       </c>
-      <c r="B184" s="6" t="inlineStr">
-        <is>
-          <t>Espaguete termorretrátil (kit)</t>
-        </is>
-      </c>
-      <c r="C184" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D184" s="6" t="inlineStr">
-        <is>
-          <t>Diversas bitolas</t>
-        </is>
-      </c>
-      <c r="E184" s="6" t="inlineStr">
-        <is>
-          <t>Isolação de emendas</t>
-        </is>
-      </c>
-      <c r="F184" s="7" t="inlineStr"/>
-      <c r="G184" s="8" t="inlineStr"/>
-      <c r="H184" s="8">
-        <f>IF(C184*G184=0,"",C184*G184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="9" t="n">
-        <v>164</v>
-      </c>
-      <c r="B185" s="10" t="inlineStr">
-        <is>
-          <t>Abraçadeiras de nylon 100 mm</t>
-        </is>
-      </c>
-      <c r="C185" s="9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="D185" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E185" s="10" t="inlineStr">
-        <is>
-          <t>Amarração</t>
-        </is>
-      </c>
-      <c r="F185" s="11" t="inlineStr"/>
-      <c r="G185" s="12" t="inlineStr"/>
-      <c r="H185" s="12">
-        <f>IF(C185*G185=0,"",C185*G185)</f>
+      <c r="B185" s="11" t="inlineStr">
+        <is>
+          <t>Cabo flexível 1,5 mm² preto</t>
+        </is>
+      </c>
+      <c r="C185" s="10" t="inlineStr">
+        <is>
+          <t>3 m</t>
+        </is>
+      </c>
+      <c r="D185" s="11" t="inlineStr">
+        <is>
+          <t>750 V</t>
+        </is>
+      </c>
+      <c r="E185" s="11" t="inlineStr">
+        <is>
+          <t>Retorno geral 0 V (6,9 A — soma dos 3 ramais)</t>
+        </is>
+      </c>
+      <c r="F185" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-flexivel-1-5-mm-preto","🔎 cabo flexivel 1,5 mm preto")</f>
+        <v/>
+      </c>
+      <c r="G185" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+flexivel+1%2C5+mm+preto","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H185" s="13" t="inlineStr"/>
+      <c r="I185" s="14" t="inlineStr"/>
+      <c r="J185" s="14">
+        <f>IF(C185*I185=0,"",C185*I185)</f>
         <v/>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="5" t="n">
+        <v>164</v>
+      </c>
+      <c r="B186" s="6" t="inlineStr">
+        <is>
+          <t>Cabo flexível 1,5 mm² vermelho</t>
+        </is>
+      </c>
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>2 m</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr">
+        <is>
+          <t>750 V</t>
+        </is>
+      </c>
+      <c r="E186" s="6" t="inlineStr">
+        <is>
+          <t>24 V de potência — P1 → painel → BTS (6,0 A)</t>
+        </is>
+      </c>
+      <c r="F186" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-flexivel-1-5-mm-vermelho","🔎 cabo flexivel 1,5 mm vermelh")</f>
+        <v/>
+      </c>
+      <c r="G186" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+flexivel+1%2C5+mm+vermelho","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H186" s="8" t="inlineStr"/>
+      <c r="I186" s="9" t="inlineStr"/>
+      <c r="J186" s="9">
+        <f>IF(C186*I186=0,"",C186*I186)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="10" t="n">
         <v>165</v>
       </c>
-      <c r="B186" s="6" t="inlineStr">
+      <c r="B187" s="11" t="inlineStr">
+        <is>
+          <t>Cabo flexível 0,75 mm² vermelho/preto</t>
+        </is>
+      </c>
+      <c r="C187" s="10" t="inlineStr">
+        <is>
+          <t>3 m</t>
+        </is>
+      </c>
+      <c r="D187" s="11" t="inlineStr">
+        <is>
+          <t>750 V</t>
+        </is>
+      </c>
+      <c r="E187" s="11" t="inlineStr">
+        <is>
+          <t>Barramento 24 V (trechos internos) e saída de 12 V do T3 (1,0 A)</t>
+        </is>
+      </c>
+      <c r="F187" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-flexivel-0-75-mm-vermelho-preto","🔎 cabo flexivel 0,75 mm vermel")</f>
+        <v/>
+      </c>
+      <c r="G187" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+flexivel+0%2C75+mm+vermelho+preto","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H187" s="13" t="inlineStr"/>
+      <c r="I187" s="14" t="inlineStr"/>
+      <c r="J187" s="14">
+        <f>IF(C187*I187=0,"",C187*I187)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="5" t="n">
+        <v>166</v>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
+        <is>
+          <t>Cabo flexível 0,5 mm² (5 cores)</t>
+        </is>
+      </c>
+      <c r="C188" s="5" t="inlineStr">
+        <is>
+          <t>10 m</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
+        <is>
+          <t>750 V</t>
+        </is>
+      </c>
+      <c r="E188" s="6" t="inlineStr">
+        <is>
+          <t>5 V e derivações do 12 V auxiliar</t>
+        </is>
+      </c>
+      <c r="F188" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-flexivel-0-5-mm","🔎 cabo flexivel 0,5 mm")</f>
+        <v/>
+      </c>
+      <c r="G188" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+flexivel+0%2C5+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H188" s="8" t="inlineStr"/>
+      <c r="I188" s="9" t="inlineStr"/>
+      <c r="J188" s="9">
+        <f>IF(C188*I188=0,"",C188*I188)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="10" t="n">
+        <v>167</v>
+      </c>
+      <c r="B189" s="11" t="inlineStr">
+        <is>
+          <t>Cabo flexível 0,25 mm² (8 cores)</t>
+        </is>
+      </c>
+      <c r="C189" s="10" t="inlineStr">
+        <is>
+          <t>15 m</t>
+        </is>
+      </c>
+      <c r="D189" s="11" t="inlineStr">
+        <is>
+          <t>Sinais</t>
+        </is>
+      </c>
+      <c r="E189" s="11" t="inlineStr">
+        <is>
+          <t>Sensores, botões, comunicação</t>
+        </is>
+      </c>
+      <c r="F189" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-flexivel-0-25-mm","🔎 cabo flexivel 0,25 mm")</f>
+        <v/>
+      </c>
+      <c r="G189" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+flexivel+0%2C25+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H189" s="13" t="inlineStr"/>
+      <c r="I189" s="14" t="inlineStr"/>
+      <c r="J189" s="14">
+        <f>IF(C189*I189=0,"",C189*I189)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="5" t="n">
+        <v>168</v>
+      </c>
+      <c r="B190" s="6" t="inlineStr">
+        <is>
+          <t>Cabo par trançado blindado 2×0,25 mm²</t>
+        </is>
+      </c>
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t>2 m</t>
+        </is>
+      </c>
+      <c r="D190" s="6" t="inlineStr">
+        <is>
+          <t>Blindado, malha aterrada em um ponto</t>
+        </is>
+      </c>
+      <c r="E190" s="6" t="inlineStr">
+        <is>
+          <t>I²C e 1-Wire (trecho câmara → painel)</t>
+        </is>
+      </c>
+      <c r="F190" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-par-trancado-blindado-2-0-25-mm","🔎 cabo par trancado blindado 2")</f>
+        <v/>
+      </c>
+      <c r="G190" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+par+trancado+blindado+2+0%2C25+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H190" s="8" t="inlineStr"/>
+      <c r="I190" s="9" t="inlineStr"/>
+      <c r="J190" s="9">
+        <f>IF(C190*I190=0,"",C190*I190)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="10" t="n">
+        <v>169</v>
+      </c>
+      <c r="B191" s="11" t="inlineStr">
+        <is>
+          <t>Terminal tubular (ilhós) 0,25 / 0,5 / 1,5 mm²</t>
+        </is>
+      </c>
+      <c r="C191" s="10" t="inlineStr">
+        <is>
+          <t>1 kit</t>
+        </is>
+      </c>
+      <c r="D191" s="11" t="inlineStr">
+        <is>
+          <t>Com colarinho colorido</t>
+        </is>
+      </c>
+      <c r="E191" s="11" t="inlineStr">
+        <is>
+          <t>Obrigatório em todo borne parafuso</t>
+        </is>
+      </c>
+      <c r="F191" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/terminal-tubular-0-25-0-5-1-5-mm","🔎 terminal tubular 0,25 0,5 1,")</f>
+        <v/>
+      </c>
+      <c r="G191" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=terminal+tubular+0%2C25+0%2C5+1%2C5+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H191" s="13" t="inlineStr"/>
+      <c r="I191" s="14" t="inlineStr"/>
+      <c r="J191" s="14">
+        <f>IF(C191*I191=0,"",C191*I191)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="5" t="n">
+        <v>170</v>
+      </c>
+      <c r="B192" s="6" t="inlineStr">
+        <is>
+          <t>Alicate de crimpar terminal tubular</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D192" s="6" t="inlineStr">
+        <is>
+          <t>Tipo quadrado/hexagonal</t>
+        </is>
+      </c>
+      <c r="E192" s="6" t="inlineStr">
+        <is>
+          <t>Ferramenta</t>
+        </is>
+      </c>
+      <c r="F192" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/alicate-crimpar-terminal-tubular","🔎 alicate crimpar terminal tub")</f>
+        <v/>
+      </c>
+      <c r="G192" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=alicate+crimpar+terminal+tubular","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H192" s="8" t="inlineStr"/>
+      <c r="I192" s="9" t="inlineStr"/>
+      <c r="J192" s="9">
+        <f>IF(C192*I192=0,"",C192*I192)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="10" t="n">
+        <v>171</v>
+      </c>
+      <c r="B193" s="11" t="inlineStr">
+        <is>
+          <t>Terminal olhal M4</t>
+        </is>
+      </c>
+      <c r="C193" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D193" s="11" t="inlineStr">
+        <is>
+          <t>Amarelo/vermelho</t>
+        </is>
+      </c>
+      <c r="E193" s="11" t="inlineStr">
+        <is>
+          <t>Aterramento</t>
+        </is>
+      </c>
+      <c r="F193" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/terminal-olhal-m4","🔎 terminal olhal m4")</f>
+        <v/>
+      </c>
+      <c r="G193" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=terminal+olhal+m4","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H193" s="13" t="inlineStr"/>
+      <c r="I193" s="14" t="inlineStr"/>
+      <c r="J193" s="14">
+        <f>IF(C193*I193=0,"",C193*I193)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="5" t="n">
+        <v>172</v>
+      </c>
+      <c r="B194" s="6" t="inlineStr">
+        <is>
+          <t>Espaguete termorretrátil (kit)</t>
+        </is>
+      </c>
+      <c r="C194" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D194" s="6" t="inlineStr">
+        <is>
+          <t>Diversas bitolas</t>
+        </is>
+      </c>
+      <c r="E194" s="6" t="inlineStr">
+        <is>
+          <t>Isolação de emendas</t>
+        </is>
+      </c>
+      <c r="F194" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/espaguete-termorretratil","🔎 espaguete termorretratil")</f>
+        <v/>
+      </c>
+      <c r="G194" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=espaguete+termorretratil","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H194" s="8" t="inlineStr"/>
+      <c r="I194" s="9" t="inlineStr"/>
+      <c r="J194" s="9">
+        <f>IF(C194*I194=0,"",C194*I194)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="10" t="n">
+        <v>173</v>
+      </c>
+      <c r="B195" s="11" t="inlineStr">
+        <is>
+          <t>Abraçadeiras de nylon 100 mm</t>
+        </is>
+      </c>
+      <c r="C195" s="10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D195" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E195" s="11" t="inlineStr">
+        <is>
+          <t>Amarração</t>
+        </is>
+      </c>
+      <c r="F195" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/abracadeiras-nylon-100-mm","🔎 abracadeiras nylon 100 mm")</f>
+        <v/>
+      </c>
+      <c r="G195" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=abracadeiras+nylon+100+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H195" s="13" t="inlineStr"/>
+      <c r="I195" s="14" t="inlineStr"/>
+      <c r="J195" s="14">
+        <f>IF(C195*I195=0,"",C195*I195)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="5" t="n">
+        <v>174</v>
+      </c>
+      <c r="B196" s="6" t="inlineStr">
         <is>
           <t>Anilhas de identificação de cabo</t>
         </is>
       </c>
-      <c r="C186" s="5" t="inlineStr">
+      <c r="C196" s="5" t="inlineStr">
         <is>
           <t>1 kit</t>
         </is>
       </c>
-      <c r="D186" s="6" t="inlineStr">
+      <c r="D196" s="6" t="inlineStr">
         <is>
           <t>Numeradas 0–9</t>
         </is>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="E196" s="6" t="inlineStr">
         <is>
           <t>Identificação (norma de painel)</t>
         </is>
       </c>
-      <c r="F186" s="7" t="inlineStr"/>
-      <c r="G186" s="8" t="inlineStr"/>
-      <c r="H186" s="8">
-        <f>IF(C186*G186=0,"",C186*G186)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="9" t="n">
-        <v>166</v>
-      </c>
-      <c r="B187" s="10" t="inlineStr">
+      <c r="F196" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/anilhas-identificacao-cabo","🔎 anilhas identificacao cabo")</f>
+        <v/>
+      </c>
+      <c r="G196" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=anilhas+identificacao+cabo","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H196" s="8" t="inlineStr"/>
+      <c r="I196" s="9" t="inlineStr"/>
+      <c r="J196" s="9">
+        <f>IF(C196*I196=0,"",C196*I196)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="10" t="n">
+        <v>175</v>
+      </c>
+      <c r="B197" s="11" t="inlineStr">
         <is>
           <t>Espiral organizador Ø 8 mm</t>
         </is>
       </c>
-      <c r="C187" s="9" t="inlineStr">
+      <c r="C197" s="10" t="inlineStr">
         <is>
           <t>2 m</t>
         </is>
       </c>
-      <c r="D187" s="10" t="inlineStr">
+      <c r="D197" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E187" s="10" t="inlineStr">
+      <c r="E197" s="11" t="inlineStr">
         <is>
           <t>Chicote painel → câmara</t>
         </is>
       </c>
-      <c r="F187" s="11" t="inlineStr"/>
-      <c r="G187" s="12" t="inlineStr"/>
-      <c r="H187" s="12">
-        <f>IF(C187*G187=0,"",C187*G187)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="189">
-      <c r="F189" s="13" t="inlineStr">
+      <c r="F197" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/espiral-organizador-8-mm","🔎 espiral organizador 8 mm")</f>
+        <v/>
+      </c>
+      <c r="G197" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=espiral+organizador+8+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H197" s="13" t="inlineStr"/>
+      <c r="I197" s="14" t="inlineStr"/>
+      <c r="J197" s="14">
+        <f>IF(C197*I197=0,"",C197*I197)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="H199" s="15" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="H189" s="14">
-        <f>SUM(H5:H187)</f>
+      <c r="J199" s="16">
+        <f>SUM(J5:J197)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H187"/>
-  <mergeCells count="19">
-    <mergeCell ref="A142:H142"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A88:H88"/>
-    <mergeCell ref="A174:H174"/>
-    <mergeCell ref="A128:H128"/>
-    <mergeCell ref="A164:H164"/>
-    <mergeCell ref="A158:H158"/>
-    <mergeCell ref="A74:H74"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A104:H104"/>
-    <mergeCell ref="A151:H151"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A38:H38"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A44:H44"/>
-    <mergeCell ref="A93:H93"/>
-    <mergeCell ref="A58:H58"/>
+  <autoFilter ref="A4:J197"/>
+  <mergeCells count="20">
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A184:J184"/>
+    <mergeCell ref="A38:J38"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A44:J44"/>
+    <mergeCell ref="A93:J93"/>
+    <mergeCell ref="A58:J58"/>
+    <mergeCell ref="A142:J142"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A88:J88"/>
+    <mergeCell ref="A174:J174"/>
+    <mergeCell ref="A128:J128"/>
+    <mergeCell ref="A164:J164"/>
+    <mergeCell ref="A74:J74"/>
+    <mergeCell ref="A158:J158"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A104:J104"/>
+    <mergeCell ref="A151:J151"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5407,161 +7073,161 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>ORDEM DE CONSTRUÇÃO — 5 camadas</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>Camada</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>Documentos</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>Critério de aceitação</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>CAMADA 0</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>Fundamentos</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>Visão geral · Arquitetura de energia · BOM</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>Entregável: BOM fechada e cálculos feitos</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>CAMADA 1</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>Maquete</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>Base e chão de fábrica · Subestação e postes · Câmara térmica</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>Entregável: cenário pronto, sem eletrônica</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>CAMADA 2</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>Painel</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>Dimensionamento · Layout · Furação · Fixação nos trilhos</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>Entregável: painel montado, sem um fio ligado</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>CAMADA 3</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>Elétrica</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>Força e distribuição · Comando e proteções · Sinais e sensores</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>Entregável: energizado e medido, sem firmware</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>CAMADA 4</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Programação</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>Firmware Arduino · ESP32, IHM e IoT</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>Entregável: software gravado e testado em bancada</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>CAMADA 5</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>Integração</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>Montagem final · Comissionamento · Ensaios</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>Entregável: projeto funcionando e documentado</t>
         </is>
@@ -5589,295 +7255,295 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>NÚMEROS DO PROJETO</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>Arquitetura de energia</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>Potência em 24 V — carga térmica sem conversor</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Tensão de entrada</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>127 V CA</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Barramento de distribuição</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>24 V CC (SELV)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Potência instalada (fonte)</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>240 W · 10 A</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Consumo calculado</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>≈ 166 W · 6,9 A @ 24 V</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Folga da fonte</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>1,44× (44 %) — a fonte de 150 W NÃO atende</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>Corrente CA de entrada</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>2,37 A</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Queda de tensão na linha dos postes</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>0,21 V (0,86 %)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>Conversores</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>2 × LM2596 com display (T2 e T3) · P1 é derivação direta</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>Tensões derivadas</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>24,0 V potência (direto) · 12,0 V auxiliar · 5,10 V comando · 3,3 V ESP32</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>Fusíveis dos ramais</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>F1 = 10 A · F2 = 2 A · F3 = 2 A (sem F4/F5, sem crowbar)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>Níveis de proteção</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>5 (do disjuntor ao intertravamento por software)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>Volume útil da câmara</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>5,0 litros (200 × 100 × 250 mm)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>Carga térmica calculada</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>≈ 9,5 W</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>Refrigeração</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>2 × TEC1-12706 EM SÉRIE · 24 V · 6,0 A · 144 W</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="A18" s="23" t="inlineStr">
         <is>
           <t>Capacidade das Peltier a ΔT = 20 K</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>≈ 60 W (margem de 6,3×)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>Dissipação no lado quente</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>≈ 200 W — 2 conjuntos dissipador + cooler 80 mm</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="inlineStr">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>Aquecimento</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>PTC cerâmico de 24 V · 60 W · 2,5 A</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>Isolamento</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>XPS 30 mm + barreira de vapor · U = 0,86 W/m²·K</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="21" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>Porta</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>Dupla · U = 2,42 W/m²·K (não condensa)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>Base da maquete</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>1500 × 500 mm · escala cenográfica 1:50</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>Painel</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>400 × 500 × 200 mm · 3 trilhos DIN</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>Componentes discretos</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>6 + 1 CI ULN2803 na PI-1 · 2 nos BTS7960 · 4 nos postes da maquete</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="21" t="inlineStr">
+      <c r="A26" s="23" t="inlineStr">
         <is>
           <t>Sinalização</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="24" t="inlineStr">
         <is>
           <t>4 sinaleiros 22 mm de 24 V (via ULN2803) · 4 LEDs brancos de 5 V na maquete</t>
         </is>

--- a/BOM_Projeto_Integrador.xlsx
+++ b/BOM_Projeto_Integrador.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Dados do Projeto" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lista de Compras'!$A$4:$J$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lista de Compras'!$A$4:$K$197</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,11 @@
     </font>
     <font>
       <color rgb="000563C1"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <color rgb="00C55A11"/>
       <sz val="9"/>
       <u val="single"/>
     </font>
@@ -129,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -173,25 +178,31 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -562,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J199"/>
+  <dimension ref="A1:K199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -570,11 +581,12 @@
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="56" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -587,7 +599,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Lista de materiais · gerada de 03_lista_materiais.md em 13/08/2026 23:11 · arquitetura 127 V CA → 24 V CC → 12 / 5 / 3,3 V</t>
+          <t>Lista de materiais · gerada de 03_lista_materiais.md em 14/08/2026 07:42 · arquitetura 127 V CA → 24 V CC → 12 / 5 / 3,3 V</t>
         </is>
       </c>
     </row>
@@ -619,25 +631,30 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>🔎 Buscar no Mercado Livre</t>
+          <t>🔎 Mercado Livre</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>🔎 Buscar na Amazon</t>
+          <t>🔎 Amazon BR</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
+          <t>🌏 AliExpress (importar)</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>Link escolhido (cole aqui)</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Preço unit. (R$)</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Total (R$)</t>
         </is>
@@ -683,9 +700,10 @@
         <v/>
       </c>
       <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="9" t="inlineStr"/>
-      <c r="J6" s="9">
-        <f>IF(C6*I6=0,"",C6*I6)</f>
+      <c r="I6" s="8" t="inlineStr"/>
+      <c r="J6" s="9" t="inlineStr"/>
+      <c r="K6" s="9">
+        <f>IF(C6*J6=0,"",C6*J6)</f>
         <v/>
       </c>
     </row>
@@ -722,9 +740,10 @@
         <v/>
       </c>
       <c r="H7" s="13" t="inlineStr"/>
-      <c r="I7" s="14" t="inlineStr"/>
-      <c r="J7" s="14">
-        <f>IF(C7*I7=0,"",C7*I7)</f>
+      <c r="I7" s="13" t="inlineStr"/>
+      <c r="J7" s="14" t="inlineStr"/>
+      <c r="K7" s="14">
+        <f>IF(C7*J7=0,"",C7*J7)</f>
         <v/>
       </c>
     </row>
@@ -761,9 +780,10 @@
         <v/>
       </c>
       <c r="H8" s="8" t="inlineStr"/>
-      <c r="I8" s="9" t="inlineStr"/>
-      <c r="J8" s="9">
-        <f>IF(C8*I8=0,"",C8*I8)</f>
+      <c r="I8" s="8" t="inlineStr"/>
+      <c r="J8" s="9" t="inlineStr"/>
+      <c r="K8" s="9">
+        <f>IF(C8*J8=0,"",C8*J8)</f>
         <v/>
       </c>
     </row>
@@ -800,9 +820,10 @@
         <v/>
       </c>
       <c r="H9" s="13" t="inlineStr"/>
-      <c r="I9" s="14" t="inlineStr"/>
-      <c r="J9" s="14">
-        <f>IF(C9*I9=0,"",C9*I9)</f>
+      <c r="I9" s="13" t="inlineStr"/>
+      <c r="J9" s="14" t="inlineStr"/>
+      <c r="K9" s="14">
+        <f>IF(C9*J9=0,"",C9*J9)</f>
         <v/>
       </c>
     </row>
@@ -839,9 +860,10 @@
         <v/>
       </c>
       <c r="H10" s="8" t="inlineStr"/>
-      <c r="I10" s="9" t="inlineStr"/>
-      <c r="J10" s="9">
-        <f>IF(C10*I10=0,"",C10*I10)</f>
+      <c r="I10" s="8" t="inlineStr"/>
+      <c r="J10" s="9" t="inlineStr"/>
+      <c r="K10" s="9">
+        <f>IF(C10*J10=0,"",C10*J10)</f>
         <v/>
       </c>
     </row>
@@ -878,9 +900,10 @@
         <v/>
       </c>
       <c r="H11" s="13" t="inlineStr"/>
-      <c r="I11" s="14" t="inlineStr"/>
-      <c r="J11" s="14">
-        <f>IF(C11*I11=0,"",C11*I11)</f>
+      <c r="I11" s="13" t="inlineStr"/>
+      <c r="J11" s="14" t="inlineStr"/>
+      <c r="K11" s="14">
+        <f>IF(C11*J11=0,"",C11*J11)</f>
         <v/>
       </c>
     </row>
@@ -916,10 +939,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=cooler+60mm+24v","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H12" s="8" t="inlineStr"/>
-      <c r="I12" s="9" t="inlineStr"/>
-      <c r="J12" s="9">
-        <f>IF(C12*I12=0,"",C12*I12)</f>
+      <c r="H12" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-60mm-fan-24v-dc.html","🌏 60mm fan 24V DC")</f>
+        <v/>
+      </c>
+      <c r="I12" s="8" t="inlineStr"/>
+      <c r="J12" s="9" t="inlineStr"/>
+      <c r="K12" s="9">
+        <f>IF(C12*J12=0,"",C12*J12)</f>
         <v/>
       </c>
     </row>
@@ -956,9 +983,10 @@
         <v/>
       </c>
       <c r="H13" s="13" t="inlineStr"/>
-      <c r="I13" s="14" t="inlineStr"/>
-      <c r="J13" s="14">
-        <f>IF(C13*I13=0,"",C13*I13)</f>
+      <c r="I13" s="13" t="inlineStr"/>
+      <c r="J13" s="14" t="inlineStr"/>
+      <c r="K13" s="14">
+        <f>IF(C13*J13=0,"",C13*J13)</f>
         <v/>
       </c>
     </row>
@@ -1001,14 +1029,18 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=kit+2+modulo+lm2596+display","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H15" s="13" t="inlineStr">
+      <c r="H15" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-lm2596-buck-converter-voltmeter-display.html","🌏 LM2596 buck converter volt")</f>
+        <v/>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
         <is>
           <t>Mercado Livre</t>
         </is>
       </c>
-      <c r="I15" s="14" t="inlineStr"/>
-      <c r="J15" s="14">
-        <f>IF(C15*I15=0,"",C15*I15)</f>
+      <c r="J15" s="14" t="inlineStr"/>
+      <c r="K15" s="14">
+        <f>IF(C15*J15=0,"",C15*J15)</f>
         <v/>
       </c>
     </row>
@@ -1039,9 +1071,10 @@
       <c r="F16" s="8" t="inlineStr"/>
       <c r="G16" s="8" t="inlineStr"/>
       <c r="H16" s="8" t="inlineStr"/>
-      <c r="I16" s="9" t="inlineStr"/>
-      <c r="J16" s="9">
-        <f>IF(C16*I16=0,"",C16*I16)</f>
+      <c r="I16" s="8" t="inlineStr"/>
+      <c r="J16" s="9" t="inlineStr"/>
+      <c r="K16" s="9">
+        <f>IF(C16*J16=0,"",C16*J16)</f>
         <v/>
       </c>
     </row>
@@ -1072,9 +1105,10 @@
       <c r="F17" s="13" t="inlineStr"/>
       <c r="G17" s="13" t="inlineStr"/>
       <c r="H17" s="13" t="inlineStr"/>
-      <c r="I17" s="14" t="inlineStr"/>
-      <c r="J17" s="14">
-        <f>IF(C17*I17=0,"",C17*I17)</f>
+      <c r="I17" s="13" t="inlineStr"/>
+      <c r="J17" s="14" t="inlineStr"/>
+      <c r="K17" s="14">
+        <f>IF(C17*J17=0,"",C17*J17)</f>
         <v/>
       </c>
     </row>
@@ -1110,10 +1144,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=kit+lm2596+reserva","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H18" s="8" t="inlineStr"/>
-      <c r="I18" s="9" t="inlineStr"/>
-      <c r="J18" s="9">
-        <f>IF(C18*I18=0,"",C18*I18)</f>
+      <c r="H18" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-lm2596-buck-converter-voltmeter-display.html","🌏 LM2596 buck converter volt")</f>
+        <v/>
+      </c>
+      <c r="I18" s="8" t="inlineStr"/>
+      <c r="J18" s="9" t="inlineStr"/>
+      <c r="K18" s="9">
+        <f>IF(C18*J18=0,"",C18*J18)</f>
         <v/>
       </c>
     </row>
@@ -1149,10 +1187,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=dissipador+aluminio+20+15+10+mm","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H19" s="13" t="inlineStr"/>
-      <c r="I19" s="14" t="inlineStr"/>
-      <c r="J19" s="14">
-        <f>IF(C19*I19=0,"",C19*I19)</f>
+      <c r="H19" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-aluminum-heatsink-small.html","🌏 aluminum heatsink small")</f>
+        <v/>
+      </c>
+      <c r="I19" s="13" t="inlineStr"/>
+      <c r="J19" s="14" t="inlineStr"/>
+      <c r="K19" s="14">
+        <f>IF(C19*J19=0,"",C19*J19)</f>
         <v/>
       </c>
     </row>
@@ -1188,10 +1230,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+termica+dupla+face","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H20" s="8" t="inlineStr"/>
-      <c r="I20" s="9" t="inlineStr"/>
-      <c r="J20" s="9">
-        <f>IF(C20*I20=0,"",C20*I20)</f>
+      <c r="H20" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-thermal-adhesive-tape-double-sided.html","🌏 thermal adhesive tape doub")</f>
+        <v/>
+      </c>
+      <c r="I20" s="8" t="inlineStr"/>
+      <c r="J20" s="9" t="inlineStr"/>
+      <c r="K20" s="9">
+        <f>IF(C20*J20=0,"",C20*J20)</f>
         <v/>
       </c>
     </row>
@@ -1228,9 +1274,10 @@
         <v/>
       </c>
       <c r="H21" s="13" t="inlineStr"/>
-      <c r="I21" s="14" t="inlineStr"/>
-      <c r="J21" s="14">
-        <f>IF(C21*I21=0,"",C21*I21)</f>
+      <c r="I21" s="13" t="inlineStr"/>
+      <c r="J21" s="14" t="inlineStr"/>
+      <c r="K21" s="14">
+        <f>IF(C21*J21=0,"",C21*J21)</f>
         <v/>
       </c>
     </row>
@@ -1266,10 +1313,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=voltimetro+amperimetro+digital+3+fios","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H22" s="8" t="inlineStr"/>
-      <c r="I22" s="9" t="inlineStr"/>
-      <c r="J22" s="9">
-        <f>IF(C22*I22=0,"",C22*I22)</f>
+      <c r="H22" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-dc-voltmeter-ammeter-100v-10a-digital.html","🌏 DC voltmeter ammeter 100V ")</f>
+        <v/>
+      </c>
+      <c r="I22" s="8" t="inlineStr"/>
+      <c r="J22" s="9" t="inlineStr"/>
+      <c r="K22" s="9">
+        <f>IF(C22*J22=0,"",C22*J22)</f>
         <v/>
       </c>
     </row>
@@ -1313,9 +1364,10 @@
         <v/>
       </c>
       <c r="H24" s="8" t="inlineStr"/>
-      <c r="I24" s="9" t="inlineStr"/>
-      <c r="J24" s="9">
-        <f>IF(C24*I24=0,"",C24*I24)</f>
+      <c r="I24" s="8" t="inlineStr"/>
+      <c r="J24" s="9" t="inlineStr"/>
+      <c r="K24" s="9">
+        <f>IF(C24*J24=0,"",C24*J24)</f>
         <v/>
       </c>
     </row>
@@ -1352,9 +1404,10 @@
         <v/>
       </c>
       <c r="H25" s="13" t="inlineStr"/>
-      <c r="I25" s="14" t="inlineStr"/>
-      <c r="J25" s="14">
-        <f>IF(C25*I25=0,"",C25*I25)</f>
+      <c r="I25" s="13" t="inlineStr"/>
+      <c r="J25" s="14" t="inlineStr"/>
+      <c r="K25" s="14">
+        <f>IF(C25*J25=0,"",C25*J25)</f>
         <v/>
       </c>
     </row>
@@ -1391,9 +1444,10 @@
         <v/>
       </c>
       <c r="H26" s="8" t="inlineStr"/>
-      <c r="I26" s="9" t="inlineStr"/>
-      <c r="J26" s="9">
-        <f>IF(C26*I26=0,"",C26*I26)</f>
+      <c r="I26" s="8" t="inlineStr"/>
+      <c r="J26" s="9" t="inlineStr"/>
+      <c r="K26" s="9">
+        <f>IF(C26*J26=0,"",C26*J26)</f>
         <v/>
       </c>
     </row>
@@ -1430,9 +1484,10 @@
         <v/>
       </c>
       <c r="H27" s="13" t="inlineStr"/>
-      <c r="I27" s="14" t="inlineStr"/>
-      <c r="J27" s="14">
-        <f>IF(C27*I27=0,"",C27*I27)</f>
+      <c r="I27" s="13" t="inlineStr"/>
+      <c r="J27" s="14" t="inlineStr"/>
+      <c r="K27" s="14">
+        <f>IF(C27*J27=0,"",C27*J27)</f>
         <v/>
       </c>
     </row>
@@ -1472,9 +1527,10 @@
         <v/>
       </c>
       <c r="H29" s="13" t="inlineStr"/>
-      <c r="I29" s="14" t="inlineStr"/>
-      <c r="J29" s="14">
-        <f>IF(C29*I29=0,"",C29*I29)</f>
+      <c r="I29" s="13" t="inlineStr"/>
+      <c r="J29" s="14" t="inlineStr"/>
+      <c r="K29" s="14">
+        <f>IF(C29*J29=0,"",C29*J29)</f>
         <v/>
       </c>
     </row>
@@ -1507,9 +1563,10 @@
         <v/>
       </c>
       <c r="H30" s="8" t="inlineStr"/>
-      <c r="I30" s="9" t="inlineStr"/>
-      <c r="J30" s="9">
-        <f>IF(C30*I30=0,"",C30*I30)</f>
+      <c r="I30" s="8" t="inlineStr"/>
+      <c r="J30" s="9" t="inlineStr"/>
+      <c r="K30" s="9">
+        <f>IF(C30*J30=0,"",C30*J30)</f>
         <v/>
       </c>
     </row>
@@ -1542,9 +1599,10 @@
         <v/>
       </c>
       <c r="H31" s="13" t="inlineStr"/>
-      <c r="I31" s="14" t="inlineStr"/>
-      <c r="J31" s="14">
-        <f>IF(C31*I31=0,"",C31*I31)</f>
+      <c r="I31" s="13" t="inlineStr"/>
+      <c r="J31" s="14" t="inlineStr"/>
+      <c r="K31" s="14">
+        <f>IF(C31*J31=0,"",C31*J31)</f>
         <v/>
       </c>
     </row>
@@ -1577,9 +1635,10 @@
         <v/>
       </c>
       <c r="H32" s="8" t="inlineStr"/>
-      <c r="I32" s="9" t="inlineStr"/>
-      <c r="J32" s="9">
-        <f>IF(C32*I32=0,"",C32*I32)</f>
+      <c r="I32" s="8" t="inlineStr"/>
+      <c r="J32" s="9" t="inlineStr"/>
+      <c r="K32" s="9">
+        <f>IF(C32*J32=0,"",C32*J32)</f>
         <v/>
       </c>
     </row>
@@ -1611,10 +1670,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=conector+circular+gx16+8+pinos","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H33" s="13" t="inlineStr"/>
-      <c r="I33" s="14" t="inlineStr"/>
-      <c r="J33" s="14">
-        <f>IF(C33*I33=0,"",C33*I33)</f>
+      <c r="H33" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-gx16-8-pin-aviation-connector.html","🌏 GX16 8 pin aviation connec")</f>
+        <v/>
+      </c>
+      <c r="I33" s="13" t="inlineStr"/>
+      <c r="J33" s="14" t="inlineStr"/>
+      <c r="K33" s="14">
+        <f>IF(C33*J33=0,"",C33*J33)</f>
         <v/>
       </c>
     </row>
@@ -1647,9 +1710,10 @@
         <v/>
       </c>
       <c r="H34" s="8" t="inlineStr"/>
-      <c r="I34" s="9" t="inlineStr"/>
-      <c r="J34" s="9">
-        <f>IF(C34*I34=0,"",C34*I34)</f>
+      <c r="I34" s="8" t="inlineStr"/>
+      <c r="J34" s="9" t="inlineStr"/>
+      <c r="K34" s="9">
+        <f>IF(C34*J34=0,"",C34*J34)</f>
         <v/>
       </c>
     </row>
@@ -1682,9 +1746,10 @@
         <v/>
       </c>
       <c r="H35" s="13" t="inlineStr"/>
-      <c r="I35" s="14" t="inlineStr"/>
-      <c r="J35" s="14">
-        <f>IF(C35*I35=0,"",C35*I35)</f>
+      <c r="I35" s="13" t="inlineStr"/>
+      <c r="J35" s="14" t="inlineStr"/>
+      <c r="K35" s="14">
+        <f>IF(C35*J35=0,"",C35*J35)</f>
         <v/>
       </c>
     </row>
@@ -1717,9 +1782,10 @@
         <v/>
       </c>
       <c r="H36" s="8" t="inlineStr"/>
-      <c r="I36" s="9" t="inlineStr"/>
-      <c r="J36" s="9">
-        <f>IF(C36*I36=0,"",C36*I36)</f>
+      <c r="I36" s="8" t="inlineStr"/>
+      <c r="J36" s="9" t="inlineStr"/>
+      <c r="K36" s="9">
+        <f>IF(C36*J36=0,"",C36*J36)</f>
         <v/>
       </c>
     </row>
@@ -1752,9 +1818,10 @@
         <v/>
       </c>
       <c r="H37" s="13" t="inlineStr"/>
-      <c r="I37" s="14" t="inlineStr"/>
-      <c r="J37" s="14">
-        <f>IF(C37*I37=0,"",C37*I37)</f>
+      <c r="I37" s="13" t="inlineStr"/>
+      <c r="J37" s="14" t="inlineStr"/>
+      <c r="K37" s="14">
+        <f>IF(C37*J37=0,"",C37*J37)</f>
         <v/>
       </c>
     </row>
@@ -1794,9 +1861,10 @@
         <v/>
       </c>
       <c r="H39" s="13" t="inlineStr"/>
-      <c r="I39" s="14" t="inlineStr"/>
-      <c r="J39" s="14">
-        <f>IF(C39*I39=0,"",C39*I39)</f>
+      <c r="I39" s="13" t="inlineStr"/>
+      <c r="J39" s="14" t="inlineStr"/>
+      <c r="K39" s="14">
+        <f>IF(C39*J39=0,"",C39*J39)</f>
         <v/>
       </c>
     </row>
@@ -1829,9 +1897,10 @@
         <v/>
       </c>
       <c r="H40" s="8" t="inlineStr"/>
-      <c r="I40" s="9" t="inlineStr"/>
-      <c r="J40" s="9">
-        <f>IF(C40*I40=0,"",C40*I40)</f>
+      <c r="I40" s="8" t="inlineStr"/>
+      <c r="J40" s="9" t="inlineStr"/>
+      <c r="K40" s="9">
+        <f>IF(C40*J40=0,"",C40*J40)</f>
         <v/>
       </c>
     </row>
@@ -1864,9 +1933,10 @@
         <v/>
       </c>
       <c r="H41" s="13" t="inlineStr"/>
-      <c r="I41" s="14" t="inlineStr"/>
-      <c r="J41" s="14">
-        <f>IF(C41*I41=0,"",C41*I41)</f>
+      <c r="I41" s="13" t="inlineStr"/>
+      <c r="J41" s="14" t="inlineStr"/>
+      <c r="K41" s="14">
+        <f>IF(C41*J41=0,"",C41*J41)</f>
         <v/>
       </c>
     </row>
@@ -1899,9 +1969,10 @@
         <v/>
       </c>
       <c r="H42" s="8" t="inlineStr"/>
-      <c r="I42" s="9" t="inlineStr"/>
-      <c r="J42" s="9">
-        <f>IF(C42*I42=0,"",C42*I42)</f>
+      <c r="I42" s="8" t="inlineStr"/>
+      <c r="J42" s="9" t="inlineStr"/>
+      <c r="K42" s="9">
+        <f>IF(C42*J42=0,"",C42*J42)</f>
         <v/>
       </c>
     </row>
@@ -1934,9 +2005,10 @@
         <v/>
       </c>
       <c r="H43" s="13" t="inlineStr"/>
-      <c r="I43" s="14" t="inlineStr"/>
-      <c r="J43" s="14">
-        <f>IF(C43*I43=0,"",C43*I43)</f>
+      <c r="I43" s="13" t="inlineStr"/>
+      <c r="J43" s="14" t="inlineStr"/>
+      <c r="K43" s="14">
+        <f>IF(C43*J43=0,"",C43*J43)</f>
         <v/>
       </c>
     </row>
@@ -1976,9 +2048,10 @@
         <v/>
       </c>
       <c r="H45" s="13" t="inlineStr"/>
-      <c r="I45" s="14" t="inlineStr"/>
-      <c r="J45" s="14">
-        <f>IF(C45*I45=0,"",C45*I45)</f>
+      <c r="I45" s="13" t="inlineStr"/>
+      <c r="J45" s="14" t="inlineStr"/>
+      <c r="K45" s="14">
+        <f>IF(C45*J45=0,"",C45*J45)</f>
         <v/>
       </c>
     </row>
@@ -2011,9 +2084,10 @@
         <v/>
       </c>
       <c r="H46" s="8" t="inlineStr"/>
-      <c r="I46" s="9" t="inlineStr"/>
-      <c r="J46" s="9">
-        <f>IF(C46*I46=0,"",C46*I46)</f>
+      <c r="I46" s="8" t="inlineStr"/>
+      <c r="J46" s="9" t="inlineStr"/>
+      <c r="K46" s="9">
+        <f>IF(C46*J46=0,"",C46*J46)</f>
         <v/>
       </c>
     </row>
@@ -2046,9 +2120,10 @@
         <v/>
       </c>
       <c r="H47" s="13" t="inlineStr"/>
-      <c r="I47" s="14" t="inlineStr"/>
-      <c r="J47" s="14">
-        <f>IF(C47*I47=0,"",C47*I47)</f>
+      <c r="I47" s="13" t="inlineStr"/>
+      <c r="J47" s="14" t="inlineStr"/>
+      <c r="K47" s="14">
+        <f>IF(C47*J47=0,"",C47*J47)</f>
         <v/>
       </c>
     </row>
@@ -2081,9 +2156,10 @@
         <v/>
       </c>
       <c r="H48" s="8" t="inlineStr"/>
-      <c r="I48" s="9" t="inlineStr"/>
-      <c r="J48" s="9">
-        <f>IF(C48*I48=0,"",C48*I48)</f>
+      <c r="I48" s="8" t="inlineStr"/>
+      <c r="J48" s="9" t="inlineStr"/>
+      <c r="K48" s="9">
+        <f>IF(C48*J48=0,"",C48*J48)</f>
         <v/>
       </c>
     </row>
@@ -2116,9 +2192,10 @@
         <v/>
       </c>
       <c r="H49" s="13" t="inlineStr"/>
-      <c r="I49" s="14" t="inlineStr"/>
-      <c r="J49" s="14">
-        <f>IF(C49*I49=0,"",C49*I49)</f>
+      <c r="I49" s="13" t="inlineStr"/>
+      <c r="J49" s="14" t="inlineStr"/>
+      <c r="K49" s="14">
+        <f>IF(C49*J49=0,"",C49*J49)</f>
         <v/>
       </c>
     </row>
@@ -2151,9 +2228,10 @@
         <v/>
       </c>
       <c r="H50" s="8" t="inlineStr"/>
-      <c r="I50" s="9" t="inlineStr"/>
-      <c r="J50" s="9">
-        <f>IF(C50*I50=0,"",C50*I50)</f>
+      <c r="I50" s="8" t="inlineStr"/>
+      <c r="J50" s="9" t="inlineStr"/>
+      <c r="K50" s="9">
+        <f>IF(C50*J50=0,"",C50*J50)</f>
         <v/>
       </c>
     </row>
@@ -2186,9 +2264,10 @@
         <v/>
       </c>
       <c r="H51" s="13" t="inlineStr"/>
-      <c r="I51" s="14" t="inlineStr"/>
-      <c r="J51" s="14">
-        <f>IF(C51*I51=0,"",C51*I51)</f>
+      <c r="I51" s="13" t="inlineStr"/>
+      <c r="J51" s="14" t="inlineStr"/>
+      <c r="K51" s="14">
+        <f>IF(C51*J51=0,"",C51*J51)</f>
         <v/>
       </c>
     </row>
@@ -2221,9 +2300,10 @@
         <v/>
       </c>
       <c r="H52" s="8" t="inlineStr"/>
-      <c r="I52" s="9" t="inlineStr"/>
-      <c r="J52" s="9">
-        <f>IF(C52*I52=0,"",C52*I52)</f>
+      <c r="I52" s="8" t="inlineStr"/>
+      <c r="J52" s="9" t="inlineStr"/>
+      <c r="K52" s="9">
+        <f>IF(C52*J52=0,"",C52*J52)</f>
         <v/>
       </c>
     </row>
@@ -2256,9 +2336,10 @@
         <v/>
       </c>
       <c r="H53" s="13" t="inlineStr"/>
-      <c r="I53" s="14" t="inlineStr"/>
-      <c r="J53" s="14">
-        <f>IF(C53*I53=0,"",C53*I53)</f>
+      <c r="I53" s="13" t="inlineStr"/>
+      <c r="J53" s="14" t="inlineStr"/>
+      <c r="K53" s="14">
+        <f>IF(C53*J53=0,"",C53*J53)</f>
         <v/>
       </c>
     </row>
@@ -2291,9 +2372,10 @@
         <v/>
       </c>
       <c r="H54" s="8" t="inlineStr"/>
-      <c r="I54" s="9" t="inlineStr"/>
-      <c r="J54" s="9">
-        <f>IF(C54*I54=0,"",C54*I54)</f>
+      <c r="I54" s="8" t="inlineStr"/>
+      <c r="J54" s="9" t="inlineStr"/>
+      <c r="K54" s="9">
+        <f>IF(C54*J54=0,"",C54*J54)</f>
         <v/>
       </c>
     </row>
@@ -2326,9 +2408,10 @@
         <v/>
       </c>
       <c r="H55" s="13" t="inlineStr"/>
-      <c r="I55" s="14" t="inlineStr"/>
-      <c r="J55" s="14">
-        <f>IF(C55*I55=0,"",C55*I55)</f>
+      <c r="I55" s="13" t="inlineStr"/>
+      <c r="J55" s="14" t="inlineStr"/>
+      <c r="K55" s="14">
+        <f>IF(C55*J55=0,"",C55*J55)</f>
         <v/>
       </c>
     </row>
@@ -2361,9 +2444,10 @@
         <v/>
       </c>
       <c r="H56" s="8" t="inlineStr"/>
-      <c r="I56" s="9" t="inlineStr"/>
-      <c r="J56" s="9">
-        <f>IF(C56*I56=0,"",C56*I56)</f>
+      <c r="I56" s="8" t="inlineStr"/>
+      <c r="J56" s="9" t="inlineStr"/>
+      <c r="K56" s="9">
+        <f>IF(C56*J56=0,"",C56*J56)</f>
         <v/>
       </c>
     </row>
@@ -2396,9 +2480,10 @@
         <v/>
       </c>
       <c r="H57" s="13" t="inlineStr"/>
-      <c r="I57" s="14" t="inlineStr"/>
-      <c r="J57" s="14">
-        <f>IF(C57*I57=0,"",C57*I57)</f>
+      <c r="I57" s="13" t="inlineStr"/>
+      <c r="J57" s="14" t="inlineStr"/>
+      <c r="K57" s="14">
+        <f>IF(C57*J57=0,"",C57*J57)</f>
         <v/>
       </c>
     </row>
@@ -2438,9 +2523,10 @@
         <v/>
       </c>
       <c r="H59" s="13" t="inlineStr"/>
-      <c r="I59" s="14" t="inlineStr"/>
-      <c r="J59" s="14">
-        <f>IF(C59*I59=0,"",C59*I59)</f>
+      <c r="I59" s="13" t="inlineStr"/>
+      <c r="J59" s="14" t="inlineStr"/>
+      <c r="K59" s="14">
+        <f>IF(C59*J59=0,"",C59*J59)</f>
         <v/>
       </c>
     </row>
@@ -2473,9 +2559,10 @@
         <v/>
       </c>
       <c r="H60" s="8" t="inlineStr"/>
-      <c r="I60" s="9" t="inlineStr"/>
-      <c r="J60" s="9">
-        <f>IF(C60*I60=0,"",C60*I60)</f>
+      <c r="I60" s="8" t="inlineStr"/>
+      <c r="J60" s="9" t="inlineStr"/>
+      <c r="K60" s="9">
+        <f>IF(C60*J60=0,"",C60*J60)</f>
         <v/>
       </c>
     </row>
@@ -2508,9 +2595,10 @@
         <v/>
       </c>
       <c r="H61" s="13" t="inlineStr"/>
-      <c r="I61" s="14" t="inlineStr"/>
-      <c r="J61" s="14">
-        <f>IF(C61*I61=0,"",C61*I61)</f>
+      <c r="I61" s="13" t="inlineStr"/>
+      <c r="J61" s="14" t="inlineStr"/>
+      <c r="K61" s="14">
+        <f>IF(C61*J61=0,"",C61*J61)</f>
         <v/>
       </c>
     </row>
@@ -2542,10 +2630,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=led+3+mm+branco+quente","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H62" s="8" t="inlineStr"/>
-      <c r="I62" s="9" t="inlineStr"/>
-      <c r="J62" s="9">
-        <f>IF(C62*I62=0,"",C62*I62)</f>
+      <c r="H62" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-3mm-warm-white-led.html","🌏 3mm warm white LED")</f>
+        <v/>
+      </c>
+      <c r="I62" s="8" t="inlineStr"/>
+      <c r="J62" s="9" t="inlineStr"/>
+      <c r="K62" s="9">
+        <f>IF(C62*J62=0,"",C62*J62)</f>
         <v/>
       </c>
     </row>
@@ -2577,10 +2669,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+220+1+4+w","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H63" s="13" t="inlineStr"/>
-      <c r="I63" s="14" t="inlineStr"/>
-      <c r="J63" s="14">
-        <f>IF(C63*I63=0,"",C63*I63)</f>
+      <c r="H63" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
+        <v/>
+      </c>
+      <c r="I63" s="13" t="inlineStr"/>
+      <c r="J63" s="14" t="inlineStr"/>
+      <c r="K63" s="14">
+        <f>IF(C63*J63=0,"",C63*J63)</f>
         <v/>
       </c>
     </row>
@@ -2613,9 +2709,10 @@
         <v/>
       </c>
       <c r="H64" s="8" t="inlineStr"/>
-      <c r="I64" s="9" t="inlineStr"/>
-      <c r="J64" s="9">
-        <f>IF(C64*I64=0,"",C64*I64)</f>
+      <c r="I64" s="8" t="inlineStr"/>
+      <c r="J64" s="9" t="inlineStr"/>
+      <c r="K64" s="9">
+        <f>IF(C64*J64=0,"",C64*J64)</f>
         <v/>
       </c>
     </row>
@@ -2648,9 +2745,10 @@
         <v/>
       </c>
       <c r="H65" s="13" t="inlineStr"/>
-      <c r="I65" s="14" t="inlineStr"/>
-      <c r="J65" s="14">
-        <f>IF(C65*I65=0,"",C65*I65)</f>
+      <c r="I65" s="13" t="inlineStr"/>
+      <c r="J65" s="14" t="inlineStr"/>
+      <c r="K65" s="14">
+        <f>IF(C65*J65=0,"",C65*J65)</f>
         <v/>
       </c>
     </row>
@@ -2683,9 +2781,10 @@
         <v/>
       </c>
       <c r="H66" s="8" t="inlineStr"/>
-      <c r="I66" s="9" t="inlineStr"/>
-      <c r="J66" s="9">
-        <f>IF(C66*I66=0,"",C66*I66)</f>
+      <c r="I66" s="8" t="inlineStr"/>
+      <c r="J66" s="9" t="inlineStr"/>
+      <c r="K66" s="9">
+        <f>IF(C66*J66=0,"",C66*J66)</f>
         <v/>
       </c>
     </row>
@@ -2718,9 +2817,10 @@
         <v/>
       </c>
       <c r="H67" s="13" t="inlineStr"/>
-      <c r="I67" s="14" t="inlineStr"/>
-      <c r="J67" s="14">
-        <f>IF(C67*I67=0,"",C67*I67)</f>
+      <c r="I67" s="13" t="inlineStr"/>
+      <c r="J67" s="14" t="inlineStr"/>
+      <c r="K67" s="14">
+        <f>IF(C67*J67=0,"",C67*J67)</f>
         <v/>
       </c>
     </row>
@@ -2753,9 +2853,10 @@
         <v/>
       </c>
       <c r="H68" s="8" t="inlineStr"/>
-      <c r="I68" s="9" t="inlineStr"/>
-      <c r="J68" s="9">
-        <f>IF(C68*I68=0,"",C68*I68)</f>
+      <c r="I68" s="8" t="inlineStr"/>
+      <c r="J68" s="9" t="inlineStr"/>
+      <c r="K68" s="9">
+        <f>IF(C68*J68=0,"",C68*J68)</f>
         <v/>
       </c>
     </row>
@@ -2788,9 +2889,10 @@
         <v/>
       </c>
       <c r="H69" s="13" t="inlineStr"/>
-      <c r="I69" s="14" t="inlineStr"/>
-      <c r="J69" s="14">
-        <f>IF(C69*I69=0,"",C69*I69)</f>
+      <c r="I69" s="13" t="inlineStr"/>
+      <c r="J69" s="14" t="inlineStr"/>
+      <c r="K69" s="14">
+        <f>IF(C69*J69=0,"",C69*J69)</f>
         <v/>
       </c>
     </row>
@@ -2823,9 +2925,10 @@
         <v/>
       </c>
       <c r="H70" s="8" t="inlineStr"/>
-      <c r="I70" s="9" t="inlineStr"/>
-      <c r="J70" s="9">
-        <f>IF(C70*I70=0,"",C70*I70)</f>
+      <c r="I70" s="8" t="inlineStr"/>
+      <c r="J70" s="9" t="inlineStr"/>
+      <c r="K70" s="9">
+        <f>IF(C70*J70=0,"",C70*J70)</f>
         <v/>
       </c>
     </row>
@@ -2858,9 +2961,10 @@
         <v/>
       </c>
       <c r="H71" s="13" t="inlineStr"/>
-      <c r="I71" s="14" t="inlineStr"/>
-      <c r="J71" s="14">
-        <f>IF(C71*I71=0,"",C71*I71)</f>
+      <c r="I71" s="13" t="inlineStr"/>
+      <c r="J71" s="14" t="inlineStr"/>
+      <c r="K71" s="14">
+        <f>IF(C71*J71=0,"",C71*J71)</f>
         <v/>
       </c>
     </row>
@@ -2893,9 +2997,10 @@
         <v/>
       </c>
       <c r="H72" s="8" t="inlineStr"/>
-      <c r="I72" s="9" t="inlineStr"/>
-      <c r="J72" s="9">
-        <f>IF(C72*I72=0,"",C72*I72)</f>
+      <c r="I72" s="8" t="inlineStr"/>
+      <c r="J72" s="9" t="inlineStr"/>
+      <c r="K72" s="9">
+        <f>IF(C72*J72=0,"",C72*J72)</f>
         <v/>
       </c>
     </row>
@@ -2928,9 +3033,10 @@
         <v/>
       </c>
       <c r="H73" s="13" t="inlineStr"/>
-      <c r="I73" s="14" t="inlineStr"/>
-      <c r="J73" s="14">
-        <f>IF(C73*I73=0,"",C73*I73)</f>
+      <c r="I73" s="13" t="inlineStr"/>
+      <c r="J73" s="14" t="inlineStr"/>
+      <c r="K73" s="14">
+        <f>IF(C73*J73=0,"",C73*J73)</f>
         <v/>
       </c>
     </row>
@@ -2970,9 +3076,10 @@
         <v/>
       </c>
       <c r="H75" s="13" t="inlineStr"/>
-      <c r="I75" s="14" t="inlineStr"/>
-      <c r="J75" s="14">
-        <f>IF(C75*I75=0,"",C75*I75)</f>
+      <c r="I75" s="13" t="inlineStr"/>
+      <c r="J75" s="14" t="inlineStr"/>
+      <c r="K75" s="14">
+        <f>IF(C75*J75=0,"",C75*J75)</f>
         <v/>
       </c>
     </row>
@@ -3005,9 +3112,10 @@
         <v/>
       </c>
       <c r="H76" s="8" t="inlineStr"/>
-      <c r="I76" s="9" t="inlineStr"/>
-      <c r="J76" s="9">
-        <f>IF(C76*I76=0,"",C76*I76)</f>
+      <c r="I76" s="8" t="inlineStr"/>
+      <c r="J76" s="9" t="inlineStr"/>
+      <c r="K76" s="9">
+        <f>IF(C76*J76=0,"",C76*J76)</f>
         <v/>
       </c>
     </row>
@@ -3040,9 +3148,10 @@
         <v/>
       </c>
       <c r="H77" s="13" t="inlineStr"/>
-      <c r="I77" s="14" t="inlineStr"/>
-      <c r="J77" s="14">
-        <f>IF(C77*I77=0,"",C77*I77)</f>
+      <c r="I77" s="13" t="inlineStr"/>
+      <c r="J77" s="14" t="inlineStr"/>
+      <c r="K77" s="14">
+        <f>IF(C77*J77=0,"",C77*J77)</f>
         <v/>
       </c>
     </row>
@@ -3075,9 +3184,10 @@
         <v/>
       </c>
       <c r="H78" s="8" t="inlineStr"/>
-      <c r="I78" s="9" t="inlineStr"/>
-      <c r="J78" s="9">
-        <f>IF(C78*I78=0,"",C78*I78)</f>
+      <c r="I78" s="8" t="inlineStr"/>
+      <c r="J78" s="9" t="inlineStr"/>
+      <c r="K78" s="9">
+        <f>IF(C78*J78=0,"",C78*J78)</f>
         <v/>
       </c>
     </row>
@@ -3110,9 +3220,10 @@
         <v/>
       </c>
       <c r="H79" s="13" t="inlineStr"/>
-      <c r="I79" s="14" t="inlineStr"/>
-      <c r="J79" s="14">
-        <f>IF(C79*I79=0,"",C79*I79)</f>
+      <c r="I79" s="13" t="inlineStr"/>
+      <c r="J79" s="14" t="inlineStr"/>
+      <c r="K79" s="14">
+        <f>IF(C79*J79=0,"",C79*J79)</f>
         <v/>
       </c>
     </row>
@@ -3145,9 +3256,10 @@
         <v/>
       </c>
       <c r="H80" s="8" t="inlineStr"/>
-      <c r="I80" s="9" t="inlineStr"/>
-      <c r="J80" s="9">
-        <f>IF(C80*I80=0,"",C80*I80)</f>
+      <c r="I80" s="8" t="inlineStr"/>
+      <c r="J80" s="9" t="inlineStr"/>
+      <c r="K80" s="9">
+        <f>IF(C80*J80=0,"",C80*J80)</f>
         <v/>
       </c>
     </row>
@@ -3180,9 +3292,10 @@
         <v/>
       </c>
       <c r="H81" s="13" t="inlineStr"/>
-      <c r="I81" s="14" t="inlineStr"/>
-      <c r="J81" s="14">
-        <f>IF(C81*I81=0,"",C81*I81)</f>
+      <c r="I81" s="13" t="inlineStr"/>
+      <c r="J81" s="14" t="inlineStr"/>
+      <c r="K81" s="14">
+        <f>IF(C81*J81=0,"",C81*J81)</f>
         <v/>
       </c>
     </row>
@@ -3215,9 +3328,10 @@
         <v/>
       </c>
       <c r="H82" s="8" t="inlineStr"/>
-      <c r="I82" s="9" t="inlineStr"/>
-      <c r="J82" s="9">
-        <f>IF(C82*I82=0,"",C82*I82)</f>
+      <c r="I82" s="8" t="inlineStr"/>
+      <c r="J82" s="9" t="inlineStr"/>
+      <c r="K82" s="9">
+        <f>IF(C82*J82=0,"",C82*J82)</f>
         <v/>
       </c>
     </row>
@@ -3250,9 +3364,10 @@
         <v/>
       </c>
       <c r="H83" s="13" t="inlineStr"/>
-      <c r="I83" s="14" t="inlineStr"/>
-      <c r="J83" s="14">
-        <f>IF(C83*I83=0,"",C83*I83)</f>
+      <c r="I83" s="13" t="inlineStr"/>
+      <c r="J83" s="14" t="inlineStr"/>
+      <c r="K83" s="14">
+        <f>IF(C83*J83=0,"",C83*J83)</f>
         <v/>
       </c>
     </row>
@@ -3285,9 +3400,10 @@
         <v/>
       </c>
       <c r="H84" s="8" t="inlineStr"/>
-      <c r="I84" s="9" t="inlineStr"/>
-      <c r="J84" s="9">
-        <f>IF(C84*I84=0,"",C84*I84)</f>
+      <c r="I84" s="8" t="inlineStr"/>
+      <c r="J84" s="9" t="inlineStr"/>
+      <c r="K84" s="9">
+        <f>IF(C84*J84=0,"",C84*J84)</f>
         <v/>
       </c>
     </row>
@@ -3320,9 +3436,10 @@
         <v/>
       </c>
       <c r="H85" s="13" t="inlineStr"/>
-      <c r="I85" s="14" t="inlineStr"/>
-      <c r="J85" s="14">
-        <f>IF(C85*I85=0,"",C85*I85)</f>
+      <c r="I85" s="13" t="inlineStr"/>
+      <c r="J85" s="14" t="inlineStr"/>
+      <c r="K85" s="14">
+        <f>IF(C85*J85=0,"",C85*J85)</f>
         <v/>
       </c>
     </row>
@@ -3355,9 +3472,10 @@
         <v/>
       </c>
       <c r="H86" s="8" t="inlineStr"/>
-      <c r="I86" s="9" t="inlineStr"/>
-      <c r="J86" s="9">
-        <f>IF(C86*I86=0,"",C86*I86)</f>
+      <c r="I86" s="8" t="inlineStr"/>
+      <c r="J86" s="9" t="inlineStr"/>
+      <c r="K86" s="9">
+        <f>IF(C86*J86=0,"",C86*J86)</f>
         <v/>
       </c>
     </row>
@@ -3390,9 +3508,10 @@
         <v/>
       </c>
       <c r="H87" s="13" t="inlineStr"/>
-      <c r="I87" s="14" t="inlineStr"/>
-      <c r="J87" s="14">
-        <f>IF(C87*I87=0,"",C87*I87)</f>
+      <c r="I87" s="13" t="inlineStr"/>
+      <c r="J87" s="14" t="inlineStr"/>
+      <c r="K87" s="14">
+        <f>IF(C87*J87=0,"",C87*J87)</f>
         <v/>
       </c>
     </row>
@@ -3432,9 +3551,10 @@
         <v/>
       </c>
       <c r="H89" s="13" t="inlineStr"/>
-      <c r="I89" s="14" t="inlineStr"/>
-      <c r="J89" s="14">
-        <f>IF(C89*I89=0,"",C89*I89)</f>
+      <c r="I89" s="13" t="inlineStr"/>
+      <c r="J89" s="14" t="inlineStr"/>
+      <c r="K89" s="14">
+        <f>IF(C89*J89=0,"",C89*J89)</f>
         <v/>
       </c>
     </row>
@@ -3467,9 +3587,10 @@
         <v/>
       </c>
       <c r="H90" s="8" t="inlineStr"/>
-      <c r="I90" s="9" t="inlineStr"/>
-      <c r="J90" s="9">
-        <f>IF(C90*I90=0,"",C90*I90)</f>
+      <c r="I90" s="8" t="inlineStr"/>
+      <c r="J90" s="9" t="inlineStr"/>
+      <c r="K90" s="9">
+        <f>IF(C90*J90=0,"",C90*J90)</f>
         <v/>
       </c>
     </row>
@@ -3502,9 +3623,10 @@
         <v/>
       </c>
       <c r="H91" s="13" t="inlineStr"/>
-      <c r="I91" s="14" t="inlineStr"/>
-      <c r="J91" s="14">
-        <f>IF(C91*I91=0,"",C91*I91)</f>
+      <c r="I91" s="13" t="inlineStr"/>
+      <c r="J91" s="14" t="inlineStr"/>
+      <c r="K91" s="14">
+        <f>IF(C91*J91=0,"",C91*J91)</f>
         <v/>
       </c>
     </row>
@@ -3537,9 +3659,10 @@
         <v/>
       </c>
       <c r="H92" s="8" t="inlineStr"/>
-      <c r="I92" s="9" t="inlineStr"/>
-      <c r="J92" s="9">
-        <f>IF(C92*I92=0,"",C92*I92)</f>
+      <c r="I92" s="8" t="inlineStr"/>
+      <c r="J92" s="9" t="inlineStr"/>
+      <c r="K92" s="9">
+        <f>IF(C92*J92=0,"",C92*J92)</f>
         <v/>
       </c>
     </row>
@@ -3579,9 +3702,10 @@
         <v/>
       </c>
       <c r="H94" s="8" t="inlineStr"/>
-      <c r="I94" s="9" t="inlineStr"/>
-      <c r="J94" s="9">
-        <f>IF(C94*I94=0,"",C94*I94)</f>
+      <c r="I94" s="8" t="inlineStr"/>
+      <c r="J94" s="9" t="inlineStr"/>
+      <c r="K94" s="9">
+        <f>IF(C94*J94=0,"",C94*J94)</f>
         <v/>
       </c>
     </row>
@@ -3614,9 +3738,10 @@
         <v/>
       </c>
       <c r="H95" s="13" t="inlineStr"/>
-      <c r="I95" s="14" t="inlineStr"/>
-      <c r="J95" s="14">
-        <f>IF(C95*I95=0,"",C95*I95)</f>
+      <c r="I95" s="13" t="inlineStr"/>
+      <c r="J95" s="14" t="inlineStr"/>
+      <c r="K95" s="14">
+        <f>IF(C95*J95=0,"",C95*J95)</f>
         <v/>
       </c>
     </row>
@@ -3649,9 +3774,10 @@
         <v/>
       </c>
       <c r="H96" s="8" t="inlineStr"/>
-      <c r="I96" s="9" t="inlineStr"/>
-      <c r="J96" s="9">
-        <f>IF(C96*I96=0,"",C96*I96)</f>
+      <c r="I96" s="8" t="inlineStr"/>
+      <c r="J96" s="9" t="inlineStr"/>
+      <c r="K96" s="9">
+        <f>IF(C96*J96=0,"",C96*J96)</f>
         <v/>
       </c>
     </row>
@@ -3684,9 +3810,10 @@
         <v/>
       </c>
       <c r="H97" s="13" t="inlineStr"/>
-      <c r="I97" s="14" t="inlineStr"/>
-      <c r="J97" s="14">
-        <f>IF(C97*I97=0,"",C97*I97)</f>
+      <c r="I97" s="13" t="inlineStr"/>
+      <c r="J97" s="14" t="inlineStr"/>
+      <c r="K97" s="14">
+        <f>IF(C97*J97=0,"",C97*J97)</f>
         <v/>
       </c>
     </row>
@@ -3719,9 +3846,10 @@
         <v/>
       </c>
       <c r="H98" s="8" t="inlineStr"/>
-      <c r="I98" s="9" t="inlineStr"/>
-      <c r="J98" s="9">
-        <f>IF(C98*I98=0,"",C98*I98)</f>
+      <c r="I98" s="8" t="inlineStr"/>
+      <c r="J98" s="9" t="inlineStr"/>
+      <c r="K98" s="9">
+        <f>IF(C98*J98=0,"",C98*J98)</f>
         <v/>
       </c>
     </row>
@@ -3754,9 +3882,10 @@
         <v/>
       </c>
       <c r="H99" s="13" t="inlineStr"/>
-      <c r="I99" s="14" t="inlineStr"/>
-      <c r="J99" s="14">
-        <f>IF(C99*I99=0,"",C99*I99)</f>
+      <c r="I99" s="13" t="inlineStr"/>
+      <c r="J99" s="14" t="inlineStr"/>
+      <c r="K99" s="14">
+        <f>IF(C99*J99=0,"",C99*J99)</f>
         <v/>
       </c>
     </row>
@@ -3789,9 +3918,10 @@
         <v/>
       </c>
       <c r="H100" s="8" t="inlineStr"/>
-      <c r="I100" s="9" t="inlineStr"/>
-      <c r="J100" s="9">
-        <f>IF(C100*I100=0,"",C100*I100)</f>
+      <c r="I100" s="8" t="inlineStr"/>
+      <c r="J100" s="9" t="inlineStr"/>
+      <c r="K100" s="9">
+        <f>IF(C100*J100=0,"",C100*J100)</f>
         <v/>
       </c>
     </row>
@@ -3824,9 +3954,10 @@
         <v/>
       </c>
       <c r="H101" s="13" t="inlineStr"/>
-      <c r="I101" s="14" t="inlineStr"/>
-      <c r="J101" s="14">
-        <f>IF(C101*I101=0,"",C101*I101)</f>
+      <c r="I101" s="13" t="inlineStr"/>
+      <c r="J101" s="14" t="inlineStr"/>
+      <c r="K101" s="14">
+        <f>IF(C101*J101=0,"",C101*J101)</f>
         <v/>
       </c>
     </row>
@@ -3859,9 +3990,10 @@
         <v/>
       </c>
       <c r="H102" s="8" t="inlineStr"/>
-      <c r="I102" s="9" t="inlineStr"/>
-      <c r="J102" s="9">
-        <f>IF(C102*I102=0,"",C102*I102)</f>
+      <c r="I102" s="8" t="inlineStr"/>
+      <c r="J102" s="9" t="inlineStr"/>
+      <c r="K102" s="9">
+        <f>IF(C102*J102=0,"",C102*J102)</f>
         <v/>
       </c>
     </row>
@@ -3894,9 +4026,10 @@
         <v/>
       </c>
       <c r="H103" s="13" t="inlineStr"/>
-      <c r="I103" s="14" t="inlineStr"/>
-      <c r="J103" s="14">
-        <f>IF(C103*I103=0,"",C103*I103)</f>
+      <c r="I103" s="13" t="inlineStr"/>
+      <c r="J103" s="14" t="inlineStr"/>
+      <c r="K103" s="14">
+        <f>IF(C103*J103=0,"",C103*J103)</f>
         <v/>
       </c>
     </row>
@@ -3936,9 +4069,10 @@
         <v/>
       </c>
       <c r="H105" s="13" t="inlineStr"/>
-      <c r="I105" s="14" t="inlineStr"/>
-      <c r="J105" s="14">
-        <f>IF(C105*I105=0,"",C105*I105)</f>
+      <c r="I105" s="13" t="inlineStr"/>
+      <c r="J105" s="14" t="inlineStr"/>
+      <c r="K105" s="14">
+        <f>IF(C105*J105=0,"",C105*J105)</f>
         <v/>
       </c>
     </row>
@@ -3971,9 +4105,10 @@
         <v/>
       </c>
       <c r="H106" s="8" t="inlineStr"/>
-      <c r="I106" s="9" t="inlineStr"/>
-      <c r="J106" s="9">
-        <f>IF(C106*I106=0,"",C106*I106)</f>
+      <c r="I106" s="8" t="inlineStr"/>
+      <c r="J106" s="9" t="inlineStr"/>
+      <c r="K106" s="9">
+        <f>IF(C106*J106=0,"",C106*J106)</f>
         <v/>
       </c>
     </row>
@@ -4006,9 +4141,10 @@
         <v/>
       </c>
       <c r="H107" s="13" t="inlineStr"/>
-      <c r="I107" s="14" t="inlineStr"/>
-      <c r="J107" s="14">
-        <f>IF(C107*I107=0,"",C107*I107)</f>
+      <c r="I107" s="13" t="inlineStr"/>
+      <c r="J107" s="14" t="inlineStr"/>
+      <c r="K107" s="14">
+        <f>IF(C107*J107=0,"",C107*J107)</f>
         <v/>
       </c>
     </row>
@@ -4041,9 +4177,10 @@
         <v/>
       </c>
       <c r="H108" s="8" t="inlineStr"/>
-      <c r="I108" s="9" t="inlineStr"/>
-      <c r="J108" s="9">
-        <f>IF(C108*I108=0,"",C108*I108)</f>
+      <c r="I108" s="8" t="inlineStr"/>
+      <c r="J108" s="9" t="inlineStr"/>
+      <c r="K108" s="9">
+        <f>IF(C108*J108=0,"",C108*J108)</f>
         <v/>
       </c>
     </row>
@@ -4076,9 +4213,10 @@
         <v/>
       </c>
       <c r="H109" s="13" t="inlineStr"/>
-      <c r="I109" s="14" t="inlineStr"/>
-      <c r="J109" s="14">
-        <f>IF(C109*I109=0,"",C109*I109)</f>
+      <c r="I109" s="13" t="inlineStr"/>
+      <c r="J109" s="14" t="inlineStr"/>
+      <c r="K109" s="14">
+        <f>IF(C109*J109=0,"",C109*J109)</f>
         <v/>
       </c>
     </row>
@@ -4111,9 +4249,10 @@
         <v/>
       </c>
       <c r="H110" s="8" t="inlineStr"/>
-      <c r="I110" s="9" t="inlineStr"/>
-      <c r="J110" s="9">
-        <f>IF(C110*I110=0,"",C110*I110)</f>
+      <c r="I110" s="8" t="inlineStr"/>
+      <c r="J110" s="9" t="inlineStr"/>
+      <c r="K110" s="9">
+        <f>IF(C110*J110=0,"",C110*J110)</f>
         <v/>
       </c>
     </row>
@@ -4146,9 +4285,10 @@
         <v/>
       </c>
       <c r="H111" s="13" t="inlineStr"/>
-      <c r="I111" s="14" t="inlineStr"/>
-      <c r="J111" s="14">
-        <f>IF(C111*I111=0,"",C111*I111)</f>
+      <c r="I111" s="13" t="inlineStr"/>
+      <c r="J111" s="14" t="inlineStr"/>
+      <c r="K111" s="14">
+        <f>IF(C111*J111=0,"",C111*J111)</f>
         <v/>
       </c>
     </row>
@@ -4181,9 +4321,10 @@
         <v/>
       </c>
       <c r="H112" s="8" t="inlineStr"/>
-      <c r="I112" s="9" t="inlineStr"/>
-      <c r="J112" s="9">
-        <f>IF(C112*I112=0,"",C112*I112)</f>
+      <c r="I112" s="8" t="inlineStr"/>
+      <c r="J112" s="9" t="inlineStr"/>
+      <c r="K112" s="9">
+        <f>IF(C112*J112=0,"",C112*J112)</f>
         <v/>
       </c>
     </row>
@@ -4216,9 +4357,10 @@
         <v/>
       </c>
       <c r="H113" s="13" t="inlineStr"/>
-      <c r="I113" s="14" t="inlineStr"/>
-      <c r="J113" s="14">
-        <f>IF(C113*I113=0,"",C113*I113)</f>
+      <c r="I113" s="13" t="inlineStr"/>
+      <c r="J113" s="14" t="inlineStr"/>
+      <c r="K113" s="14">
+        <f>IF(C113*J113=0,"",C113*J113)</f>
         <v/>
       </c>
     </row>
@@ -4251,9 +4393,10 @@
         <v/>
       </c>
       <c r="H114" s="8" t="inlineStr"/>
-      <c r="I114" s="9" t="inlineStr"/>
-      <c r="J114" s="9">
-        <f>IF(C114*I114=0,"",C114*I114)</f>
+      <c r="I114" s="8" t="inlineStr"/>
+      <c r="J114" s="9" t="inlineStr"/>
+      <c r="K114" s="9">
+        <f>IF(C114*J114=0,"",C114*J114)</f>
         <v/>
       </c>
     </row>
@@ -4286,9 +4429,10 @@
         <v/>
       </c>
       <c r="H115" s="13" t="inlineStr"/>
-      <c r="I115" s="14" t="inlineStr"/>
-      <c r="J115" s="14">
-        <f>IF(C115*I115=0,"",C115*I115)</f>
+      <c r="I115" s="13" t="inlineStr"/>
+      <c r="J115" s="14" t="inlineStr"/>
+      <c r="K115" s="14">
+        <f>IF(C115*J115=0,"",C115*J115)</f>
         <v/>
       </c>
     </row>
@@ -4321,9 +4465,10 @@
         <v/>
       </c>
       <c r="H116" s="8" t="inlineStr"/>
-      <c r="I116" s="9" t="inlineStr"/>
-      <c r="J116" s="9">
-        <f>IF(C116*I116=0,"",C116*I116)</f>
+      <c r="I116" s="8" t="inlineStr"/>
+      <c r="J116" s="9" t="inlineStr"/>
+      <c r="K116" s="9">
+        <f>IF(C116*J116=0,"",C116*J116)</f>
         <v/>
       </c>
     </row>
@@ -4356,9 +4501,10 @@
         <v/>
       </c>
       <c r="H117" s="13" t="inlineStr"/>
-      <c r="I117" s="14" t="inlineStr"/>
-      <c r="J117" s="14">
-        <f>IF(C117*I117=0,"",C117*I117)</f>
+      <c r="I117" s="13" t="inlineStr"/>
+      <c r="J117" s="14" t="inlineStr"/>
+      <c r="K117" s="14">
+        <f>IF(C117*J117=0,"",C117*J117)</f>
         <v/>
       </c>
     </row>
@@ -4390,10 +4536,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=botao+emergencia+cogumelo+22+mm","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H118" s="8" t="inlineStr"/>
-      <c r="I118" s="9" t="inlineStr"/>
-      <c r="J118" s="9">
-        <f>IF(C118*I118=0,"",C118*I118)</f>
+      <c r="H118" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-22mm-emergency-stop-mushroom-button.html","🌏 22mm emergency stop mushro")</f>
+        <v/>
+      </c>
+      <c r="I118" s="8" t="inlineStr"/>
+      <c r="J118" s="9" t="inlineStr"/>
+      <c r="K118" s="9">
+        <f>IF(C118*J118=0,"",C118*J118)</f>
         <v/>
       </c>
     </row>
@@ -4425,10 +4575,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=botao+start+22+mm","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H119" s="13" t="inlineStr"/>
-      <c r="I119" s="14" t="inlineStr"/>
-      <c r="J119" s="14">
-        <f>IF(C119*I119=0,"",C119*I119)</f>
+      <c r="H119" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-22mm-push-button-switch-green.html","🌏 22mm push button switch gr")</f>
+        <v/>
+      </c>
+      <c r="I119" s="13" t="inlineStr"/>
+      <c r="J119" s="14" t="inlineStr"/>
+      <c r="K119" s="14">
+        <f>IF(C119*J119=0,"",C119*J119)</f>
         <v/>
       </c>
     </row>
@@ -4460,10 +4614,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=botao+stop+22+mm","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H120" s="8" t="inlineStr"/>
-      <c r="I120" s="9" t="inlineStr"/>
-      <c r="J120" s="9">
-        <f>IF(C120*I120=0,"",C120*I120)</f>
+      <c r="H120" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-22mm-push-button-switch-red.html","🌏 22mm push button switch re")</f>
+        <v/>
+      </c>
+      <c r="I120" s="8" t="inlineStr"/>
+      <c r="J120" s="9" t="inlineStr"/>
+      <c r="K120" s="9">
+        <f>IF(C120*J120=0,"",C120*J120)</f>
         <v/>
       </c>
     </row>
@@ -4495,10 +4653,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=botao+rearme+22+mm","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H121" s="13" t="inlineStr"/>
-      <c r="I121" s="14" t="inlineStr"/>
-      <c r="J121" s="14">
-        <f>IF(C121*I121=0,"",C121*I121)</f>
+      <c r="H121" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-22mm-push-button-switch-blue.html","🌏 22mm push button switch bl")</f>
+        <v/>
+      </c>
+      <c r="I121" s="13" t="inlineStr"/>
+      <c r="J121" s="14" t="inlineStr"/>
+      <c r="K121" s="14">
+        <f>IF(C121*J121=0,"",C121*J121)</f>
         <v/>
       </c>
     </row>
@@ -4530,10 +4692,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=blocos+contato+22+mm+avulsos","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H122" s="8" t="inlineStr"/>
-      <c r="I122" s="9" t="inlineStr"/>
-      <c r="J122" s="9">
-        <f>IF(C122*I122=0,"",C122*I122)</f>
+      <c r="H122" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-22mm-push-button-contact-block-no-nc.html","🌏 22mm push button contact b")</f>
+        <v/>
+      </c>
+      <c r="I122" s="8" t="inlineStr"/>
+      <c r="J122" s="9" t="inlineStr"/>
+      <c r="K122" s="9">
+        <f>IF(C122*J122=0,"",C122*J122)</f>
         <v/>
       </c>
     </row>
@@ -4566,9 +4732,10 @@
         <v/>
       </c>
       <c r="H123" s="13" t="inlineStr"/>
-      <c r="I123" s="14" t="inlineStr"/>
-      <c r="J123" s="14">
-        <f>IF(C123*I123=0,"",C123*I123)</f>
+      <c r="I123" s="13" t="inlineStr"/>
+      <c r="J123" s="14" t="inlineStr"/>
+      <c r="K123" s="14">
+        <f>IF(C123*J123=0,"",C123*J123)</f>
         <v/>
       </c>
     </row>
@@ -4600,10 +4767,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=sinaleiros+led+22+mm+24+v","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H124" s="8" t="inlineStr"/>
-      <c r="I124" s="9" t="inlineStr"/>
-      <c r="J124" s="9">
-        <f>IF(C124*I124=0,"",C124*I124)</f>
+      <c r="H124" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-22mm-led-pilot-indicator-lamp-24v.html","🌏 22mm LED pilot indicator l")</f>
+        <v/>
+      </c>
+      <c r="I124" s="8" t="inlineStr"/>
+      <c r="J124" s="9" t="inlineStr"/>
+      <c r="K124" s="9">
+        <f>IF(C124*J124=0,"",C124*J124)</f>
         <v/>
       </c>
     </row>
@@ -4636,9 +4807,10 @@
         <v/>
       </c>
       <c r="H125" s="13" t="inlineStr"/>
-      <c r="I125" s="14" t="inlineStr"/>
-      <c r="J125" s="14">
-        <f>IF(C125*I125=0,"",C125*I125)</f>
+      <c r="I125" s="13" t="inlineStr"/>
+      <c r="J125" s="14" t="inlineStr"/>
+      <c r="K125" s="14">
+        <f>IF(C125*J125=0,"",C125*J125)</f>
         <v/>
       </c>
     </row>
@@ -4671,9 +4843,10 @@
         <v/>
       </c>
       <c r="H126" s="8" t="inlineStr"/>
-      <c r="I126" s="9" t="inlineStr"/>
-      <c r="J126" s="9">
-        <f>IF(C126*I126=0,"",C126*I126)</f>
+      <c r="I126" s="8" t="inlineStr"/>
+      <c r="J126" s="9" t="inlineStr"/>
+      <c r="K126" s="9">
+        <f>IF(C126*J126=0,"",C126*J126)</f>
         <v/>
       </c>
     </row>
@@ -4706,9 +4879,10 @@
         <v/>
       </c>
       <c r="H127" s="13" t="inlineStr"/>
-      <c r="I127" s="14" t="inlineStr"/>
-      <c r="J127" s="14">
-        <f>IF(C127*I127=0,"",C127*I127)</f>
+      <c r="I127" s="13" t="inlineStr"/>
+      <c r="J127" s="14" t="inlineStr"/>
+      <c r="K127" s="14">
+        <f>IF(C127*J127=0,"",C127*J127)</f>
         <v/>
       </c>
     </row>
@@ -4747,10 +4921,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=arduino+mega+2560+r3","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H129" s="13" t="inlineStr"/>
-      <c r="I129" s="14" t="inlineStr"/>
-      <c r="J129" s="14">
-        <f>IF(C129*I129=0,"",C129*I129)</f>
+      <c r="H129" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-arduino-mega-2560-r3.html","🌏 Arduino Mega 2560 R3")</f>
+        <v/>
+      </c>
+      <c r="I129" s="13" t="inlineStr"/>
+      <c r="J129" s="14" t="inlineStr"/>
+      <c r="K129" s="14">
+        <f>IF(C129*J129=0,"",C129*J129)</f>
         <v/>
       </c>
     </row>
@@ -4783,9 +4961,10 @@
         <v/>
       </c>
       <c r="H130" s="8" t="inlineStr"/>
-      <c r="I130" s="9" t="inlineStr"/>
-      <c r="J130" s="9">
-        <f>IF(C130*I130=0,"",C130*I130)</f>
+      <c r="I130" s="8" t="inlineStr"/>
+      <c r="J130" s="9" t="inlineStr"/>
+      <c r="K130" s="9">
+        <f>IF(C130*J130=0,"",C130*J130)</f>
         <v/>
       </c>
     </row>
@@ -4818,9 +4997,10 @@
         <v/>
       </c>
       <c r="H131" s="13" t="inlineStr"/>
-      <c r="I131" s="14" t="inlineStr"/>
-      <c r="J131" s="14">
-        <f>IF(C131*I131=0,"",C131*I131)</f>
+      <c r="I131" s="13" t="inlineStr"/>
+      <c r="J131" s="14" t="inlineStr"/>
+      <c r="K131" s="14">
+        <f>IF(C131*J131=0,"",C131*J131)</f>
         <v/>
       </c>
     </row>
@@ -4852,10 +5032,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=tela+nextion+basic+3+2","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H132" s="8" t="inlineStr"/>
-      <c r="I132" s="9" t="inlineStr"/>
-      <c r="J132" s="9">
-        <f>IF(C132*I132=0,"",C132*I132)</f>
+      <c r="H132" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-nextion-nx4024t032-3-2-inch-hmi.html","🌏 Nextion NX4024T032 3.2 inc")</f>
+        <v/>
+      </c>
+      <c r="I132" s="8" t="inlineStr"/>
+      <c r="J132" s="9" t="inlineStr"/>
+      <c r="K132" s="9">
+        <f>IF(C132*J132=0,"",C132*J132)</f>
         <v/>
       </c>
     </row>
@@ -4887,10 +5071,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=esp32+wroom+32u","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H133" s="13" t="inlineStr"/>
-      <c r="I133" s="14" t="inlineStr"/>
-      <c r="J133" s="14">
-        <f>IF(C133*I133=0,"",C133*I133)</f>
+      <c r="H133" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-esp32-wroom-32u.html","🌏 ESP32 WROOM 32U")</f>
+        <v/>
+      </c>
+      <c r="I133" s="13" t="inlineStr"/>
+      <c r="J133" s="14" t="inlineStr"/>
+      <c r="K133" s="14">
+        <f>IF(C133*J133=0,"",C133*J133)</f>
         <v/>
       </c>
     </row>
@@ -4923,9 +5111,10 @@
         <v/>
       </c>
       <c r="H134" s="8" t="inlineStr"/>
-      <c r="I134" s="9" t="inlineStr"/>
-      <c r="J134" s="9">
-        <f>IF(C134*I134=0,"",C134*I134)</f>
+      <c r="I134" s="8" t="inlineStr"/>
+      <c r="J134" s="9" t="inlineStr"/>
+      <c r="K134" s="9">
+        <f>IF(C134*J134=0,"",C134*J134)</f>
         <v/>
       </c>
     </row>
@@ -4957,10 +5146,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=pigtail+ipex+sma+macho%2C+20+30+cm","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H135" s="13" t="inlineStr"/>
-      <c r="I135" s="14" t="inlineStr"/>
-      <c r="J135" s="14">
-        <f>IF(C135*I135=0,"",C135*I135)</f>
+      <c r="H135" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-ipex-u-fl-to-sma-pigtail-cable.html","🌏 IPEX u.FL to SMA pigtail c")</f>
+        <v/>
+      </c>
+      <c r="I135" s="13" t="inlineStr"/>
+      <c r="J135" s="14" t="inlineStr"/>
+      <c r="K135" s="14">
+        <f>IF(C135*J135=0,"",C135*J135)</f>
         <v/>
       </c>
     </row>
@@ -4992,10 +5185,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=conector+sma+femea+painel","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H136" s="8" t="inlineStr"/>
-      <c r="I136" s="9" t="inlineStr"/>
-      <c r="J136" s="9">
-        <f>IF(C136*I136=0,"",C136*I136)</f>
+      <c r="H136" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-sma-bulkhead-panel-connector-female.html","🌏 SMA bulkhead panel connect")</f>
+        <v/>
+      </c>
+      <c r="I136" s="8" t="inlineStr"/>
+      <c r="J136" s="9" t="inlineStr"/>
+      <c r="K136" s="9">
+        <f>IF(C136*J136=0,"",C136*J136)</f>
         <v/>
       </c>
     </row>
@@ -5027,10 +5224,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=antena+2%2C4+ghz+sma+macho+3+dbi","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H137" s="13" t="inlineStr"/>
-      <c r="I137" s="14" t="inlineStr"/>
-      <c r="J137" s="14">
-        <f>IF(C137*I137=0,"",C137*I137)</f>
+      <c r="H137" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-2-4ghz-sma-antenna-3dbi.html","🌏 2.4GHz SMA antenna 3dBi")</f>
+        <v/>
+      </c>
+      <c r="I137" s="13" t="inlineStr"/>
+      <c r="J137" s="14" t="inlineStr"/>
+      <c r="K137" s="14">
+        <f>IF(C137*J137=0,"",C137*J137)</f>
         <v/>
       </c>
     </row>
@@ -5062,10 +5263,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=modulo+micro+sd","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H138" s="8" t="inlineStr"/>
-      <c r="I138" s="9" t="inlineStr"/>
-      <c r="J138" s="9">
-        <f>IF(C138*I138=0,"",C138*I138)</f>
+      <c r="H138" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-micro-sd-card-module-spi-arduino.html","🌏 micro SD card module SPI a")</f>
+        <v/>
+      </c>
+      <c r="I138" s="8" t="inlineStr"/>
+      <c r="J138" s="9" t="inlineStr"/>
+      <c r="K138" s="9">
+        <f>IF(C138*J138=0,"",C138*J138)</f>
         <v/>
       </c>
     </row>
@@ -5097,10 +5302,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=cartao+micro+sd","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H139" s="13" t="inlineStr"/>
-      <c r="I139" s="14" t="inlineStr"/>
-      <c r="J139" s="14">
-        <f>IF(C139*I139=0,"",C139*I139)</f>
+      <c r="H139" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-micro-sd-card-module-spi-arduino.html","🌏 micro SD card module SPI a")</f>
+        <v/>
+      </c>
+      <c r="I139" s="13" t="inlineStr"/>
+      <c r="J139" s="14" t="inlineStr"/>
+      <c r="K139" s="14">
+        <f>IF(C139*J139=0,"",C139*J139)</f>
         <v/>
       </c>
     </row>
@@ -5132,10 +5341,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=modulo+rtc+ds3231","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H140" s="8" t="inlineStr"/>
-      <c r="I140" s="9" t="inlineStr"/>
-      <c r="J140" s="9">
-        <f>IF(C140*I140=0,"",C140*I140)</f>
+      <c r="H140" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-ds3231-rtc-module.html","🌏 DS3231 RTC module")</f>
+        <v/>
+      </c>
+      <c r="I140" s="8" t="inlineStr"/>
+      <c r="J140" s="9" t="inlineStr"/>
+      <c r="K140" s="9">
+        <f>IF(C140*J140=0,"",C140*J140)</f>
         <v/>
       </c>
     </row>
@@ -5168,9 +5381,10 @@
         <v/>
       </c>
       <c r="H141" s="13" t="inlineStr"/>
-      <c r="I141" s="14" t="inlineStr"/>
-      <c r="J141" s="14">
-        <f>IF(C141*I141=0,"",C141*I141)</f>
+      <c r="I141" s="13" t="inlineStr"/>
+      <c r="J141" s="14" t="inlineStr"/>
+      <c r="K141" s="14">
+        <f>IF(C141*J141=0,"",C141*J141)</f>
         <v/>
       </c>
     </row>
@@ -5209,10 +5423,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=driver+ponte+h+bts7960","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H143" s="13" t="inlineStr"/>
-      <c r="I143" s="14" t="inlineStr"/>
-      <c r="J143" s="14">
-        <f>IF(C143*I143=0,"",C143*I143)</f>
+      <c r="H143" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-bts7960-43a-motor-driver-module.html","🌏 BTS7960 43A motor driver m")</f>
+        <v/>
+      </c>
+      <c r="I143" s="13" t="inlineStr"/>
+      <c r="J143" s="14" t="inlineStr"/>
+      <c r="K143" s="14">
+        <f>IF(C143*J143=0,"",C143*J143)</f>
         <v/>
       </c>
     </row>
@@ -5245,9 +5463,10 @@
         <v/>
       </c>
       <c r="H144" s="8" t="inlineStr"/>
-      <c r="I144" s="9" t="inlineStr"/>
-      <c r="J144" s="9">
-        <f>IF(C144*I144=0,"",C144*I144)</f>
+      <c r="I144" s="8" t="inlineStr"/>
+      <c r="J144" s="9" t="inlineStr"/>
+      <c r="K144" s="9">
+        <f>IF(C144*J144=0,"",C144*J144)</f>
         <v/>
       </c>
     </row>
@@ -5279,10 +5498,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=cooler+40+mm+12+v","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H145" s="13" t="inlineStr"/>
-      <c r="I145" s="14" t="inlineStr"/>
-      <c r="J145" s="14">
-        <f>IF(C145*I145=0,"",C145*I145)</f>
+      <c r="H145" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-40mm-fan-12v-dc.html","🌏 40mm fan 12V DC")</f>
+        <v/>
+      </c>
+      <c r="I145" s="13" t="inlineStr"/>
+      <c r="J145" s="14" t="inlineStr"/>
+      <c r="K145" s="14">
+        <f>IF(C145*J145=0,"",C145*J145)</f>
         <v/>
       </c>
     </row>
@@ -5315,9 +5538,10 @@
         <v/>
       </c>
       <c r="H146" s="8" t="inlineStr"/>
-      <c r="I146" s="9" t="inlineStr"/>
-      <c r="J146" s="9">
-        <f>IF(C146*I146=0,"",C146*I146)</f>
+      <c r="I146" s="8" t="inlineStr"/>
+      <c r="J146" s="9" t="inlineStr"/>
+      <c r="K146" s="9">
+        <f>IF(C146*J146=0,"",C146*J146)</f>
         <v/>
       </c>
     </row>
@@ -5350,9 +5574,10 @@
         <v/>
       </c>
       <c r="H147" s="13" t="inlineStr"/>
-      <c r="I147" s="14" t="inlineStr"/>
-      <c r="J147" s="14">
-        <f>IF(C147*I147=0,"",C147*I147)</f>
+      <c r="I147" s="13" t="inlineStr"/>
+      <c r="J147" s="14" t="inlineStr"/>
+      <c r="K147" s="14">
+        <f>IF(C147*J147=0,"",C147*J147)</f>
         <v/>
       </c>
     </row>
@@ -5384,10 +5609,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+10+k+1+4+w","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H148" s="8" t="inlineStr"/>
-      <c r="I148" s="9" t="inlineStr"/>
-      <c r="J148" s="9">
-        <f>IF(C148*I148=0,"",C148*I148)</f>
+      <c r="H148" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
+        <v/>
+      </c>
+      <c r="I148" s="8" t="inlineStr"/>
+      <c r="J148" s="9" t="inlineStr"/>
+      <c r="K148" s="9">
+        <f>IF(C148*J148=0,"",C148*J148)</f>
         <v/>
       </c>
     </row>
@@ -5419,10 +5648,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+22+k+1+4+w","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H149" s="13" t="inlineStr"/>
-      <c r="I149" s="14" t="inlineStr"/>
-      <c r="J149" s="14">
-        <f>IF(C149*I149=0,"",C149*I149)</f>
+      <c r="H149" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
+        <v/>
+      </c>
+      <c r="I149" s="13" t="inlineStr"/>
+      <c r="J149" s="14" t="inlineStr"/>
+      <c r="K149" s="14">
+        <f>IF(C149*J149=0,"",C149*J149)</f>
         <v/>
       </c>
     </row>
@@ -5454,10 +5687,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+4%2C7+k+1+4+w","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H150" s="8" t="inlineStr"/>
-      <c r="I150" s="9" t="inlineStr"/>
-      <c r="J150" s="9">
-        <f>IF(C150*I150=0,"",C150*I150)</f>
+      <c r="H150" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
+        <v/>
+      </c>
+      <c r="I150" s="8" t="inlineStr"/>
+      <c r="J150" s="9" t="inlineStr"/>
+      <c r="K150" s="9">
+        <f>IF(C150*J150=0,"",C150*J150)</f>
         <v/>
       </c>
     </row>
@@ -5496,10 +5733,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=pastilha+peltier+tec1+12706","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H152" s="8" t="inlineStr"/>
-      <c r="I152" s="9" t="inlineStr"/>
-      <c r="J152" s="9">
-        <f>IF(C152*I152=0,"",C152*I152)</f>
+      <c r="H152" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-tec1-12706-peltier-module.html","🌏 TEC1-12706 peltier module")</f>
+        <v/>
+      </c>
+      <c r="I152" s="8" t="inlineStr"/>
+      <c r="J152" s="9" t="inlineStr"/>
+      <c r="K152" s="9">
+        <f>IF(C152*J152=0,"",C152*J152)</f>
         <v/>
       </c>
     </row>
@@ -5531,10 +5772,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=aquecedor+ptc+ceramico+24+v+80+w","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H153" s="13" t="inlineStr"/>
-      <c r="I153" s="14" t="inlineStr"/>
-      <c r="J153" s="14">
-        <f>IF(C153*I153=0,"",C153*I153)</f>
+      <c r="H153" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-24v-ptc-heater-element-with-fan.html","🌏 24V PTC heater element wit")</f>
+        <v/>
+      </c>
+      <c r="I153" s="13" t="inlineStr"/>
+      <c r="J153" s="14" t="inlineStr"/>
+      <c r="K153" s="14">
+        <f>IF(C153*J153=0,"",C153*J153)</f>
         <v/>
       </c>
     </row>
@@ -5566,10 +5811,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=dissipador+cooler+80+mm+p+lado+quente","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H154" s="8" t="inlineStr"/>
-      <c r="I154" s="9" t="inlineStr"/>
-      <c r="J154" s="9">
-        <f>IF(C154*I154=0,"",C154*I154)</f>
+      <c r="H154" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-80mm-heatsink-fan-cpu-cooler-3pin.html","🌏 80mm heatsink fan CPU cool")</f>
+        <v/>
+      </c>
+      <c r="I154" s="8" t="inlineStr"/>
+      <c r="J154" s="9" t="inlineStr"/>
+      <c r="K154" s="9">
+        <f>IF(C154*J154=0,"",C154*J154)</f>
         <v/>
       </c>
     </row>
@@ -5601,10 +5850,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=pasta+termica","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H155" s="13" t="inlineStr"/>
-      <c r="I155" s="14" t="inlineStr"/>
-      <c r="J155" s="14">
-        <f>IF(C155*I155=0,"",C155*I155)</f>
+      <c r="H155" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-thermal-paste-syringe.html","🌏 thermal paste syringe")</f>
+        <v/>
+      </c>
+      <c r="I155" s="13" t="inlineStr"/>
+      <c r="J155" s="14" t="inlineStr"/>
+      <c r="K155" s="14">
+        <f>IF(C155*J155=0,"",C155*J155)</f>
         <v/>
       </c>
     </row>
@@ -5636,10 +5889,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=fan+60+60+mm+12+v","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H156" s="8" t="inlineStr"/>
-      <c r="I156" s="9" t="inlineStr"/>
-      <c r="J156" s="9">
-        <f>IF(C156*I156=0,"",C156*I156)</f>
+      <c r="H156" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-60mm-fan-12v-dc.html","🌏 60mm fan 12V DC")</f>
+        <v/>
+      </c>
+      <c r="I156" s="8" t="inlineStr"/>
+      <c r="J156" s="9" t="inlineStr"/>
+      <c r="K156" s="9">
+        <f>IF(C156*J156=0,"",C156*J156)</f>
         <v/>
       </c>
     </row>
@@ -5671,10 +5928,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=fan+40+40+mm+12+v","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H157" s="13" t="inlineStr"/>
-      <c r="I157" s="14" t="inlineStr"/>
-      <c r="J157" s="14">
-        <f>IF(C157*I157=0,"",C157*I157)</f>
+      <c r="H157" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-40mm-fan-12v-dc.html","🌏 40mm fan 12V DC")</f>
+        <v/>
+      </c>
+      <c r="I157" s="13" t="inlineStr"/>
+      <c r="J157" s="14" t="inlineStr"/>
+      <c r="K157" s="14">
+        <f>IF(C157*J157=0,"",C157*J157)</f>
         <v/>
       </c>
     </row>
@@ -5713,10 +5974,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=sensor+ds18b20+prova+d+agua","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H159" s="13" t="inlineStr"/>
-      <c r="I159" s="14" t="inlineStr"/>
-      <c r="J159" s="14">
-        <f>IF(C159*I159=0,"",C159*I159)</f>
+      <c r="H159" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-ds18b20-waterproof-temperature-sensor.html","🌏 DS18B20 waterproof tempera")</f>
+        <v/>
+      </c>
+      <c r="I159" s="13" t="inlineStr"/>
+      <c r="J159" s="14" t="inlineStr"/>
+      <c r="K159" s="14">
+        <f>IF(C159*J159=0,"",C159*J159)</f>
         <v/>
       </c>
     </row>
@@ -5748,10 +6013,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+4%2C7+k+1+4+w","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H160" s="8" t="inlineStr"/>
-      <c r="I160" s="9" t="inlineStr"/>
-      <c r="J160" s="9">
-        <f>IF(C160*I160=0,"",C160*I160)</f>
+      <c r="H160" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
+        <v/>
+      </c>
+      <c r="I160" s="8" t="inlineStr"/>
+      <c r="J160" s="9" t="inlineStr"/>
+      <c r="K160" s="9">
+        <f>IF(C160*J160=0,"",C160*J160)</f>
         <v/>
       </c>
     </row>
@@ -5783,10 +6052,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=sensor+am2315c","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H161" s="13" t="inlineStr"/>
-      <c r="I161" s="14" t="inlineStr"/>
-      <c r="J161" s="14">
-        <f>IF(C161*I161=0,"",C161*I161)</f>
+      <c r="H161" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-am2315c-temperature-humidity-sensor.html","🌏 AM2315C temperature humidi")</f>
+        <v/>
+      </c>
+      <c r="I161" s="13" t="inlineStr"/>
+      <c r="J161" s="14" t="inlineStr"/>
+      <c r="K161" s="14">
+        <f>IF(C161*J161=0,"",C161*J161)</f>
         <v/>
       </c>
     </row>
@@ -5818,10 +6091,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=capacitor+ceramico+100+nf","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H162" s="8" t="inlineStr"/>
-      <c r="I162" s="9" t="inlineStr"/>
-      <c r="J162" s="9">
-        <f>IF(C162*I162=0,"",C162*I162)</f>
+      <c r="H162" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-100nf-ceramic-capacitor.html","🌏 100nF ceramic capacitor")</f>
+        <v/>
+      </c>
+      <c r="I162" s="8" t="inlineStr"/>
+      <c r="J162" s="9" t="inlineStr"/>
+      <c r="K162" s="9">
+        <f>IF(C162*J162=0,"",C162*J162)</f>
         <v/>
       </c>
     </row>
@@ -5853,10 +6130,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+220+1+4+w","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H163" s="13" t="inlineStr"/>
-      <c r="I163" s="14" t="inlineStr"/>
-      <c r="J163" s="14">
-        <f>IF(C163*I163=0,"",C163*I163)</f>
+      <c r="H163" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
+        <v/>
+      </c>
+      <c r="I163" s="13" t="inlineStr"/>
+      <c r="J163" s="14" t="inlineStr"/>
+      <c r="K163" s="14">
+        <f>IF(C163*J163=0,"",C163*J163)</f>
         <v/>
       </c>
     </row>
@@ -5895,10 +6176,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=sensor+ina219","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H165" s="13" t="inlineStr"/>
-      <c r="I165" s="14" t="inlineStr"/>
-      <c r="J165" s="14">
-        <f>IF(C165*I165=0,"",C165*I165)</f>
+      <c r="H165" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-ina219-current-sensor-module.html","🌏 INA219 current sensor modu")</f>
+        <v/>
+      </c>
+      <c r="I165" s="13" t="inlineStr"/>
+      <c r="J165" s="14" t="inlineStr"/>
+      <c r="K165" s="14">
+        <f>IF(C165*J165=0,"",C165*J165)</f>
         <v/>
       </c>
     </row>
@@ -5931,9 +6216,10 @@
         <v/>
       </c>
       <c r="H166" s="8" t="inlineStr"/>
-      <c r="I166" s="9" t="inlineStr"/>
-      <c r="J166" s="9">
-        <f>IF(C166*I166=0,"",C166*I166)</f>
+      <c r="I166" s="8" t="inlineStr"/>
+      <c r="J166" s="9" t="inlineStr"/>
+      <c r="K166" s="9">
+        <f>IF(C166*J166=0,"",C166*J166)</f>
         <v/>
       </c>
     </row>
@@ -5966,9 +6252,10 @@
         <v/>
       </c>
       <c r="H167" s="13" t="inlineStr"/>
-      <c r="I167" s="14" t="inlineStr"/>
-      <c r="J167" s="14">
-        <f>IF(C167*I167=0,"",C167*I167)</f>
+      <c r="I167" s="13" t="inlineStr"/>
+      <c r="J167" s="14" t="inlineStr"/>
+      <c r="K167" s="14">
+        <f>IF(C167*J167=0,"",C167*J167)</f>
         <v/>
       </c>
     </row>
@@ -6000,10 +6287,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=placa+ilhada+pequena","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H168" s="8" t="inlineStr"/>
-      <c r="I168" s="9" t="inlineStr"/>
-      <c r="J168" s="9">
-        <f>IF(C168*I168=0,"",C168*I168)</f>
+      <c r="H168" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-perfboard-prototype-pcb.html","🌏 perfboard prototype PCB")</f>
+        <v/>
+      </c>
+      <c r="I168" s="8" t="inlineStr"/>
+      <c r="J168" s="9" t="inlineStr"/>
+      <c r="K168" s="9">
+        <f>IF(C168*J168=0,"",C168*J168)</f>
         <v/>
       </c>
     </row>
@@ -6035,10 +6326,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+220+5+w","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H169" s="13" t="inlineStr"/>
-      <c r="I169" s="14" t="inlineStr"/>
-      <c r="J169" s="14">
-        <f>IF(C169*I169=0,"",C169*I169)</f>
+      <c r="H169" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
+        <v/>
+      </c>
+      <c r="I169" s="13" t="inlineStr"/>
+      <c r="J169" s="14" t="inlineStr"/>
+      <c r="K169" s="14">
+        <f>IF(C169*J169=0,"",C169*J169)</f>
         <v/>
       </c>
     </row>
@@ -6070,10 +6365,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+1%2C2+k+1+4+w","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H170" s="8" t="inlineStr"/>
-      <c r="I170" s="9" t="inlineStr"/>
-      <c r="J170" s="9">
-        <f>IF(C170*I170=0,"",C170*I170)</f>
+      <c r="H170" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
+        <v/>
+      </c>
+      <c r="I170" s="8" t="inlineStr"/>
+      <c r="J170" s="9" t="inlineStr"/>
+      <c r="K170" s="9">
+        <f>IF(C170*J170=0,"",C170*J170)</f>
         <v/>
       </c>
     </row>
@@ -6105,10 +6404,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=led+5+mm+difuso","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H171" s="13" t="inlineStr"/>
-      <c r="I171" s="14" t="inlineStr"/>
-      <c r="J171" s="14">
-        <f>IF(C171*I171=0,"",C171*I171)</f>
+      <c r="H171" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-5mm-diffused-led.html","🌏 5mm diffused LED")</f>
+        <v/>
+      </c>
+      <c r="I171" s="13" t="inlineStr"/>
+      <c r="J171" s="14" t="inlineStr"/>
+      <c r="K171" s="14">
+        <f>IF(C171*J171=0,"",C171*J171)</f>
         <v/>
       </c>
     </row>
@@ -6140,10 +6443,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=micro+chave+jumper","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H172" s="8" t="inlineStr"/>
-      <c r="I172" s="9" t="inlineStr"/>
-      <c r="J172" s="9">
-        <f>IF(C172*I172=0,"",C172*I172)</f>
+      <c r="H172" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-spdt-micro-switch-small.html","🌏 SPDT micro switch small")</f>
+        <v/>
+      </c>
+      <c r="I172" s="8" t="inlineStr"/>
+      <c r="J172" s="9" t="inlineStr"/>
+      <c r="K172" s="9">
+        <f>IF(C172*J172=0,"",C172*J172)</f>
         <v/>
       </c>
     </row>
@@ -6176,9 +6483,10 @@
         <v/>
       </c>
       <c r="H173" s="13" t="inlineStr"/>
-      <c r="I173" s="14" t="inlineStr"/>
-      <c r="J173" s="14">
-        <f>IF(C173*I173=0,"",C173*I173)</f>
+      <c r="I173" s="13" t="inlineStr"/>
+      <c r="J173" s="14" t="inlineStr"/>
+      <c r="K173" s="14">
+        <f>IF(C173*J173=0,"",C173*J173)</f>
         <v/>
       </c>
     </row>
@@ -6217,10 +6525,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=placa+ilhada","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H175" s="13" t="inlineStr"/>
-      <c r="I175" s="14" t="inlineStr"/>
-      <c r="J175" s="14">
-        <f>IF(C175*I175=0,"",C175*I175)</f>
+      <c r="H175" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-perfboard-prototype-pcb.html","🌏 perfboard prototype PCB")</f>
+        <v/>
+      </c>
+      <c r="I175" s="13" t="inlineStr"/>
+      <c r="J175" s="14" t="inlineStr"/>
+      <c r="K175" s="14">
+        <f>IF(C175*J175=0,"",C175*J175)</f>
         <v/>
       </c>
     </row>
@@ -6253,9 +6565,10 @@
         <v/>
       </c>
       <c r="H176" s="8" t="inlineStr"/>
-      <c r="I176" s="9" t="inlineStr"/>
-      <c r="J176" s="9">
-        <f>IF(C176*I176=0,"",C176*I176)</f>
+      <c r="I176" s="8" t="inlineStr"/>
+      <c r="J176" s="9" t="inlineStr"/>
+      <c r="K176" s="9">
+        <f>IF(C176*J176=0,"",C176*J176)</f>
         <v/>
       </c>
     </row>
@@ -6287,10 +6600,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=borne+kf350+kre+passo+3%2C5+mm","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H177" s="13" t="inlineStr"/>
-      <c r="I177" s="14" t="inlineStr"/>
-      <c r="J177" s="14">
-        <f>IF(C177*I177=0,"",C177*I177)</f>
+      <c r="H177" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-kf350-3-5mm-pcb-screw-terminal-block.html","🌏 KF350 3.5mm PCB screw term")</f>
+        <v/>
+      </c>
+      <c r="I177" s="13" t="inlineStr"/>
+      <c r="J177" s="14" t="inlineStr"/>
+      <c r="K177" s="14">
+        <f>IF(C177*J177=0,"",C177*J177)</f>
         <v/>
       </c>
     </row>
@@ -6322,10 +6639,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=ci+uln2803a","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H178" s="8" t="inlineStr"/>
-      <c r="I178" s="9" t="inlineStr"/>
-      <c r="J178" s="9">
-        <f>IF(C178*I178=0,"",C178*I178)</f>
+      <c r="H178" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-uln2803a-dip18-darlington.html","🌏 ULN2803A DIP18 darlington")</f>
+        <v/>
+      </c>
+      <c r="I178" s="8" t="inlineStr"/>
+      <c r="J178" s="9" t="inlineStr"/>
+      <c r="K178" s="9">
+        <f>IF(C178*J178=0,"",C178*J178)</f>
         <v/>
       </c>
     </row>
@@ -6357,10 +6678,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=soquete+dip+18+pinos","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H179" s="13" t="inlineStr"/>
-      <c r="I179" s="14" t="inlineStr"/>
-      <c r="J179" s="14">
-        <f>IF(C179*I179=0,"",C179*I179)</f>
+      <c r="H179" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-dip18-ic-socket.html","🌏 DIP18 IC socket")</f>
+        <v/>
+      </c>
+      <c r="I179" s="13" t="inlineStr"/>
+      <c r="J179" s="14" t="inlineStr"/>
+      <c r="K179" s="14">
+        <f>IF(C179*J179=0,"",C179*J179)</f>
         <v/>
       </c>
     </row>
@@ -6393,9 +6718,10 @@
         <v/>
       </c>
       <c r="H180" s="8" t="inlineStr"/>
-      <c r="I180" s="9" t="inlineStr"/>
-      <c r="J180" s="9">
-        <f>IF(C180*I180=0,"",C180*I180)</f>
+      <c r="I180" s="8" t="inlineStr"/>
+      <c r="J180" s="9" t="inlineStr"/>
+      <c r="K180" s="9">
+        <f>IF(C180*J180=0,"",C180*J180)</f>
         <v/>
       </c>
     </row>
@@ -6428,9 +6754,10 @@
         <v/>
       </c>
       <c r="H181" s="13" t="inlineStr"/>
-      <c r="I181" s="14" t="inlineStr"/>
-      <c r="J181" s="14">
-        <f>IF(C181*I181=0,"",C181*I181)</f>
+      <c r="I181" s="13" t="inlineStr"/>
+      <c r="J181" s="14" t="inlineStr"/>
+      <c r="K181" s="14">
+        <f>IF(C181*J181=0,"",C181*J181)</f>
         <v/>
       </c>
     </row>
@@ -6462,10 +6789,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=termorretratil+2+mm","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H182" s="8" t="inlineStr"/>
-      <c r="I182" s="9" t="inlineStr"/>
-      <c r="J182" s="9">
-        <f>IF(C182*I182=0,"",C182*I182)</f>
+      <c r="H182" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-heat-shrink-tubing-kit.html","🌏 heat shrink tubing kit")</f>
+        <v/>
+      </c>
+      <c r="I182" s="8" t="inlineStr"/>
+      <c r="J182" s="9" t="inlineStr"/>
+      <c r="K182" s="9">
+        <f>IF(C182*J182=0,"",C182*J182)</f>
         <v/>
       </c>
     </row>
@@ -6498,9 +6829,10 @@
         <v/>
       </c>
       <c r="H183" s="13" t="inlineStr"/>
-      <c r="I183" s="14" t="inlineStr"/>
-      <c r="J183" s="14">
-        <f>IF(C183*I183=0,"",C183*I183)</f>
+      <c r="I183" s="13" t="inlineStr"/>
+      <c r="J183" s="14" t="inlineStr"/>
+      <c r="K183" s="14">
+        <f>IF(C183*J183=0,"",C183*J183)</f>
         <v/>
       </c>
     </row>
@@ -6544,9 +6876,10 @@
         <v/>
       </c>
       <c r="H185" s="13" t="inlineStr"/>
-      <c r="I185" s="14" t="inlineStr"/>
-      <c r="J185" s="14">
-        <f>IF(C185*I185=0,"",C185*I185)</f>
+      <c r="I185" s="13" t="inlineStr"/>
+      <c r="J185" s="14" t="inlineStr"/>
+      <c r="K185" s="14">
+        <f>IF(C185*J185=0,"",C185*J185)</f>
         <v/>
       </c>
     </row>
@@ -6583,9 +6916,10 @@
         <v/>
       </c>
       <c r="H186" s="8" t="inlineStr"/>
-      <c r="I186" s="9" t="inlineStr"/>
-      <c r="J186" s="9">
-        <f>IF(C186*I186=0,"",C186*I186)</f>
+      <c r="I186" s="8" t="inlineStr"/>
+      <c r="J186" s="9" t="inlineStr"/>
+      <c r="K186" s="9">
+        <f>IF(C186*J186=0,"",C186*J186)</f>
         <v/>
       </c>
     </row>
@@ -6622,9 +6956,10 @@
         <v/>
       </c>
       <c r="H187" s="13" t="inlineStr"/>
-      <c r="I187" s="14" t="inlineStr"/>
-      <c r="J187" s="14">
-        <f>IF(C187*I187=0,"",C187*I187)</f>
+      <c r="I187" s="13" t="inlineStr"/>
+      <c r="J187" s="14" t="inlineStr"/>
+      <c r="K187" s="14">
+        <f>IF(C187*J187=0,"",C187*J187)</f>
         <v/>
       </c>
     </row>
@@ -6661,9 +6996,10 @@
         <v/>
       </c>
       <c r="H188" s="8" t="inlineStr"/>
-      <c r="I188" s="9" t="inlineStr"/>
-      <c r="J188" s="9">
-        <f>IF(C188*I188=0,"",C188*I188)</f>
+      <c r="I188" s="8" t="inlineStr"/>
+      <c r="J188" s="9" t="inlineStr"/>
+      <c r="K188" s="9">
+        <f>IF(C188*J188=0,"",C188*J188)</f>
         <v/>
       </c>
     </row>
@@ -6700,9 +7036,10 @@
         <v/>
       </c>
       <c r="H189" s="13" t="inlineStr"/>
-      <c r="I189" s="14" t="inlineStr"/>
-      <c r="J189" s="14">
-        <f>IF(C189*I189=0,"",C189*I189)</f>
+      <c r="I189" s="13" t="inlineStr"/>
+      <c r="J189" s="14" t="inlineStr"/>
+      <c r="K189" s="14">
+        <f>IF(C189*J189=0,"",C189*J189)</f>
         <v/>
       </c>
     </row>
@@ -6739,9 +7076,10 @@
         <v/>
       </c>
       <c r="H190" s="8" t="inlineStr"/>
-      <c r="I190" s="9" t="inlineStr"/>
-      <c r="J190" s="9">
-        <f>IF(C190*I190=0,"",C190*I190)</f>
+      <c r="I190" s="8" t="inlineStr"/>
+      <c r="J190" s="9" t="inlineStr"/>
+      <c r="K190" s="9">
+        <f>IF(C190*J190=0,"",C190*J190)</f>
         <v/>
       </c>
     </row>
@@ -6778,9 +7116,10 @@
         <v/>
       </c>
       <c r="H191" s="13" t="inlineStr"/>
-      <c r="I191" s="14" t="inlineStr"/>
-      <c r="J191" s="14">
-        <f>IF(C191*I191=0,"",C191*I191)</f>
+      <c r="I191" s="13" t="inlineStr"/>
+      <c r="J191" s="14" t="inlineStr"/>
+      <c r="K191" s="14">
+        <f>IF(C191*J191=0,"",C191*J191)</f>
         <v/>
       </c>
     </row>
@@ -6817,9 +7156,10 @@
         <v/>
       </c>
       <c r="H192" s="8" t="inlineStr"/>
-      <c r="I192" s="9" t="inlineStr"/>
-      <c r="J192" s="9">
-        <f>IF(C192*I192=0,"",C192*I192)</f>
+      <c r="I192" s="8" t="inlineStr"/>
+      <c r="J192" s="9" t="inlineStr"/>
+      <c r="K192" s="9">
+        <f>IF(C192*J192=0,"",C192*J192)</f>
         <v/>
       </c>
     </row>
@@ -6856,9 +7196,10 @@
         <v/>
       </c>
       <c r="H193" s="13" t="inlineStr"/>
-      <c r="I193" s="14" t="inlineStr"/>
-      <c r="J193" s="14">
-        <f>IF(C193*I193=0,"",C193*I193)</f>
+      <c r="I193" s="13" t="inlineStr"/>
+      <c r="J193" s="14" t="inlineStr"/>
+      <c r="K193" s="14">
+        <f>IF(C193*J193=0,"",C193*J193)</f>
         <v/>
       </c>
     </row>
@@ -6894,10 +7235,14 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=espaguete+termorretratil","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H194" s="8" t="inlineStr"/>
-      <c r="I194" s="9" t="inlineStr"/>
-      <c r="J194" s="9">
-        <f>IF(C194*I194=0,"",C194*I194)</f>
+      <c r="H194" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-heat-shrink-tubing-kit.html","🌏 heat shrink tubing kit")</f>
+        <v/>
+      </c>
+      <c r="I194" s="8" t="inlineStr"/>
+      <c r="J194" s="9" t="inlineStr"/>
+      <c r="K194" s="9">
+        <f>IF(C194*J194=0,"",C194*J194)</f>
         <v/>
       </c>
     </row>
@@ -6934,9 +7279,10 @@
         <v/>
       </c>
       <c r="H195" s="13" t="inlineStr"/>
-      <c r="I195" s="14" t="inlineStr"/>
-      <c r="J195" s="14">
-        <f>IF(C195*I195=0,"",C195*I195)</f>
+      <c r="I195" s="13" t="inlineStr"/>
+      <c r="J195" s="14" t="inlineStr"/>
+      <c r="K195" s="14">
+        <f>IF(C195*J195=0,"",C195*J195)</f>
         <v/>
       </c>
     </row>
@@ -6973,9 +7319,10 @@
         <v/>
       </c>
       <c r="H196" s="8" t="inlineStr"/>
-      <c r="I196" s="9" t="inlineStr"/>
-      <c r="J196" s="9">
-        <f>IF(C196*I196=0,"",C196*I196)</f>
+      <c r="I196" s="8" t="inlineStr"/>
+      <c r="J196" s="9" t="inlineStr"/>
+      <c r="K196" s="9">
+        <f>IF(C196*J196=0,"",C196*J196)</f>
         <v/>
       </c>
     </row>
@@ -7012,46 +7359,47 @@
         <v/>
       </c>
       <c r="H197" s="13" t="inlineStr"/>
-      <c r="I197" s="14" t="inlineStr"/>
-      <c r="J197" s="14">
-        <f>IF(C197*I197=0,"",C197*I197)</f>
+      <c r="I197" s="13" t="inlineStr"/>
+      <c r="J197" s="14" t="inlineStr"/>
+      <c r="K197" s="14">
+        <f>IF(C197*J197=0,"",C197*J197)</f>
         <v/>
       </c>
     </row>
     <row r="199">
-      <c r="H199" s="15" t="inlineStr">
+      <c r="I199" s="17" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="J199" s="16">
-        <f>SUM(J5:J197)</f>
+      <c r="K199" s="18">
+        <f>SUM(K5:K197)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J197"/>
+  <autoFilter ref="A4:K197"/>
   <mergeCells count="20">
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A184:J184"/>
-    <mergeCell ref="A38:J38"/>
-    <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A44:J44"/>
-    <mergeCell ref="A93:J93"/>
-    <mergeCell ref="A58:J58"/>
-    <mergeCell ref="A142:J142"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A88:J88"/>
-    <mergeCell ref="A174:J174"/>
-    <mergeCell ref="A128:J128"/>
-    <mergeCell ref="A164:J164"/>
-    <mergeCell ref="A74:J74"/>
-    <mergeCell ref="A158:J158"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A104:J104"/>
-    <mergeCell ref="A151:J151"/>
+    <mergeCell ref="A58:K58"/>
+    <mergeCell ref="A142:K142"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A88:K88"/>
+    <mergeCell ref="A128:K128"/>
+    <mergeCell ref="A174:K174"/>
+    <mergeCell ref="A164:K164"/>
+    <mergeCell ref="A158:K158"/>
+    <mergeCell ref="A74:K74"/>
+    <mergeCell ref="A104:K104"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A151:K151"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="A184:K184"/>
+    <mergeCell ref="A38:K38"/>
+    <mergeCell ref="A28:K28"/>
+    <mergeCell ref="A93:K93"/>
+    <mergeCell ref="A44:K44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7073,161 +7421,161 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>ORDEM DE CONSTRUÇÃO — 5 camadas</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>Camada</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>Documentos</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>Critério de aceitação</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>CAMADA 0</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>Fundamentos</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>Visão geral · Arquitetura de energia · BOM</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="22" t="inlineStr">
         <is>
           <t>Entregável: BOM fechada e cálculos feitos</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>CAMADA 1</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Maquete</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>Base e chão de fábrica · Subestação e postes · Câmara térmica</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>Entregável: cenário pronto, sem eletrônica</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>CAMADA 2</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Painel</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>Dimensionamento · Layout · Furação · Fixação nos trilhos</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>Entregável: painel montado, sem um fio ligado</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>CAMADA 3</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>Elétrica</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>Força e distribuição · Comando e proteções · Sinais e sensores</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>Entregável: energizado e medido, sem firmware</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>CAMADA 4</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Programação</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>Firmware Arduino · ESP32, IHM e IoT</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>Entregável: software gravado e testado em bancada</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>CAMADA 5</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>Integração</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>Montagem final · Comissionamento · Ensaios</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>Entregável: projeto funcionando e documentado</t>
         </is>
@@ -7255,295 +7603,295 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>NÚMEROS DO PROJETO</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Arquitetura de energia</t>
         </is>
       </c>
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>Potência em 24 V — carga térmica sem conversor</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Tensão de entrada</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>127 V CA</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Barramento de distribuição</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>24 V CC (SELV)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Potência instalada (fonte)</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>240 W · 10 A</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Consumo calculado</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>≈ 166 W · 6,9 A @ 24 V</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Folga da fonte</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>1,44× (44 %) — a fonte de 150 W NÃO atende</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Corrente CA de entrada</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>2,37 A</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Queda de tensão na linha dos postes</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>0,21 V (0,86 %)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>Conversores</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>2 × LM2596 com display (T2 e T3) · P1 é derivação direta</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>Tensões derivadas</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>24,0 V potência (direto) · 12,0 V auxiliar · 5,10 V comando · 3,3 V ESP32</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>Fusíveis dos ramais</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>F1 = 10 A · F2 = 2 A · F3 = 2 A (sem F4/F5, sem crowbar)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Níveis de proteção</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>5 (do disjuntor ao intertravamento por software)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>Volume útil da câmara</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>5,0 litros (200 × 100 × 250 mm)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>Carga térmica calculada</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>≈ 9,5 W</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t>Refrigeração</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>2 × TEC1-12706 EM SÉRIE · 24 V · 6,0 A · 144 W</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>Capacidade das Peltier a ΔT = 20 K</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>≈ 60 W (margem de 6,3×)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="inlineStr">
+      <c r="A19" s="23" t="inlineStr">
         <is>
           <t>Dissipação no lado quente</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>≈ 200 W — 2 conjuntos dissipador + cooler 80 mm</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>Aquecimento</t>
         </is>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>PTC cerâmico de 24 V · 60 W · 2,5 A</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>Isolamento</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>XPS 30 mm + barreira de vapor · U = 0,86 W/m²·K</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>Porta</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>Dupla · U = 2,42 W/m²·K (não condensa)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="23" t="inlineStr">
         <is>
           <t>Base da maquete</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>1500 × 500 mm · escala cenográfica 1:50</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>Painel</t>
         </is>
       </c>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>400 × 500 × 200 mm · 3 trilhos DIN</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>Componentes discretos</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>6 + 1 CI ULN2803 na PI-1 · 2 nos BTS7960 · 4 nos postes da maquete</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="23" t="inlineStr">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t>Sinalização</t>
         </is>
       </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>4 sinaleiros 22 mm de 24 V (via ULN2803) · 4 LEDs brancos de 5 V na maquete</t>
         </is>

--- a/BOM_Projeto_Integrador.xlsx
+++ b/BOM_Projeto_Integrador.xlsx
@@ -8,11 +8,17 @@
   </bookViews>
   <sheets>
     <sheet name="Lista de Compras" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Ordem de Construção" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Dados do Projeto" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Inventario React" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Fiacao React" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Divergencias" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Ordem de Construção" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Dados do Projeto" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lista de Compras'!$A$4:$K$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lista de Compras'!$A$4:$K$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Inventario React'!$A$1:$E$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Fiacao React'!$A$1:$E$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Divergencias'!$A$1:$E$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -134,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -178,22 +184,25 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -573,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K199"/>
+  <dimension ref="A1:K174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -599,7 +608,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Lista de materiais · gerada de 03_lista_materiais.md em 14/08/2026 07:42 · arquitetura 127 V CA → 24 V CC → 12 / 5 / 3,3 V</t>
+          <t>Lista de materiais · gerada de 03_lista_materiais.md em 18/08/2026 17:45 · arquitetura 127 V CA → 24 V CC → 12 / 5 / 3,3 V</t>
         </is>
       </c>
     </row>
@@ -753,30 +762,30 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Chave rotativa 0-1 22 mm</t>
+          <t>Cabo PP 3×1,5 mm² + plugue</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,5 m</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>≥ 6 A / 250 V AC, 2 posições com retenção, fixação 22 mm</t>
+          <t>Cabo de entrada AC com plugue 2P+T 10 A</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>chave seletora 2 posicoes 22mm</t>
+          <t>cabo pp 3x1,5 com plugue</t>
         </is>
       </c>
       <c r="F8" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/chave-seletora-2-posicoes-22mm","🔎 chave seletora 2 posicoes 22")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-pp-3x1-5-com-plugue","🔎 cabo pp 3x1,5 com plugue")</f>
         <v/>
       </c>
       <c r="G8" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=chave+seletora+2+posicoes+22mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+pp+3x1%2C5+com+plugue","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H8" s="8" t="inlineStr"/>
@@ -793,30 +802,30 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Cabo PP 3×1,5 mm² + plugue</t>
+          <t>Prensa-cabo PG9 / PG13</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>1,5 m</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Cabo de entrada AC com plugue 2P+T 10 A</t>
+          <t>Entrada e saída de cabos da caixa da subestação</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>cabo pp 3x1,5 com plugue</t>
+          <t>prensa cabo pg9</t>
         </is>
       </c>
       <c r="F9" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-pp-3x1-5-com-plugue","🔎 cabo pp 3x1,5 com plugue")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/prensa-cabo-pg9","🔎 prensa cabo pg9")</f>
         <v/>
       </c>
       <c r="G9" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+pp+3x1%2C5+com+plugue","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=prensa+cabo+pg9","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H9" s="13" t="inlineStr"/>
@@ -833,30 +842,30 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Prensa-cabo PG9 / PG13</t>
+          <t>Borne DIN 4 mm²</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Entrada e saída de cabos da caixa da subestação</t>
+          <t>Distribuição 24 V e 0 V na subestação</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>prensa cabo pg9</t>
+          <t>borne trilho din 4mm parafuso</t>
         </is>
       </c>
       <c r="F10" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/prensa-cabo-pg9","🔎 prensa cabo pg9")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/borne-trilho-din-4mm-parafuso","🔎 borne trilho din 4mm parafus")</f>
         <v/>
       </c>
       <c r="G10" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=prensa+cabo+pg9","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=borne+trilho+din+4mm+parafuso","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H10" s="8" t="inlineStr"/>
@@ -873,33 +882,36 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Borne DIN 4 mm²</t>
+          <t>Cooler 60 mm 24 V</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Distribuição 24 V e 0 V na subestação</t>
+          <t>Exaustão da casa de comando (~29 W de perda da fonte). ⚠️ Obrigatório, não opcional — a casinha encolheu para 250 × 150 × 90 mm e a fonte continua dissipando o mesmo. ⚠️ 24 V: é a única tensão de saída disponível. Alternativa: 2× de 12 V em série</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>borne trilho din 4mm parafuso</t>
+          <t>cooler 60mm 24v</t>
         </is>
       </c>
       <c r="F11" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/borne-trilho-din-4mm-parafuso","🔎 borne trilho din 4mm parafus")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cooler-60mm-24v","🔎 cooler 60mm 24v")</f>
         <v/>
       </c>
       <c r="G11" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=borne+trilho+din+4mm+parafuso","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H11" s="13" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cooler+60mm+24v","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H11" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-60mm-fan-24v-dc.html","🌏 60mm fan 24V DC")</f>
+        <v/>
+      </c>
       <c r="I11" s="13" t="inlineStr"/>
       <c r="J11" s="14" t="inlineStr"/>
       <c r="K11" s="14">
@@ -913,7 +925,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Cooler 60 mm 24 V</t>
+          <t>Grade + filtro 60 mm</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -923,26 +935,23 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Exaustão da caixa da subestação (~18 W de perda). ⚠️ 24 V — é a única tensão que existe dentro da caixa. Alternativa: 2× de 12 V em série</t>
+          <t>Veneziana de entrada de ar da subestação</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>cooler 60mm 24v</t>
+          <t>grade cooler 60mm com filtro</t>
         </is>
       </c>
       <c r="F12" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/cooler-60mm-24v","🔎 cooler 60mm 24v")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/grade-cooler-60mm-com-filtro","🔎 grade cooler 60mm com filtro")</f>
         <v/>
       </c>
       <c r="G12" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=cooler+60mm+24v","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H12" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-60mm-fan-24v-dc.html","🌏 60mm fan 24V DC")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=grade+cooler+60mm+com+filtro","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H12" s="8" t="inlineStr"/>
       <c r="I12" s="8" t="inlineStr"/>
       <c r="J12" s="9" t="inlineStr"/>
       <c r="K12" s="9">
@@ -950,51 +959,58 @@
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="10" t="n">
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>E.2 — Conversores de tensão (os "transformadores" da maquete)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>Grade + filtro 60 mm</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>Veneziana de entrada de ar da subestação</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>grade cooler 60mm com filtro</t>
-        </is>
-      </c>
-      <c r="F13" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/grade-cooler-60mm-com-filtro","🔎 grade cooler 60mm com filtro")</f>
-        <v/>
-      </c>
-      <c r="G13" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=grade+cooler+60mm+com+filtro","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H13" s="13" t="inlineStr"/>
-      <c r="I13" s="13" t="inlineStr"/>
-      <c r="J13" s="14" t="inlineStr"/>
-      <c r="K13" s="14">
-        <f>IF(C13*J13=0,"",C13*J13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>E.2 — Conversores de tensão (os "transformadores" da maquete)</t>
-        </is>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>⭐ Kit 2× Módulo LM2596 com display</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>1 kit</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Step-down 3 A, Vin até 40 V, saída ajustável, display LED vermelho de 3 dígitos integrado. Um módulo vira o T2, o outro vira o T3</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>ver abaixo</t>
+        </is>
+      </c>
+      <c r="F14" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/kit-2-modulo-lm2596-display","🔎 kit 2 modulo lm2596 display")</f>
+        <v/>
+      </c>
+      <c r="G14" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=kit+2+modulo+lm2596+display","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H14" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-lm2596-buck-converter-voltmeter-display.html","🌏 LM2596 buck converter volt")</f>
+        <v/>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>Mercado Livre</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr"/>
+      <c r="K14" s="9">
+        <f>IF(C14*J14=0,"",C14*J14)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1003,41 +1019,28 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>⭐ Kit 2× Módulo LM2596 com display</t>
+          <t>→ T2 (poste P2, comando)</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>1 kit</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Step-down 3 A, Vin até 40 V, saída ajustável, display LED vermelho de 3 dígitos integrado. Um módulo vira o T2, o outro vira o T3</t>
+          <t>1º módulo do kit — alimenta Arduino, tela ES3C28P, RTC, lógica dos BTS, placa PI-1 e os LEDs da iluminação da maquete</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>ver abaixo</t>
-        </is>
-      </c>
-      <c r="F15" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/kit-2-modulo-lm2596-display","🔎 kit 2 modulo lm2596 display")</f>
-        <v/>
-      </c>
-      <c r="G15" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=kit+2+modulo+lm2596+display","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H15" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-lm2596-buck-converter-voltmeter-display.html","🌏 LM2596 buck converter volt")</f>
-        <v/>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>Mercado Livre</t>
-        </is>
-      </c>
+          <t>5,10 V</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr"/>
+      <c r="G15" s="13" t="inlineStr"/>
+      <c r="H15" s="13" t="inlineStr"/>
+      <c r="I15" s="13" t="inlineStr"/>
       <c r="J15" s="14" t="inlineStr"/>
       <c r="K15" s="14">
         <f>IF(C15*J15=0,"",C15*J15)</f>
@@ -1050,7 +1053,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>→ T2 (poste P2, comando)</t>
+          <t>→ T3 (poste P3, auxiliares)</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -1060,12 +1063,12 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>1º módulo do kit — alimenta Arduino, Nextion, SD/RTC, lógica dos BTS, placa PI-1 e os LEDs da iluminação da maquete</t>
+          <t>2º módulo do kit — alimenta as fans internas e os coolers</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>5,10 V</t>
+          <t>12,0 V</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr"/>
@@ -1084,27 +1087,36 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>→ T3 (poste P3, auxiliares)</t>
+          <t>Kit LM2596 reserva</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
+          <t>1 kit</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Opcional mas recomendado. São os únicos conversores do projeto; queimar um na véspera sem reserva significa não apresentar</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>2º módulo do kit — alimenta as fans internas e os coolers</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>12,0 V</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr"/>
-      <c r="G17" s="13" t="inlineStr"/>
-      <c r="H17" s="13" t="inlineStr"/>
+      <c r="F17" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/kit-lm2596-reserva","🔎 kit lm2596 reserva")</f>
+        <v/>
+      </c>
+      <c r="G17" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=kit+lm2596+reserva","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H17" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-lm2596-buck-converter-voltmeter-display.html","🌏 LM2596 buck converter volt")</f>
+        <v/>
+      </c>
       <c r="I17" s="13" t="inlineStr"/>
       <c r="J17" s="14" t="inlineStr"/>
       <c r="K17" s="14">
@@ -1118,17 +1130,17 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Kit LM2596 reserva</t>
+          <t>Dissipador de alumínio ~20 × 15 × 10 mm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>1 kit</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Opcional mas recomendado. São os únicos conversores do projeto; queimar um na véspera sem reserva significa não apresentar</t>
+          <t>⚠️ Obrigatório, colado no CI LM2596S de cada módulo. Sem ele o T3 passa dos 100 °C dentro do tubo — ver Doc 02 §2.8</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -1137,15 +1149,15 @@
         </is>
       </c>
       <c r="F18" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/kit-lm2596-reserva","🔎 kit lm2596 reserva")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/dissipador-aluminio-20-15-10-mm","🔎 dissipador aluminio 20 15 10")</f>
         <v/>
       </c>
       <c r="G18" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=kit+lm2596+reserva","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H18" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-lm2596-buck-converter-voltmeter-display.html","🌏 LM2596 buck converter volt")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=dissipador+aluminio+20+15+10+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H18" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-aluminum-heatsink-small.html","🌏 aluminum heatsink small")</f>
         <v/>
       </c>
       <c r="I18" s="8" t="inlineStr"/>
@@ -1161,17 +1173,17 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Dissipador de alumínio ~20 × 15 × 10 mm</t>
+          <t>Fita térmica dupla face</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>⚠️ Obrigatório, colado no CI LM2596S de cada módulo. Sem ele o T3 passa dos 100 °C dentro do tubo — ver Doc 02 §2.8</t>
+          <t>Fixação dos dissipadores</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
@@ -1180,15 +1192,15 @@
         </is>
       </c>
       <c r="F19" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/dissipador-aluminio-20-15-10-mm","🔎 dissipador aluminio 20 15 10")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-termica-dupla-face","🔎 fita termica dupla face")</f>
         <v/>
       </c>
       <c r="G19" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=dissipador+aluminio+20+15+10+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H19" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-aluminum-heatsink-small.html","🌏 aluminum heatsink small")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+termica+dupla+face","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H19" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-thermal-adhesive-tape-double-sided.html","🌏 thermal adhesive tape doub")</f>
         <v/>
       </c>
       <c r="I19" s="13" t="inlineStr"/>
@@ -1204,17 +1216,17 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Fita térmica dupla face</t>
+          <t>Acrílico transparente 1 mm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 lâmina</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Fixação dos dissipadores</t>
+          <t>Janelas de visualização nos 3 tubos dos postes (~20 × 12 mm cada) — protege o display e mantém o visual fechado</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -1223,17 +1235,14 @@
         </is>
       </c>
       <c r="F20" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-termica-dupla-face","🔎 fita termica dupla face")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/acrilico-transparente-1-mm","🔎 acrilico transparente 1 mm")</f>
         <v/>
       </c>
       <c r="G20" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+termica+dupla+face","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H20" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-thermal-adhesive-tape-double-sided.html","🌏 thermal adhesive tape doub")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=acrilico+transparente+1+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H20" s="8" t="inlineStr"/>
       <c r="I20" s="8" t="inlineStr"/>
       <c r="J20" s="9" t="inlineStr"/>
       <c r="K20" s="9">
@@ -1247,17 +1256,17 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Acrílico transparente 1 mm</t>
+          <t>Voltímetro + amperímetro digital 3 fios</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>1 lâmina</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Janelas de visualização nos 3 tubos dos postes (~20 × 12 mm cada) — protege o display e mantém o visual fechado</t>
+          <t>Único medidor comprado à parte — vai na caixa de derivação do P1, mostrando os 24,0 V do barramento e a corrente das Peltier ao vivo. Faixa: 0-100 V / 10 A</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -1266,14 +1275,17 @@
         </is>
       </c>
       <c r="F21" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/acrilico-transparente-1-mm","🔎 acrilico transparente 1 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/voltimetro-amperimetro-digital-3-fios","🔎 voltimetro amperimetro digit")</f>
         <v/>
       </c>
       <c r="G21" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=acrilico+transparente+1+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H21" s="13" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=voltimetro+amperimetro+digital+3+fios","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H21" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-dc-voltmeter-ammeter-100v-10a-digital.html","🌏 DC voltmeter ammeter 100V ")</f>
+        <v/>
+      </c>
       <c r="I21" s="13" t="inlineStr"/>
       <c r="J21" s="14" t="inlineStr"/>
       <c r="K21" s="14">
@@ -1281,54 +1293,51 @@
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="5" t="n">
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>E.3 — Proteção do sistema de energia</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Voltímetro + amperímetro digital 3 fios</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>Único medidor comprado à parte — vai na caixa de derivação do P1, mostrando os 24,0 V do barramento e a corrente das Peltier ao vivo. Faixa: 0-100 V / 10 A</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F22" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/voltimetro-amperimetro-digital-3-fios","🔎 voltimetro amperimetro digit")</f>
-        <v/>
-      </c>
-      <c r="G22" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=voltimetro+amperimetro+digital+3+fios","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H22" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-dc-voltmeter-ammeter-100v-10a-digital.html","🌏 DC voltmeter ammeter 100V ")</f>
-        <v/>
-      </c>
-      <c r="I22" s="8" t="inlineStr"/>
-      <c r="J22" s="9" t="inlineStr"/>
-      <c r="K22" s="9">
-        <f>IF(C22*J22=0,"",C22*J22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>E.3 — Proteção do sistema de energia</t>
-        </is>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Porta-fusível mini automotivo</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Fusível de LÂMINA (automotivo), não de vidro. Trilho DIN 35 mm ou bloco parafusado — ver nota abaixo</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>F1, F2, F3 — entrada dos 3 ramais, na subestação</t>
+        </is>
+      </c>
+      <c r="F23" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/porta-fusivel-mini-automotivo","🔎 porta fusivel mini automotiv")</f>
+        <v/>
+      </c>
+      <c r="G23" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=porta+fusivel+mini+automotivo","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H23" s="13" t="inlineStr"/>
+      <c r="I23" s="13" t="inlineStr"/>
+      <c r="J23" s="14" t="inlineStr"/>
+      <c r="K23" s="14">
+        <f>IF(C23*J23=0,"",C23*J23)</f>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -1337,30 +1346,30 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Porta-fusível mini automotivo DIN</t>
+          <t>*Alternativa:* bloco de 3 posições para fusível lâmina</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Trilho DIN 35 mm</t>
+          <t>Substitui os 3 suportes acima. ⚠️ Conferir: fusível lâmina · ≥ 10 A por posição · ≥ 32 Vdc · preferir entrada comum (1 entrada + 3 saídas). Parafusa na parede da caixa — dispensa trilho DIN na subestação</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>F1, F2, F3 — entrada dos 3 ramais</t>
+          <t>idem</t>
         </is>
       </c>
       <c r="F24" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/porta-fusivel-mini-automotivo-din","🔎 porta fusivel mini automotiv")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/alternativa-bloco-3-posicoes-fusivel-lamina","🔎 alternativa bloco 3 posicoes")</f>
         <v/>
       </c>
       <c r="G24" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=porta+fusivel+mini+automotivo+din","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=alternativa+bloco+3+posicoes+fusivel+lamina","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H24" s="8" t="inlineStr"/>
@@ -1670,7 +1679,7 @@
         <f>HYPERLINK("https://www.amazon.com.br/s?k=conector+circular+gx16+8+pinos","🔎 Amazon")</f>
         <v/>
       </c>
-      <c r="H33" s="16">
+      <c r="H33" s="15">
         <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-gx16-8-pin-aviation-connector.html","🌏 GX16 8 pin aviation connec")</f>
         <v/>
       </c>
@@ -1848,7 +1857,7 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Caixa 260 × 190 × 150 mm (L×P×A), frente voltada para a rua</t>
+          <t>CASA DE COMANDO 250 × 150 × 90 mm (L×P×A), face de operação voltada para a rua. Abriga apenas fonte, disjuntor e chave — os fusíveis de 24 V ficam no pátio aberto</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr"/>
@@ -1874,26 +1883,26 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Dobradiça pequena + fecho</t>
+          <t>Fio verde-amarelo 0,75 mm²</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>1 jogo</t>
+          <t>1 m</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Tampa de manutenção</t>
+          <t>⚡ Aterramento das estruturas metálicas do pátio à barra de terra (equipotencialização). Torre real é aterrada — vale ponto na defesa</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr"/>
       <c r="F40" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/dobradica-pequena-fecho","🔎 dobradica pequena fecho")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-verde-amarelo-0-75-mm","🔎 fio verde amarelo 0,75 mm")</f>
         <v/>
       </c>
       <c r="G40" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=dobradica+pequena+fecho","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+verde+amarelo+0%2C75+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H40" s="8" t="inlineStr"/>
@@ -1910,26 +1919,26 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>Tela metálica / alambrado miniatura</t>
+          <t>*Opcional:* arame / barra de latão 1,5–2 mm</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2 m</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Cerca do pátio da subestação (tela de aço, malha 3 mm)</t>
+          <t>Estruturas treliçadas do pátio. ⚠️ Latão aceita solda de estanho; alumínio não — se quiser treliça soldada, é latão</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr"/>
       <c r="F41" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/tela-metalica-alambrado-miniatura","🔎 tela metalica alambrado mini")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/arame-barra-latao-1-5-2-mm","🔎 arame barra latao 1,5 2 mm")</f>
         <v/>
       </c>
       <c r="G41" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=tela+metalica+alambrado+miniatura","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=arame+barra+latao+1%2C5+2+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H41" s="13" t="inlineStr"/>
@@ -1946,26 +1955,26 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Pedrisco / brita fina (aquário)</t>
+          <t>Dobradiça pequena + fecho</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>500 g</t>
+          <t>1 jogo</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Piso do pátio da subestação — como nas subestações reais</t>
+          <t>Tampa de manutenção</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr"/>
       <c r="F42" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/pedrisco-brita-fina","🔎 pedrisco brita fina")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/dobradica-pequena-fecho","🔎 dobradica pequena fecho")</f>
         <v/>
       </c>
       <c r="G42" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=pedrisco+brita+fina","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=dobradica+pequena+fecho","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H42" s="8" t="inlineStr"/>
@@ -1982,26 +1991,26 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>Placa "PERIGO ALTA TENSÃO"</t>
+          <t>Tela metálica / alambrado miniatura</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Impressa em papel adesivo, ~15 × 10 mm</t>
+          <t>Cerca do pátio (tela de aço, malha 3 mm). ⚠️ Funcional, não decorativa: com o pátio aberto, é ela que delimita a área e impede aproximação — mesma função da cerca de uma subestação real</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr"/>
       <c r="F43" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/placa-perigo-alta-tensao","🔎 placa perigo alta tensao")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tela-metalica-alambrado-miniatura","🔎 tela metalica alambrado mini")</f>
         <v/>
       </c>
       <c r="G43" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=placa+perigo+alta+tensao","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tela+metalica+alambrado+miniatura","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H43" s="13" t="inlineStr"/>
@@ -2012,39 +2021,68 @@
         <v/>
       </c>
     </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>M.3 — Postes e linha de distribuição</t>
-        </is>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Pedrisco / brita fina (aquário)</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>500 g</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Piso do pátio da subestação — como nas subestações reais</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr"/>
+      <c r="F44" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/pedrisco-brita-fina","🔎 pedrisco brita fina")</f>
+        <v/>
+      </c>
+      <c r="G44" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=pedrisco+brita+fina","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H44" s="8" t="inlineStr"/>
+      <c r="I44" s="8" t="inlineStr"/>
+      <c r="J44" s="9" t="inlineStr"/>
+      <c r="K44" s="9">
+        <f>IF(C44*J44=0,"",C44*J44)</f>
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>Tubo de alumínio Ø 8 mm</t>
+          <t>Placa "PERIGO ALTA TENSÃO"</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>1,5 m</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Cortar em 3 postes de 350 mm (300 mm visíveis + 50 mm de encaixe)</t>
+          <t>Impressa em papel adesivo, ~15 × 10 mm</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr"/>
       <c r="F45" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/tubo-aluminio-8-mm","🔎 tubo aluminio 8 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/placa-perigo-alta-tensao","🔎 placa perigo alta tensao")</f>
         <v/>
       </c>
       <c r="G45" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=tubo+aluminio+8+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=placa+perigo+alta+tensao","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H45" s="13" t="inlineStr"/>
@@ -2055,40 +2093,11 @@
         <v/>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>Barra chata de alumínio 12 × 2 mm</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>40 cm</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>Cruzetas — 3 peças de 90 mm + 3 de 60 mm</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr"/>
-      <c r="F46" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/barra-chata-aluminio-12-2-mm","🔎 barra chata aluminio 12 2 mm")</f>
-        <v/>
-      </c>
-      <c r="G46" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=barra+chata+aluminio+12+2+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H46" s="8" t="inlineStr"/>
-      <c r="I46" s="8" t="inlineStr"/>
-      <c r="J46" s="9" t="inlineStr"/>
-      <c r="K46" s="9">
-        <f>IF(C46*J46=0,"",C46*J46)</f>
-        <v/>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>M.3 — Postes e linha de distribuição</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -2097,26 +2106,26 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Fio rígido ENCAPADO 1,00 mm² VERMELHO ⬆</t>
+          <t>Tubo de alumínio Ø 8 mm</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>2 m</t>
+          <t>1,5 m</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Ramal R1 (potência, 6,0 A). ⚠️ Subiu de 0,75 para 1,00 mm² por causa da corrente das 2 Peltier. Nunca condutor nu — em CC qualquer ponte metálica é curto franco</t>
+          <t>Cortar em 3 postes de 350 mm (300 mm visíveis + 50 mm de encaixe)</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr"/>
       <c r="F47" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-rigido-encapado-1-00-mm-vermelho","🔎 fio rigido encapado 1,00 mm ")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tubo-aluminio-8-mm","🔎 tubo aluminio 8 mm")</f>
         <v/>
       </c>
       <c r="G47" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+rigido+encapado+1%2C00+mm+vermelho","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tubo+aluminio+8+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H47" s="13" t="inlineStr"/>
@@ -2133,26 +2142,26 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Fio rígido ENCAPADO 0,50 mm² MARROM</t>
+          <t>Barra chata de alumínio 12 × 2 mm</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>2 m</t>
+          <t>40 cm</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>Ramal R2 (comando)</t>
+          <t>Cruzetas — 3 peças de 90 mm + 3 de 60 mm</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr"/>
       <c r="F48" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-rigido-encapado-0-50-mm-marrom","🔎 fio rigido encapado 0,50 mm ")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/barra-chata-aluminio-12-2-mm","🔎 barra chata aluminio 12 2 mm")</f>
         <v/>
       </c>
       <c r="G48" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+rigido+encapado+0%2C50+mm+marrom","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=barra+chata+aluminio+12+2+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H48" s="8" t="inlineStr"/>
@@ -2169,7 +2178,7 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>Fio rígido ENCAPADO 0,50 mm² CINZA</t>
+          <t>Fio rígido ENCAPADO 1,00 mm² VERMELHO ⬆</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -2179,16 +2188,16 @@
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Ramal R3 (auxiliares)</t>
+          <t>Ramal R1 (potência, 6,0 A). ⚠️ Subiu de 0,75 para 1,00 mm² por causa da corrente das 2 Peltier. Nunca condutor nu — em CC qualquer ponte metálica é curto franco</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr"/>
       <c r="F49" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-rigido-encapado-0-50-mm-cinza","🔎 fio rigido encapado 0,50 mm ")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-rigido-encapado-1-00-mm-vermelho","🔎 fio rigido encapado 1,00 mm ")</f>
         <v/>
       </c>
       <c r="G49" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+rigido+encapado+0%2C50+mm+cinza","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+rigido+encapado+1%2C00+mm+vermelho","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H49" s="13" t="inlineStr"/>
@@ -2205,7 +2214,7 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Fio rígido ENCAPADO 1,50 mm² AZUL CLARO ⬆</t>
+          <t>Fio rígido ENCAPADO 0,50 mm² MARROM</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -2215,16 +2224,16 @@
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Retorno comum 0 V — o "neutro" da linha, 40 mm abaixo da cruzeta. Subiu de 1,00 para 1,50 mm²: conduz a soma dos 3 ramais (6,9 A)</t>
+          <t>Ramal R2 (comando)</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr"/>
       <c r="F50" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-rigido-encapado-1-50-mm-azul-claro","🔎 fio rigido encapado 1,50 mm ")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-rigido-encapado-0-50-mm-marrom","🔎 fio rigido encapado 0,50 mm ")</f>
         <v/>
       </c>
       <c r="G50" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+rigido+encapado+1%2C50+mm+azul+claro","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+rigido+encapado+0%2C50+mm+marrom","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H50" s="8" t="inlineStr"/>
@@ -2241,26 +2250,26 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Contas/miçangas marrom ou branca Ø 6 mm</t>
+          <t>Fio rígido ENCAPADO 0,50 mm² CINZA</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2 m</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Isoladores de pino da cruzeta</t>
+          <t>Ramal R3 (auxiliares)</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr"/>
       <c r="F51" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/contas-micangas-marrom-branca-6-mm","🔎 contas micangas marrom branc")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-rigido-encapado-0-50-mm-cinza","🔎 fio rigido encapado 0,50 mm ")</f>
         <v/>
       </c>
       <c r="G51" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=contas+micangas+marrom+branca+6+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+rigido+encapado+0%2C50+mm+cinza","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H51" s="13" t="inlineStr"/>
@@ -2277,26 +2286,26 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Tubo de PVC Ø 50 mm</t>
+          <t>Fio rígido ENCAPADO 1,50 mm² AZUL CLARO ⬆</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>24 cm</t>
+          <t>2 m</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Corpos dos 3 postes — 8 cm cada: T2 (P2), T3 (P3) e a caixa de derivação (P1). Agora os três têm o mesmo diâmetro, porque o P1 deixou de ter conversor</t>
+          <t>Retorno comum 0 V — o "neutro" da linha, 40 mm abaixo da cruzeta. Subiu de 1,00 para 1,50 mm²: conduz a soma dos 3 ramais (6,9 A)</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr"/>
       <c r="F52" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/tubo-pvc-50-mm","🔎 tubo pvc 50 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-rigido-encapado-1-50-mm-azul-claro","🔎 fio rigido encapado 1,50 mm ")</f>
         <v/>
       </c>
       <c r="G52" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=tubo+pvc+50+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+rigido+encapado+1%2C50+mm+azul+claro","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H52" s="8" t="inlineStr"/>
@@ -2313,26 +2322,26 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>Tampa/cap PVC Ø 50 mm</t>
+          <t>Contas/miçangas marrom ou branca Ø 6 mm</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>Tampas dos 3 corpos</t>
+          <t>Isoladores de pino da cruzeta</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr"/>
       <c r="F53" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/tampa-cap-pvc-50-mm","🔎 tampa cap pvc 50 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/contas-micangas-marrom-branca-6-mm","🔎 contas micangas marrom branc")</f>
         <v/>
       </c>
       <c r="G53" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=tampa+cap+pvc+50+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=contas+micangas+marrom+branca+6+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H53" s="13" t="inlineStr"/>
@@ -2349,26 +2358,26 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Cinta de alumínio 10 mm</t>
+          <t>Tubo de PVC Ø 50 mm</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>1 m</t>
+          <t>24 cm</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Fixação dos transformadores e da caixa de derivação nos postes</t>
+          <t>Corpos dos 3 postes — 8 cm cada: T2 (P2), T3 (P3) e a caixa de derivação (P1). Agora os três têm o mesmo diâmetro, porque o P1 deixou de ter conversor</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr"/>
       <c r="F54" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/cinta-aluminio-10-mm","🔎 cinta aluminio 10 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tubo-pvc-50-mm","🔎 tubo pvc 50 mm")</f>
         <v/>
       </c>
       <c r="G54" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=cinta+aluminio+10+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tubo+pvc+50+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H54" s="8" t="inlineStr"/>
@@ -2385,26 +2394,26 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>Bornes de emenda pequenos (2 ou 3 vias)</t>
+          <t>Tampa/cap PVC Ø 50 mm</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Dentro da caixa de derivação do P1 — ali os 24 V só se distribuem, não se transformam</t>
+          <t>Tampas dos 3 corpos</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr"/>
       <c r="F55" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/bornes-emenda-pequenos","🔎 bornes emenda pequenos")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tampa-cap-pvc-50-mm","🔎 tampa cap pvc 50 mm")</f>
         <v/>
       </c>
       <c r="G55" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=bornes+emenda+pequenos","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tampa+cap+pvc+50+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H55" s="13" t="inlineStr"/>
@@ -2421,26 +2430,26 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Flange/base de fixação dos postes</t>
+          <t>Cinta de alumínio 10 mm</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1 m</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Podem ser feitas com sobra de MDF + insertos M4</t>
+          <t>Fixação dos transformadores e da caixa de derivação nos postes</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr"/>
       <c r="F56" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/flange-base-fixacao-postes","🔎 flange base fixacao postes")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cinta-aluminio-10-mm","🔎 cinta aluminio 10 mm")</f>
         <v/>
       </c>
       <c r="G56" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=flange+base+fixacao+postes","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cinta+aluminio+10+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H56" s="8" t="inlineStr"/>
@@ -2457,26 +2466,26 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>Etiquetas adesivas impressas</t>
+          <t>Bornes de emenda pequenos (2 ou 3 vias)</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>Identificação dos corpos: "P1 — DERIVAÇÃO 24 V", "T2 — 24/5 V", "T3 — 24/12 V"</t>
+          <t>Dentro da caixa de derivação do P1 — ali os 24 V só se distribuem, não se transformam</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr"/>
       <c r="F57" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/etiquetas-adesivas-impressas","🔎 etiquetas adesivas impressas")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/bornes-emenda-pequenos","🔎 bornes emenda pequenos")</f>
         <v/>
       </c>
       <c r="G57" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=etiquetas+adesivas+impressas","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=bornes+emenda+pequenos","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H57" s="13" t="inlineStr"/>
@@ -2487,39 +2496,68 @@
         <v/>
       </c>
     </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>M.4 — Rua e entrada da empresa (zona externa)</t>
-        </is>
+    <row r="58">
+      <c r="A58" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>Flange/base de fixação dos postes</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Podem ser feitas com sobra de MDF + insertos M4</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr"/>
+      <c r="F58" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/flange-base-fixacao-postes","🔎 flange base fixacao postes")</f>
+        <v/>
+      </c>
+      <c r="G58" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=flange+base+fixacao+postes","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H58" s="8" t="inlineStr"/>
+      <c r="I58" s="8" t="inlineStr"/>
+      <c r="J58" s="9" t="inlineStr"/>
+      <c r="K58" s="9">
+        <f>IF(C58*J58=0,"",C58*J58)</f>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>Tinta spray cinza-asfalto escuro fosco</t>
+          <t>Etiquetas adesivas impressas</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Pista da rua</t>
+          <t>Identificação dos corpos: "P1 — DERIVAÇÃO 24 V", "T2 — 24/5 V", "T3 — 24/12 V"</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr"/>
       <c r="F59" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/tinta-spray-cinza-asfalto-escuro-fosco","🔎 tinta spray cinza asfalto es")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/etiquetas-adesivas-impressas","🔎 etiquetas adesivas impressas")</f>
         <v/>
       </c>
       <c r="G59" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=tinta+spray+cinza+asfalto+escuro+fosco","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=etiquetas+adesivas+impressas","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H59" s="13" t="inlineStr"/>
@@ -2530,40 +2568,11 @@
         <v/>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>Tubo de alumínio Ø 5 mm</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>60 cm</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>3 postes de iluminação pública de 180 mm — ⚠️ diferentes dos postes de distribuição</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr"/>
-      <c r="F60" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/tubo-aluminio-5-mm","🔎 tubo aluminio 5 mm")</f>
-        <v/>
-      </c>
-      <c r="G60" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=tubo+aluminio+5+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H60" s="8" t="inlineStr"/>
-      <c r="I60" s="8" t="inlineStr"/>
-      <c r="J60" s="9" t="inlineStr"/>
-      <c r="K60" s="9">
-        <f>IF(C60*J60=0,"",C60*J60)</f>
-        <v/>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>M.4 — Rua e entrada da empresa (zona externa)</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -2572,26 +2581,26 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Arame 1,5 mm</t>
+          <t>Tinta spray cinza-asfalto escuro fosco</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>1 m</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>Braço curvo das luminárias e estrutura do portão</t>
+          <t>Pista da rua</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr"/>
       <c r="F61" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/arame-1-5-mm","🔎 arame 1,5 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tinta-spray-cinza-asfalto-escuro-fosco","🔎 tinta spray cinza asfalto es")</f>
         <v/>
       </c>
       <c r="G61" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=arame+1%2C5+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tinta+spray+cinza+asfalto+escuro+fosco","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H61" s="13" t="inlineStr"/>
@@ -2608,32 +2617,29 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>LED 3 mm branco quente</t>
+          <t>Tubo de alumínio Ø 5 mm</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>60 cm</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>3 luminárias da rua + 1 na guarita. Alimentados em 5 V (BD-5V), com 220 Ω em série, sempre acesos. Vf ≈ 3,1 V</t>
+          <t>3 postes de iluminação pública de 180 mm — ⚠️ diferentes dos postes de distribuição</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr"/>
       <c r="F62" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/led-3-mm-branco-quente","🔎 led 3 mm branco quente")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tubo-aluminio-5-mm","🔎 tubo aluminio 5 mm")</f>
         <v/>
       </c>
       <c r="G62" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=led+3+mm+branco+quente","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H62" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-3mm-warm-white-led.html","🌏 3mm warm white LED")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tubo+aluminio+5+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H62" s="8" t="inlineStr"/>
       <c r="I62" s="8" t="inlineStr"/>
       <c r="J62" s="9" t="inlineStr"/>
       <c r="K62" s="9">
@@ -2647,32 +2653,29 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Resistor 220 Ω 1/4 W</t>
+          <t>Arame 1,5 mm</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 m</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>Limitador dos LEDs da rua — já contabilizado na lista L.4, não compre de novo. ⚠️ Valor dimensionado para 5 V: (5 − 3,1)/220 = 8,6 mA. Monte cada um dentro da base do poste, com termorretrátil</t>
+          <t>Braço curvo das luminárias e estrutura do portão</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr"/>
       <c r="F63" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-220-1-4-w","🔎 resistor 220 1 4 w")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/arame-1-5-mm","🔎 arame 1,5 mm")</f>
         <v/>
       </c>
       <c r="G63" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+220+1+4+w","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H63" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=arame+1%2C5+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H63" s="13" t="inlineStr"/>
       <c r="I63" s="13" t="inlineStr"/>
       <c r="J63" s="14" t="inlineStr"/>
       <c r="K63" s="14">
@@ -2686,29 +2689,32 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Carro de passeio miniatura 1:50</t>
+          <t>LED 3 mm branco quente</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>~88 mm. Se só achar 1:64 (68 mm), pode usar — mas não misture escalas</t>
+          <t>3 luminárias da rua + 1 na guarita. Alimentados em 5 V (BD-5V), com 220 Ω em série, sempre acesos. Vf ≈ 3,1 V</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr"/>
       <c r="F64" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/carro-passeio-miniatura-1-50","🔎 carro passeio miniatura 1 50")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/led-3-mm-branco-quente","🔎 led 3 mm branco quente")</f>
         <v/>
       </c>
       <c r="G64" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=carro+passeio+miniatura+1+50","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H64" s="8" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=led+3+mm+branco+quente","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H64" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-3mm-warm-white-led.html","🌏 3mm warm white LED")</f>
+        <v/>
+      </c>
       <c r="I64" s="8" t="inlineStr"/>
       <c r="J64" s="9" t="inlineStr"/>
       <c r="K64" s="9">
@@ -2722,29 +2728,32 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>Caminhão / van 1:50</t>
+          <t>Resistor 220 Ω 1/4 W</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>~150 mm, entrando pelo portão</t>
+          <t>Limitador dos LEDs da rua — já contabilizado na lista L.4, não compre de novo. ⚠️ Valor dimensionado para 5 V: (5 − 3,1)/220 = 8,6 mA. Monte cada um dentro da base do poste, com termorretrátil</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr"/>
       <c r="F65" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/caminhao-van-1-50","🔎 caminhao van 1 50")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-220-1-4-w","🔎 resistor 220 1 4 w")</f>
         <v/>
       </c>
       <c r="G65" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=caminhao+van+1+50","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H65" s="13" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+220+1+4+w","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H65" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
+        <v/>
+      </c>
       <c r="I65" s="13" t="inlineStr"/>
       <c r="J65" s="14" t="inlineStr"/>
       <c r="K65" s="14">
@@ -2758,26 +2767,26 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Tira de MDF 3 mm</t>
+          <t>Carro de passeio miniatura 1:50</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>1,5 m</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>Meio-fio (guia), 4 mm de altura, pintado de branco</t>
+          <t>~88 mm. Se só achar 1:64 (68 mm), pode usar — mas não misture escalas</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr"/>
       <c r="F66" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/tira-mdf-3-mm","🔎 tira mdf 3 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/carro-passeio-miniatura-1-50","🔎 carro passeio miniatura 1 50")</f>
         <v/>
       </c>
       <c r="G66" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=tira+mdf+3+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=carro+passeio+miniatura+1+50","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H66" s="8" t="inlineStr"/>
@@ -2794,7 +2803,7 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>Fita branca 2 mm ou caneta posca branca</t>
+          <t>Caminhão / van 1:50</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
@@ -2804,16 +2813,16 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>Faixa central tracejada, faixa de bordo e faixa de pedestres</t>
+          <t>~150 mm, entrando pelo portão</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr"/>
       <c r="F67" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-branca-2-mm-caneta-posca-branca","🔎 fita branca 2 mm caneta posc")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/caminhao-van-1-50","🔎 caminhao van 1 50")</f>
         <v/>
       </c>
       <c r="G67" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+branca+2+mm+caneta+posca+branca","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=caminhao+van+1+50","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H67" s="13" t="inlineStr"/>
@@ -2830,26 +2839,26 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>MDF 4 mm</t>
+          <t>Tira de MDF 3 mm</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,5 m</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>Muro da empresa: 50 mm de altura × 290 mm, em X = 640</t>
+          <t>Meio-fio (guia), 4 mm de altura, pintado de branco</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr"/>
       <c r="F68" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/mdf-4-mm","🔎 mdf 4 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tira-mdf-3-mm","🔎 tira mdf 3 mm")</f>
         <v/>
       </c>
       <c r="G68" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=mdf+4+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tira+mdf+3+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H68" s="8" t="inlineStr"/>
@@ -2866,26 +2875,26 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>MDF 4 mm</t>
+          <t>Fita branca 2 mm ou caneta posca branca</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>Guarita 45 × 45 × 55 mm, com janela recortada</t>
+          <t>Faixa central tracejada, faixa de bordo e faixa de pedestres</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr"/>
       <c r="F69" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/mdf-4-mm","🔎 mdf 4 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-branca-2-mm-caneta-posca-branca","🔎 fita branca 2 mm caneta posc")</f>
         <v/>
       </c>
       <c r="G69" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=mdf+4+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+branca+2+mm+caneta+posca+branca","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H69" s="13" t="inlineStr"/>
@@ -2902,26 +2911,26 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Tinta azul industrial</t>
+          <t>MDF 4 mm</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Portão corrediço</t>
+          <t>Muro da empresa: 50 mm de altura × 290 mm, em X = 640</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr"/>
       <c r="F70" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/tinta-azul-industrial","🔎 tinta azul industrial")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/mdf-4-mm","🔎 mdf 4 mm")</f>
         <v/>
       </c>
       <c r="G70" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=tinta+azul+industrial","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=mdf+4+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H70" s="8" t="inlineStr"/>
@@ -2938,26 +2947,26 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Árvores de maquete</t>
+          <t>MDF 4 mm</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Escala 1:50, na calçada da frente</t>
+          <t>Guarita 45 × 45 × 55 mm, com janela recortada</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr"/>
       <c r="F71" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/arvores-maquete","🔎 arvores maquete")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/mdf-4-mm","🔎 mdf 4 mm")</f>
         <v/>
       </c>
       <c r="G71" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=arvores+maquete","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=mdf+4+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H71" s="13" t="inlineStr"/>
@@ -2974,26 +2983,26 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Placas de trânsito miniatura</t>
+          <t>Tinta azul industrial</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>"PARE" e "VELOCIDADE MÁXIMA 10 km/h"</t>
+          <t>Portão corrediço</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr"/>
       <c r="F72" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/placas-transito-miniatura","🔎 placas transito miniatura")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tinta-azul-industrial","🔎 tinta azul industrial")</f>
         <v/>
       </c>
       <c r="G72" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=placas+transito+miniatura","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tinta+azul+industrial","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H72" s="8" t="inlineStr"/>
@@ -3010,26 +3019,26 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>Lixeira urbana + abrigo de ônibus</t>
+          <t>Árvores de maquete</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>1 cada</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>Opcional — enriquece a cena</t>
+          <t>Escala 1:50, na calçada da frente</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr"/>
       <c r="F73" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/lixeira-urbana-abrigo-onibus","🔎 lixeira urbana abrigo onibus")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/arvores-maquete","🔎 arvores maquete")</f>
         <v/>
       </c>
       <c r="G73" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=lixeira+urbana+abrigo+onibus","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=arvores+maquete","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H73" s="13" t="inlineStr"/>
@@ -3040,39 +3049,68 @@
         <v/>
       </c>
     </row>
-    <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>M.5 — Chão de fábrica (cenografia)</t>
-        </is>
+    <row r="74">
+      <c r="A74" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>Placas de trânsito miniatura</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>"PARE" e "VELOCIDADE MÁXIMA 10 km/h"</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr"/>
+      <c r="F74" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/placas-transito-miniatura","🔎 placas transito miniatura")</f>
+        <v/>
+      </c>
+      <c r="G74" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=placas+transito+miniatura","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H74" s="8" t="inlineStr"/>
+      <c r="I74" s="8" t="inlineStr"/>
+      <c r="J74" s="9" t="inlineStr"/>
+      <c r="K74" s="9">
+        <f>IF(C74*J74=0,"",C74*J74)</f>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="10" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>Tinta spray cinza claro fosco</t>
+          <t>Lixeira urbana + abrigo de ônibus</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 cada</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>Piso industrial (epóxi)</t>
+          <t>Opcional — enriquece a cena</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr"/>
       <c r="F75" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/tinta-spray-cinza-claro-fosco","🔎 tinta spray cinza claro fosc")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/lixeira-urbana-abrigo-onibus","🔎 lixeira urbana abrigo onibus")</f>
         <v/>
       </c>
       <c r="G75" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=tinta+spray+cinza+claro+fosco","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=lixeira+urbana+abrigo+onibus","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H75" s="13" t="inlineStr"/>
@@ -3083,40 +3121,11 @@
         <v/>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>Tinta spray preto fosco</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>Estruturas e acabamento</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="inlineStr"/>
-      <c r="F76" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/tinta-spray-preto-fosco","🔎 tinta spray preto fosco")</f>
-        <v/>
-      </c>
-      <c r="G76" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=tinta+spray+preto+fosco","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H76" s="8" t="inlineStr"/>
-      <c r="I76" s="8" t="inlineStr"/>
-      <c r="J76" s="9" t="inlineStr"/>
-      <c r="K76" s="9">
-        <f>IF(C76*J76=0,"",C76*J76)</f>
-        <v/>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>M.5 — Chão de fábrica (cenografia)</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -3125,26 +3134,26 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>Verniz fosco spray</t>
+          <t>Tinta spray cinza claro fosco</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>Proteção final do piso pintado</t>
+          <t>Piso industrial (epóxi)</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr"/>
       <c r="F77" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/verniz-fosco-spray","🔎 verniz fosco spray")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tinta-spray-cinza-claro-fosco","🔎 tinta spray cinza claro fosc")</f>
         <v/>
       </c>
       <c r="G77" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=verniz+fosco+spray","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tinta+spray+cinza+claro+fosco","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H77" s="13" t="inlineStr"/>
@@ -3161,26 +3170,26 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Fita adesiva amarela 10 mm</t>
+          <t>Tinta spray preto fosco</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>1 rolo</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>Demarcação de corredores e áreas</t>
+          <t>Estruturas e acabamento</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr"/>
       <c r="F78" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-adesiva-amarela-10-mm","🔎 fita adesiva amarela 10 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tinta-spray-preto-fosco","🔎 tinta spray preto fosco")</f>
         <v/>
       </c>
       <c r="G78" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+adesiva+amarela+10+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tinta+spray+preto+fosco","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H78" s="8" t="inlineStr"/>
@@ -3197,26 +3206,26 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>Fita zebrada amarelo/preto 20 mm</t>
+          <t>Verniz fosco spray</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>1 rolo</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>Faixa de segurança em frente ao painel (exigência NR-10 — zona de trabalho)</t>
+          <t>Proteção final do piso pintado</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr"/>
       <c r="F79" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-zebrada-amarelo-preto-20-mm","🔎 fita zebrada amarelo preto 2")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/verniz-fosco-spray","🔎 verniz fosco spray")</f>
         <v/>
       </c>
       <c r="G79" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+zebrada+amarelo+preto+20+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=verniz+fosco+spray","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H79" s="13" t="inlineStr"/>
@@ -3233,7 +3242,7 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Fita adesiva verde 10 mm</t>
+          <t>Fita adesiva amarela 10 mm</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -3243,16 +3252,16 @@
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>Rota de fuga</t>
+          <t>Demarcação de corredores e áreas</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr"/>
       <c r="F80" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-adesiva-verde-10-mm","🔎 fita adesiva verde 10 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-adesiva-amarela-10-mm","🔎 fita adesiva amarela 10 mm")</f>
         <v/>
       </c>
       <c r="G80" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+adesiva+verde+10+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+adesiva+amarela+10+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H80" s="8" t="inlineStr"/>
@@ -3269,26 +3278,26 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>Figuras de maquete escala 1:50</t>
+          <t>Fita zebrada amarelo/preto 20 mm</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1 rolo</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>(4 na fábrica, 3 na rua, 3 reservas) Pessoas com EPI (loja de maquetaria/arquitetura)</t>
+          <t>Faixa de segurança em frente ao painel (exigência NR-10 — zona de trabalho)</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr"/>
       <c r="F81" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/figuras-maquete-escala-1-50","🔎 figuras maquete escala 1 50")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-zebrada-amarelo-preto-20-mm","🔎 fita zebrada amarelo preto 2")</f>
         <v/>
       </c>
       <c r="G81" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=figuras+maquete+escala+1+50","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+zebrada+amarelo+preto+20+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H81" s="13" t="inlineStr"/>
@@ -3305,26 +3314,26 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>Miniaturas: empilhadeira, pallets, tambores</t>
+          <t>Fita adesiva verde 10 mm</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 rolo</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>Ambientação do chão de fábrica</t>
+          <t>Rota de fuga</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr"/>
       <c r="F82" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/miniaturas-empilhadeira-pallets-tambores","🔎 miniaturas empilhadeira, pal")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-adesiva-verde-10-mm","🔎 fita adesiva verde 10 mm")</f>
         <v/>
       </c>
       <c r="G82" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=miniaturas+empilhadeira%2C+pallets%2C+tambores","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+adesiva+verde+10+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H82" s="8" t="inlineStr"/>
@@ -3341,26 +3350,26 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>Extintor miniatura + placa</t>
+          <t>Figuras de maquete escala 1:50</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>Sinalização de segurança</t>
+          <t>(4 na fábrica, 3 na rua, 3 reservas) Pessoas com EPI (loja de maquetaria/arquitetura)</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr"/>
       <c r="F83" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/extintor-miniatura-placa","🔎 extintor miniatura placa")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/figuras-maquete-escala-1-50","🔎 figuras maquete escala 1 50")</f>
         <v/>
       </c>
       <c r="G83" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=extintor+miniatura+placa","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=figuras+maquete+escala+1+50","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H83" s="13" t="inlineStr"/>
@@ -3377,26 +3386,26 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>Placas de sinalização impressas</t>
+          <t>Miniaturas: empilhadeira, pallets, tambores</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>1 folha</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>"RISCO ELÉTRICO", "USO OBRIGATÓRIO DE EPI", "SAÍDA" — papel adesivo</t>
+          <t>Ambientação do chão de fábrica</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr"/>
       <c r="F84" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/placas-sinalizacao-impressas","🔎 placas sinalizacao impressas")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/miniaturas-empilhadeira-pallets-tambores","🔎 miniaturas empilhadeira, pal")</f>
         <v/>
       </c>
       <c r="G84" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=placas+sinalizacao+impressas","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=miniaturas+empilhadeira%2C+pallets%2C+tambores","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H84" s="8" t="inlineStr"/>
@@ -3413,26 +3422,26 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>Eletrocalha / perfilado aéreo</t>
+          <t>Extintor miniatura + placa</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>60 cm</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>Canaleta de acrílico ou perfil U de alumínio — leva os cabos do painel à câmara por cima, como na indústria</t>
+          <t>Sinalização de segurança</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr"/>
       <c r="F85" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/eletrocalha-perfilado-aereo","🔎 eletrocalha perfilado aereo")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/extintor-miniatura-placa","🔎 extintor miniatura placa")</f>
         <v/>
       </c>
       <c r="G85" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=eletrocalha+perfilado+aereo","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=extintor+miniatura+placa","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H85" s="13" t="inlineStr"/>
@@ -3449,26 +3458,26 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Suportes/mãos-francesas da eletrocalha</t>
+          <t>Placas de sinalização impressas</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1 folha</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>Cantoneira de alumínio</t>
+          <t>"RISCO ELÉTRICO", "USO OBRIGATÓRIO DE EPI", "SAÍDA" — papel adesivo</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr"/>
       <c r="F86" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/suportes-maos-francesas-eletrocalha","🔎 suportes maos francesas elet")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/placas-sinalizacao-impressas","🔎 placas sinalizacao impressas")</f>
         <v/>
       </c>
       <c r="G86" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=suportes+maos+francesas+eletrocalha","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=placas+sinalizacao+impressas","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H86" s="8" t="inlineStr"/>
@@ -3485,26 +3494,26 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>EVA ou MDF 6 mm</t>
+          <t>Eletrocalha / perfilado aéreo</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>60 cm</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>Bases de máquinas fictícias e plataformas</t>
+          <t>Canaleta de acrílico ou perfil U de alumínio — leva os cabos do painel à câmara por cima, como na indústria</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr"/>
       <c r="F87" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/eva-mdf-6-mm","🔎 eva mdf 6 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/eletrocalha-perfilado-aereo","🔎 eletrocalha perfilado aereo")</f>
         <v/>
       </c>
       <c r="G87" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=eva+mdf+6+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=eletrocalha+perfilado+aereo","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H87" s="13" t="inlineStr"/>
@@ -3515,39 +3524,68 @@
         <v/>
       </c>
     </row>
-    <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t>C.2 — Isolamento térmico</t>
-        </is>
+    <row r="88">
+      <c r="A88" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>Suportes/mãos-francesas da eletrocalha</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>Cantoneira de alumínio</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr"/>
+      <c r="F88" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/suportes-maos-francesas-eletrocalha","🔎 suportes maos francesas elet")</f>
+        <v/>
+      </c>
+      <c r="G88" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=suportes+maos+francesas+eletrocalha","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H88" s="8" t="inlineStr"/>
+      <c r="I88" s="8" t="inlineStr"/>
+      <c r="J88" s="9" t="inlineStr"/>
+      <c r="K88" s="9">
+        <f>IF(C88*J88=0,"",C88*J88)</f>
+        <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="10" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>XPS 30 mm (poliestireno extrudado)</t>
+          <t>EVA ou MDF 6 mm</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>1 m²</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>Isolante principal — k ≈ 0,033 W/m·K. 30 mm, não 20 mm (ver Doc 12)</t>
+          <t>Bases de máquinas fictícias e plataformas</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr"/>
       <c r="F89" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/xps-30-mm","🔎 xps 30 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/eva-mdf-6-mm","🔎 eva mdf 6 mm")</f>
         <v/>
       </c>
       <c r="G89" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=xps+30+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=eva+mdf+6+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H89" s="13" t="inlineStr"/>
@@ -3558,40 +3596,11 @@
         <v/>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="5" t="n">
-        <v>77</v>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>Fita adesiva de alumínio 50 mm</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>1 rolo</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>⚠️ Barreira de vapor — obrigatória em todas as juntas do XPS, pelo lado externo (quente)</t>
-        </is>
-      </c>
-      <c r="E90" s="6" t="inlineStr"/>
-      <c r="F90" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-adesiva-aluminio-50-mm","🔎 fita adesiva aluminio 50 mm")</f>
-        <v/>
-      </c>
-      <c r="G90" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+adesiva+aluminio+50+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H90" s="8" t="inlineStr"/>
-      <c r="I90" s="8" t="inlineStr"/>
-      <c r="J90" s="9" t="inlineStr"/>
-      <c r="K90" s="9">
-        <f>IF(C90*J90=0,"",C90*J90)</f>
-        <v/>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>C.2 — Isolamento térmico</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -3600,26 +3609,26 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>Manta elastomérica autoadesiva 6 mm</t>
+          <t>⭐ Fita adesiva de alumínio 50 mm</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>1 m²</t>
+          <t>3 rolos</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>Tipo Armaflex — cantos, arestas e ao redor das passagens de cabo</t>
+          <t>🔧 Virou o isolamento E a superfície externa da câmara. Reveste toda a caixa por fora e sela todas as juntas coladas do acrílico. Com ε ≈ 0,05 ela mais que dobra a resistência de superfície (0,13 → 0,31 m²·K/W). ⚠️ Barreira de vapor é a função mais importante dela — quanto menos vapor entra, mais a sílica dura e menos gelo se forma</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr"/>
       <c r="F91" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/manta-elastomerica-autoadesiva-6-mm","🔎 manta elastomerica autoadesi")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-adesiva-aluminio-50-mm","🔎 fita adesiva aluminio 50 mm")</f>
         <v/>
       </c>
       <c r="G91" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=manta+elastomerica+autoadesiva+6+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+adesiva+aluminio+50+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H91" s="13" t="inlineStr"/>
@@ -3636,26 +3645,26 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>Espuma expansiva PU (mini)</t>
+          <t>Manta elastomérica autoadesiva 6 mm</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 m²</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>Selagem de passagens de cabo e dreno</t>
+          <t>Tipo Armaflex — cantos, arestas e ao redor das passagens de cabo</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr"/>
       <c r="F92" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/espuma-expansiva-pu","🔎 espuma expansiva pu")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/manta-elastomerica-autoadesiva-6-mm","🔎 manta elastomerica autoadesi")</f>
         <v/>
       </c>
       <c r="G92" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=espuma+expansiva+pu","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=manta+elastomerica+autoadesiva+6+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H92" s="8" t="inlineStr"/>
@@ -3666,47 +3675,47 @@
         <v/>
       </c>
     </row>
-    <row r="93" ht="22" customHeight="1">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>C.3 — Vedação, porta e dreno</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="n">
+    <row r="93">
+      <c r="A93" s="10" t="n">
         <v>80</v>
       </c>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>Perfil EPDM tubular autoadesivo 9 × 6 mm</t>
-        </is>
-      </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>2 m</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>Vedação da porta — perfil tubular comprime muito melhor que o chato de 5 mm</t>
-        </is>
-      </c>
-      <c r="E94" s="6" t="inlineStr"/>
-      <c r="F94" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/perfil-epdm-tubular-autoadesivo-9-6-mm","🔎 perfil epdm tubular autoades")</f>
-        <v/>
-      </c>
-      <c r="G94" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=perfil+epdm+tubular+autoadesivo+9+6+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H94" s="8" t="inlineStr"/>
-      <c r="I94" s="8" t="inlineStr"/>
-      <c r="J94" s="9" t="inlineStr"/>
-      <c r="K94" s="9">
-        <f>IF(C94*J94=0,"",C94*J94)</f>
-        <v/>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>Espuma expansiva PU (mini)</t>
+        </is>
+      </c>
+      <c r="C93" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>Selagem das passagens de cabo</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr"/>
+      <c r="F93" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/espuma-expansiva-pu","🔎 espuma expansiva pu")</f>
+        <v/>
+      </c>
+      <c r="G93" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=espuma+expansiva+pu","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H93" s="13" t="inlineStr"/>
+      <c r="I93" s="13" t="inlineStr"/>
+      <c r="J93" s="14" t="inlineStr"/>
+      <c r="K93" s="14">
+        <f>IF(C93*J93=0,"",C93*J93)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>C.3 — Vedação, porta e condensado</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -3715,26 +3724,26 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>Dobradiça piano de alumínio</t>
+          <t>Perfil EPDM tubular autoadesivo 9 × 6 mm</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2 m</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>250 mm (cortar de uma barra de 75 cm)</t>
+          <t>Vedação da porta — perfil tubular comprime muito melhor que o chato de 5 mm</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr"/>
       <c r="F95" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/dobradica-piano-aluminio","🔎 dobradica piano aluminio")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/perfil-epdm-tubular-autoadesivo-9-6-mm","🔎 perfil epdm tubular autoades")</f>
         <v/>
       </c>
       <c r="G95" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=dobradica+piano+aluminio","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=perfil+epdm+tubular+autoadesivo+9+6+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H95" s="13" t="inlineStr"/>
@@ -3751,26 +3760,26 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>Fecho de pressão (borboleta) inox</t>
+          <t>Dobradiça piano de alumínio</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>Comprime a vedação — tipo fecho de baú</t>
+          <t>250 mm (cortar de uma barra de 75 cm)</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr"/>
       <c r="F96" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fecho-pressao-inox","🔎 fecho pressao inox")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/dobradica-piano-aluminio","🔎 dobradica piano aluminio")</f>
         <v/>
       </c>
       <c r="G96" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fecho+pressao+inox","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=dobradica+piano+aluminio","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H96" s="8" t="inlineStr"/>
@@ -3787,26 +3796,26 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>Puxador de câmara fria (miniatura)</t>
+          <t>Fecho de pressão (borboleta) inox</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>Estética — pode ser um puxador de móvel pequeno</t>
+          <t>Comprime a vedação — tipo fecho de baú</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr"/>
       <c r="F97" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/puxador-camara-fria","🔎 puxador camara fria")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fecho-pressao-inox","🔎 fecho pressao inox")</f>
         <v/>
       </c>
       <c r="G97" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=puxador+camara+fria","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fecho+pressao+inox","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H97" s="13" t="inlineStr"/>
@@ -3823,26 +3832,26 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>Cola S-320 Sinteglas</t>
+          <t>Puxador de câmara fria (miniatura)</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>250 ml</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>Colagem de acrílico por capilaridade</t>
+          <t>Estética — pode ser um puxador de móvel pequeno</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr"/>
       <c r="F98" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/cola-s-320-sinteglas","🔎 cola s 320 sinteglas")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/puxador-camara-fria","🔎 puxador camara fria")</f>
         <v/>
       </c>
       <c r="G98" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=cola+s+320+sinteglas","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=puxador+camara+fria","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H98" s="8" t="inlineStr"/>
@@ -3859,26 +3868,26 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>Silicone neutro transparente</t>
+          <t>Cola S-320 Sinteglas</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>1 tubo</t>
+          <t>250 ml</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>Vedação de juntas (⚠️ neutro, o acético ataca o acrílico)</t>
+          <t>Colagem de acrílico por capilaridade</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr"/>
       <c r="F99" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/silicone-neutro-transparente","🔎 silicone neutro transparente")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cola-s-320-sinteglas","🔎 cola s 320 sinteglas")</f>
         <v/>
       </c>
       <c r="G99" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=silicone+neutro+transparente","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cola+s+320+sinteglas","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H99" s="13" t="inlineStr"/>
@@ -3895,26 +3904,26 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>Bandeja de alumínio</t>
+          <t>Silicone neutro transparente</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 tubo</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>~190 × 90 mm — coleta de condensado</t>
+          <t>Vedação de juntas (⚠️ neutro, o acético ataca o acrílico)</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr"/>
       <c r="F100" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/bandeja-aluminio","🔎 bandeja aluminio")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/silicone-neutro-transparente","🔎 silicone neutro transparente")</f>
         <v/>
       </c>
       <c r="G100" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=bandeja+aluminio","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=silicone+neutro+transparente","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H100" s="8" t="inlineStr"/>
@@ -3931,26 +3940,26 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>Tubo de silicone Ø 6 mm</t>
+          <t>⭐ Bandeja de alumínio REMOVÍVEL</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>40 cm</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>Dreno até o recipiente externo</t>
+          <t>~190 × 90 mm, sem furo — desliza para fora para esvaziar. 🔧 Era fixa e inclinada, com dreno</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr"/>
       <c r="F101" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/tubo-silicone-6-mm","🔎 tubo silicone 6 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/bandeja-aluminio-removivel","🔎 bandeja aluminio removivel")</f>
         <v/>
       </c>
       <c r="G101" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=tubo+silicone+6+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=bandeja+aluminio+removivel","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H101" s="13" t="inlineStr"/>
@@ -3967,26 +3976,26 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Sílica gel indicadora</t>
+          <t>⭐ Tubo de silicone Ø 4 mm</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>3 sachês</t>
+          <t>40 cm</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>2 na câmara + 1 dentro da câmara de ar da porta dupla</t>
+          <t>RESPIRO, enrolado em espiral dentro da câmara. ⚠️ Não é opcional: resfriar de 25 para 5 °C contrai o ar 6,7 % e, numa câmara bem vedada, isso dá 34 kgf puxando a porta para dentro. O caminho longo e estreito equaliza a pressão e quase não deixa vapor passar</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr"/>
       <c r="F102" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/silica-gel-indicadora","🔎 silica gel indicadora")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tubo-silicone-4-mm","🔎 tubo silicone 4 mm")</f>
         <v/>
       </c>
       <c r="G102" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=silica+gel+indicadora","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tubo+silicone+4+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H102" s="8" t="inlineStr"/>
@@ -4003,26 +4012,26 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>Recipiente coletor de condensado</t>
+          <t>⭐ Sílica gel indicadora</t>
         </is>
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4 sachês</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>Frasco pequeno, embutido na maquete</t>
+          <t>3 na câmara + 1 dentro da câmara de ar da porta dupla. Azul → rosa = trocar. Regenera no forno a 120 °C por 2 h</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr"/>
       <c r="F103" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/recipiente-coletor-condensado","🔎 recipiente coletor condensad")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/silica-gel-indicadora","🔎 silica gel indicadora")</f>
         <v/>
       </c>
       <c r="G103" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=recipiente+coletor+condensado","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=silica+gel+indicadora","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H103" s="13" t="inlineStr"/>
@@ -4056,7 +4065,7 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>400 × 500 × 200 mm — comprada pronta ou feita em MDF 15 mm</t>
+          <t>500 x 500 x 200 mm — dimensao exigida pelo layout React</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr"/>
@@ -4159,12 +4168,12 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>2 m</t>
+          <t>3 m</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>Com tampa — organização profissional dos cabos</t>
+          <t>Com tampa. Placa de montagem: 4 horizontais + 2 verticais ≈ 2,8 m</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr"/>
@@ -4190,26 +4199,26 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>Bloco de distribuição DIN — 1 entrada 4 mm² + 4 saídas</t>
+          <t>⭐ Canaleta perfurada 25 × 25 mm</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2 m</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>BD-POT — 24 V de potência comutados pelo KA2 → BTS #1, BTS #2 e reservas. ⚠️ Cai com a emergência</t>
+          <t>PORTA — 5 horizontais + 1 vertical na dobradiça ≈ 1,5 m. Mais estreita que a da placa porque a porta tem menos fio e não pode ficar pesada</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr"/>
       <c r="F109" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/bloco-distribuicao-din","🔎 bloco distribuicao din")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/canaleta-perfurada-25-25-mm","🔎 canaleta perfurada 25 25 mm")</f>
         <v/>
       </c>
       <c r="G109" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=bloco+distribuicao+din","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=canaleta+perfurada+25+25+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H109" s="13" t="inlineStr"/>
@@ -4226,26 +4235,26 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Bloco de distribuição DIN — 1 entrada 2,5 mm² + 4 saídas</t>
+          <t>⭐ Espiral organizador Ø 12 mm</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40 cm</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>BD-AUX (12 V auxiliar, do T3) e BD-24V (24 V permanentes: DNLCB30/ESP32, cadeia de comando e o positivo comum dos 4 sinaleiros). ⚠️ Não confundir com o BD-POT — este não cai com a emergência, é o que mantém a supervisão viva para publicar o evento por MQTT</t>
+          <t>A passagem flexível entre a placa e a porta. Protege o chicote nos ciclos de abertura</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr"/>
       <c r="F110" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/bloco-distribuicao-din","🔎 bloco distribuicao din")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/espiral-organizador-12-mm","🔎 espiral organizador 12 mm")</f>
         <v/>
       </c>
       <c r="G110" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=bloco+distribuicao+din","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=espiral+organizador+12+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H110" s="8" t="inlineStr"/>
@@ -4262,7 +4271,7 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>Bloco de distribuição DIN — 1 entrada 2,5 mm² + 6 saídas</t>
+          <t>Bloco de distribuição DIN — 1 entrada 4 mm² + 4 saídas</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
@@ -4272,7 +4281,7 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>BD-5V — Arduino, Nextion, SD/RTC, lógica dos 2 BTS, LEDs</t>
+          <t>BD-POT — 24 V de potência comutados pelo KA2 → BTS #1, BTS #2, medição do D25 e 1 reserva. ⚠️ Cai com a emergência</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr"/>
@@ -4298,7 +4307,7 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>Bloco de distribuição DIN — 1 entrada 10 mm² + 8 saídas</t>
+          <t>Bloco de distribuição DIN — 1 entrada 2,5 mm² + 4 saídas</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
@@ -4308,7 +4317,7 @@
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>BD-0V — ⭐ o star ground do projeto. Todos os retornos convergem aqui</t>
+          <t>BD-AUX — 12 V auxiliar (do T3): cooler dos BTS + 2 coolers das Peltier + 1 reserva</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr"/>
@@ -4334,26 +4343,26 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>Bornes DIN parafuso 2,5 mm²</t>
+          <t>Bloco de distribuição DIN — 1 entrada 2,5 mm² + 6 saídas ⬆</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>Passagem e reservas</t>
+          <t>BD-24V — 24 V permanentes. ⚠️ Subiu de 4 para 6: são 5 cargas (DNLCB30/ESP32, cadeia de comando, positivo comum dos sinaleiros, COM do ULN2803 na PI-1, e a alimentação das 2 posições de ensaio) + 1 reserva. Não confundir com o BD-POT — este não cai com a emergência</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr"/>
       <c r="F113" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/bornes-din-parafuso-2-5-mm","🔎 bornes din parafuso 2,5 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/bloco-distribuicao-din","🔎 bloco distribuicao din")</f>
         <v/>
       </c>
       <c r="G113" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=bornes+din+parafuso+2%2C5+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=bloco+distribuicao+din","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H113" s="13" t="inlineStr"/>
@@ -4370,26 +4379,26 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>Separadores/tampas de borne</t>
+          <t>Bloco de distribuição DIN — 1 entrada 2,5 mm² + 8 saídas ⬆</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>Acabamento das réguas</t>
+          <t>BD-5V — ⚠️ Subiu de 6 para 8: são 7 cargas (Arduino, tela ES3C28P, RTC, lógica do BTS #1, lógica do BTS #2, placa PI-1 e os LEDs da maquete) + 1 reserva</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr"/>
       <c r="F114" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/separadores-tampas-borne","🔎 separadores tampas borne")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/bloco-distribuicao-din","🔎 bloco distribuicao din")</f>
         <v/>
       </c>
       <c r="G114" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=separadores+tampas+borne","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=bloco+distribuicao+din","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H114" s="8" t="inlineStr"/>
@@ -4406,26 +4415,26 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>Alternativa mais barata: bornes comuns + ponte de interligação (pente)</t>
+          <t>⭐ Barra de distribuição / régua com pente — mín. 20 pontos ⬆⬆</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>Funciona igual aos blocos, custa menos, menos prático para alterar depois</t>
+          <t>BD-0V — o star ground do projeto. ⚠️ Um bloco de 8 saídas NÃO serve: aqui convergem 4 entradas + ~16 retornos. Use uma barra de neutro/terra de 16–20 furos em suporte DIN, ou dois blocos de 1×8 interligados por ponte de 4 mm². Entrada de 10 mm²</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr"/>
       <c r="F115" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/alternativa-mais-barata-bornes-comuns-ponte-interligacao","🔎 alternativa mais barata born")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/barra-distribuicao-regua-pente","🔎 barra distribuicao regua pen")</f>
         <v/>
       </c>
       <c r="G115" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=alternativa+mais+barata+bornes+comuns+ponte+interligacao","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=barra+distribuicao+regua+pente","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H115" s="13" t="inlineStr"/>
@@ -4436,71 +4445,45 @@
         <v/>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="5" t="n">
-        <v>101</v>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>Identificadores de borne e de cabo</t>
-        </is>
-      </c>
-      <c r="C116" s="5" t="inlineStr">
-        <is>
-          <t>1 kit</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>Anilhas numeradas — exigido em painel industrial</t>
-        </is>
-      </c>
-      <c r="E116" s="6" t="inlineStr"/>
-      <c r="F116" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/identificadores-borne-cabo","🔎 identificadores borne cabo")</f>
-        <v/>
-      </c>
-      <c r="G116" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=identificadores+borne+cabo","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H116" s="8" t="inlineStr"/>
-      <c r="I116" s="8" t="inlineStr"/>
-      <c r="J116" s="9" t="inlineStr"/>
-      <c r="K116" s="9">
-        <f>IF(C116*J116=0,"",C116*J116)</f>
-        <v/>
+    <row r="116" ht="22" customHeight="1">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>L.1 — Controle e interface</t>
+        </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="10" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>Trava-fim de trilho DIN</t>
+          <t>Arduino Mega 2560 R3</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>Impede os componentes de deslizarem</t>
+          <t>1 controlador em uso; reserva opcional</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr"/>
       <c r="F117" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/trava-fim-trilho-din","🔎 trava fim trilho din")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/arduino-mega-2560-r3","🔎 arduino mega 2560 r3")</f>
         <v/>
       </c>
       <c r="G117" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=trava+fim+trilho+din","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H117" s="13" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=arduino+mega+2560+r3","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H117" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-arduino-mega-2560-r3.html","🌏 Arduino Mega 2560 R3")</f>
+        <v/>
+      </c>
       <c r="I117" s="13" t="inlineStr"/>
       <c r="J117" s="14" t="inlineStr"/>
       <c r="K117" s="14">
@@ -4510,11 +4493,11 @@
     </row>
     <row r="118">
       <c r="A118" s="5" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Botão de Emergência cogumelo 22 mm</t>
+          <t>Shield de expansão Mega (bornes parafuso)</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
@@ -4524,22 +4507,19 @@
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>Com trava (girar p/ destravar) — 2 blocos NF (1 para o comando 24 V, 1 para a leitura do Arduino)</t>
+          <t>Sensor Shield V2.0</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr"/>
       <c r="F118" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/botao-emergencia-cogumelo-22-mm","🔎 botao emergencia cogumelo 22")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/shield-expansao-mega","🔎 shield expansao mega")</f>
         <v/>
       </c>
       <c r="G118" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=botao+emergencia+cogumelo+22+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H118" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-22mm-emergency-stop-mushroom-button.html","🌏 22mm emergency stop mushro")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=shield+expansao+mega","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H118" s="8" t="inlineStr"/>
       <c r="I118" s="8" t="inlineStr"/>
       <c r="J118" s="9" t="inlineStr"/>
       <c r="K118" s="9">
@@ -4549,11 +4529,11 @@
     </row>
     <row r="119">
       <c r="A119" s="10" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>Botão START 22 mm</t>
+          <t>Suporte DIN para Arduino Mega</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
@@ -4563,22 +4543,19 @@
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>Verde, momentâneo — 1 bloco NA (só informa o Arduino)</t>
+          <t>Ou SPCI4/adaptador</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr"/>
       <c r="F119" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/botao-start-22-mm","🔎 botao start 22 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/suporte-din-arduino-mega","🔎 suporte din arduino mega")</f>
         <v/>
       </c>
       <c r="G119" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=botao+start+22+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H119" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-22mm-push-button-switch-green.html","🌏 22mm push button switch gr")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=suporte+din+arduino+mega","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H119" s="13" t="inlineStr"/>
       <c r="I119" s="13" t="inlineStr"/>
       <c r="J119" s="14" t="inlineStr"/>
       <c r="K119" s="14">
@@ -4588,11 +4565,11 @@
     </row>
     <row r="120">
       <c r="A120" s="5" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>Botão STOP 22 mm</t>
+          <t>⭐ ES3C28P — ESP32-S3 2,8" toque capacitivo, microSD, microfone (LCDWIKI)</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
@@ -4602,22 +4579,19 @@
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>Vermelho, momentâneo — 1 NF (corta o KA2 em 24 V) + 1 NA (avisa o Arduino)</t>
+          <t>A IHM do projeto. Substitui a tela Nextion e o módulo de cartão SD. 8 MB de PSRAM → a Xiaozhi roda. ILI9341V 240×320, toque capacitivo FT6336G, 5 V / 140 mA, −30 a 80 °C. Vem com alto-falante. ⚠️ Comprar a versão ES3C28P (com toque) — a ES3N28P é sem toque</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr"/>
       <c r="F120" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/botao-stop-22-mm","🔎 botao stop 22 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/es3c28p-esp32-s3-2-8-toque-capacitivo-microsd","🔎 es3c28p esp32 s3 2,8 toque c")</f>
         <v/>
       </c>
       <c r="G120" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=botao+stop+22+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H120" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-22mm-push-button-switch-red.html","🌏 22mm push button switch re")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=es3c28p+esp32+s3+2%2C8+toque+capacitivo%2C+microsd%2C","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H120" s="8" t="inlineStr"/>
       <c r="I120" s="8" t="inlineStr"/>
       <c r="J120" s="9" t="inlineStr"/>
       <c r="K120" s="9">
@@ -4625,75 +4599,43 @@
         <v/>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="10" t="n">
-        <v>106</v>
-      </c>
-      <c r="B121" s="11" t="inlineStr">
-        <is>
-          <t>Botão REARME 22 mm</t>
-        </is>
-      </c>
-      <c r="C121" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D121" s="11" t="inlineStr">
-        <is>
-          <t>AZUL, momentâneo — 1 bloco NA. Refaz o selo do KA1 após a emergência. Buscar botão pulsador azul 22mm</t>
-        </is>
-      </c>
-      <c r="E121" s="11" t="inlineStr"/>
-      <c r="F121" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/botao-rearme-22-mm","🔎 botao rearme 22 mm")</f>
-        <v/>
-      </c>
-      <c r="G121" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=botao+rearme+22+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H121" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-22mm-push-button-switch-blue.html","🌏 22mm push button switch bl")</f>
-        <v/>
-      </c>
-      <c r="I121" s="13" t="inlineStr"/>
-      <c r="J121" s="14" t="inlineStr"/>
-      <c r="K121" s="14">
-        <f>IF(C121*J121=0,"",C121*J121)</f>
-        <v/>
+    <row r="121" ht="22" customHeight="1">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>L.2 — Potência e acionamento</t>
+        </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>Blocos de contato 22 mm avulsos</t>
+          <t>Driver ponte-H BTS7960</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>3 NF + 1 NA: emergência (2 NF), STOP (1 NF + 1 NA). Ver Doc 31 §31.3</t>
+          <t>43 A, pino IS de diagnóstico</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr"/>
       <c r="F122" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/blocos-contato-22-mm-avulsos","🔎 blocos contato 22 mm avulsos")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/driver-ponte-h-bts7960","🔎 driver ponte h bts7960")</f>
         <v/>
       </c>
       <c r="G122" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=blocos+contato+22+mm+avulsos","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H122" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-22mm-push-button-contact-block-no-nc.html","🌏 22mm push button contact b")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=driver+ponte+h+bts7960","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H122" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-bts7960-43a-motor-driver-module.html","🌏 BTS7960 43A motor driver m")</f>
         <v/>
       </c>
       <c r="I122" s="8" t="inlineStr"/>
@@ -4705,30 +4647,30 @@
     </row>
     <row r="123">
       <c r="A123" s="10" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>Chave seccionadora 24 V no painel</t>
+          <t>Suporte SPCI4 trilho DIN</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>Rotativa 2 posições 22 mm — chave geral local da máquina</t>
+          <t>Fixa PCI 100 × 79 mm</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr"/>
       <c r="F123" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/chave-seccionadora-24-v-painel","🔎 chave seccionadora 24 v pain")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/suporte-spci4-trilho-din","🔎 suporte spci4 trilho din")</f>
         <v/>
       </c>
       <c r="G123" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=chave+seccionadora+24+v+painel","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=suporte+spci4+trilho+din","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H123" s="13" t="inlineStr"/>
@@ -4741,34 +4683,34 @@
     </row>
     <row r="124">
       <c r="A124" s="5" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>Sinaleiros LED 22 mm 24 V</t>
+          <t>Cooler 40 mm 12 V</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>Verde (RUN), Azul (COOL), Amarelo (HEAT), Vermelho (FAULT). ⚠️ 24 V confirmado — acionados pelo ULN2803 da placa PI-1, alimentados pelo BD-24V permanente (o vermelho de FALHA precisa continuar aceso com a emergência acionada). ~20 mA cada, resistor interno já incluso</t>
+          <t>Refrigeração dos BTS</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr"/>
       <c r="F124" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/sinaleiros-led-22-mm-24-v","🔎 sinaleiros led 22 mm 24 v")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cooler-40-mm-12-v","🔎 cooler 40 mm 12 v")</f>
         <v/>
       </c>
       <c r="G124" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=sinaleiros+led+22+mm+24+v","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H124" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-22mm-led-pilot-indicator-lamp-24v.html","🌏 22mm LED pilot indicator l")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cooler+40+mm+12+v","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H124" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-40mm-fan-12v-dc.html","🌏 40mm fan 12V DC")</f>
         <v/>
       </c>
       <c r="I124" s="8" t="inlineStr"/>
@@ -4780,33 +4722,36 @@
     </row>
     <row r="125">
       <c r="A125" s="10" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>Prensa-cabo PG9</t>
+          <t>KA1 e KA2 — Relé 8 pinos 24 Vcc + base DIN</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>Entrada 24 V de potência (vindo do P1) · saída de potência para a câmara · saída de sinais</t>
+          <t>2 conjuntos em uso; 24 Vcc, 2 contatos reversiveis, KA2 com 10 A em CC</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr"/>
       <c r="F125" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/prensa-cabo-pg9","🔎 prensa cabo pg9")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/ka1-ka2","🔎 ka1 ka2")</f>
         <v/>
       </c>
       <c r="G125" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=prensa+cabo+pg9","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H125" s="13" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=ka1+ka2","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H125" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-jqx-13f-ly2n-24vdc-relay-8-pin-2co-with-socket.html","🌏 JQX-13F LY2N 24VDC relay 8")</f>
+        <v/>
+      </c>
       <c r="I125" s="13" t="inlineStr"/>
       <c r="J125" s="14" t="inlineStr"/>
       <c r="K125" s="14">
@@ -4816,30 +4761,30 @@
     </row>
     <row r="126">
       <c r="A126" s="5" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>Prensa-cabo PG7</t>
+          <t>*Alternativa premium (só se sobrar orçamento)*</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>Entrada 5 V (do T2) e entrada 12 V auxiliar + 24 V (do T3)</t>
+          <t>Finder 46.61 24VDC (1 reversível 16 A) + base 95.05 para o KA2, ~R$ 80–110. Vale se você quiser folga grande sobre os 6,0 A e datasheet publicado</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr"/>
       <c r="F126" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/prensa-cabo-pg7","🔎 prensa cabo pg7")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/alternativa-premium","🔎 alternativa premium")</f>
         <v/>
       </c>
       <c r="G126" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=prensa+cabo+pg7","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=alternativa+premium","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H126" s="8" t="inlineStr"/>
@@ -4852,33 +4797,36 @@
     </row>
     <row r="127">
       <c r="A127" s="10" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>Bolsa porta-documentos p/ porta</t>
+          <t>Resistor 10 kΩ 1/4 W</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>Guarda o diagrama elétrico — padrão em painel industrial</t>
+          <t>Pull-down em cada R_EN dos BTS7960 (2) + reservas. ⚠️ Garante que pino solto = driver desligado — ficou ainda mais crítico com os 24 V permanentes na entrada dos BTS</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr"/>
       <c r="F127" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/bolsa-porta-documentos-p-porta","🔎 bolsa porta documentos p por")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-10-k-1-4-w","🔎 resistor 10 k 1 4 w")</f>
         <v/>
       </c>
       <c r="G127" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=bolsa+porta+documentos+p+porta","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H127" s="13" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+10+k+1+4+w","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H127" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
+        <v/>
+      </c>
       <c r="I127" s="13" t="inlineStr"/>
       <c r="J127" s="14" t="inlineStr"/>
       <c r="K127" s="14">
@@ -4886,43 +4834,75 @@
         <v/>
       </c>
     </row>
-    <row r="128" ht="22" customHeight="1">
-      <c r="A128" s="4" t="inlineStr">
-        <is>
-          <t>L.1 — Controle e interface</t>
-        </is>
+    <row r="128">
+      <c r="A128" s="5" t="n">
+        <v>111</v>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>Resistor 22 kΩ 1/4 W ⬆</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>Braço superior do divisor de realimentação de tensão para o pino D25</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr"/>
+      <c r="F128" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-22-k-1-4-w","🔎 resistor 22 k 1 4 w")</f>
+        <v/>
+      </c>
+      <c r="G128" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+22+k+1+4+w","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H128" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
+        <v/>
+      </c>
+      <c r="I128" s="8" t="inlineStr"/>
+      <c r="J128" s="9" t="inlineStr"/>
+      <c r="K128" s="9">
+        <f>IF(C128*J128=0,"",C128*J128)</f>
+        <v/>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="10" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>Arduino Mega 2560 R3</t>
+          <t>Resistor 4,7 kΩ 1/4 W</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>ATmega2560, 54 GPIO, 4 UARTs</t>
+          <t>Braço inferior do mesmo divisor</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr"/>
       <c r="F129" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/arduino-mega-2560-r3","🔎 arduino mega 2560 r3")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-4-7-k-1-4-w","🔎 resistor 4,7 k 1 4 w")</f>
         <v/>
       </c>
       <c r="G129" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=arduino+mega+2560+r3","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H129" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-arduino-mega-2560-r3.html","🌏 Arduino Mega 2560 R3")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+4%2C7+k+1+4+w","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H129" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
         <v/>
       </c>
       <c r="I129" s="13" t="inlineStr"/>
@@ -4932,49 +4912,20 @@
         <v/>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="5" t="n">
-        <v>114</v>
-      </c>
-      <c r="B130" s="6" t="inlineStr">
-        <is>
-          <t>Shield de expansão Mega (bornes parafuso)</t>
-        </is>
-      </c>
-      <c r="C130" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>Sensor Shield V2.0</t>
-        </is>
-      </c>
-      <c r="E130" s="6" t="inlineStr"/>
-      <c r="F130" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/shield-expansao-mega","🔎 shield expansao mega")</f>
-        <v/>
-      </c>
-      <c r="G130" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=shield+expansao+mega","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H130" s="8" t="inlineStr"/>
-      <c r="I130" s="8" t="inlineStr"/>
-      <c r="J130" s="9" t="inlineStr"/>
-      <c r="K130" s="9">
-        <f>IF(C130*J130=0,"",C130*J130)</f>
-        <v/>
+    <row r="130" ht="22" customHeight="1">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>L.3 — Atuadores térmicos e ventilação</t>
+        </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="10" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>Suporte DIN para Arduino Mega</t>
+          <t>⭐ Kit duplo de refrigeração Peltier (2× TEC1-12706)</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
@@ -4984,19 +4935,22 @@
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>Ou SPCI4/adaptador</t>
+          <t>Adotado — kit já conferido por foto (imagens/peltir.avif): 2 conjuntos lado a lado, cada pastilha com seu par de fios e cada ventoinha com cabo próprio, o que viabiliza as modificações 1 e 2 sem cortar nada. Traz 2 pastilhas + radiador + 2 blocos frios + ventoinhas + montagem térmica pronta. Anunciado como 12 V / 15 A, ou seja, vem ligado em PARALELO — ⚠️ religar em SÉRIE para 24 V / 6,0 A (ver as 3 modificações abaixo). ~200 × 115 × 85 mm. Buscar kit peltier duplo TEC1-12706 refrigeração</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr"/>
       <c r="F131" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/suporte-din-arduino-mega","🔎 suporte din arduino mega")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/kit-duplo-refrigeracao-peltier","🔎 kit duplo refrigeracao pelti")</f>
         <v/>
       </c>
       <c r="G131" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=suporte+din+arduino+mega","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H131" s="13" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=kit+duplo+refrigeracao+peltier","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H131" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-dual-tec1-12706-peltier-cooler-kit-12v.html","🌏 dual TEC1-12706 peltier co")</f>
+        <v/>
+      </c>
       <c r="I131" s="13" t="inlineStr"/>
       <c r="J131" s="14" t="inlineStr"/>
       <c r="K131" s="14">
@@ -5006,11 +4960,11 @@
     </row>
     <row r="132">
       <c r="A132" s="5" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>Tela Nextion Basic 3.2"</t>
+          <t>Pastilha Peltier TEC1-12706 avulsa</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
@@ -5020,20 +4974,20 @@
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>NX4024T032, 400×240, TTL 5 V</t>
+          <t>Reserva. ⚠️ Trocar uma pastilha do kit exige desmontar a junta térmica — tenha a peça, mas conte com o trabalho</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr"/>
       <c r="F132" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/tela-nextion-basic-3-2","🔎 tela nextion basic 3 2")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/pastilha-peltier-tec1-12706-avulsa","🔎 pastilha peltier tec1 12706 ")</f>
         <v/>
       </c>
       <c r="G132" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=tela+nextion+basic+3+2","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H132" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-nextion-nx4024t032-3-2-inch-hmi.html","🌏 Nextion NX4024T032 3.2 inc")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=pastilha+peltier+tec1+12706+avulsa","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H132" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-tec1-12706-peltier-module.html","🌏 TEC1-12706 peltier module")</f>
         <v/>
       </c>
       <c r="I132" s="8" t="inlineStr"/>
@@ -5045,11 +4999,11 @@
     </row>
     <row r="133">
       <c r="A133" s="10" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>ESP32-WROOM-32U</t>
+          <t>⭐ Módulo MOSFET 4 canais isolado — LR7843 (MV-1)</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
@@ -5059,22 +5013,19 @@
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>30 pinos, conector de antena IPEX</t>
+          <t>66 × 50,5 mm, optoacoplador por canal, jumper H/L por canal, 60 W por canal. Comanda os 3 grupos de ventoinha e sobra 1 canal. Buscar modulo mosfet 4 canais optoacoplador LR7843</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr"/>
       <c r="F133" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/esp32-wroom-32u","🔎 esp32 wroom 32u")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/modulo-mosfet-4-canais-isolado","🔎 modulo mosfet 4 canais isola")</f>
         <v/>
       </c>
       <c r="G133" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=esp32+wroom+32u","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H133" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-esp32-wroom-32u.html","🌏 ESP32 WROOM 32U")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=modulo+mosfet+4+canais+isolado","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H133" s="13" t="inlineStr"/>
       <c r="I133" s="13" t="inlineStr"/>
       <c r="J133" s="14" t="inlineStr"/>
       <c r="K133" s="14">
@@ -5082,49 +5033,20 @@
         <v/>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="5" t="n">
-        <v>118</v>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
-        <is>
-          <t>DNLCB30 — base DIN para ESP32</t>
-        </is>
-      </c>
-      <c r="C134" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
-        <is>
-          <t>Entrada 7–35 V (alimentada direto do barramento 24 V), conversão 3,3 ↔ 5 V automática. Não inclui o ESP32</t>
-        </is>
-      </c>
-      <c r="E134" s="6" t="inlineStr"/>
-      <c r="F134" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/dnlcb30-base-din-esp32","🔎 dnlcb30 base din esp32")</f>
-        <v/>
-      </c>
-      <c r="G134" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=dnlcb30+base+din+esp32","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H134" s="8" t="inlineStr"/>
-      <c r="I134" s="8" t="inlineStr"/>
-      <c r="J134" s="9" t="inlineStr"/>
-      <c r="K134" s="9">
-        <f>IF(C134*J134=0,"",C134*J134)</f>
-        <v/>
+    <row r="134" ht="22" customHeight="1">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>L.4 — Sensores</t>
+        </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="10" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>Pigtail IPEX (u.FL) → SMA macho, 20–30 cm</t>
+          <t>Sensor DS18B20 à prova d'água</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
@@ -5134,20 +5056,20 @@
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>Liga o ESP32 ao conector de painel</t>
+          <t>1-Wire, 3 fios, colado no dissipador quente; nao fica no centro da camara</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr"/>
       <c r="F135" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/pigtail-ipex-sma-macho-20-30-cm","🔎 pigtail ipex sma macho, 20 3")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/sensor-ds18b20-prova-d-agua","🔎 sensor ds18b20 prova d agua")</f>
         <v/>
       </c>
       <c r="G135" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=pigtail+ipex+sma+macho%2C+20+30+cm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H135" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-ipex-u-fl-to-sma-pigtail-cable.html","🌏 IPEX u.FL to SMA pigtail c")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=sensor+ds18b20+prova+d+agua","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H135" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-ds18b20-waterproof-temperature-sensor.html","🌏 DS18B20 waterproof tempera")</f>
         <v/>
       </c>
       <c r="I135" s="13" t="inlineStr"/>
@@ -5159,34 +5081,34 @@
     </row>
     <row r="136">
       <c r="A136" s="5" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>Conector SMA fêmea de painel (bulkhead)</t>
+          <t>Resistor 4,7 kΩ 1/4 W</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>Rosca de painel Ø 6,5 mm, com porca e arruela de pressão. ⚠️ Nunca passar o coaxial por prensa-cabo</t>
+          <t>Pull-up do barramento 1-Wire</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr"/>
       <c r="F136" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/conector-sma-femea-painel","🔎 conector sma femea painel")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-4-7-k-1-4-w","🔎 resistor 4,7 k 1 4 w")</f>
         <v/>
       </c>
       <c r="G136" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=conector+sma+femea+painel","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H136" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-sma-bulkhead-panel-connector-female.html","🌏 SMA bulkhead panel connect")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+4%2C7+k+1+4+w","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H136" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
         <v/>
       </c>
       <c r="I136" s="8" t="inlineStr"/>
@@ -5198,11 +5120,11 @@
     </row>
     <row r="137">
       <c r="A137" s="10" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>Antena 2,4 GHz SMA macho 3 dBi articulável</t>
+          <t>Sensor AM2315C</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
@@ -5212,20 +5134,20 @@
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>Rosqueada por fora, na lateral direita, parte alta do painel</t>
+          <t>I²C, umidade + temperatura, carcaça selada</t>
         </is>
       </c>
       <c r="E137" s="11" t="inlineStr"/>
       <c r="F137" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/antena-2-4-ghz-sma-macho-3-dbi","🔎 antena 2,4 ghz sma macho 3 d")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/sensor-am2315c","🔎 sensor am2315c")</f>
         <v/>
       </c>
       <c r="G137" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=antena+2%2C4+ghz+sma+macho+3+dbi","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H137" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-2-4ghz-sma-antenna-3dbi.html","🌏 2.4GHz SMA antenna 3dBi")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=sensor+am2315c","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H137" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-am2315c-temperature-humidity-sensor.html","🌏 AM2315C temperature humidi")</f>
         <v/>
       </c>
       <c r="I137" s="13" t="inlineStr"/>
@@ -5237,34 +5159,34 @@
     </row>
     <row r="138">
       <c r="A138" s="5" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>Módulo Micro SD (SPI)</t>
+          <t>Capacitor cerâmico 100 nF</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>5 V, com regulador e level shifter</t>
+          <t>Filtro dos pinos IS dos BTS (2) + filtro do divisor D25 (1) + reservas</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr"/>
       <c r="F138" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/modulo-micro-sd","🔎 modulo micro sd")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/capacitor-ceramico-100-nf","🔎 capacitor ceramico 100 nf")</f>
         <v/>
       </c>
       <c r="G138" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=modulo+micro+sd","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H138" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-micro-sd-card-module-spi-arduino.html","🌏 micro SD card module SPI a")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=capacitor+ceramico+100+nf","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H138" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-100nf-ceramic-capacitor.html","🌏 100nF ceramic capacitor")</f>
         <v/>
       </c>
       <c r="I138" s="8" t="inlineStr"/>
@@ -5276,34 +5198,34 @@
     </row>
     <row r="139">
       <c r="A139" s="10" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>Cartão Micro SD</t>
+          <t>Resistor 220 Ω 1/4 W</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>8–16 GB, Classe 10</t>
+          <t>4 usos + 2 reservas — série dos LEDs brancos da iluminação da maquete (5 V). ⚠️ Não são mais dos sinaleiros do painel, que agora são de 24 V</t>
         </is>
       </c>
       <c r="E139" s="11" t="inlineStr"/>
       <c r="F139" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/cartao-micro-sd","🔎 cartao micro sd")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-220-1-4-w","🔎 resistor 220 1 4 w")</f>
         <v/>
       </c>
       <c r="G139" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=cartao+micro+sd","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H139" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-micro-sd-card-module-spi-arduino.html","🌏 micro SD card module SPI a")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+220+1+4+w","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H139" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
         <v/>
       </c>
       <c r="I139" s="13" t="inlineStr"/>
@@ -5313,71 +5235,39 @@
         <v/>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="5" t="n">
-        <v>124</v>
-      </c>
-      <c r="B140" s="6" t="inlineStr">
-        <is>
-          <t>Módulo RTC DS3231</t>
-        </is>
-      </c>
-      <c r="C140" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr">
-        <is>
-          <t>I²C, ±2 ppm</t>
-        </is>
-      </c>
-      <c r="E140" s="6" t="inlineStr"/>
-      <c r="F140" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/modulo-rtc-ds3231","🔎 modulo rtc ds3231")</f>
-        <v/>
-      </c>
-      <c r="G140" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=modulo+rtc+ds3231","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H140" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-ds3231-rtc-module.html","🌏 DS3231 RTC module")</f>
-        <v/>
-      </c>
-      <c r="I140" s="8" t="inlineStr"/>
-      <c r="J140" s="9" t="inlineStr"/>
-      <c r="K140" s="9">
-        <f>IF(C140*J140=0,"",C140*J140)</f>
-        <v/>
+    <row r="140" ht="22" customHeight="1">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>L.4b — Posições de ensaio (dispositivos sob teste)</t>
+        </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="10" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>Bateria CR2032</t>
+          <t>⭐ Módulo multiplexador 16 canais CD74HC4067 — ⚠️ a versão em PLACA, com pinos</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 (vem em pacote de 5)</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>Backup do RTC</t>
+          <t>O coração da detecção de falha. Varre até 16 posições com uma única entrada analógica do Arduino. Buscar modulo multiplexador analogico 16 canais CD74HC4067</t>
         </is>
       </c>
       <c r="E141" s="11" t="inlineStr"/>
       <c r="F141" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/bateria-cr2032","🔎 bateria cr2032")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/modulo-multiplexador-16-canais-cd74hc4067","🔎 modulo multiplexador 16 cana")</f>
         <v/>
       </c>
       <c r="G141" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=bateria+cr2032","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=modulo+multiplexador+16+canais+cd74hc4067","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H141" s="13" t="inlineStr"/>
@@ -5391,40 +5281,40 @@
     <row r="142" ht="22" customHeight="1">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>L.2 — Potência e acionamento</t>
+          <t>L.5 — Placa de Interface PI-1 (onde os componentes discretos moram)</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="10" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>Driver ponte-H BTS7960</t>
+          <t>Placa ilhada 9 x 15 cm para PI-1 + PI-2</t>
         </is>
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>43 A, pino IS de diagnóstico</t>
+          <t>1 placa de 34 x 58 furos, cortada ao meio para formar as duas placas</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr"/>
       <c r="F143" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/driver-ponte-h-bts7960","🔎 driver ponte h bts7960")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/placa-ilhada","🔎 placa ilhada")</f>
         <v/>
       </c>
       <c r="G143" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=driver+ponte+h+bts7960","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H143" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-bts7960-43a-motor-driver-module.html","🌏 BTS7960 43A motor driver m")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=placa+ilhada","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H143" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-perfboard-prototype-pcb.html","🌏 perfboard prototype PCB")</f>
         <v/>
       </c>
       <c r="I143" s="13" t="inlineStr"/>
@@ -5436,11 +5326,11 @@
     </row>
     <row r="144">
       <c r="A144" s="5" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>Suporte SPCI4 trilho DIN</t>
+          <t>⭐ Caixa modular para trilho DIN — 6 módulos (105 mm)</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
@@ -5450,16 +5340,16 @@
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>Fixa PCI 100 × 79 mm</t>
+          <t>Invólucros da PI-1 e da PI-2, no trilho 3. ⚠️ 6 módulos, não 4: as placas passaram a 86,4 mm de largura, e uma caixa de 4M só comporta 61 mm. A largura extra é o que permite rotear os fios em canais separados por baixo. Buscar caixa para trilho din 6m modular</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr"/>
       <c r="F144" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/suporte-spci4-trilho-din","🔎 suporte spci4 trilho din")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/caixa-modular-trilho-din","🔎 caixa modular trilho din")</f>
         <v/>
       </c>
       <c r="G144" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=suporte+spci4+trilho+din","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=caixa+modular+trilho+din","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H144" s="8" t="inlineStr"/>
@@ -5472,36 +5362,33 @@
     </row>
     <row r="145">
       <c r="A145" s="10" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>Cooler 40 mm 12 V</t>
+          <t>⭐ Borne KF301 / KRE passo 5,08 mm — 3 vias</t>
         </is>
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>Refrigeração dos BTS</t>
+          <t>6 em uso + 4 reserva. Encaixam lado a lado — não se compra bloco de 11 vias, montam-se 3+3+3+2</t>
         </is>
       </c>
       <c r="E145" s="11" t="inlineStr"/>
       <c r="F145" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/cooler-40-mm-12-v","🔎 cooler 40 mm 12 v")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/borne-kf301-kre-passo-5-08-mm","🔎 borne kf301 kre passo 5,08 m")</f>
         <v/>
       </c>
       <c r="G145" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=cooler+40+mm+12+v","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H145" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-40mm-fan-12v-dc.html","🌏 40mm fan 12V DC")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=borne+kf301+kre+passo+5%2C08+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H145" s="13" t="inlineStr"/>
       <c r="I145" s="13" t="inlineStr"/>
       <c r="J145" s="14" t="inlineStr"/>
       <c r="K145" s="14">
@@ -5511,30 +5398,30 @@
     </row>
     <row r="146">
       <c r="A146" s="5" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>KA1 — Relé de interface 24 Vcc, 2 contatos</t>
+          <t>⭐ Borne KF301 / KRE passo 5,08 mm — 2 vias</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
         <is>
-          <t>Faz o selo (habilitação) e alimenta a bobina do KA2. Conduz só miliampères — 6 A basta. Buscar relé de interface 24vdc 2 contatos din. Premium: Finder 55.32.9.024.0040</t>
+          <t>7 em uso + 5 reserva. Junto com os de 3 vias formam as 32 vias das duas placas</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr"/>
       <c r="F146" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/rele-interface-24-vcc-2-contatos","🔎 rele interface 24 vcc, 2 con")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/borne-kf301-kre-passo-5-08-mm","🔎 borne kf301 kre passo 5,08 m")</f>
         <v/>
       </c>
       <c r="G146" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=rele+interface+24+vcc%2C+2+contatos","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=borne+kf301+kre+passo+5%2C08+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H146" s="8" t="inlineStr"/>
@@ -5547,11 +5434,11 @@
     </row>
     <row r="147">
       <c r="A147" s="10" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>KA2 — Relé de interface 24 Vcc, contato ≥ 10 A</t>
+          <t>CI ULN2803A (DIP 18 pinos)</t>
         </is>
       </c>
       <c r="C147" s="10" t="inlineStr">
@@ -5561,19 +5448,22 @@
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>É ele que chaveia os 24 V / 6,0 A de potência dos BTS. ⚠️ Confirme os 10 A no anúncio — a maioria dos slim é de 6 A — e confirme que a corrente é declarada em DC: muito relé de 10 A/250 VAC cai para 5 A ou menos em 24 Vcc, porque corrente contínua não tem passagem por zero e o arco custa mais a extinguir. Buscar relé de interface 24vdc 10a trilho din. Premium: Finder 46.61.9.024.0040 + base 95.05 (16 A)</t>
+          <t>Driver dos 4 sinaleiros de 24 V — 8 canais Darlington, 500 mA/50 V, com diodos de proteção internos. 1 uso + 1 reserva (o CI é barato e é o único ponto onde 24 V encosta na lógica)</t>
         </is>
       </c>
       <c r="E147" s="11" t="inlineStr"/>
       <c r="F147" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/rele-interface-24-vcc-contato-10","🔎 rele interface 24 vcc, conta")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/ci-uln2803a","🔎 ci uln2803a")</f>
         <v/>
       </c>
       <c r="G147" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=rele+interface+24+vcc%2C+contato+10","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H147" s="13" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=ci+uln2803a","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H147" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-uln2803a-dip18-darlington.html","🌏 ULN2803A DIP18 darlington")</f>
+        <v/>
+      </c>
       <c r="I147" s="13" t="inlineStr"/>
       <c r="J147" s="14" t="inlineStr"/>
       <c r="K147" s="14">
@@ -5583,34 +5473,34 @@
     </row>
     <row r="148">
       <c r="A148" s="5" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>Resistor 10 kΩ 1/4 W</t>
+          <t>Soquete DIP 18 pinos</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>Pull-down em cada R_EN dos BTS7960 (2) + reservas. ⚠️ Garante que pino solto = driver desligado — ficou ainda mais crítico com os 24 V permanentes na entrada dos BTS</t>
+          <t>⚠️ Solde o soquete, não o CI. Permite trocar o chip sem dessoldar nada</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr"/>
       <c r="F148" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-10-k-1-4-w","🔎 resistor 10 k 1 4 w")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/soquete-dip-18-pinos","🔎 soquete dip 18 pinos")</f>
         <v/>
       </c>
       <c r="G148" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+10+k+1+4+w","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H148" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=soquete+dip+18+pinos","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H148" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-dip18-ic-socket.html","🌏 DIP18 IC socket")</f>
         <v/>
       </c>
       <c r="I148" s="8" t="inlineStr"/>
@@ -5622,11 +5512,11 @@
     </row>
     <row r="149">
       <c r="A149" s="10" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>Resistor 22 kΩ 1/4 W ⬆</t>
+          <t>⭐ Módulo relé 1 canal 5 V, optoacoplado</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
@@ -5636,22 +5526,19 @@
       </c>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>Braço superior do divisor de realimentação de tensão para o pino D25</t>
+          <t>KA3 (NO) e KA4 (NC), optoacoplados; reservas opcionais</t>
         </is>
       </c>
       <c r="E149" s="11" t="inlineStr"/>
       <c r="F149" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-22-k-1-4-w","🔎 resistor 22 k 1 4 w")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/modulo-rele-1-canal-5-v-optoacoplado","🔎 modulo rele 1 canal 5 v, opt")</f>
         <v/>
       </c>
       <c r="G149" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+22+k+1+4+w","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H149" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=modulo+rele+1+canal+5+v%2C+optoacoplado","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H149" s="13" t="inlineStr"/>
       <c r="I149" s="13" t="inlineStr"/>
       <c r="J149" s="14" t="inlineStr"/>
       <c r="K149" s="14">
@@ -5661,36 +5548,33 @@
     </row>
     <row r="150">
       <c r="A150" s="5" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>Resistor 4,7 kΩ 1/4 W</t>
+          <t>⭐ Caixa modular DIN 4 módulos (70 mm)</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>Braço inferior do mesmo divisor</t>
+          <t>Abriga os dois módulos de relé empilhados, no trilho 2. Buscar caixa para trilho din 4m modular</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr"/>
       <c r="F150" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-4-7-k-1-4-w","🔎 resistor 4,7 k 1 4 w")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/caixa-modular-din-4-modulos","🔎 caixa modular din 4 modulos")</f>
         <v/>
       </c>
       <c r="G150" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+4%2C7+k+1+4+w","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H150" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=caixa+modular+din+4+modulos","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H150" s="8" t="inlineStr"/>
       <c r="I150" s="8" t="inlineStr"/>
       <c r="J150" s="9" t="inlineStr"/>
       <c r="K150" s="9">
@@ -5698,43 +5582,75 @@
         <v/>
       </c>
     </row>
-    <row r="151" ht="22" customHeight="1">
-      <c r="A151" s="4" t="inlineStr">
-        <is>
-          <t>L.3 — Atuadores térmicos e ventilação</t>
-        </is>
+    <row r="151">
+      <c r="A151" s="10" t="n">
+        <v>130</v>
+      </c>
+      <c r="B151" s="11" t="inlineStr">
+        <is>
+          <t>⭐ Resistor 10 kΩ · ¼ W</t>
+        </is>
+      </c>
+      <c r="C151" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D151" s="11" t="inlineStr">
+        <is>
+          <t>R10 e R11 — pull-down do IN de cada módulo para o 0 V. 2 em uso + 2 reserva. ⚠️ É o que torna o fail-safe medível: Arduino ausente ou fio rompido → IN em 0 V → relé aberto → potência cortada e ventoinha parada</t>
+        </is>
+      </c>
+      <c r="E151" s="11" t="inlineStr"/>
+      <c r="F151" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-10-k","🔎 resistor 10 k")</f>
+        <v/>
+      </c>
+      <c r="G151" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+10+k","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H151" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
+        <v/>
+      </c>
+      <c r="I151" s="13" t="inlineStr"/>
+      <c r="J151" s="14" t="inlineStr"/>
+      <c r="K151" s="14">
+        <f>IF(C151*J151=0,"",C151*J151)</f>
+        <v/>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>Pastilha Peltier TEC1-12706</t>
+          <t>⭐ Diodo 1N4007</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>12 V / ~6 A / 60 W cada. 2 em uso, ligadas EM SÉRIE (24 V / 6,0 A / 144 W) + 1 reserva. ⚠️ Comprar do mesmo lote/vendedor — em série as duas conduzem a mesma corrente, e pastilhas descasadas trabalham desequilibradas</t>
+          <t>D1 (bobina do KA2) e D2 (ventoinhas do radiador). ⭐ Não compre de novo: já estão na lista L.2, com 2 reservas. 🔥 Ficaram MAIS importantes com os módulos de relé: um contato seco abrindo uma bobina forma arco no contato do KA3, e um contato que pita acaba soldando — o veto do firmware perdido em silêncio. 🔎 O D1 pode ser dispensável: teste o KA2 em *teste de diodo* entre A1 e A2; se conduzir num sentido só, ele já tem diodo interno. ⚠️ O D2 é obrigatório — o motor é indutivo e nada o grampeia. Catodo no +12 V</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr"/>
       <c r="F152" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/pastilha-peltier-tec1-12706","🔎 pastilha peltier tec1 12706")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/diodo-1n4007","🔎 diodo 1n4007")</f>
         <v/>
       </c>
       <c r="G152" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=pastilha+peltier+tec1+12706","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H152" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-tec1-12706-peltier-module.html","🌏 TEC1-12706 peltier module")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=diodo+1n4007","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H152" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1n4007-diode.html","🌏 1N4007 diode")</f>
         <v/>
       </c>
       <c r="I152" s="8" t="inlineStr"/>
@@ -5746,36 +5662,33 @@
     </row>
     <row r="153">
       <c r="A153" s="10" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>Aquecedor PTC cerâmico 24 V / 80 W</t>
+          <t>Fio rígido 0,25 mm² para interligação</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 m</t>
         </is>
       </c>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>Com aletas e ventilador, versão de 24 V (~3,3 A) para ligar direto no barramento. ⚠️ 60 W não existe no mercado brasileiro — as versões reais são 80 W, 100 W e 150 W. Use a de 80 W: fica bem equilibrada contra os ~60 W de capacidade de refrigeração das 2 Peltier, e mantém a corrente em 3,3 A (metade da Peltier). A de 150 W passaria a ser o pior caso do ramal (6,25 A) e desequilibra o controle. Buscar aquecedor ptc 24v ventilador</t>
+          <t>Ligações por baixo da placa. ⚠️ Não usar "sobra de perna" de componente em trecho longo — oxida e não é isolada</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr"/>
       <c r="F153" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/aquecedor-ptc-ceramico-24-v-80-w","🔎 aquecedor ptc ceramico 24 v ")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-rigido-0-25-mm-interligacao","🔎 fio rigido 0,25 mm interliga")</f>
         <v/>
       </c>
       <c r="G153" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=aquecedor+ptc+ceramico+24+v+80+w","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H153" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-24v-ptc-heater-element-with-fan.html","🌏 24V PTC heater element wit")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+rigido+0%2C25+mm+interligacao","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H153" s="13" t="inlineStr"/>
       <c r="I153" s="13" t="inlineStr"/>
       <c r="J153" s="14" t="inlineStr"/>
       <c r="K153" s="14">
@@ -5785,36 +5698,33 @@
     </row>
     <row r="154">
       <c r="A154" s="5" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>Dissipador + cooler 80 mm p/ lado quente da Peltier</t>
+          <t>Verniz spray para PCI (ou esmalte incolor)</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
-          <t>Um para cada pastilha. ⚠️ 3 fios (com sinal de RPM) nos dois — o firmware monitora os dois tacômetros e bloqueia a refrigeração se qualquer um parar</t>
+          <t>Proteção do lado da solda contra umidade e oxidação</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr"/>
       <c r="F154" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/dissipador-cooler-80-mm-p-lado-quente","🔎 dissipador cooler 80 mm p la")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/verniz-spray-pci","🔎 verniz spray pci")</f>
         <v/>
       </c>
       <c r="G154" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=dissipador+cooler+80+mm+p+lado+quente","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H154" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-80mm-heatsink-fan-cpu-cooler-3pin.html","🌏 80mm heatsink fan CPU cool")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=verniz+spray+pci","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H154" s="8" t="inlineStr"/>
       <c r="I154" s="8" t="inlineStr"/>
       <c r="J154" s="9" t="inlineStr"/>
       <c r="K154" s="9">
@@ -5824,34 +5734,34 @@
     </row>
     <row r="155">
       <c r="A155" s="10" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>Pasta térmica</t>
+          <t>Termorretrátil Ø 2 mm</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30 cm</t>
         </is>
       </c>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>Seringa 5 g — dá para os 2 conjuntos</t>
+          <t>Isolação dos 2 resistores de 10 kΩ soldados nos BTS7960</t>
         </is>
       </c>
       <c r="E155" s="11" t="inlineStr"/>
       <c r="F155" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/pasta-termica","🔎 pasta termica")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/termorretratil-2-mm","🔎 termorretratil 2 mm")</f>
         <v/>
       </c>
       <c r="G155" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=pasta+termica","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H155" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-thermal-paste-syringe.html","🌏 thermal paste syringe")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=termorretratil+2+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H155" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-heat-shrink-tubing-kit.html","🌏 heat shrink tubing kit")</f>
         <v/>
       </c>
       <c r="I155" s="13" t="inlineStr"/>
@@ -5863,36 +5773,33 @@
     </row>
     <row r="156">
       <c r="A156" s="5" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>Fan 60 × 60 mm 12 V</t>
+          <t>Etiqueta impressa em papel adesivo</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr">
         <is>
-          <t>Internas — lado PTC (1 sopra ↑, 1 sopra ↓)</t>
+          <t>Identificação das 20 vias na frente da caixa — é o que torna a placa auditável</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr"/>
       <c r="F156" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fan-60-60-mm-12-v","🔎 fan 60 60 mm 12 v")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/etiqueta-impressa-papel-adesivo","🔎 etiqueta impressa papel ades")</f>
         <v/>
       </c>
       <c r="G156" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fan+60+60+mm+12+v","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H156" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-60mm-fan-12v-dc.html","🌏 60mm fan 12V DC")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=etiqueta+impressa+papel+adesivo","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H156" s="8" t="inlineStr"/>
       <c r="I156" s="8" t="inlineStr"/>
       <c r="J156" s="9" t="inlineStr"/>
       <c r="K156" s="9">
@@ -5900,84 +5807,86 @@
         <v/>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="10" t="n">
-        <v>139</v>
-      </c>
-      <c r="B157" s="11" t="inlineStr">
-        <is>
-          <t>Fan 40 × 40 mm 12 V</t>
-        </is>
-      </c>
-      <c r="C157" s="10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D157" s="11" t="inlineStr">
-        <is>
-          <t>Internas — lado Peltier (1 sopra ↓, 1 sopra ↑)</t>
-        </is>
-      </c>
-      <c r="E157" s="11" t="inlineStr"/>
-      <c r="F157" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fan-40-40-mm-12-v","🔎 fan 40 40 mm 12 v")</f>
-        <v/>
-      </c>
-      <c r="G157" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fan+40+40+mm+12+v","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H157" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-40mm-fan-12v-dc.html","🌏 40mm fan 12V DC")</f>
-        <v/>
-      </c>
-      <c r="I157" s="13" t="inlineStr"/>
-      <c r="J157" s="14" t="inlineStr"/>
-      <c r="K157" s="14">
-        <f>IF(C157*J157=0,"",C157*J157)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="158" ht="22" customHeight="1">
-      <c r="A158" s="4" t="inlineStr">
-        <is>
-          <t>L.4 — Sensores</t>
-        </is>
+    <row r="157" ht="22" customHeight="1">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>🔧 CAMADA 3 — CABOS E ACESSÓRIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="n">
+        <v>136</v>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>Cabo flexivel 1,5 mm² azul escuro</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>3 m</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t>750 V; 0 V comum conforme a codificacao do React</t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>Retorno geral 0 V (6,9 A — soma dos 3 ramais)</t>
+        </is>
+      </c>
+      <c r="F158" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-flexivel-1-5-mm-preto","🔎 cabo flexivel 1,5 mm preto")</f>
+        <v/>
+      </c>
+      <c r="G158" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+flexivel+1%2C5+mm+preto","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H158" s="8" t="inlineStr"/>
+      <c r="I158" s="8" t="inlineStr"/>
+      <c r="J158" s="9" t="inlineStr"/>
+      <c r="K158" s="9">
+        <f>IF(C158*J158=0,"",C158*J158)</f>
+        <v/>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="10" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>Sensor DS18B20 à prova d'água</t>
+          <t>Cabo flexível 1,5 mm² vermelho</t>
         </is>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2 m</t>
         </is>
       </c>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>1-Wire, ±0,5 °C — centro da câmara</t>
-        </is>
-      </c>
-      <c r="E159" s="11" t="inlineStr"/>
+          <t>750 V</t>
+        </is>
+      </c>
+      <c r="E159" s="11" t="inlineStr">
+        <is>
+          <t>24 V de potência — P1 → painel → BTS (6,0 A)</t>
+        </is>
+      </c>
       <c r="F159" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/sensor-ds18b20-prova-d-agua","🔎 sensor ds18b20 prova d agua")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-flexivel-1-5-mm-vermelho","🔎 cabo flexivel 1,5 mm vermelh")</f>
         <v/>
       </c>
       <c r="G159" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=sensor+ds18b20+prova+d+agua","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H159" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-ds18b20-waterproof-temperature-sensor.html","🌏 DS18B20 waterproof tempera")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+flexivel+1%2C5+mm+vermelho","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H159" s="13" t="inlineStr"/>
       <c r="I159" s="13" t="inlineStr"/>
       <c r="J159" s="14" t="inlineStr"/>
       <c r="K159" s="14">
@@ -5987,36 +5896,37 @@
     </row>
     <row r="160">
       <c r="A160" s="5" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>Resistor 4,7 kΩ 1/4 W</t>
+          <t>Cabo flexível 0,75 mm² vermelho/preto</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3 m</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>Pull-up do barramento 1-Wire</t>
-        </is>
-      </c>
-      <c r="E160" s="6" t="inlineStr"/>
+          <t>750 V</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="inlineStr">
+        <is>
+          <t>Barramento 24 V (trechos internos) e saída de 12 V do T3 (1,0 A)</t>
+        </is>
+      </c>
       <c r="F160" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-4-7-k-1-4-w","🔎 resistor 4,7 k 1 4 w")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-flexivel-0-75-mm-vermelho-preto","🔎 cabo flexivel 0,75 mm vermel")</f>
         <v/>
       </c>
       <c r="G160" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+4%2C7+k+1+4+w","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H160" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+flexivel+0%2C75+mm+vermelho+preto","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H160" s="8" t="inlineStr"/>
       <c r="I160" s="8" t="inlineStr"/>
       <c r="J160" s="9" t="inlineStr"/>
       <c r="K160" s="9">
@@ -6026,36 +5936,37 @@
     </row>
     <row r="161">
       <c r="A161" s="10" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>Sensor AM2315C</t>
+          <t>Cabo flexível 0,5 mm² (5 cores)</t>
         </is>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10 m</t>
         </is>
       </c>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>I²C, umidade + temperatura, carcaça selada</t>
-        </is>
-      </c>
-      <c r="E161" s="11" t="inlineStr"/>
+          <t>750 V</t>
+        </is>
+      </c>
+      <c r="E161" s="11" t="inlineStr">
+        <is>
+          <t>5 V e derivações do 12 V auxiliar</t>
+        </is>
+      </c>
       <c r="F161" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/sensor-am2315c","🔎 sensor am2315c")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-flexivel-0-5-mm","🔎 cabo flexivel 0,5 mm")</f>
         <v/>
       </c>
       <c r="G161" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=sensor+am2315c","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H161" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-am2315c-temperature-humidity-sensor.html","🌏 AM2315C temperature humidi")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+flexivel+0%2C5+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H161" s="13" t="inlineStr"/>
       <c r="I161" s="13" t="inlineStr"/>
       <c r="J161" s="14" t="inlineStr"/>
       <c r="K161" s="14">
@@ -6065,36 +5976,37 @@
     </row>
     <row r="162">
       <c r="A162" s="5" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>Capacitor cerâmico 100 nF</t>
+          <t>Cabo flexível 0,25 mm² (8 cores)</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15 m</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>Filtro dos pinos IS dos BTS (2) + filtro do divisor D25 (1) + reservas</t>
-        </is>
-      </c>
-      <c r="E162" s="6" t="inlineStr"/>
+          <t>Sinais</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>Sensores, botões, comunicação</t>
+        </is>
+      </c>
       <c r="F162" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/capacitor-ceramico-100-nf","🔎 capacitor ceramico 100 nf")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-flexivel-0-25-mm","🔎 cabo flexivel 0,25 mm")</f>
         <v/>
       </c>
       <c r="G162" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=capacitor+ceramico+100+nf","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H162" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-100nf-ceramic-capacitor.html","🌏 100nF ceramic capacitor")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+flexivel+0%2C25+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H162" s="8" t="inlineStr"/>
       <c r="I162" s="8" t="inlineStr"/>
       <c r="J162" s="9" t="inlineStr"/>
       <c r="K162" s="9">
@@ -6104,36 +6016,37 @@
     </row>
     <row r="163">
       <c r="A163" s="10" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>Resistor 220 Ω 1/4 W</t>
+          <t>Cabo par trançado blindado 2×0,25 mm²</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2 m</t>
         </is>
       </c>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>4 usos + 2 reservas — série dos LEDs brancos da iluminação da maquete (5 V). ⚠️ Não são mais dos sinaleiros do painel, que agora são de 24 V</t>
-        </is>
-      </c>
-      <c r="E163" s="11" t="inlineStr"/>
+          <t>Blindado, malha aterrada em um ponto</t>
+        </is>
+      </c>
+      <c r="E163" s="11" t="inlineStr">
+        <is>
+          <t>I²C e 1-Wire (trecho câmara → painel)</t>
+        </is>
+      </c>
       <c r="F163" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-220-1-4-w","🔎 resistor 220 1 4 w")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-par-trancado-blindado-2-0-25-mm","🔎 cabo par trancado blindado 2")</f>
         <v/>
       </c>
       <c r="G163" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+220+1+4+w","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H163" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+par+trancado+blindado+2+0%2C25+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H163" s="13" t="inlineStr"/>
       <c r="I163" s="13" t="inlineStr"/>
       <c r="J163" s="14" t="inlineStr"/>
       <c r="K163" s="14">
@@ -6141,45 +6054,79 @@
         <v/>
       </c>
     </row>
-    <row r="164" ht="22" customHeight="1">
-      <c r="A164" s="4" t="inlineStr">
-        <is>
-          <t>L.4b — Posições de ensaio (dispositivos sob teste)</t>
-        </is>
+    <row r="164">
+      <c r="A164" s="5" t="n">
+        <v>142</v>
+      </c>
+      <c r="B164" s="6" t="inlineStr">
+        <is>
+          <t>Terminal tubular (ilhós) 0,25 / 0,5 / 1,5 mm²</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>1 kit</t>
+        </is>
+      </c>
+      <c r="D164" s="6" t="inlineStr">
+        <is>
+          <t>Com colarinho colorido</t>
+        </is>
+      </c>
+      <c r="E164" s="6" t="inlineStr">
+        <is>
+          <t>Obrigatório em todo borne parafuso</t>
+        </is>
+      </c>
+      <c r="F164" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/terminal-tubular-0-25-0-5-1-5-mm","🔎 terminal tubular 0,25 0,5 1,")</f>
+        <v/>
+      </c>
+      <c r="G164" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=terminal+tubular+0%2C25+0%2C5+1%2C5+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H164" s="8" t="inlineStr"/>
+      <c r="I164" s="8" t="inlineStr"/>
+      <c r="J164" s="9" t="inlineStr"/>
+      <c r="K164" s="9">
+        <f>IF(C164*J164=0,"",C164*J164)</f>
+        <v/>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="10" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>Sensor INA219 (módulo I²C)</t>
+          <t>Alicate de crimpar terminal tubular</t>
         </is>
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>Mede tensão e corrente, ±3,2 A. ⚠️ 4 endereços selecionáveis (0x40/0x41/0x44/0x45) — um por posição, todos no mesmo par de fios</t>
-        </is>
-      </c>
-      <c r="E165" s="11" t="inlineStr"/>
+          <t>Tipo quadrado/hexagonal</t>
+        </is>
+      </c>
+      <c r="E165" s="11" t="inlineStr">
+        <is>
+          <t>Ferramenta</t>
+        </is>
+      </c>
       <c r="F165" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/sensor-ina219","🔎 sensor ina219")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/alicate-crimpar-terminal-tubular","🔎 alicate crimpar terminal tub")</f>
         <v/>
       </c>
       <c r="G165" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=sensor+ina219","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H165" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-ina219-current-sensor-module.html","🌏 INA219 current sensor modu")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=alicate+crimpar+terminal+tubular","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H165" s="13" t="inlineStr"/>
       <c r="I165" s="13" t="inlineStr"/>
       <c r="J165" s="14" t="inlineStr"/>
       <c r="K165" s="14">
@@ -6189,30 +6136,34 @@
     </row>
     <row r="166">
       <c r="A166" s="5" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>Porta-fusível mini automotivo DIN</t>
+          <t>Terminal olhal M4</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>F-P1 a F-P4 — proteção individual de cada posição de ensaio</t>
-        </is>
-      </c>
-      <c r="E166" s="6" t="inlineStr"/>
+          <t>Amarelo/vermelho</t>
+        </is>
+      </c>
+      <c r="E166" s="6" t="inlineStr">
+        <is>
+          <t>Aterramento</t>
+        </is>
+      </c>
       <c r="F166" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/porta-fusivel-mini-automotivo-din","🔎 porta fusivel mini automotiv")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/terminal-olhal-m4","🔎 terminal olhal m4")</f>
         <v/>
       </c>
       <c r="G166" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=porta+fusivel+mini+automotivo+din","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=terminal+olhal+m4","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H166" s="8" t="inlineStr"/>
@@ -6225,33 +6176,40 @@
     </row>
     <row r="167">
       <c r="A167" s="10" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>Fusível mini automotivo 500 mA</t>
+          <t>Espaguete termorretrátil (kit)</t>
         </is>
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D167" s="11" t="inlineStr">
         <is>
-          <t>4 usos + 4 reservas</t>
-        </is>
-      </c>
-      <c r="E167" s="11" t="inlineStr"/>
+          <t>Diversas bitolas</t>
+        </is>
+      </c>
+      <c r="E167" s="11" t="inlineStr">
+        <is>
+          <t>Isolação de emendas</t>
+        </is>
+      </c>
       <c r="F167" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fusivel-mini-automotivo-500-ma","🔎 fusivel mini automotivo 500 ")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/espaguete-termorretratil","🔎 espaguete termorretratil")</f>
         <v/>
       </c>
       <c r="G167" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fusivel+mini+automotivo+500+ma","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H167" s="13" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=espaguete+termorretratil","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H167" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-heat-shrink-tubing-kit.html","🌏 heat shrink tubing kit")</f>
+        <v/>
+      </c>
       <c r="I167" s="13" t="inlineStr"/>
       <c r="J167" s="14" t="inlineStr"/>
       <c r="K167" s="14">
@@ -6261,36 +6219,37 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>Placa ilhada pequena</t>
+          <t>Abraçadeiras de nylon 100 mm</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>~30 × 40 mm — corpo de cada placa simuladora de dispositivo</t>
-        </is>
-      </c>
-      <c r="E168" s="6" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E168" s="6" t="inlineStr">
+        <is>
+          <t>Amarração</t>
+        </is>
+      </c>
       <c r="F168" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/placa-ilhada-pequena","🔎 placa ilhada pequena")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/abracadeiras-nylon-100-mm","🔎 abracadeiras nylon 100 mm")</f>
         <v/>
       </c>
       <c r="G168" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=placa+ilhada+pequena","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H168" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-perfboard-prototype-pcb.html","🌏 perfboard prototype PCB")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=abracadeiras+nylon+100+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H168" s="8" t="inlineStr"/>
       <c r="I168" s="8" t="inlineStr"/>
       <c r="J168" s="9" t="inlineStr"/>
       <c r="K168" s="9">
@@ -6300,36 +6259,37 @@
     </row>
     <row r="169">
       <c r="A169" s="10" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>Resistor 220 Ω / 5 W</t>
+          <t>Anilhas de identificação de cabo</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1 kit</t>
         </is>
       </c>
       <c r="D169" s="11" t="inlineStr">
         <is>
-          <t>Carga térmica de cada simulador (~3 W). ⚠️ 5 W, não 1/4 W</t>
-        </is>
-      </c>
-      <c r="E169" s="11" t="inlineStr"/>
+          <t>Numeradas 0–9</t>
+        </is>
+      </c>
+      <c r="E169" s="11" t="inlineStr">
+        <is>
+          <t>Identificação (norma de painel)</t>
+        </is>
+      </c>
       <c r="F169" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-220-5-w","🔎 resistor 220 5 w")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/anilhas-identificacao-cabo","🔎 anilhas identificacao cabo")</f>
         <v/>
       </c>
       <c r="G169" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+220+5+w","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H169" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=anilhas+identificacao+cabo","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H169" s="13" t="inlineStr"/>
       <c r="I169" s="13" t="inlineStr"/>
       <c r="J169" s="14" t="inlineStr"/>
       <c r="K169" s="14">
@@ -6339,36 +6299,37 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>Resistor 1,2 kΩ 1/4 W</t>
+          <t>Espiral organizador Ø 8 mm</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2 m</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
         <is>
-          <t>Limitador do LED indicador de cada posição</t>
-        </is>
-      </c>
-      <c r="E170" s="6" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E170" s="6" t="inlineStr">
+        <is>
+          <t>Chicote painel → câmara</t>
+        </is>
+      </c>
       <c r="F170" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-1-2-k-1-4-w","🔎 resistor 1,2 k 1 4 w")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/espiral-organizador-8-mm","🔎 espiral organizador 8 mm")</f>
         <v/>
       </c>
       <c r="G170" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+1%2C2+k+1+4+w","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H170" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=espiral+organizador+8+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H170" s="8" t="inlineStr"/>
       <c r="I170" s="8" t="inlineStr"/>
       <c r="J170" s="9" t="inlineStr"/>
       <c r="K170" s="9">
@@ -6376,77 +6337,40 @@
         <v/>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="10" t="n">
-        <v>151</v>
-      </c>
-      <c r="B171" s="11" t="inlineStr">
-        <is>
-          <t>LED 5 mm difuso</t>
-        </is>
-      </c>
-      <c r="C171" s="10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D171" s="11" t="inlineStr">
-        <is>
-          <t>Indica "posição viva", visível pela porta da câmara</t>
-        </is>
-      </c>
-      <c r="E171" s="11" t="inlineStr"/>
-      <c r="F171" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/led-5-mm-difuso","🔎 led 5 mm difuso")</f>
-        <v/>
-      </c>
-      <c r="G171" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=led+5+mm+difuso","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H171" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-5mm-diffused-led.html","🌏 5mm diffused LED")</f>
-        <v/>
-      </c>
-      <c r="I171" s="13" t="inlineStr"/>
-      <c r="J171" s="14" t="inlineStr"/>
-      <c r="K171" s="14">
-        <f>IF(C171*J171=0,"",C171*J171)</f>
-        <v/>
+    <row r="171" ht="22" customHeight="1">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>L.3 — Atuadores térmicos e ventilação</t>
+        </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>Micro-chave ou jumper</t>
+          <t>Ventoinha interna 12 V — grupo React</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>⭐ Simula a falha do dispositivo — é o que permite demonstrar a detecção ao vivo na apresentação</t>
-        </is>
-      </c>
-      <c r="E172" s="6" t="inlineStr"/>
-      <c r="F172" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/micro-chave-jumper","🔎 micro chave jumper")</f>
-        <v/>
-      </c>
-      <c r="G172" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=micro+chave+jumper","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H172" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-spdt-micro-switch-small.html","🌏 SPDT micro switch small")</f>
-        <v/>
-      </c>
+          <t>Cinco unidades compatíveis com a geometria atual: 2 frias, 2 dos dutos e 1 do PTC; ligadas em paralelo</t>
+        </is>
+      </c>
+      <c r="E172" s="6" t="inlineStr">
+        <is>
+          <t>Confirmar dimensao fisica antes da compra</t>
+        </is>
+      </c>
+      <c r="F172" s="8" t="inlineStr"/>
+      <c r="G172" s="8" t="inlineStr"/>
+      <c r="H172" s="8" t="inlineStr"/>
       <c r="I172" s="8" t="inlineStr"/>
       <c r="J172" s="9" t="inlineStr"/>
       <c r="K172" s="9">
@@ -6454,958 +6378,1355 @@
         <v/>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="10" t="n">
-        <v>153</v>
-      </c>
-      <c r="B173" s="11" t="inlineStr">
-        <is>
-          <t>Borne DIN 2,5 mm²</t>
-        </is>
-      </c>
-      <c r="C173" s="10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D173" s="11" t="inlineStr">
-        <is>
-          <t>Entrada e saída de cada posição</t>
-        </is>
-      </c>
-      <c r="E173" s="11" t="inlineStr"/>
-      <c r="F173" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/borne-din-2-5-mm","🔎 borne din 2,5 mm")</f>
-        <v/>
-      </c>
-      <c r="G173" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=borne+din+2%2C5+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H173" s="13" t="inlineStr"/>
-      <c r="I173" s="13" t="inlineStr"/>
-      <c r="J173" s="14" t="inlineStr"/>
-      <c r="K173" s="14">
-        <f>IF(C173*J173=0,"",C173*J173)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="174" ht="22" customHeight="1">
-      <c r="A174" s="4" t="inlineStr">
-        <is>
-          <t>L.5 — Placa de Interface PI-1 (onde os componentes discretos moram)</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="10" t="n">
-        <v>154</v>
-      </c>
-      <c r="B175" s="11" t="inlineStr">
-        <is>
-          <t>Placa ilhada (padrão furos isolados)</t>
-        </is>
-      </c>
-      <c r="C175" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D175" s="11" t="inlineStr">
-        <is>
-          <t>~5 × 7 cm. ⚠️ Ilhada, não de barramento — na de barramento você acaba tendo que cortar trilha, e é dali que saem os curtos difíceis de achar</t>
-        </is>
-      </c>
-      <c r="E175" s="11" t="inlineStr"/>
-      <c r="F175" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/placa-ilhada","🔎 placa ilhada")</f>
-        <v/>
-      </c>
-      <c r="G175" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=placa+ilhada","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H175" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-perfboard-prototype-pcb.html","🌏 perfboard prototype PCB")</f>
-        <v/>
-      </c>
-      <c r="I175" s="13" t="inlineStr"/>
-      <c r="J175" s="14" t="inlineStr"/>
-      <c r="K175" s="14">
-        <f>IF(C175*J175=0,"",C175*J175)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="5" t="n">
-        <v>155</v>
-      </c>
-      <c r="B176" s="6" t="inlineStr">
-        <is>
-          <t>Caixa modular para trilho DIN — 3 módulos (52,5 mm)</t>
-        </is>
-      </c>
-      <c r="C176" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D176" s="6" t="inlineStr">
-        <is>
-          <t>Invólucro da PI-1. Cabe no espaço livre do trilho 3, ao lado do Arduino. Buscar caixa para trilho din 3m modular</t>
-        </is>
-      </c>
-      <c r="E176" s="6" t="inlineStr"/>
-      <c r="F176" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/caixa-modular-trilho-din","🔎 caixa modular trilho din")</f>
-        <v/>
-      </c>
-      <c r="G176" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=caixa+modular+trilho+din","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H176" s="8" t="inlineStr"/>
-      <c r="I176" s="8" t="inlineStr"/>
-      <c r="J176" s="9" t="inlineStr"/>
-      <c r="K176" s="9">
-        <f>IF(C176*J176=0,"",C176*J176)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="10" t="n">
-        <v>156</v>
-      </c>
-      <c r="B177" s="11" t="inlineStr">
-        <is>
-          <t>Borne KF350 / KRE passo 3,5 mm — 10 vias</t>
-        </is>
-      </c>
-      <c r="C177" s="10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D177" s="11" t="inlineStr">
-        <is>
-          <t>Um borne superior (lado Arduino) e um inferior (lado campo). Passo de 3,5 mm porque todos os cabos são de 0,25 mm²</t>
-        </is>
-      </c>
-      <c r="E177" s="11" t="inlineStr"/>
-      <c r="F177" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/borne-kf350-kre-passo-3-5-mm","🔎 borne kf350 kre passo 3,5 mm")</f>
-        <v/>
-      </c>
-      <c r="G177" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=borne+kf350+kre+passo+3%2C5+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H177" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-kf350-3-5mm-pcb-screw-terminal-block.html","🌏 KF350 3.5mm PCB screw term")</f>
-        <v/>
-      </c>
-      <c r="I177" s="13" t="inlineStr"/>
-      <c r="J177" s="14" t="inlineStr"/>
-      <c r="K177" s="14">
-        <f>IF(C177*J177=0,"",C177*J177)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="5" t="n">
-        <v>157</v>
-      </c>
-      <c r="B178" s="6" t="inlineStr">
-        <is>
-          <t>CI ULN2803A (DIP 18 pinos)</t>
-        </is>
-      </c>
-      <c r="C178" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D178" s="6" t="inlineStr">
-        <is>
-          <t>Driver dos 4 sinaleiros de 24 V — 8 canais Darlington, 500 mA/50 V, com diodos de proteção internos. 1 uso + 1 reserva (o CI é barato e é o único ponto onde 24 V encosta na lógica)</t>
-        </is>
-      </c>
-      <c r="E178" s="6" t="inlineStr"/>
-      <c r="F178" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/ci-uln2803a","🔎 ci uln2803a")</f>
-        <v/>
-      </c>
-      <c r="G178" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=ci+uln2803a","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H178" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-uln2803a-dip18-darlington.html","🌏 ULN2803A DIP18 darlington")</f>
-        <v/>
-      </c>
-      <c r="I178" s="8" t="inlineStr"/>
-      <c r="J178" s="9" t="inlineStr"/>
-      <c r="K178" s="9">
-        <f>IF(C178*J178=0,"",C178*J178)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="10" t="n">
-        <v>158</v>
-      </c>
-      <c r="B179" s="11" t="inlineStr">
-        <is>
-          <t>Soquete DIP 18 pinos</t>
-        </is>
-      </c>
-      <c r="C179" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D179" s="11" t="inlineStr">
-        <is>
-          <t>⚠️ Solde o soquete, não o CI. Permite trocar o chip sem dessoldar nada</t>
-        </is>
-      </c>
-      <c r="E179" s="11" t="inlineStr"/>
-      <c r="F179" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/soquete-dip-18-pinos","🔎 soquete dip 18 pinos")</f>
-        <v/>
-      </c>
-      <c r="G179" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=soquete+dip+18+pinos","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H179" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-dip18-ic-socket.html","🌏 DIP18 IC socket")</f>
-        <v/>
-      </c>
-      <c r="I179" s="13" t="inlineStr"/>
-      <c r="J179" s="14" t="inlineStr"/>
-      <c r="K179" s="14">
-        <f>IF(C179*J179=0,"",C179*J179)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="5" t="n">
-        <v>159</v>
-      </c>
-      <c r="B180" s="6" t="inlineStr">
-        <is>
-          <t>Fio rígido 0,25 mm² para interligação</t>
-        </is>
-      </c>
-      <c r="C180" s="5" t="inlineStr">
-        <is>
-          <t>1 m</t>
-        </is>
-      </c>
-      <c r="D180" s="6" t="inlineStr">
-        <is>
-          <t>Ligações por baixo da placa. ⚠️ Não usar "sobra de perna" de componente em trecho longo — oxida e não é isolada</t>
-        </is>
-      </c>
-      <c r="E180" s="6" t="inlineStr"/>
-      <c r="F180" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-rigido-0-25-mm-interligacao","🔎 fio rigido 0,25 mm interliga")</f>
-        <v/>
-      </c>
-      <c r="G180" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+rigido+0%2C25+mm+interligacao","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H180" s="8" t="inlineStr"/>
-      <c r="I180" s="8" t="inlineStr"/>
-      <c r="J180" s="9" t="inlineStr"/>
-      <c r="K180" s="9">
-        <f>IF(C180*J180=0,"",C180*J180)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="10" t="n">
-        <v>160</v>
-      </c>
-      <c r="B181" s="11" t="inlineStr">
-        <is>
-          <t>Verniz spray para PCI (ou esmalte incolor)</t>
-        </is>
-      </c>
-      <c r="C181" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D181" s="11" t="inlineStr">
-        <is>
-          <t>Proteção do lado da solda contra umidade e oxidação</t>
-        </is>
-      </c>
-      <c r="E181" s="11" t="inlineStr"/>
-      <c r="F181" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/verniz-spray-pci","🔎 verniz spray pci")</f>
-        <v/>
-      </c>
-      <c r="G181" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=verniz+spray+pci","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H181" s="13" t="inlineStr"/>
-      <c r="I181" s="13" t="inlineStr"/>
-      <c r="J181" s="14" t="inlineStr"/>
-      <c r="K181" s="14">
-        <f>IF(C181*J181=0,"",C181*J181)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="5" t="n">
-        <v>161</v>
-      </c>
-      <c r="B182" s="6" t="inlineStr">
-        <is>
-          <t>Termorretrátil Ø 2 mm</t>
-        </is>
-      </c>
-      <c r="C182" s="5" t="inlineStr">
-        <is>
-          <t>30 cm</t>
-        </is>
-      </c>
-      <c r="D182" s="6" t="inlineStr">
-        <is>
-          <t>Isolação dos 2 resistores de 10 kΩ soldados nos BTS7960</t>
-        </is>
-      </c>
-      <c r="E182" s="6" t="inlineStr"/>
-      <c r="F182" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/termorretratil-2-mm","🔎 termorretratil 2 mm")</f>
-        <v/>
-      </c>
-      <c r="G182" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=termorretratil+2+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H182" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-heat-shrink-tubing-kit.html","🌏 heat shrink tubing kit")</f>
-        <v/>
-      </c>
-      <c r="I182" s="8" t="inlineStr"/>
-      <c r="J182" s="9" t="inlineStr"/>
-      <c r="K182" s="9">
-        <f>IF(C182*J182=0,"",C182*J182)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="10" t="n">
-        <v>162</v>
-      </c>
-      <c r="B183" s="11" t="inlineStr">
-        <is>
-          <t>Etiqueta impressa em papel adesivo</t>
-        </is>
-      </c>
-      <c r="C183" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D183" s="11" t="inlineStr">
-        <is>
-          <t>Identificação das 20 vias na frente da caixa — é o que torna a placa auditável</t>
-        </is>
-      </c>
-      <c r="E183" s="11" t="inlineStr"/>
-      <c r="F183" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/etiqueta-impressa-papel-adesivo","🔎 etiqueta impressa papel ades")</f>
-        <v/>
-      </c>
-      <c r="G183" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=etiqueta+impressa+papel+adesivo","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H183" s="13" t="inlineStr"/>
-      <c r="I183" s="13" t="inlineStr"/>
-      <c r="J183" s="14" t="inlineStr"/>
-      <c r="K183" s="14">
-        <f>IF(C183*J183=0,"",C183*J183)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="184" ht="22" customHeight="1">
-      <c r="A184" s="4" t="inlineStr">
-        <is>
-          <t>🔧 CAMADA 3 — CABOS E ACESSÓRIOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="10" t="n">
-        <v>163</v>
-      </c>
-      <c r="B185" s="11" t="inlineStr">
-        <is>
-          <t>Cabo flexível 1,5 mm² preto</t>
-        </is>
-      </c>
-      <c r="C185" s="10" t="inlineStr">
-        <is>
-          <t>3 m</t>
-        </is>
-      </c>
-      <c r="D185" s="11" t="inlineStr">
-        <is>
-          <t>750 V</t>
-        </is>
-      </c>
-      <c r="E185" s="11" t="inlineStr">
-        <is>
-          <t>Retorno geral 0 V (6,9 A — soma dos 3 ramais)</t>
-        </is>
-      </c>
-      <c r="F185" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-flexivel-1-5-mm-preto","🔎 cabo flexivel 1,5 mm preto")</f>
-        <v/>
-      </c>
-      <c r="G185" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+flexivel+1%2C5+mm+preto","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H185" s="13" t="inlineStr"/>
-      <c r="I185" s="13" t="inlineStr"/>
-      <c r="J185" s="14" t="inlineStr"/>
-      <c r="K185" s="14">
-        <f>IF(C185*J185=0,"",C185*J185)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="5" t="n">
-        <v>164</v>
-      </c>
-      <c r="B186" s="6" t="inlineStr">
-        <is>
-          <t>Cabo flexível 1,5 mm² vermelho</t>
-        </is>
-      </c>
-      <c r="C186" s="5" t="inlineStr">
-        <is>
-          <t>2 m</t>
-        </is>
-      </c>
-      <c r="D186" s="6" t="inlineStr">
-        <is>
-          <t>750 V</t>
-        </is>
-      </c>
-      <c r="E186" s="6" t="inlineStr">
-        <is>
-          <t>24 V de potência — P1 → painel → BTS (6,0 A)</t>
-        </is>
-      </c>
-      <c r="F186" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-flexivel-1-5-mm-vermelho","🔎 cabo flexivel 1,5 mm vermelh")</f>
-        <v/>
-      </c>
-      <c r="G186" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+flexivel+1%2C5+mm+vermelho","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H186" s="8" t="inlineStr"/>
-      <c r="I186" s="8" t="inlineStr"/>
-      <c r="J186" s="9" t="inlineStr"/>
-      <c r="K186" s="9">
-        <f>IF(C186*J186=0,"",C186*J186)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="10" t="n">
-        <v>165</v>
-      </c>
-      <c r="B187" s="11" t="inlineStr">
-        <is>
-          <t>Cabo flexível 0,75 mm² vermelho/preto</t>
-        </is>
-      </c>
-      <c r="C187" s="10" t="inlineStr">
-        <is>
-          <t>3 m</t>
-        </is>
-      </c>
-      <c r="D187" s="11" t="inlineStr">
-        <is>
-          <t>750 V</t>
-        </is>
-      </c>
-      <c r="E187" s="11" t="inlineStr">
-        <is>
-          <t>Barramento 24 V (trechos internos) e saída de 12 V do T3 (1,0 A)</t>
-        </is>
-      </c>
-      <c r="F187" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-flexivel-0-75-mm-vermelho-preto","🔎 cabo flexivel 0,75 mm vermel")</f>
-        <v/>
-      </c>
-      <c r="G187" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+flexivel+0%2C75+mm+vermelho+preto","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H187" s="13" t="inlineStr"/>
-      <c r="I187" s="13" t="inlineStr"/>
-      <c r="J187" s="14" t="inlineStr"/>
-      <c r="K187" s="14">
-        <f>IF(C187*J187=0,"",C187*J187)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="5" t="n">
-        <v>166</v>
-      </c>
-      <c r="B188" s="6" t="inlineStr">
-        <is>
-          <t>Cabo flexível 0,5 mm² (5 cores)</t>
-        </is>
-      </c>
-      <c r="C188" s="5" t="inlineStr">
-        <is>
-          <t>10 m</t>
-        </is>
-      </c>
-      <c r="D188" s="6" t="inlineStr">
-        <is>
-          <t>750 V</t>
-        </is>
-      </c>
-      <c r="E188" s="6" t="inlineStr">
-        <is>
-          <t>5 V e derivações do 12 V auxiliar</t>
-        </is>
-      </c>
-      <c r="F188" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-flexivel-0-5-mm","🔎 cabo flexivel 0,5 mm")</f>
-        <v/>
-      </c>
-      <c r="G188" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+flexivel+0%2C5+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H188" s="8" t="inlineStr"/>
-      <c r="I188" s="8" t="inlineStr"/>
-      <c r="J188" s="9" t="inlineStr"/>
-      <c r="K188" s="9">
-        <f>IF(C188*J188=0,"",C188*J188)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="10" t="n">
-        <v>167</v>
-      </c>
-      <c r="B189" s="11" t="inlineStr">
-        <is>
-          <t>Cabo flexível 0,25 mm² (8 cores)</t>
-        </is>
-      </c>
-      <c r="C189" s="10" t="inlineStr">
-        <is>
-          <t>15 m</t>
-        </is>
-      </c>
-      <c r="D189" s="11" t="inlineStr">
-        <is>
-          <t>Sinais</t>
-        </is>
-      </c>
-      <c r="E189" s="11" t="inlineStr">
-        <is>
-          <t>Sensores, botões, comunicação</t>
-        </is>
-      </c>
-      <c r="F189" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-flexivel-0-25-mm","🔎 cabo flexivel 0,25 mm")</f>
-        <v/>
-      </c>
-      <c r="G189" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+flexivel+0%2C25+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H189" s="13" t="inlineStr"/>
-      <c r="I189" s="13" t="inlineStr"/>
-      <c r="J189" s="14" t="inlineStr"/>
-      <c r="K189" s="14">
-        <f>IF(C189*J189=0,"",C189*J189)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="5" t="n">
-        <v>168</v>
-      </c>
-      <c r="B190" s="6" t="inlineStr">
-        <is>
-          <t>Cabo par trançado blindado 2×0,25 mm²</t>
-        </is>
-      </c>
-      <c r="C190" s="5" t="inlineStr">
-        <is>
-          <t>2 m</t>
-        </is>
-      </c>
-      <c r="D190" s="6" t="inlineStr">
-        <is>
-          <t>Blindado, malha aterrada em um ponto</t>
-        </is>
-      </c>
-      <c r="E190" s="6" t="inlineStr">
-        <is>
-          <t>I²C e 1-Wire (trecho câmara → painel)</t>
-        </is>
-      </c>
-      <c r="F190" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-par-trancado-blindado-2-0-25-mm","🔎 cabo par trancado blindado 2")</f>
-        <v/>
-      </c>
-      <c r="G190" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+par+trancado+blindado+2+0%2C25+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H190" s="8" t="inlineStr"/>
-      <c r="I190" s="8" t="inlineStr"/>
-      <c r="J190" s="9" t="inlineStr"/>
-      <c r="K190" s="9">
-        <f>IF(C190*J190=0,"",C190*J190)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="10" t="n">
-        <v>169</v>
-      </c>
-      <c r="B191" s="11" t="inlineStr">
-        <is>
-          <t>Terminal tubular (ilhós) 0,25 / 0,5 / 1,5 mm²</t>
-        </is>
-      </c>
-      <c r="C191" s="10" t="inlineStr">
-        <is>
-          <t>1 kit</t>
-        </is>
-      </c>
-      <c r="D191" s="11" t="inlineStr">
-        <is>
-          <t>Com colarinho colorido</t>
-        </is>
-      </c>
-      <c r="E191" s="11" t="inlineStr">
-        <is>
-          <t>Obrigatório em todo borne parafuso</t>
-        </is>
-      </c>
-      <c r="F191" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/terminal-tubular-0-25-0-5-1-5-mm","🔎 terminal tubular 0,25 0,5 1,")</f>
-        <v/>
-      </c>
-      <c r="G191" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=terminal+tubular+0%2C25+0%2C5+1%2C5+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H191" s="13" t="inlineStr"/>
-      <c r="I191" s="13" t="inlineStr"/>
-      <c r="J191" s="14" t="inlineStr"/>
-      <c r="K191" s="14">
-        <f>IF(C191*J191=0,"",C191*J191)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="5" t="n">
-        <v>170</v>
-      </c>
-      <c r="B192" s="6" t="inlineStr">
-        <is>
-          <t>Alicate de crimpar terminal tubular</t>
-        </is>
-      </c>
-      <c r="C192" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D192" s="6" t="inlineStr">
-        <is>
-          <t>Tipo quadrado/hexagonal</t>
-        </is>
-      </c>
-      <c r="E192" s="6" t="inlineStr">
-        <is>
-          <t>Ferramenta</t>
-        </is>
-      </c>
-      <c r="F192" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/alicate-crimpar-terminal-tubular","🔎 alicate crimpar terminal tub")</f>
-        <v/>
-      </c>
-      <c r="G192" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=alicate+crimpar+terminal+tubular","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H192" s="8" t="inlineStr"/>
-      <c r="I192" s="8" t="inlineStr"/>
-      <c r="J192" s="9" t="inlineStr"/>
-      <c r="K192" s="9">
-        <f>IF(C192*J192=0,"",C192*J192)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="10" t="n">
-        <v>171</v>
-      </c>
-      <c r="B193" s="11" t="inlineStr">
-        <is>
-          <t>Terminal olhal M4</t>
-        </is>
-      </c>
-      <c r="C193" s="10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D193" s="11" t="inlineStr">
-        <is>
-          <t>Amarelo/vermelho</t>
-        </is>
-      </c>
-      <c r="E193" s="11" t="inlineStr">
-        <is>
-          <t>Aterramento</t>
-        </is>
-      </c>
-      <c r="F193" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/terminal-olhal-m4","🔎 terminal olhal m4")</f>
-        <v/>
-      </c>
-      <c r="G193" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=terminal+olhal+m4","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H193" s="13" t="inlineStr"/>
-      <c r="I193" s="13" t="inlineStr"/>
-      <c r="J193" s="14" t="inlineStr"/>
-      <c r="K193" s="14">
-        <f>IF(C193*J193=0,"",C193*J193)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="5" t="n">
-        <v>172</v>
-      </c>
-      <c r="B194" s="6" t="inlineStr">
-        <is>
-          <t>Espaguete termorretrátil (kit)</t>
-        </is>
-      </c>
-      <c r="C194" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D194" s="6" t="inlineStr">
-        <is>
-          <t>Diversas bitolas</t>
-        </is>
-      </c>
-      <c r="E194" s="6" t="inlineStr">
-        <is>
-          <t>Isolação de emendas</t>
-        </is>
-      </c>
-      <c r="F194" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/espaguete-termorretratil","🔎 espaguete termorretratil")</f>
-        <v/>
-      </c>
-      <c r="G194" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=espaguete+termorretratil","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H194" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-heat-shrink-tubing-kit.html","🌏 heat shrink tubing kit")</f>
-        <v/>
-      </c>
-      <c r="I194" s="8" t="inlineStr"/>
-      <c r="J194" s="9" t="inlineStr"/>
-      <c r="K194" s="9">
-        <f>IF(C194*J194=0,"",C194*J194)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="10" t="n">
-        <v>173</v>
-      </c>
-      <c r="B195" s="11" t="inlineStr">
-        <is>
-          <t>Abraçadeiras de nylon 100 mm</t>
-        </is>
-      </c>
-      <c r="C195" s="10" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="D195" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E195" s="11" t="inlineStr">
-        <is>
-          <t>Amarração</t>
-        </is>
-      </c>
-      <c r="F195" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/abracadeiras-nylon-100-mm","🔎 abracadeiras nylon 100 mm")</f>
-        <v/>
-      </c>
-      <c r="G195" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=abracadeiras+nylon+100+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H195" s="13" t="inlineStr"/>
-      <c r="I195" s="13" t="inlineStr"/>
-      <c r="J195" s="14" t="inlineStr"/>
-      <c r="K195" s="14">
-        <f>IF(C195*J195=0,"",C195*J195)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="5" t="n">
-        <v>174</v>
-      </c>
-      <c r="B196" s="6" t="inlineStr">
-        <is>
-          <t>Anilhas de identificação de cabo</t>
-        </is>
-      </c>
-      <c r="C196" s="5" t="inlineStr">
-        <is>
-          <t>1 kit</t>
-        </is>
-      </c>
-      <c r="D196" s="6" t="inlineStr">
-        <is>
-          <t>Numeradas 0–9</t>
-        </is>
-      </c>
-      <c r="E196" s="6" t="inlineStr">
-        <is>
-          <t>Identificação (norma de painel)</t>
-        </is>
-      </c>
-      <c r="F196" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/anilhas-identificacao-cabo","🔎 anilhas identificacao cabo")</f>
-        <v/>
-      </c>
-      <c r="G196" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=anilhas+identificacao+cabo","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H196" s="8" t="inlineStr"/>
-      <c r="I196" s="8" t="inlineStr"/>
-      <c r="J196" s="9" t="inlineStr"/>
-      <c r="K196" s="9">
-        <f>IF(C196*J196=0,"",C196*J196)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="10" t="n">
-        <v>175</v>
-      </c>
-      <c r="B197" s="11" t="inlineStr">
-        <is>
-          <t>Espiral organizador Ø 8 mm</t>
-        </is>
-      </c>
-      <c r="C197" s="10" t="inlineStr">
-        <is>
-          <t>2 m</t>
-        </is>
-      </c>
-      <c r="D197" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E197" s="11" t="inlineStr">
-        <is>
-          <t>Chicote painel → câmara</t>
-        </is>
-      </c>
-      <c r="F197" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/espiral-organizador-8-mm","🔎 espiral organizador 8 mm")</f>
-        <v/>
-      </c>
-      <c r="G197" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=espiral+organizador+8+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H197" s="13" t="inlineStr"/>
-      <c r="I197" s="13" t="inlineStr"/>
-      <c r="J197" s="14" t="inlineStr"/>
-      <c r="K197" s="14">
-        <f>IF(C197*J197=0,"",C197*J197)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="199">
-      <c r="I199" s="17" t="inlineStr">
+    <row r="174">
+      <c r="I174" s="17" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="K199" s="18">
-        <f>SUM(K5:K197)</f>
+      <c r="K174" s="18">
+        <f>SUM(K5:K172)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K197"/>
-  <mergeCells count="20">
-    <mergeCell ref="A58:K58"/>
+  <autoFilter ref="A4:K172"/>
+  <mergeCells count="21">
+    <mergeCell ref="A130:K130"/>
+    <mergeCell ref="A157:K157"/>
     <mergeCell ref="A142:K142"/>
+    <mergeCell ref="A60:K60"/>
+    <mergeCell ref="A94:K94"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A88:K88"/>
-    <mergeCell ref="A128:K128"/>
-    <mergeCell ref="A174:K174"/>
-    <mergeCell ref="A164:K164"/>
-    <mergeCell ref="A158:K158"/>
-    <mergeCell ref="A74:K74"/>
+    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="A90:K90"/>
     <mergeCell ref="A104:K104"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A151:K151"/>
-    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A76:K76"/>
+    <mergeCell ref="A116:K116"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A23:K23"/>
-    <mergeCell ref="A184:K184"/>
+    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="A140:K140"/>
+    <mergeCell ref="A171:K171"/>
+    <mergeCell ref="A134:K134"/>
     <mergeCell ref="A38:K38"/>
+    <mergeCell ref="A121:K121"/>
     <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A93:K93"/>
-    <mergeCell ref="A44:K44"/>
+    <mergeCell ref="A13:K13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Componente</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Qtd</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Especificacao conferida</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Fonte React</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Painel</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>Caixa do painel</t>
+        </is>
+      </c>
+      <c r="C2" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="19" t="inlineStr">
+        <is>
+          <t>500 x 500 x 200 mm</t>
+        </is>
+      </c>
+      <c r="E2" s="19" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/painel_completo.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>Painel</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>BD-POT</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>24 V de potencia, 1 entrada + 4 saidas</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/painel.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>Painel</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>BD-AUX</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>12 V auxiliar, 1 entrada + 4 saidas</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/painel.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Painel</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>BD-24V</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>24 V permanente, 1 entrada + 6 saidas</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/painel_completo.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>Painel</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>BD-5V</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>5 V, 1 entrada + 8 saidas</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/painel_completo.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Painel</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>BD-0V</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>barra star ground, minimo 20 pontos</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/painel_completo.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>Painel</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>BTS7960</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>1 para Peltier; 1 para PTC</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/painel_completo.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>Painel</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>Rele 8 pinos + base DIN</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>KA1 e KA2, bobina 24 Vcc; KA2 com contato 10 A em CC</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/reles_fisico.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>Painel</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>Modulo rele 1 canal 5 V</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>KA3 NO e KA4 NC, optoacoplados</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/reles_fisico.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Painel</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>Arduino Mega 2560</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>Controlador principal</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/painel_completo.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Painel</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>Placa PI-1</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Placa ilhada com ULN2803A, filtros e divisor D25</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/pi1_fisico.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>Painel</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>Placa PI-2</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>Placa ilhada com CD74HC4067, shunts e INA219</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/pi2_fisico.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>Painel</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>DNLCB30 + ESP32-WROOM-32U</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>Supervisao Wi-Fi/MQTT; entrada 24 V</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/painel_completo.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>Painel</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>ES3C28P ESP32-S3</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>IHM 2,8 pol, touch, microSD; alimentacao pelo Type-C</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/pinagens.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>Painel</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>Conversor de nivel UART</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>2 canais, 5 V &lt;-&gt; 3,3 V</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/pinagens.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>Painel</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>Sinaleiro LED 22 mm 24 V</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>RUN verde, COOL azul, HEAT amarelo, FAULT vermelho</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/painel.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>Painel</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>Botoeiras</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>Emergencia, START, STOP e REARME</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/painel.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>Camara</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>Peltier TEC1-12706</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>Ligadas em serie, carga de 24 V / aproximadamente 6 A</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/camara.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>Camara</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>PTC 24 V</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>Aquecedor; comandado pelo BTS #2</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/camara.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>Camara</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>Ventoinhas internas 12 V</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>4 de circulacao + 1 do PTC, em paralelo</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/camara_ligacoes.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>Fora da camara</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>Cooler do radiador 3 fios</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>12 V, com RPM individual; lado quente</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/camara_ligacoes.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>Camara</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>AM2315C</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>Temperatura e umidade, dentro da camara</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/camara.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>Fora da camara</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>DS18B20</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>Temperatura do dissipador quente, 3 fios</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/camara_ligacoes.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>Camara</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>Posicao de ensaio / DUT</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>LED + resistor; retornos individuais RET-1 e RET-2</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/camara.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>Camara</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>Porta-fusivel das posicoes</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>2 vias, fusivel 100 mA por DUT</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/camara_ligacoes.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>Camara</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>Modulo CD74HC4067</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>Multiplexador de 16 canais</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/pi2_fisico.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>Camara</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>Modulo INA219</t>
+        </is>
+      </c>
+      <c r="C28" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>Medicao de referencia da posicao 1</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/pi2_fisico.js</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E28"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Circuito</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Cor(es)</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Bitola</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Fonte React</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>127 V CA</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>preto / azul / verde-amarelo</t>
+        </is>
+      </c>
+      <c r="C2" s="19" t="inlineStr">
+        <is>
+          <t>1,5 mm2</t>
+        </is>
+      </c>
+      <c r="D2" s="19" t="inlineStr">
+        <is>
+          <t>Tomada -&gt; disjuntor -&gt; fonte; PE aterra a carcaça</t>
+        </is>
+      </c>
+      <c r="E2" s="19" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/maquete.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>24 V potencia</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>vermelho</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>1,5 mm2</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>P1/painel -&gt; KA2 -&gt; BD-POT -&gt; BTS</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/fiacao.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>0 V comum</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>preto ou azul escuro</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>1,5 mm2</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>Retorno geral e star ground BD-0V</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/fiacao.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>24 V linha R1</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>vermelho rigido encapado</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>1,00 mm2</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Ramal das Peltier, 6,0 A</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/maquete.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>24 V linha R2</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>marrom rigido encapado</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>0,50 mm2</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>Ramal do T2 e 24 V de servicos</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/maquete.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>24 V linha R3</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>cinza rigido encapado</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>0,50 mm2</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>Ramal do T3 e auxiliares</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/maquete.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>0 V linha</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>azul claro rigido encapado</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>1,50 mm2</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Retorno comum dos tres ramais, 6,9 A</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/maquete.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>12 V auxiliar</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>amarelo / preto</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>0,75 mm2</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>T3/BD-AUX -&gt; ventoinhas</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/fiacao.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>5 V logica</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>violeta ou vermelho / preto</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>0,50 mm2</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>T2/BD-5V -&gt; Arduino, IHM e modulos</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/fiacao.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Sinais</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>cinza, azul, amarelo ou verde</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>0,25 mm2</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>Sensores, RPM, I2C, UART e comandos</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/fiacao_etapa4.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>I2C / 1-Wire</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>par trançado blindado</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>2 x 0,25 mm2</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Painel &lt;-&gt; camara; blindagem aterrada em um ponto</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>painel_interativo/src/data/fiacao_etapa4.js</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E12"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="64" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Prioridade</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Tema</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>BOM/Documentacao</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>React atual</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Decisao para compra</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Critica</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>Dimensao do painel</t>
+        </is>
+      </c>
+      <c r="C2" s="19" t="inlineStr">
+        <is>
+          <t>BOM: 400 x 500 x 200 mm</t>
+        </is>
+      </c>
+      <c r="D2" s="19" t="inlineStr">
+        <is>
+          <t>React: 500 x 500 x 200 mm</t>
+        </is>
+      </c>
+      <c r="E2" s="19" t="inlineStr">
+        <is>
+          <t>Comprar/fabricar com 500 mm de largura; o layout atual precisa disso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>Critica</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>PI-2 e ensaio</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>BOM descreve itens espalhados e ainda cita 4 em alguns trechos</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>React: 2 DUTs, CD74HC4067 e 1 INA219</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>Comprar para 2 posicoes; manter 1 mux e 1 INA219.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>Critica</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>Ventoinhas internas</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>BOM separa 2 fans de 60 mm e 2 fans de 40 mm</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>React: 5 internas no mesmo grupo: 4 de circulacao + 1 do PTC</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>Conferir fisicamente o tamanho das 5; a fiação atual trata as cinco em paralelo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>BD-5V e BD-24V</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>Trechos antigos do BOM/React antigo mostram 6 e 4 saidas</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>React atual: BD-5V com 8 e BD-24V com 6</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>Comprar os blocos maiores da aba Inventario React.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>IHM</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>BOM antiga ainda cita Nextion e modulo SD separado em partes do texto</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>React: ES3C28P com microSD integrado</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>Nao comprar Nextion nem modulo SD separado; comprar conversor de nivel e rabicho Type-C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>Cores de fiação</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>BOM resume positivos/negativos por cor</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>React usa cor funcional: 24 V permanente laranja, 5 V violeta, sinal cinza/verde</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>Seguir a aba Fiacao React e identificar cada cabo com anilha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>Geometria da camara</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>BOM/documentos têm dimensoes revisadas diferentes</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>React ainda conserva constantes antigas em camara.js, enquanto montagem/ligacoes refletem a revisao</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>Nao cortar acrilico sem confirmar a lista de corte e o desenho final.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7421,161 +7742,161 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>ORDEM DE CONSTRUÇÃO — 5 camadas</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>Camada</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="C3" s="20" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>Documentos</t>
         </is>
       </c>
-      <c r="D3" s="20" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>Critério de aceitação</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>CAMADA 0</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>Fundamentos</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>Visão geral · Arquitetura de energia · BOM</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>Entregável: BOM fechada e cálculos feitos</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>CAMADA 1</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>Maquete</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>Base e chão de fábrica · Subestação e postes · Câmara térmica</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>Entregável: cenário pronto, sem eletrônica</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>CAMADA 2</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>Painel</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>Dimensionamento · Layout · Furação · Fixação nos trilhos</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>Entregável: painel montado, sem um fio ligado</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>CAMADA 3</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>Elétrica</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>Força e distribuição · Comando e proteções · Sinais e sensores</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>Entregável: energizado e medido, sem firmware</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>CAMADA 4</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Programação</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>Firmware Arduino · ESP32, IHM e IoT</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>Entregável: software gravado e testado em bancada</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>CAMADA 5</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>Integração</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>Montagem final · Comissionamento · Ensaios</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>Entregável: projeto funcionando e documentado</t>
         </is>
@@ -7589,7 +7910,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7603,295 +7924,295 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>NÚMEROS DO PROJETO</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>Arquitetura de energia</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>Potência em 24 V — carga térmica sem conversor</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>Tensão de entrada</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="27" t="inlineStr">
         <is>
           <t>127 V CA</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>Barramento de distribuição</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>24 V CC (SELV)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>Potência instalada (fonte)</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>240 W · 10 A</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>Consumo calculado</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>≈ 166 W · 6,9 A @ 24 V</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>Folga da fonte</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>1,44× (44 %) — a fonte de 150 W NÃO atende</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>Corrente CA de entrada</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>2,37 A</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>Queda de tensão na linha dos postes</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>0,21 V (0,86 %)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>Conversores</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>2 × LM2596 com display (T2 e T3) · P1 é derivação direta</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>Tensões derivadas</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>24,0 V potência (direto) · 12,0 V auxiliar · 5,10 V comando · 3,3 V ESP32</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>Fusíveis dos ramais</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>F1 = 10 A · F2 = 2 A · F3 = 2 A (sem F4/F5, sem crowbar)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>Níveis de proteção</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>5 (do disjuntor ao intertravamento por software)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>Volume útil da câmara</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>5,0 litros (200 × 100 × 250 mm)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>Carga térmica calculada</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>≈ 9,5 W</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>Refrigeração</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>2 × TEC1-12706 EM SÉRIE · 24 V · 6,0 A · 144 W</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="26" t="inlineStr">
         <is>
           <t>Capacidade das Peltier a ΔT = 20 K</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="27" t="inlineStr">
         <is>
           <t>≈ 60 W (margem de 6,3×)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="24" t="inlineStr">
         <is>
           <t>Dissipação no lado quente</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>≈ 200 W — 2 conjuntos dissipador + cooler 80 mm</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t>Aquecimento</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
-        <is>
-          <t>PTC cerâmico de 24 V · 60 W · 2,5 A</t>
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>PTC cerâmico de 24 V · 80 W · 3,3 A</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>Isolamento</t>
         </is>
       </c>
-      <c r="B21" s="24" t="inlineStr">
+      <c r="B21" s="25" t="inlineStr">
         <is>
           <t>XPS 30 mm + barreira de vapor · U = 0,86 W/m²·K</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t>Porta</t>
         </is>
       </c>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B22" s="27" t="inlineStr">
         <is>
           <t>Dupla · U = 2,42 W/m²·K (não condensa)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="23" t="inlineStr">
+      <c r="A23" s="24" t="inlineStr">
         <is>
           <t>Base da maquete</t>
         </is>
       </c>
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>1500 × 500 mm · escala cenográfica 1:50</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="26" t="inlineStr">
         <is>
           <t>Painel</t>
         </is>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B24" s="27" t="inlineStr">
         <is>
           <t>400 × 500 × 200 mm · 3 trilhos DIN</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="23" t="inlineStr">
+      <c r="A25" s="24" t="inlineStr">
         <is>
           <t>Componentes discretos</t>
         </is>
       </c>
-      <c r="B25" s="24" t="inlineStr">
+      <c r="B25" s="25" t="inlineStr">
         <is>
           <t>6 + 1 CI ULN2803 na PI-1 · 2 nos BTS7960 · 4 nos postes da maquete</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t>Sinalização</t>
         </is>
       </c>
-      <c r="B26" s="26" t="inlineStr">
+      <c r="B26" s="27" t="inlineStr">
         <is>
           <t>4 sinaleiros 22 mm de 24 V (via ULN2803) · 4 LEDs brancos de 5 V na maquete</t>
         </is>

--- a/BOM_Projeto_Integrador.xlsx
+++ b/BOM_Projeto_Integrador.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Dados do Projeto" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lista de Compras'!$A$4:$K$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lista de Compras'!$A$4:$K$166</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Inventario React'!$A$1:$E$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Fiacao React'!$A$1:$E$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Divergencias'!$A$1:$E$8</definedName>
@@ -582,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K174"/>
+  <dimension ref="A1:K168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Lista de materiais · gerada de 03_lista_materiais.md em 18/08/2026 17:45 · arquitetura 127 V CA → 24 V CC → 12 / 5 / 3,3 V</t>
+          <t>Lista de materiais · gerada de 03_lista_materiais.md em 20/08/2026 16:42 · arquitetura 127 V CA → 24 V CC → 12 / 5 / 3,3 V</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>E.1 — Subestação: entrada AC e fonte principal</t>
+          <t>✅ O que está certo e pode fechar</t>
         </is>
       </c>
     </row>
@@ -682,30 +682,22 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Fonte chaveada 24 Vcc</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>24 V / 10 A / 240 W, bivolt 110-220 V (chave seletora ou auto-range). Modelo tipo S-240-24</t>
-        </is>
-      </c>
+          <t>Módulo sensor de tensão DC 0-25 V (5 pçs)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>fonte chaveada 24v 10a 240w</t>
+          <t>Meça a saída com 24 V: ~4,8 V. Ver Doc 33 §33.4</t>
         </is>
       </c>
       <c r="F6" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fonte-chaveada-24v-10a-240w","🔎 fonte chaveada 24v 10a 240w")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/modulo-sensor-tensao-dc-0-25-v","🔎 modulo sensor tensao dc 0 25")</f>
         <v/>
       </c>
       <c r="G6" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fonte+chaveada+24v+10a+240w","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=modulo+sensor+tensao+dc+0+25+v","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H6" s="8" t="inlineStr"/>
@@ -722,30 +714,22 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Disjuntor DIN 2P 6 A curva C</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Bipolar, 6 A, curva C (por causa do inrush da fonte), 3 kA</t>
-        </is>
-      </c>
+          <t>Sensor WCS2702 ajustável</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr"/>
+      <c r="D7" s="11" t="inlineStr"/>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>disjuntor bipolar 6a curva c din</t>
+          <t>Que tenha furo de passagem para o fio (é por ele que entram as 10 voltas)</t>
         </is>
       </c>
       <c r="F7" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/disjuntor-bipolar-6a-curva-c-din","🔎 disjuntor bipolar 6a curva c")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/sensor-wcs2702-ajustavel","🔎 sensor wcs2702 ajustavel")</f>
         <v/>
       </c>
       <c r="G7" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=disjuntor+bipolar+6a+curva+c+din","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=sensor+wcs2702+ajustavel","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H7" s="13" t="inlineStr"/>
@@ -762,30 +746,22 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Cabo PP 3×1,5 mm² + plugue</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>1,5 m</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Cabo de entrada AC com plugue 2P+T 10 A</t>
-        </is>
-      </c>
+          <t>Conversor de nível lógico 4 canais I²C</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>cabo pp 3x1,5 com plugue</t>
+          <t>Bidirecional, com os dois lados alimentados</t>
         </is>
       </c>
       <c r="F8" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-pp-3x1-5-com-plugue","🔎 cabo pp 3x1,5 com plugue")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/conversor-nivel-logico-4-canais-i-c","🔎 conversor nivel logico 4 can")</f>
         <v/>
       </c>
       <c r="G8" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+pp+3x1%2C5+com+plugue","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=conversor+nivel+logico+4+canais+i+c","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H8" s="8" t="inlineStr"/>
@@ -802,33 +778,28 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prensa-cabo PG9 / PG13</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>Entrada e saída de cabos da caixa da subestação</t>
-        </is>
-      </c>
+          <t>BTS7960 ponte-H 43 A (2 pçs)</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr"/>
+      <c r="D9" s="11" t="inlineStr"/>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>prensa cabo pg9</t>
+          <t>Barra de pinos com R_EN, L_EN, R_IS, GND</t>
         </is>
       </c>
       <c r="F9" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/prensa-cabo-pg9","🔎 prensa cabo pg9")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/bts7960-ponte-h-43","🔎 bts7960 ponte h 43")</f>
         <v/>
       </c>
       <c r="G9" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=prensa+cabo+pg9","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H9" s="13" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=bts7960+ponte+h+43","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H9" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-bts7960-43a-motor-driver-module.html","🌏 BTS7960 43A motor driver m")</f>
+        <v/>
+      </c>
       <c r="I9" s="13" t="inlineStr"/>
       <c r="J9" s="14" t="inlineStr"/>
       <c r="K9" s="14">
@@ -842,30 +813,22 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Borne DIN 4 mm²</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Distribuição 24 V e 0 V na subestação</t>
-        </is>
-      </c>
+          <t>LM2596 com display (2 pçs)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="6" t="inlineStr"/>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>borne trilho din 4mm parafuso</t>
+          <t>⚠️ Ajuste na bancada antes de fechar no poste</t>
         </is>
       </c>
       <c r="F10" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/borne-trilho-din-4mm-parafuso","🔎 borne trilho din 4mm parafus")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/lm2596-display","🔎 lm2596 display")</f>
         <v/>
       </c>
       <c r="G10" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=borne+trilho+din+4mm+parafuso","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=lm2596+display","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H10" s="8" t="inlineStr"/>
@@ -882,36 +845,33 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Cooler 60 mm 24 V</t>
+          <t>Módulo relé 1 canal 5 V (2 pçs)</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Exaustão da casa de comando (~29 W de perda da fonte). ⚠️ Obrigatório, não opcional — a casinha encolheu para 250 × 150 × 90 mm e a fonte continua dissipando o mesmo. ⚠️ 24 V: é a única tensão de saída disponível. Alternativa: 2× de 12 V em série</t>
+          <t>KA1 (NO), KA2 (NC) e KA3 (NO), optoacoplados, caixa DIN 6M; reservas opcionais</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>cooler 60mm 24v</t>
+          <t>⭐ "5VDC" no corpo do relé e jumper em H</t>
         </is>
       </c>
       <c r="F11" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/cooler-60mm-24v","🔎 cooler 60mm 24v")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/modulo-rele-1-canal-5-v","🔎 modulo rele 1 canal 5 v")</f>
         <v/>
       </c>
       <c r="G11" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=cooler+60mm+24v","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H11" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-60mm-fan-24v-dc.html","🌏 60mm fan 24V DC")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=modulo+rele+1+canal+5+v","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H11" s="13" t="inlineStr"/>
       <c r="I11" s="13" t="inlineStr"/>
       <c r="J11" s="14" t="inlineStr"/>
       <c r="K11" s="14">
@@ -925,33 +885,28 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Grade + filtro 60 mm</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Veneziana de entrada de ar da subestação</t>
-        </is>
-      </c>
+          <t>AM2315C I²C</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="6" t="inlineStr"/>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>grade cooler 60mm com filtro</t>
+          <t>Endereço 0x38, não conflita com o RTC (0x68)</t>
         </is>
       </c>
       <c r="F12" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/grade-cooler-60mm-com-filtro","🔎 grade cooler 60mm com filtro")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/am2315c-i-c","🔎 am2315c i c")</f>
         <v/>
       </c>
       <c r="G12" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=grade+cooler+60mm+com+filtro","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H12" s="8" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=am2315c+i+c","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H12" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-am2315c-temperature-humidity-sensor.html","🌏 AM2315C temperature humidi")</f>
+        <v/>
+      </c>
       <c r="I12" s="8" t="inlineStr"/>
       <c r="J12" s="9" t="inlineStr"/>
       <c r="K12" s="9">
@@ -959,54 +914,70 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>E.2 — Conversores de tensão (os "transformadores" da maquete)</t>
-        </is>
+    <row r="13">
+      <c r="A13" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>ESP32-WROOM-32U DevKitC</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr"/>
+      <c r="D13" s="11" t="inlineStr"/>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Versão U = conector de antena externa ✔</t>
+        </is>
+      </c>
+      <c r="F13" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/esp32-wroom-32u-devkitc","🔎 esp32 wroom 32u devkitc")</f>
+        <v/>
+      </c>
+      <c r="G13" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=esp32+wroom+32u+devkitc","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H13" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-esp32-wroom-32u.html","🌏 ESP32 WROOM 32U")</f>
+        <v/>
+      </c>
+      <c r="I13" s="13" t="inlineStr"/>
+      <c r="J13" s="14" t="inlineStr"/>
+      <c r="K13" s="14">
+        <f>IF(C13*J13=0,"",C13*J13)</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>⭐ Kit 2× Módulo LM2596 com display</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>1 kit</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Step-down 3 A, Vin até 40 V, saída ajustável, display LED vermelho de 3 dígitos integrado. Um módulo vira o T2, o outro vira o T3</t>
-        </is>
-      </c>
+          <t>Antena 2,4 GHz RP-SMA + cabo U.FL→SMA + flange</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr"/>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>ver abaixo</t>
+          <t>⚠️ RP-SMA e SMA não encaixam entre si — confira que antena e flange são o mesmo padrão</t>
         </is>
       </c>
       <c r="F14" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/kit-2-modulo-lm2596-display","🔎 kit 2 modulo lm2596 display")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/antena-2-4-ghz-rp-sma-cabo-u","🔎 antena 2,4 ghz rp sma cabo u")</f>
         <v/>
       </c>
       <c r="G14" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=kit+2+modulo+lm2596+display","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=antena+2%2C4+ghz+rp+sma+cabo+u","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H14" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-lm2596-buck-converter-voltmeter-display.html","🌏 LM2596 buck converter volt")</f>
-        <v/>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>Mercado Livre</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-2-4ghz-sma-antenna-3dbi.html","🌏 2.4GHz SMA antenna 3dBi")</f>
+        <v/>
+      </c>
+      <c r="I14" s="8" t="inlineStr"/>
       <c r="J14" s="9" t="inlineStr"/>
       <c r="K14" s="9">
         <f>IF(C14*J14=0,"",C14*J14)</f>
@@ -1015,31 +986,32 @@
     </row>
     <row r="15">
       <c r="A15" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>→ T2 (poste P2, comando)</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>1º módulo do kit — alimenta Arduino, tela ES3C28P, RTC, lógica dos BTS, placa PI-1 e os LEDs da iluminação da maquete</t>
-        </is>
-      </c>
+          <t>Aquecedor PTC 24 V com ventilador</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr"/>
+      <c r="D15" s="11" t="inlineStr"/>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>5,10 V</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr"/>
-      <c r="G15" s="13" t="inlineStr"/>
-      <c r="H15" s="13" t="inlineStr"/>
+          <t>⚠️ Confirme 24 V (o anúncio vende 12/24/110/220)</t>
+        </is>
+      </c>
+      <c r="F15" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/aquecedor-ptc-24-v-ventilador","🔎 aquecedor ptc 24 v ventilado")</f>
+        <v/>
+      </c>
+      <c r="G15" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=aquecedor+ptc+24+v+ventilador","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H15" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-24v-ptc-heater-element-with-fan.html","🌏 24V PTC heater element wit")</f>
+        <v/>
+      </c>
       <c r="I15" s="13" t="inlineStr"/>
       <c r="J15" s="14" t="inlineStr"/>
       <c r="K15" s="14">
@@ -1049,31 +1021,32 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>→ T3 (poste P3, auxiliares)</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>2º módulo do kit — alimenta as fans internas e os coolers</t>
-        </is>
-      </c>
+          <t>DS18B20 à prova d'água, cabo 1 m</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="6" t="inlineStr"/>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>12,0 V</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr"/>
-      <c r="G16" s="8" t="inlineStr"/>
-      <c r="H16" s="8" t="inlineStr"/>
+          <t>⚠️ VEJA O ALERTA ABAIXO</t>
+        </is>
+      </c>
+      <c r="F16" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/ds18b20-prova-d-agua-cabo-1-m","🔎 ds18b20 prova d agua, cabo 1")</f>
+        <v/>
+      </c>
+      <c r="G16" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=ds18b20+prova+d+agua%2C+cabo+1+m","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H16" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-ds18b20-waterproof-temperature-sensor.html","🌏 DS18B20 waterproof tempera")</f>
+        <v/>
+      </c>
       <c r="I16" s="8" t="inlineStr"/>
       <c r="J16" s="9" t="inlineStr"/>
       <c r="K16" s="9">
@@ -1081,47 +1054,11 @@
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Kit LM2596 reserva</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>1 kit</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>Opcional mas recomendado. São os únicos conversores do projeto; queimar um na véspera sem reserva significa não apresentar</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/kit-lm2596-reserva","🔎 kit lm2596 reserva")</f>
-        <v/>
-      </c>
-      <c r="G17" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=kit+lm2596+reserva","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H17" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-lm2596-buck-converter-voltmeter-display.html","🌏 LM2596 buck converter volt")</f>
-        <v/>
-      </c>
-      <c r="I17" s="13" t="inlineStr"/>
-      <c r="J17" s="14" t="inlineStr"/>
-      <c r="K17" s="14">
-        <f>IF(C17*J17=0,"",C17*J17)</f>
-        <v/>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>⚠️ Os seis pontos de atenção do carrinho</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1130,36 +1067,21 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Dissipador de alumínio ~20 × 15 × 10 mm</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>⚠️ Obrigatório, colado no CI LM2596S de cada módulo. Sem ele o T3 passa dos 100 °C dentro do tubo — ver Doc 02 §2.8</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>Módulo de distribuição DC para trilho DIN, com divisora de fusíveis e interruptor</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="6" t="inlineStr"/>
+      <c r="E18" s="6" t="inlineStr"/>
       <c r="F18" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/dissipador-aluminio-20-15-10-mm","🔎 dissipador aluminio 20 15 10")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/modulo-distribuicao-dc-trilho-din-divisora-fusiveis","🔎 modulo distribuicao dc trilh")</f>
         <v/>
       </c>
       <c r="G18" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=dissipador+aluminio+20+15+10+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H18" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-aluminum-heatsink-small.html","🌏 aluminum heatsink small")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=modulo+distribuicao+dc+trilho+din%2C+divisora+fusiveis","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H18" s="8" t="inlineStr"/>
       <c r="I18" s="8" t="inlineStr"/>
       <c r="J18" s="9" t="inlineStr"/>
       <c r="K18" s="9">
@@ -1173,36 +1095,21 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Fita térmica dupla face</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>Fixação dos dissipadores</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>Módulo de interface de fusível DIN 2–15 canais (5×20 mm)</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr"/>
+      <c r="D19" s="11" t="inlineStr"/>
+      <c r="E19" s="11" t="inlineStr"/>
       <c r="F19" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-termica-dupla-face","🔎 fita termica dupla face")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/modulo-interface-fusivel-din-2-15-canais","🔎 modulo interface fusivel din")</f>
         <v/>
       </c>
       <c r="G19" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+termica+dupla+face","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H19" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-thermal-adhesive-tape-double-sided.html","🌏 thermal adhesive tape doub")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=modulo+interface+fusivel+din+2+15+canais","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H19" s="13" t="inlineStr"/>
       <c r="I19" s="13" t="inlineStr"/>
       <c r="J19" s="14" t="inlineStr"/>
       <c r="K19" s="14">
@@ -1210,53 +1117,20 @@
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Acrílico transparente 1 mm</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>1 lâmina</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>Janelas de visualização nos 3 tubos dos postes (~20 × 12 mm cada) — protege o display e mantém o visual fechado</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/acrilico-transparente-1-mm","🔎 acrilico transparente 1 mm")</f>
-        <v/>
-      </c>
-      <c r="G20" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=acrilico+transparente+1+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H20" s="8" t="inlineStr"/>
-      <c r="I20" s="8" t="inlineStr"/>
-      <c r="J20" s="9" t="inlineStr"/>
-      <c r="K20" s="9">
-        <f>IF(C20*J20=0,"",C20*J20)</f>
-        <v/>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>E.1 — Subestação: entrada AC e fonte principal</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Voltímetro + amperímetro digital 3 fios</t>
+          <t>Fonte chaveada 24 Vcc</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -1266,26 +1140,23 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Único medidor comprado à parte — vai na caixa de derivação do P1, mostrando os 24,0 V do barramento e a corrente das Peltier ao vivo. Faixa: 0-100 V / 10 A</t>
+          <t>24 V / 10 A / 240 W, bivolt 110-220 V (chave seletora ou auto-range). Modelo tipo S-240-24</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>fonte chaveada 24v 10a 240w</t>
         </is>
       </c>
       <c r="F21" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/voltimetro-amperimetro-digital-3-fios","🔎 voltimetro amperimetro digit")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fonte-chaveada-24v-10a-240w","🔎 fonte chaveada 24v 10a 240w")</f>
         <v/>
       </c>
       <c r="G21" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=voltimetro+amperimetro+digital+3+fios","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H21" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-dc-voltmeter-ammeter-100v-10a-digital.html","🌏 DC voltmeter ammeter 100V ")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fonte+chaveada+24v+10a+240w","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H21" s="13" t="inlineStr"/>
       <c r="I21" s="13" t="inlineStr"/>
       <c r="J21" s="14" t="inlineStr"/>
       <c r="K21" s="14">
@@ -1293,11 +1164,44 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>E.3 — Proteção do sistema de energia</t>
-        </is>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Disjuntor DIN 2P 6 A curva C</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Bipolar, 6 A, curva C (por causa do inrush da fonte), 3 kA</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>disjuntor bipolar 6a curva c din</t>
+        </is>
+      </c>
+      <c r="F22" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/disjuntor-bipolar-6a-curva-c-din","🔎 disjuntor bipolar 6a curva c")</f>
+        <v/>
+      </c>
+      <c r="G22" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=disjuntor+bipolar+6a+curva+c+din","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H22" s="8" t="inlineStr"/>
+      <c r="I22" s="8" t="inlineStr"/>
+      <c r="J22" s="9" t="inlineStr"/>
+      <c r="K22" s="9">
+        <f>IF(C22*J22=0,"",C22*J22)</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -1306,30 +1210,30 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Porta-fusível mini automotivo</t>
+          <t>Cabo PP 3×1,5 mm² + plugue</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1,5 m</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Fusível de LÂMINA (automotivo), não de vidro. Trilho DIN 35 mm ou bloco parafusado — ver nota abaixo</t>
+          <t>Cabo de entrada AC com plugue 2P+T 10 A</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>F1, F2, F3 — entrada dos 3 ramais, na subestação</t>
+          <t>cabo pp 3x1,5 com plugue</t>
         </is>
       </c>
       <c r="F23" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/porta-fusivel-mini-automotivo","🔎 porta fusivel mini automotiv")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-pp-3x1-5-com-plugue","🔎 cabo pp 3x1,5 com plugue")</f>
         <v/>
       </c>
       <c r="G23" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=porta+fusivel+mini+automotivo","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+pp+3x1%2C5+com+plugue","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H23" s="13" t="inlineStr"/>
@@ -1346,30 +1250,30 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>*Alternativa:* bloco de 3 posições para fusível lâmina</t>
+          <t>Prensa-cabo PG9 / PG13</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Substitui os 3 suportes acima. ⚠️ Conferir: fusível lâmina · ≥ 10 A por posição · ≥ 32 Vdc · preferir entrada comum (1 entrada + 3 saídas). Parafusa na parede da caixa — dispensa trilho DIN na subestação</t>
+          <t>Entrada e saída de cabos da caixa da subestação</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>idem</t>
+          <t>prensa cabo pg9</t>
         </is>
       </c>
       <c r="F24" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/alternativa-bloco-3-posicoes-fusivel-lamina","🔎 alternativa bloco 3 posicoes")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/prensa-cabo-pg9","🔎 prensa cabo pg9")</f>
         <v/>
       </c>
       <c r="G24" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=alternativa+bloco+3+posicoes+fusivel+lamina","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=prensa+cabo+pg9","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H24" s="8" t="inlineStr"/>
@@ -1386,30 +1290,30 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Fusível mini automotivo 10 A</t>
+          <t>Borne DIN 4 mm²</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>1 uso + 1 reserva</t>
+          <t>Distribuição 24 V e 0 V na subestação</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>F1 — ramal R1 (potência 24 V, 6,0 A)</t>
+          <t>borne trilho din 4mm parafuso</t>
         </is>
       </c>
       <c r="F25" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fusivel-mini-automotivo-10","🔎 fusivel mini automotivo 10")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/borne-trilho-din-4mm-parafuso","🔎 borne trilho din 4mm parafus")</f>
         <v/>
       </c>
       <c r="G25" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fusivel+mini+automotivo+10","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=borne+trilho+din+4mm+parafuso","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H25" s="13" t="inlineStr"/>
@@ -1426,33 +1330,36 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Fusível mini automotivo 2 A</t>
+          <t>Cooler 60 mm 24 V</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>2 usos + 2 reservas</t>
+          <t>Exaustão da casa de comando (~29 W de perda da fonte). ⚠️ Obrigatório, não opcional — a casinha encolheu para 250 × 150 × 90 mm e a fonte continua dissipando o mesmo. ⚠️ 24 V: é a única tensão de saída disponível. Alternativa: 2× de 12 V em série</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>F2 (comando) e F3 (auxiliares)</t>
+          <t>cooler 60mm 24v</t>
         </is>
       </c>
       <c r="F26" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fusivel-mini-automotivo-2","🔎 fusivel mini automotivo 2")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cooler-60mm-24v","🔎 cooler 60mm 24v")</f>
         <v/>
       </c>
       <c r="G26" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fusivel+mini+automotivo+2","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H26" s="8" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cooler+60mm+24v","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H26" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-60mm-fan-24v-dc.html","🌏 60mm fan 24V DC")</f>
+        <v/>
+      </c>
       <c r="I26" s="8" t="inlineStr"/>
       <c r="J26" s="9" t="inlineStr"/>
       <c r="K26" s="9">
@@ -1466,30 +1373,30 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Terminal olhal M4 amarelo</t>
+          <t>Grade + filtro 60 mm</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Aterramento e barramento de 0 V</t>
+          <t>Veneziana de entrada de ar da subestação</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>grade cooler 60mm com filtro</t>
         </is>
       </c>
       <c r="F27" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/terminal-olhal-m4-amarelo","🔎 terminal olhal m4 amarelo")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/grade-cooler-60mm-com-filtro","🔎 grade cooler 60mm com filtro")</f>
         <v/>
       </c>
       <c r="G27" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=terminal+olhal+m4+amarelo","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=grade+cooler+60mm+com+filtro","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H27" s="13" t="inlineStr"/>
@@ -1503,7 +1410,7 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>M.1 — Base e estrutura</t>
+          <t>E.2 — Conversores de tensão (os "transformadores" da maquete)</t>
         </is>
       </c>
     </row>
@@ -1513,30 +1420,41 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>MDF 12 mm</t>
+          <t>⭐ Kit 2× Módulo LM2596 com display</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>1 chapa</t>
+          <t>1 kit</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>1500 × 500 mm — tampo da base</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr"/>
+          <t>Step-down 3 A, Vin até 40 V, saída ajustável, display LED vermelho de 3 dígitos integrado. Um módulo vira o T2, o outro vira o T3</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>ver abaixo</t>
+        </is>
+      </c>
       <c r="F29" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/mdf-12-mm","🔎 mdf 12 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/kit-2-modulo-lm2596-display","🔎 kit 2 modulo lm2596 display")</f>
         <v/>
       </c>
       <c r="G29" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=mdf+12+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H29" s="13" t="inlineStr"/>
-      <c r="I29" s="13" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=kit+2+modulo+lm2596+display","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H29" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-lm2596-buck-converter-voltmeter-display.html","🌏 LM2596 buck converter volt")</f>
+        <v/>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>Mercado Livre</t>
+        </is>
+      </c>
       <c r="J29" s="14" t="inlineStr"/>
       <c r="K29" s="14">
         <f>IF(C29*J29=0,"",C29*J29)</f>
@@ -1549,7 +1467,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>MDF 15 mm</t>
+          <t>→ T2 (poste P2, comando)</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -1559,18 +1477,16 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Moldura perimetral 40 mm de altura (4 tiras)</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr"/>
-      <c r="F30" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/mdf-15-mm","🔎 mdf 15 mm")</f>
-        <v/>
-      </c>
-      <c r="G30" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=mdf+15+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
+          <t>1º módulo do kit — alimenta Arduino, tela ES3C28P, RTC, lógica dos BTS, placa PI-1 e os LEDs da iluminação da maquete</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>5,10 V</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr"/>
+      <c r="G30" s="8" t="inlineStr"/>
       <c r="H30" s="8" t="inlineStr"/>
       <c r="I30" s="8" t="inlineStr"/>
       <c r="J30" s="9" t="inlineStr"/>
@@ -1585,28 +1501,26 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>MDF 15 mm</t>
+          <t>→ T3 (poste P3, auxiliares)</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>3 tiras</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Travessas de reforço 15 × 40 mm, com entalhe de 20 × 25 mm no centro</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr"/>
-      <c r="F31" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/mdf-15-mm","🔎 mdf 15 mm")</f>
-        <v/>
-      </c>
-      <c r="G31" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=mdf+15+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
+          <t>2º módulo do kit — alimenta as fans internas e os coolers</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>12,0 V</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr"/>
+      <c r="G31" s="13" t="inlineStr"/>
       <c r="H31" s="13" t="inlineStr"/>
       <c r="I31" s="13" t="inlineStr"/>
       <c r="J31" s="14" t="inlineStr"/>
@@ -1621,29 +1535,36 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Pés de borracha antiderrapante</t>
+          <t>Kit LM2596 reserva</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1 kit</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Autoadesivos, Ø 25 mm — a base tem 1,5 m e pesa ~18 kg</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr"/>
+          <t>Opcional mas recomendado. São os únicos conversores do projeto; queimar um na véspera sem reserva significa não apresentar</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="F32" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/pes-borracha-antiderrapante","🔎 pes borracha antiderrapante")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/kit-lm2596-reserva","🔎 kit lm2596 reserva")</f>
         <v/>
       </c>
       <c r="G32" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=pes+borracha+antiderrapante","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H32" s="8" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=kit+lm2596+reserva","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H32" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-lm2596-buck-converter-voltmeter-display.html","🌏 LM2596 buck converter volt")</f>
+        <v/>
+      </c>
       <c r="I32" s="8" t="inlineStr"/>
       <c r="J32" s="9" t="inlineStr"/>
       <c r="K32" s="9">
@@ -1657,30 +1578,34 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Conector circular GX16 8 pinos</t>
+          <t>Dissipador de alumínio ~20 × 15 × 10 mm</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>1 par</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Opcional — só na versão modular (união elétrica entre os 2 módulos)</t>
-        </is>
-      </c>
-      <c r="E33" s="11" t="inlineStr"/>
+          <t>⚠️ Obrigatório, colado no CI LM2596S de cada módulo. Sem ele o T3 passa dos 100 °C dentro do tubo — ver Doc 02 §2.8</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="F33" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/conector-circular-gx16-8-pinos","🔎 conector circular gx16 8 pin")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/dissipador-aluminio-20-15-10-mm","🔎 dissipador aluminio 20 15 10")</f>
         <v/>
       </c>
       <c r="G33" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=conector+circular+gx16+8+pinos","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=dissipador+aluminio+20+15+10+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H33" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-gx16-8-pin-aviation-connector.html","🌏 GX16 8 pin aviation connec")</f>
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-aluminum-heatsink-small.html","🌏 aluminum heatsink small")</f>
         <v/>
       </c>
       <c r="I33" s="13" t="inlineStr"/>
@@ -1696,29 +1621,36 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Pinos-guia Ø 6 mm + buchas</t>
+          <t>Fita térmica dupla face</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Opcional — alinhamento dos módulos</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr"/>
+          <t>Fixação dos dissipadores</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="F34" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/pinos-guia-6-mm-buchas","🔎 pinos guia 6 mm buchas")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-termica-dupla-face","🔎 fita termica dupla face")</f>
         <v/>
       </c>
       <c r="G34" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=pinos+guia+6+mm+buchas","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H34" s="8" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+termica+dupla+face","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H34" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-thermal-adhesive-tape-double-sided.html","🌏 thermal adhesive tape doub")</f>
+        <v/>
+      </c>
       <c r="I34" s="8" t="inlineStr"/>
       <c r="J34" s="9" t="inlineStr"/>
       <c r="K34" s="9">
@@ -1732,26 +1664,30 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>Alças de transporte</t>
+          <t>Acrílico transparente 1 mm</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 lâmina</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Alça embutida de baú/case, laterais</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="inlineStr"/>
+          <t>Janelas de visualização nos 3 tubos dos postes (~20 × 12 mm cada) — protege o display e mantém o visual fechado</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="F35" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/alcas-transporte","🔎 alcas transporte")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/acrilico-transparente-1-mm","🔎 acrilico transparente 1 mm")</f>
         <v/>
       </c>
       <c r="G35" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=alcas+transporte","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=acrilico+transparente+1+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H35" s="13" t="inlineStr"/>
@@ -1768,29 +1704,36 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Parafusos M5×20, M4×16, M3×12</t>
+          <t>Voltímetro + amperímetro digital 3 fios</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>kits</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Fixações gerais</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr"/>
+          <t>Único medidor comprado à parte — vai na caixa de derivação do P1, mostrando os 24,0 V do barramento e a corrente das Peltier ao vivo. Faixa: 0-100 V / 10 A</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="F36" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/parafusos-m5-20-m4-16-m3-12","🔎 parafusos m5 20, m4 16, m3 1")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/voltimetro-amperimetro-digital-3-fios","🔎 voltimetro amperimetro digit")</f>
         <v/>
       </c>
       <c r="G36" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=parafusos+m5+20%2C+m4+16%2C+m3+12","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H36" s="8" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=voltimetro+amperimetro+digital+3+fios","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H36" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-dc-voltmeter-ammeter-100v-10a-digital.html","🌏 DC voltmeter ammeter 100V ")</f>
+        <v/>
+      </c>
       <c r="I36" s="8" t="inlineStr"/>
       <c r="J36" s="9" t="inlineStr"/>
       <c r="K36" s="9">
@@ -1798,47 +1741,51 @@
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="10" t="n">
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>E.3 — Proteção do sistema de energia</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>Insertos rosqueados M4/M5 p/ MDF</t>
-        </is>
-      </c>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>Evita espanar a rosca no MDF</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="inlineStr"/>
-      <c r="F37" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/insertos-rosqueados-m4-m5-p-mdf","🔎 insertos rosqueados m4 m5 p ")</f>
-        <v/>
-      </c>
-      <c r="G37" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=insertos+rosqueados+m4+m5+p+mdf","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H37" s="13" t="inlineStr"/>
-      <c r="I37" s="13" t="inlineStr"/>
-      <c r="J37" s="14" t="inlineStr"/>
-      <c r="K37" s="14">
-        <f>IF(C37*J37=0,"",C37*J37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>M.2 — Subestação (caixa)</t>
-        </is>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Porta-fusível mini automotivo</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Fusível de LÂMINA (automotivo), não de vidro. Trilho DIN 35 mm ou bloco parafusado — ver nota abaixo</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>F1, F2, F3 — entrada dos 3 ramais, na subestação</t>
+        </is>
+      </c>
+      <c r="F38" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/porta-fusivel-mini-automotivo","🔎 porta fusivel mini automotiv")</f>
+        <v/>
+      </c>
+      <c r="G38" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=porta+fusivel+mini+automotivo","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H38" s="8" t="inlineStr"/>
+      <c r="I38" s="8" t="inlineStr"/>
+      <c r="J38" s="9" t="inlineStr"/>
+      <c r="K38" s="9">
+        <f>IF(C38*J38=0,"",C38*J38)</f>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -1847,26 +1794,30 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>MDF 9 mm ou acrílico opaco 4 mm</t>
+          <t>*Alternativa:* bloco de 3 posições para fusível lâmina</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>CASA DE COMANDO 250 × 150 × 90 mm (L×P×A), face de operação voltada para a rua. Abriga apenas fonte, disjuntor e chave — os fusíveis de 24 V ficam no pátio aberto</t>
-        </is>
-      </c>
-      <c r="E39" s="11" t="inlineStr"/>
+          <t>Substitui os 3 suportes acima. ⚠️ Conferir: fusível lâmina · ≥ 10 A por posição · ≥ 32 Vdc · preferir entrada comum (1 entrada + 3 saídas). Parafusa na parede da caixa — dispensa trilho DIN na subestação</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>idem</t>
+        </is>
+      </c>
       <c r="F39" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/mdf-9-mm-acrilico-opaco-4-mm","🔎 mdf 9 mm acrilico opaco 4 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/alternativa-bloco-3-posicoes-fusivel-lamina","🔎 alternativa bloco 3 posicoes")</f>
         <v/>
       </c>
       <c r="G39" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=mdf+9+mm+acrilico+opaco+4+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=alternativa+bloco+3+posicoes+fusivel+lamina","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H39" s="13" t="inlineStr"/>
@@ -1883,26 +1834,30 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Fio verde-amarelo 0,75 mm²</t>
+          <t>Fusível mini automotivo 10 A</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>1 m</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>⚡ Aterramento das estruturas metálicas do pátio à barra de terra (equipotencialização). Torre real é aterrada — vale ponto na defesa</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr"/>
+          <t>1 uso + 1 reserva</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>F1 — ramal RM1 (potência 24 V, 6,0 A)</t>
+        </is>
+      </c>
       <c r="F40" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-verde-amarelo-0-75-mm","🔎 fio verde amarelo 0,75 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fusivel-mini-automotivo-10","🔎 fusivel mini automotivo 10")</f>
         <v/>
       </c>
       <c r="G40" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+verde+amarelo+0%2C75+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fusivel+mini+automotivo+10","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H40" s="8" t="inlineStr"/>
@@ -1919,26 +1874,30 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>*Opcional:* arame / barra de latão 1,5–2 mm</t>
+          <t>Fusível mini automotivo 2 A</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>2 m</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Estruturas treliçadas do pátio. ⚠️ Latão aceita solda de estanho; alumínio não — se quiser treliça soldada, é latão</t>
-        </is>
-      </c>
-      <c r="E41" s="11" t="inlineStr"/>
+          <t>2 usos + 2 reservas</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>F2 (comando) e F3 (auxiliares)</t>
+        </is>
+      </c>
       <c r="F41" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/arame-barra-latao-1-5-2-mm","🔎 arame barra latao 1,5 2 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fusivel-mini-automotivo-2","🔎 fusivel mini automotivo 2")</f>
         <v/>
       </c>
       <c r="G41" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=arame+barra+latao+1%2C5+2+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fusivel+mini+automotivo+2","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H41" s="13" t="inlineStr"/>
@@ -1955,26 +1914,30 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Dobradiça pequena + fecho</t>
+          <t>Terminal olhal M4 amarelo</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>1 jogo</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Tampa de manutenção</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr"/>
+          <t>Aterramento e barramento de 0 V</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="F42" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/dobradica-pequena-fecho","🔎 dobradica pequena fecho")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/terminal-olhal-m4-amarelo","🔎 terminal olhal m4 amarelo")</f>
         <v/>
       </c>
       <c r="G42" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=dobradica+pequena+fecho","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=terminal+olhal+m4+amarelo","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H42" s="8" t="inlineStr"/>
@@ -1985,68 +1948,39 @@
         <v/>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10" t="n">
-        <v>34</v>
-      </c>
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>Tela metálica / alambrado miniatura</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>Cerca do pátio (tela de aço, malha 3 mm). ⚠️ Funcional, não decorativa: com o pátio aberto, é ela que delimita a área e impede aproximação — mesma função da cerca de uma subestação real</t>
-        </is>
-      </c>
-      <c r="E43" s="11" t="inlineStr"/>
-      <c r="F43" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/tela-metalica-alambrado-miniatura","🔎 tela metalica alambrado mini")</f>
-        <v/>
-      </c>
-      <c r="G43" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=tela+metalica+alambrado+miniatura","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H43" s="13" t="inlineStr"/>
-      <c r="I43" s="13" t="inlineStr"/>
-      <c r="J43" s="14" t="inlineStr"/>
-      <c r="K43" s="14">
-        <f>IF(C43*J43=0,"",C43*J43)</f>
-        <v/>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>M.1 — Base e estrutura</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Pedrisco / brita fina (aquário)</t>
+          <t>MDF 12 mm</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>500 g</t>
+          <t>1 chapa</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Piso do pátio da subestação — como nas subestações reais</t>
+          <t>1500 × 500 mm — tampo da base</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr"/>
       <c r="F44" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/pedrisco-brita-fina","🔎 pedrisco brita fina")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/mdf-12-mm","🔎 mdf 12 mm")</f>
         <v/>
       </c>
       <c r="G44" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=pedrisco+brita+fina","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=mdf+12+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H44" s="8" t="inlineStr"/>
@@ -2059,30 +1993,30 @@
     </row>
     <row r="45">
       <c r="A45" s="10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>Placa "PERIGO ALTA TENSÃO"</t>
+          <t>MDF 15 mm</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Impressa em papel adesivo, ~15 × 10 mm</t>
+          <t>Moldura perimetral 40 mm de altura (4 tiras)</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr"/>
       <c r="F45" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/placa-perigo-alta-tensao","🔎 placa perigo alta tensao")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/mdf-15-mm","🔎 mdf 15 mm")</f>
         <v/>
       </c>
       <c r="G45" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=placa+perigo+alta+tensao","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=mdf+15+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H45" s="13" t="inlineStr"/>
@@ -2093,11 +2027,40 @@
         <v/>
       </c>
     </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>M.3 — Postes e linha de distribuição</t>
-        </is>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>MDF 15 mm</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>3 tiras</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Travessas de reforço 15 × 40 mm, com entalhe de 20 × 25 mm no centro</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr"/>
+      <c r="F46" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/mdf-15-mm","🔎 mdf 15 mm")</f>
+        <v/>
+      </c>
+      <c r="G46" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=mdf+15+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H46" s="8" t="inlineStr"/>
+      <c r="I46" s="8" t="inlineStr"/>
+      <c r="J46" s="9" t="inlineStr"/>
+      <c r="K46" s="9">
+        <f>IF(C46*J46=0,"",C46*J46)</f>
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -2106,26 +2069,26 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Tubo de alumínio Ø 8 mm</t>
+          <t>Pés de borracha antiderrapante</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>1,5 m</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Cortar em 3 postes de 350 mm (300 mm visíveis + 50 mm de encaixe)</t>
+          <t>Autoadesivos, Ø 25 mm — a base tem 1,5 m e pesa ~18 kg</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr"/>
       <c r="F47" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/tubo-aluminio-8-mm","🔎 tubo aluminio 8 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/pes-borracha-antiderrapante","🔎 pes borracha antiderrapante")</f>
         <v/>
       </c>
       <c r="G47" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=tubo+aluminio+8+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=pes+borracha+antiderrapante","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H47" s="13" t="inlineStr"/>
@@ -2142,29 +2105,32 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Barra chata de alumínio 12 × 2 mm</t>
+          <t>Conector circular GX16 8 pinos</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>40 cm</t>
+          <t>1 par</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>Cruzetas — 3 peças de 90 mm + 3 de 60 mm</t>
+          <t>Opcional — só na versão modular (união elétrica entre os 2 módulos)</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr"/>
       <c r="F48" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/barra-chata-aluminio-12-2-mm","🔎 barra chata aluminio 12 2 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/conector-circular-gx16-8-pinos","🔎 conector circular gx16 8 pin")</f>
         <v/>
       </c>
       <c r="G48" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=barra+chata+aluminio+12+2+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H48" s="8" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=conector+circular+gx16+8+pinos","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H48" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-gx16-8-pin-aviation-connector.html","🌏 GX16 8 pin aviation connec")</f>
+        <v/>
+      </c>
       <c r="I48" s="8" t="inlineStr"/>
       <c r="J48" s="9" t="inlineStr"/>
       <c r="K48" s="9">
@@ -2178,26 +2144,26 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>Fio rígido ENCAPADO 1,00 mm² VERMELHO ⬆</t>
+          <t>Pinos-guia Ø 6 mm + buchas</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>2 m</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Ramal R1 (potência, 6,0 A). ⚠️ Subiu de 0,75 para 1,00 mm² por causa da corrente das 2 Peltier. Nunca condutor nu — em CC qualquer ponte metálica é curto franco</t>
+          <t>Opcional — alinhamento dos módulos</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr"/>
       <c r="F49" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-rigido-encapado-1-00-mm-vermelho","🔎 fio rigido encapado 1,00 mm ")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/pinos-guia-6-mm-buchas","🔎 pinos guia 6 mm buchas")</f>
         <v/>
       </c>
       <c r="G49" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+rigido+encapado+1%2C00+mm+vermelho","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=pinos+guia+6+mm+buchas","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H49" s="13" t="inlineStr"/>
@@ -2214,26 +2180,26 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Fio rígido ENCAPADO 0,50 mm² MARROM</t>
+          <t>Alças de transporte</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>2 m</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Ramal R2 (comando)</t>
+          <t>Alça embutida de baú/case, laterais</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr"/>
       <c r="F50" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-rigido-encapado-0-50-mm-marrom","🔎 fio rigido encapado 0,50 mm ")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/alcas-transporte","🔎 alcas transporte")</f>
         <v/>
       </c>
       <c r="G50" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+rigido+encapado+0%2C50+mm+marrom","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=alcas+transporte","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H50" s="8" t="inlineStr"/>
@@ -2250,26 +2216,26 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Fio rígido ENCAPADO 0,50 mm² CINZA</t>
+          <t>Parafusos M5×20, M4×16, M3×12</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>2 m</t>
+          <t>kits</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Ramal R3 (auxiliares)</t>
+          <t>Fixações gerais</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr"/>
       <c r="F51" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-rigido-encapado-0-50-mm-cinza","🔎 fio rigido encapado 0,50 mm ")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/parafusos-m5-20-m4-16-m3-12","🔎 parafusos m5 20, m4 16, m3 1")</f>
         <v/>
       </c>
       <c r="G51" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+rigido+encapado+0%2C50+mm+cinza","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=parafusos+m5+20%2C+m4+16%2C+m3+12","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H51" s="13" t="inlineStr"/>
@@ -2286,26 +2252,26 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Fio rígido ENCAPADO 1,50 mm² AZUL CLARO ⬆</t>
+          <t>Insertos rosqueados M4/M5 p/ MDF</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>2 m</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Retorno comum 0 V — o "neutro" da linha, 40 mm abaixo da cruzeta. Subiu de 1,00 para 1,50 mm²: conduz a soma dos 3 ramais (6,9 A)</t>
+          <t>Evita espanar a rosca no MDF</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr"/>
       <c r="F52" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-rigido-encapado-1-50-mm-azul-claro","🔎 fio rigido encapado 1,50 mm ")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/insertos-rosqueados-m4-m5-p-mdf","🔎 insertos rosqueados m4 m5 p ")</f>
         <v/>
       </c>
       <c r="G52" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+rigido+encapado+1%2C50+mm+azul+claro","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=insertos+rosqueados+m4+m5+p+mdf","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H52" s="8" t="inlineStr"/>
@@ -2316,68 +2282,39 @@
         <v/>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="10" t="n">
-        <v>43</v>
-      </c>
-      <c r="B53" s="11" t="inlineStr">
-        <is>
-          <t>Contas/miçangas marrom ou branca Ø 6 mm</t>
-        </is>
-      </c>
-      <c r="C53" s="10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>Isoladores de pino da cruzeta</t>
-        </is>
-      </c>
-      <c r="E53" s="11" t="inlineStr"/>
-      <c r="F53" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/contas-micangas-marrom-branca-6-mm","🔎 contas micangas marrom branc")</f>
-        <v/>
-      </c>
-      <c r="G53" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=contas+micangas+marrom+branca+6+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H53" s="13" t="inlineStr"/>
-      <c r="I53" s="13" t="inlineStr"/>
-      <c r="J53" s="14" t="inlineStr"/>
-      <c r="K53" s="14">
-        <f>IF(C53*J53=0,"",C53*J53)</f>
-        <v/>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>M.2 — Subestação (caixa)</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Tubo de PVC Ø 50 mm</t>
+          <t>MDF 9 mm ou acrílico opaco 4 mm</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>24 cm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Corpos dos 3 postes — 8 cm cada: T2 (P2), T3 (P3) e a caixa de derivação (P1). Agora os três têm o mesmo diâmetro, porque o P1 deixou de ter conversor</t>
+          <t>CASA DE COMANDO 250 × 150 × 90 mm (L×P×A), face de operação voltada para a rua. Abriga apenas fonte, disjuntor e chave — os fusíveis de 24 V ficam no pátio aberto</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr"/>
       <c r="F54" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/tubo-pvc-50-mm","🔎 tubo pvc 50 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/mdf-9-mm-acrilico-opaco-4-mm","🔎 mdf 9 mm acrilico opaco 4 mm")</f>
         <v/>
       </c>
       <c r="G54" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=tubo+pvc+50+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=mdf+9+mm+acrilico+opaco+4+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H54" s="8" t="inlineStr"/>
@@ -2390,30 +2327,30 @@
     </row>
     <row r="55">
       <c r="A55" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>Tampa/cap PVC Ø 50 mm</t>
+          <t>Fio verde-amarelo 0,75 mm²</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1 m</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Tampas dos 3 corpos</t>
+          <t>⚡ Aterramento das estruturas metálicas do pátio à barra de terra (equipotencialização). Torre real é aterrada — vale ponto na defesa</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr"/>
       <c r="F55" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/tampa-cap-pvc-50-mm","🔎 tampa cap pvc 50 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-verde-amarelo-0-75-mm","🔎 fio verde amarelo 0,75 mm")</f>
         <v/>
       </c>
       <c r="G55" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=tampa+cap+pvc+50+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+verde+amarelo+0%2C75+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H55" s="13" t="inlineStr"/>
@@ -2426,30 +2363,30 @@
     </row>
     <row r="56">
       <c r="A56" s="5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Cinta de alumínio 10 mm</t>
+          <t>*Opcional:* arame / barra de latão 1,5–2 mm</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>1 m</t>
+          <t>2 m</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Fixação dos transformadores e da caixa de derivação nos postes</t>
+          <t>Estruturas treliçadas do pátio. ⚠️ Latão aceita solda de estanho; alumínio não — se quiser treliça soldada, é latão</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr"/>
       <c r="F56" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/cinta-aluminio-10-mm","🔎 cinta aluminio 10 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/arame-barra-latao-1-5-2-mm","🔎 arame barra latao 1,5 2 mm")</f>
         <v/>
       </c>
       <c r="G56" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=cinta+aluminio+10+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=arame+barra+latao+1%2C5+2+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H56" s="8" t="inlineStr"/>
@@ -2462,30 +2399,30 @@
     </row>
     <row r="57">
       <c r="A57" s="10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>Bornes de emenda pequenos (2 ou 3 vias)</t>
+          <t>Dobradiça pequena + fecho</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 jogo</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>Dentro da caixa de derivação do P1 — ali os 24 V só se distribuem, não se transformam</t>
+          <t>Tampa de manutenção</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr"/>
       <c r="F57" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/bornes-emenda-pequenos","🔎 bornes emenda pequenos")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/dobradica-pequena-fecho","🔎 dobradica pequena fecho")</f>
         <v/>
       </c>
       <c r="G57" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=bornes+emenda+pequenos","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=dobradica+pequena+fecho","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H57" s="13" t="inlineStr"/>
@@ -2498,30 +2435,30 @@
     </row>
     <row r="58">
       <c r="A58" s="5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Flange/base de fixação dos postes</t>
+          <t>Tela metálica / alambrado miniatura</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>Podem ser feitas com sobra de MDF + insertos M4</t>
+          <t>Cerca do pátio (tela de aço, malha 3 mm). ⚠️ Funcional, não decorativa: com o pátio aberto, é ela que delimita a área e impede aproximação — mesma função da cerca de uma subestação real</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr"/>
       <c r="F58" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/flange-base-fixacao-postes","🔎 flange base fixacao postes")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tela-metalica-alambrado-miniatura","🔎 tela metalica alambrado mini")</f>
         <v/>
       </c>
       <c r="G58" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=flange+base+fixacao+postes","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tela+metalica+alambrado+miniatura","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H58" s="8" t="inlineStr"/>
@@ -2534,30 +2471,30 @@
     </row>
     <row r="59">
       <c r="A59" s="10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>Etiquetas adesivas impressas</t>
+          <t>Pedrisco / brita fina (aquário)</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>500 g</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Identificação dos corpos: "P1 — DERIVAÇÃO 24 V", "T2 — 24/5 V", "T3 — 24/12 V"</t>
+          <t>Piso do pátio da subestação — como nas subestações reais</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr"/>
       <c r="F59" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/etiquetas-adesivas-impressas","🔎 etiquetas adesivas impressas")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/pedrisco-brita-fina","🔎 pedrisco brita fina")</f>
         <v/>
       </c>
       <c r="G59" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=etiquetas+adesivas+impressas","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=pedrisco+brita+fina","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H59" s="13" t="inlineStr"/>
@@ -2568,75 +2505,75 @@
         <v/>
       </c>
     </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>M.4 — Rua e entrada da empresa (zona externa)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="B61" s="11" t="inlineStr">
-        <is>
-          <t>Tinta spray cinza-asfalto escuro fosco</t>
-        </is>
-      </c>
-      <c r="C61" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D61" s="11" t="inlineStr">
-        <is>
-          <t>Pista da rua</t>
-        </is>
-      </c>
-      <c r="E61" s="11" t="inlineStr"/>
-      <c r="F61" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/tinta-spray-cinza-asfalto-escuro-fosco","🔎 tinta spray cinza asfalto es")</f>
-        <v/>
-      </c>
-      <c r="G61" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=tinta+spray+cinza+asfalto+escuro+fosco","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H61" s="13" t="inlineStr"/>
-      <c r="I61" s="13" t="inlineStr"/>
-      <c r="J61" s="14" t="inlineStr"/>
-      <c r="K61" s="14">
-        <f>IF(C61*J61=0,"",C61*J61)</f>
-        <v/>
+    <row r="60">
+      <c r="A60" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>Placa "PERIGO ALTA TENSÃO"</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Impressa em papel adesivo, ~15 × 10 mm</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr"/>
+      <c r="F60" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/placa-perigo-alta-tensao","🔎 placa perigo alta tensao")</f>
+        <v/>
+      </c>
+      <c r="G60" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=placa+perigo+alta+tensao","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H60" s="8" t="inlineStr"/>
+      <c r="I60" s="8" t="inlineStr"/>
+      <c r="J60" s="9" t="inlineStr"/>
+      <c r="K60" s="9">
+        <f>IF(C60*J60=0,"",C60*J60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>M.3 — Postes e linha de distribuição</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Tubo de alumínio Ø 5 mm</t>
+          <t>Tubo de alumínio Ø 8 mm</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>60 cm</t>
+          <t>1,5 m</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>3 postes de iluminação pública de 180 mm — ⚠️ diferentes dos postes de distribuição</t>
+          <t>Cortar em 3 postes de 350 mm (300 mm visíveis + 50 mm de encaixe)</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr"/>
       <c r="F62" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/tubo-aluminio-5-mm","🔎 tubo aluminio 5 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tubo-aluminio-8-mm","🔎 tubo aluminio 8 mm")</f>
         <v/>
       </c>
       <c r="G62" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=tubo+aluminio+5+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tubo+aluminio+8+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H62" s="8" t="inlineStr"/>
@@ -2649,30 +2586,30 @@
     </row>
     <row r="63">
       <c r="A63" s="10" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Arame 1,5 mm</t>
+          <t>Barra chata de alumínio 12 × 2 mm</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>1 m</t>
+          <t>40 cm</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>Braço curvo das luminárias e estrutura do portão</t>
+          <t>Cruzetas — 3 peças de 90 mm + 3 de 60 mm</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr"/>
       <c r="F63" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/arame-1-5-mm","🔎 arame 1,5 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/barra-chata-aluminio-12-2-mm","🔎 barra chata aluminio 12 2 mm")</f>
         <v/>
       </c>
       <c r="G63" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=arame+1%2C5+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=barra+chata+aluminio+12+2+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H63" s="13" t="inlineStr"/>
@@ -2685,36 +2622,33 @@
     </row>
     <row r="64">
       <c r="A64" s="5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>LED 3 mm branco quente</t>
+          <t>Fio rígido ENCAPADO 1,00 mm² VERMELHO ⬆</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2 m</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>3 luminárias da rua + 1 na guarita. Alimentados em 5 V (BD-5V), com 220 Ω em série, sempre acesos. Vf ≈ 3,1 V</t>
+          <t>Ramal R1 (potência, 6,0 A). ⚠️ Subiu de 0,75 para 1,00 mm² por causa da corrente das 2 Peltier. Nunca condutor nu — em CC qualquer ponte metálica é curto franco</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr"/>
       <c r="F64" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/led-3-mm-branco-quente","🔎 led 3 mm branco quente")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-rigido-encapado-1-00-mm-vermelho","🔎 fio rigido encapado 1,00 mm ")</f>
         <v/>
       </c>
       <c r="G64" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=led+3+mm+branco+quente","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H64" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-3mm-warm-white-led.html","🌏 3mm warm white LED")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+rigido+encapado+1%2C00+mm+vermelho","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H64" s="8" t="inlineStr"/>
       <c r="I64" s="8" t="inlineStr"/>
       <c r="J64" s="9" t="inlineStr"/>
       <c r="K64" s="9">
@@ -2724,36 +2658,33 @@
     </row>
     <row r="65">
       <c r="A65" s="10" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>Resistor 220 Ω 1/4 W</t>
+          <t>Fio rígido ENCAPADO 0,50 mm² MARROM</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 m</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>Limitador dos LEDs da rua — já contabilizado na lista L.4, não compre de novo. ⚠️ Valor dimensionado para 5 V: (5 − 3,1)/220 = 8,6 mA. Monte cada um dentro da base do poste, com termorretrátil</t>
+          <t>Ramal R2 (comando)</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr"/>
       <c r="F65" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-220-1-4-w","🔎 resistor 220 1 4 w")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-rigido-encapado-0-50-mm-marrom","🔎 fio rigido encapado 0,50 mm ")</f>
         <v/>
       </c>
       <c r="G65" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+220+1+4+w","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H65" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+rigido+encapado+0%2C50+mm+marrom","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H65" s="13" t="inlineStr"/>
       <c r="I65" s="13" t="inlineStr"/>
       <c r="J65" s="14" t="inlineStr"/>
       <c r="K65" s="14">
@@ -2763,30 +2694,30 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Carro de passeio miniatura 1:50</t>
+          <t>Fio rígido ENCAPADO 0,50 mm² CINZA</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 m</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>~88 mm. Se só achar 1:64 (68 mm), pode usar — mas não misture escalas</t>
+          <t>Ramal R3 (auxiliares)</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr"/>
       <c r="F66" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/carro-passeio-miniatura-1-50","🔎 carro passeio miniatura 1 50")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-rigido-encapado-0-50-mm-cinza","🔎 fio rigido encapado 0,50 mm ")</f>
         <v/>
       </c>
       <c r="G66" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=carro+passeio+miniatura+1+50","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+rigido+encapado+0%2C50+mm+cinza","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H66" s="8" t="inlineStr"/>
@@ -2799,30 +2730,30 @@
     </row>
     <row r="67">
       <c r="A67" s="10" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>Caminhão / van 1:50</t>
+          <t>Fio rígido ENCAPADO 1,50 mm² AZUL CLARO ⬆</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2 m</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>~150 mm, entrando pelo portão</t>
+          <t>Retorno comum 0 V — o "neutro" da linha, 40 mm abaixo da cruzeta. Subiu de 1,00 para 1,50 mm²: conduz a soma dos 3 ramais (6,9 A)</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr"/>
       <c r="F67" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/caminhao-van-1-50","🔎 caminhao van 1 50")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-rigido-encapado-1-50-mm-azul-claro","🔎 fio rigido encapado 1,50 mm ")</f>
         <v/>
       </c>
       <c r="G67" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=caminhao+van+1+50","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+rigido+encapado+1%2C50+mm+azul+claro","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H67" s="13" t="inlineStr"/>
@@ -2835,30 +2766,30 @@
     </row>
     <row r="68">
       <c r="A68" s="5" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Tira de MDF 3 mm</t>
+          <t>Contas/miçangas marrom ou branca Ø 6 mm</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>1,5 m</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>Meio-fio (guia), 4 mm de altura, pintado de branco</t>
+          <t>Isoladores de pino da cruzeta</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr"/>
       <c r="F68" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/tira-mdf-3-mm","🔎 tira mdf 3 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/contas-micangas-marrom-branca-6-mm","🔎 contas micangas marrom branc")</f>
         <v/>
       </c>
       <c r="G68" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=tira+mdf+3+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=contas+micangas+marrom+branca+6+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H68" s="8" t="inlineStr"/>
@@ -2871,30 +2802,30 @@
     </row>
     <row r="69">
       <c r="A69" s="10" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Fita branca 2 mm ou caneta posca branca</t>
+          <t>Tubo de PVC Ø 50 mm</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24 cm</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>Faixa central tracejada, faixa de bordo e faixa de pedestres</t>
+          <t>Corpos dos 3 postes — 8 cm cada: T2 (P2), T3 (P3) e a caixa de derivação (P1). Agora os três têm o mesmo diâmetro, porque o P1 deixou de ter conversor</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr"/>
       <c r="F69" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-branca-2-mm-caneta-posca-branca","🔎 fita branca 2 mm caneta posc")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tubo-pvc-50-mm","🔎 tubo pvc 50 mm")</f>
         <v/>
       </c>
       <c r="G69" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+branca+2+mm+caneta+posca+branca","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tubo+pvc+50+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H69" s="13" t="inlineStr"/>
@@ -2907,30 +2838,30 @@
     </row>
     <row r="70">
       <c r="A70" s="5" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>MDF 4 mm</t>
+          <t>Tampa/cap PVC Ø 50 mm</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Muro da empresa: 50 mm de altura × 290 mm, em X = 640</t>
+          <t>Tampas dos 3 corpos</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr"/>
       <c r="F70" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/mdf-4-mm","🔎 mdf 4 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tampa-cap-pvc-50-mm","🔎 tampa cap pvc 50 mm")</f>
         <v/>
       </c>
       <c r="G70" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=mdf+4+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tampa+cap+pvc+50+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H70" s="8" t="inlineStr"/>
@@ -2943,30 +2874,30 @@
     </row>
     <row r="71">
       <c r="A71" s="10" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>MDF 4 mm</t>
+          <t>Cinta de alumínio 10 mm</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 m</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Guarita 45 × 45 × 55 mm, com janela recortada</t>
+          <t>Fixação dos transformadores e da caixa de derivação nos postes</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr"/>
       <c r="F71" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/mdf-4-mm","🔎 mdf 4 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cinta-aluminio-10-mm","🔎 cinta aluminio 10 mm")</f>
         <v/>
       </c>
       <c r="G71" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=mdf+4+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cinta+aluminio+10+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H71" s="13" t="inlineStr"/>
@@ -2979,30 +2910,30 @@
     </row>
     <row r="72">
       <c r="A72" s="5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Tinta azul industrial</t>
+          <t>Bornes de emenda pequenos (2 ou 3 vias)</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>Portão corrediço</t>
+          <t>Dentro da caixa de derivação do P1 — ali os 24 V só se distribuem, não se transformam</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr"/>
       <c r="F72" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/tinta-azul-industrial","🔎 tinta azul industrial")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/bornes-emenda-pequenos","🔎 bornes emenda pequenos")</f>
         <v/>
       </c>
       <c r="G72" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=tinta+azul+industrial","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=bornes+emenda+pequenos","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H72" s="8" t="inlineStr"/>
@@ -3015,11 +2946,11 @@
     </row>
     <row r="73">
       <c r="A73" s="10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>Árvores de maquete</t>
+          <t>Flange/base de fixação dos postes</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
@@ -3029,16 +2960,16 @@
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>Escala 1:50, na calçada da frente</t>
+          <t>Podem ser feitas com sobra de MDF + insertos M4</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr"/>
       <c r="F73" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/arvores-maquete","🔎 arvores maquete")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/flange-base-fixacao-postes","🔎 flange base fixacao postes")</f>
         <v/>
       </c>
       <c r="G73" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=arvores+maquete","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=flange+base+fixacao+postes","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H73" s="13" t="inlineStr"/>
@@ -3051,30 +2982,30 @@
     </row>
     <row r="74">
       <c r="A74" s="5" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Placas de trânsito miniatura</t>
+          <t>Etiquetas adesivas impressas</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>"PARE" e "VELOCIDADE MÁXIMA 10 km/h"</t>
+          <t>Identificação dos corpos: "P1 — DERIVAÇÃO 24 V", "T2 — 24/5 V", "T3 — 24/12 V"</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr"/>
       <c r="F74" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/placas-transito-miniatura","🔎 placas transito miniatura")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/etiquetas-adesivas-impressas","🔎 etiquetas adesivas impressas")</f>
         <v/>
       </c>
       <c r="G74" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=placas+transito+miniatura","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=etiquetas+adesivas+impressas","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H74" s="8" t="inlineStr"/>
@@ -3085,75 +3016,75 @@
         <v/>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="10" t="n">
-        <v>64</v>
-      </c>
-      <c r="B75" s="11" t="inlineStr">
-        <is>
-          <t>Lixeira urbana + abrigo de ônibus</t>
-        </is>
-      </c>
-      <c r="C75" s="10" t="inlineStr">
-        <is>
-          <t>1 cada</t>
-        </is>
-      </c>
-      <c r="D75" s="11" t="inlineStr">
-        <is>
-          <t>Opcional — enriquece a cena</t>
-        </is>
-      </c>
-      <c r="E75" s="11" t="inlineStr"/>
-      <c r="F75" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/lixeira-urbana-abrigo-onibus","🔎 lixeira urbana abrigo onibus")</f>
-        <v/>
-      </c>
-      <c r="G75" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=lixeira+urbana+abrigo+onibus","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H75" s="13" t="inlineStr"/>
-      <c r="I75" s="13" t="inlineStr"/>
-      <c r="J75" s="14" t="inlineStr"/>
-      <c r="K75" s="14">
-        <f>IF(C75*J75=0,"",C75*J75)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>M.5 — Chão de fábrica (cenografia)</t>
-        </is>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>M.4 — Rua e entrada da empresa (zona externa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>Tinta spray cinza-asfalto escuro fosco</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>Pista da rua</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr"/>
+      <c r="F76" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tinta-spray-cinza-asfalto-escuro-fosco","🔎 tinta spray cinza asfalto es")</f>
+        <v/>
+      </c>
+      <c r="G76" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tinta+spray+cinza+asfalto+escuro+fosco","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H76" s="8" t="inlineStr"/>
+      <c r="I76" s="8" t="inlineStr"/>
+      <c r="J76" s="9" t="inlineStr"/>
+      <c r="K76" s="9">
+        <f>IF(C76*J76=0,"",C76*J76)</f>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>Tinta spray cinza claro fosco</t>
+          <t>Tubo de alumínio Ø 5 mm</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>60 cm</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>Piso industrial (epóxi)</t>
+          <t>3 postes de iluminação pública de 180 mm — ⚠️ diferentes dos postes de distribuição</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr"/>
       <c r="F77" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/tinta-spray-cinza-claro-fosco","🔎 tinta spray cinza claro fosc")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tubo-aluminio-5-mm","🔎 tubo aluminio 5 mm")</f>
         <v/>
       </c>
       <c r="G77" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=tinta+spray+cinza+claro+fosco","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tubo+aluminio+5+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H77" s="13" t="inlineStr"/>
@@ -3166,30 +3097,30 @@
     </row>
     <row r="78">
       <c r="A78" s="5" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Tinta spray preto fosco</t>
+          <t>Arame 1,5 mm</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 m</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>Estruturas e acabamento</t>
+          <t>Braço curvo das luminárias e estrutura do portão</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr"/>
       <c r="F78" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/tinta-spray-preto-fosco","🔎 tinta spray preto fosco")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/arame-1-5-mm","🔎 arame 1,5 mm")</f>
         <v/>
       </c>
       <c r="G78" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=tinta+spray+preto+fosco","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=arame+1%2C5+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H78" s="8" t="inlineStr"/>
@@ -3202,33 +3133,36 @@
     </row>
     <row r="79">
       <c r="A79" s="10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>Verniz fosco spray</t>
+          <t>LED 3 mm branco quente</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>Proteção final do piso pintado</t>
+          <t>3 luminárias da rua + 1 na guarita. Alimentados em 5 V (BD-5V), com 220 Ω em série, sempre acesos. Vf ≈ 3,1 V</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr"/>
       <c r="F79" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/verniz-fosco-spray","🔎 verniz fosco spray")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/led-3-mm-branco-quente","🔎 led 3 mm branco quente")</f>
         <v/>
       </c>
       <c r="G79" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=verniz+fosco+spray","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H79" s="13" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=led+3+mm+branco+quente","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H79" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-3mm-warm-white-led.html","🌏 3mm warm white LED")</f>
+        <v/>
+      </c>
       <c r="I79" s="13" t="inlineStr"/>
       <c r="J79" s="14" t="inlineStr"/>
       <c r="K79" s="14">
@@ -3238,33 +3172,36 @@
     </row>
     <row r="80">
       <c r="A80" s="5" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Fita adesiva amarela 10 mm</t>
+          <t>Resistor 220 Ω 1/4 W</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>1 rolo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>Demarcação de corredores e áreas</t>
+          <t>Limitador dos LEDs da rua — já contabilizado na lista L.4, não compre de novo. ⚠️ Valor dimensionado para 5 V: (5 − 3,1)/220 = 8,6 mA. Monte cada um dentro da base do poste, com termorretrátil</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr"/>
       <c r="F80" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-adesiva-amarela-10-mm","🔎 fita adesiva amarela 10 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-220-1-4-w","🔎 resistor 220 1 4 w")</f>
         <v/>
       </c>
       <c r="G80" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+adesiva+amarela+10+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H80" s="8" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+220+1+4+w","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H80" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
+        <v/>
+      </c>
       <c r="I80" s="8" t="inlineStr"/>
       <c r="J80" s="9" t="inlineStr"/>
       <c r="K80" s="9">
@@ -3274,30 +3211,30 @@
     </row>
     <row r="81">
       <c r="A81" s="10" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>Fita zebrada amarelo/preto 20 mm</t>
+          <t>Carro de passeio miniatura 1:50</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>1 rolo</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>Faixa de segurança em frente ao painel (exigência NR-10 — zona de trabalho)</t>
+          <t>~88 mm. Se só achar 1:64 (68 mm), pode usar — mas não misture escalas</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr"/>
       <c r="F81" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-zebrada-amarelo-preto-20-mm","🔎 fita zebrada amarelo preto 2")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/carro-passeio-miniatura-1-50","🔎 carro passeio miniatura 1 50")</f>
         <v/>
       </c>
       <c r="G81" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+zebrada+amarelo+preto+20+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=carro+passeio+miniatura+1+50","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H81" s="13" t="inlineStr"/>
@@ -3310,30 +3247,30 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>Fita adesiva verde 10 mm</t>
+          <t>Caminhão / van 1:50</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>1 rolo</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>Rota de fuga</t>
+          <t>~150 mm, entrando pelo portão</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr"/>
       <c r="F82" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-adesiva-verde-10-mm","🔎 fita adesiva verde 10 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/caminhao-van-1-50","🔎 caminhao van 1 50")</f>
         <v/>
       </c>
       <c r="G82" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+adesiva+verde+10+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=caminhao+van+1+50","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H82" s="8" t="inlineStr"/>
@@ -3346,30 +3283,30 @@
     </row>
     <row r="83">
       <c r="A83" s="10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>Figuras de maquete escala 1:50</t>
+          <t>Tira de MDF 3 mm</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1,5 m</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>(4 na fábrica, 3 na rua, 3 reservas) Pessoas com EPI (loja de maquetaria/arquitetura)</t>
+          <t>Meio-fio (guia), 4 mm de altura, pintado de branco</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr"/>
       <c r="F83" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/figuras-maquete-escala-1-50","🔎 figuras maquete escala 1 50")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tira-mdf-3-mm","🔎 tira mdf 3 mm")</f>
         <v/>
       </c>
       <c r="G83" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=figuras+maquete+escala+1+50","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tira+mdf+3+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H83" s="13" t="inlineStr"/>
@@ -3382,30 +3319,30 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>Miniaturas: empilhadeira, pallets, tambores</t>
+          <t>Fita branca 2 mm ou caneta posca branca</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>Ambientação do chão de fábrica</t>
+          <t>Faixa central tracejada, faixa de bordo e faixa de pedestres</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr"/>
       <c r="F84" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/miniaturas-empilhadeira-pallets-tambores","🔎 miniaturas empilhadeira, pal")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-branca-2-mm-caneta-posca-branca","🔎 fita branca 2 mm caneta posc")</f>
         <v/>
       </c>
       <c r="G84" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=miniaturas+empilhadeira%2C+pallets%2C+tambores","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+branca+2+mm+caneta+posca+branca","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H84" s="8" t="inlineStr"/>
@@ -3418,30 +3355,30 @@
     </row>
     <row r="85">
       <c r="A85" s="10" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>Extintor miniatura + placa</t>
+          <t>MDF 4 mm</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>Sinalização de segurança</t>
+          <t>Muro da empresa: 50 mm de altura × 290 mm, em X = 640</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr"/>
       <c r="F85" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/extintor-miniatura-placa","🔎 extintor miniatura placa")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/mdf-4-mm","🔎 mdf 4 mm")</f>
         <v/>
       </c>
       <c r="G85" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=extintor+miniatura+placa","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=mdf+4+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H85" s="13" t="inlineStr"/>
@@ -3454,30 +3391,30 @@
     </row>
     <row r="86">
       <c r="A86" s="5" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Placas de sinalização impressas</t>
+          <t>MDF 4 mm</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>1 folha</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>"RISCO ELÉTRICO", "USO OBRIGATÓRIO DE EPI", "SAÍDA" — papel adesivo</t>
+          <t>Guarita 45 × 45 × 55 mm, com janela recortada</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr"/>
       <c r="F86" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/placas-sinalizacao-impressas","🔎 placas sinalizacao impressas")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/mdf-4-mm","🔎 mdf 4 mm")</f>
         <v/>
       </c>
       <c r="G86" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=placas+sinalizacao+impressas","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=mdf+4+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H86" s="8" t="inlineStr"/>
@@ -3490,30 +3427,30 @@
     </row>
     <row r="87">
       <c r="A87" s="10" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>Eletrocalha / perfilado aéreo</t>
+          <t>Tinta azul industrial</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>60 cm</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>Canaleta de acrílico ou perfil U de alumínio — leva os cabos do painel à câmara por cima, como na indústria</t>
+          <t>Portão corrediço</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr"/>
       <c r="F87" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/eletrocalha-perfilado-aereo","🔎 eletrocalha perfilado aereo")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tinta-azul-industrial","🔎 tinta azul industrial")</f>
         <v/>
       </c>
       <c r="G87" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=eletrocalha+perfilado+aereo","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tinta+azul+industrial","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H87" s="13" t="inlineStr"/>
@@ -3526,30 +3463,30 @@
     </row>
     <row r="88">
       <c r="A88" s="5" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Suportes/mãos-francesas da eletrocalha</t>
+          <t>Árvores de maquete</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>Cantoneira de alumínio</t>
+          <t>Escala 1:50, na calçada da frente</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr"/>
       <c r="F88" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/suportes-maos-francesas-eletrocalha","🔎 suportes maos francesas elet")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/arvores-maquete","🔎 arvores maquete")</f>
         <v/>
       </c>
       <c r="G88" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=suportes+maos+francesas+eletrocalha","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=arvores+maquete","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H88" s="8" t="inlineStr"/>
@@ -3562,30 +3499,30 @@
     </row>
     <row r="89">
       <c r="A89" s="10" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>EVA ou MDF 6 mm</t>
+          <t>Placas de trânsito miniatura</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>Bases de máquinas fictícias e plataformas</t>
+          <t>"PARE" e "VELOCIDADE MÁXIMA 10 km/h"</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr"/>
       <c r="F89" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/eva-mdf-6-mm","🔎 eva mdf 6 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/placas-transito-miniatura","🔎 placas transito miniatura")</f>
         <v/>
       </c>
       <c r="G89" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=eva+mdf+6+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=placas+transito+miniatura","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H89" s="13" t="inlineStr"/>
@@ -3596,75 +3533,75 @@
         <v/>
       </c>
     </row>
-    <row r="90" ht="22" customHeight="1">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>C.2 — Isolamento térmico</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="10" t="n">
-        <v>78</v>
-      </c>
-      <c r="B91" s="11" t="inlineStr">
-        <is>
-          <t>⭐ Fita adesiva de alumínio 50 mm</t>
-        </is>
-      </c>
-      <c r="C91" s="10" t="inlineStr">
-        <is>
-          <t>3 rolos</t>
-        </is>
-      </c>
-      <c r="D91" s="11" t="inlineStr">
-        <is>
-          <t>🔧 Virou o isolamento E a superfície externa da câmara. Reveste toda a caixa por fora e sela todas as juntas coladas do acrílico. Com ε ≈ 0,05 ela mais que dobra a resistência de superfície (0,13 → 0,31 m²·K/W). ⚠️ Barreira de vapor é a função mais importante dela — quanto menos vapor entra, mais a sílica dura e menos gelo se forma</t>
-        </is>
-      </c>
-      <c r="E91" s="11" t="inlineStr"/>
-      <c r="F91" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-adesiva-aluminio-50-mm","🔎 fita adesiva aluminio 50 mm")</f>
-        <v/>
-      </c>
-      <c r="G91" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+adesiva+aluminio+50+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H91" s="13" t="inlineStr"/>
-      <c r="I91" s="13" t="inlineStr"/>
-      <c r="J91" s="14" t="inlineStr"/>
-      <c r="K91" s="14">
-        <f>IF(C91*J91=0,"",C91*J91)</f>
-        <v/>
+    <row r="90">
+      <c r="A90" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>Lixeira urbana + abrigo de ônibus</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>1 cada</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>Opcional — enriquece a cena</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr"/>
+      <c r="F90" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/lixeira-urbana-abrigo-onibus","🔎 lixeira urbana abrigo onibus")</f>
+        <v/>
+      </c>
+      <c r="G90" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=lixeira+urbana+abrigo+onibus","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H90" s="8" t="inlineStr"/>
+      <c r="I90" s="8" t="inlineStr"/>
+      <c r="J90" s="9" t="inlineStr"/>
+      <c r="K90" s="9">
+        <f>IF(C90*J90=0,"",C90*J90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>M.5 — Chão de fábrica (cenografia)</t>
+        </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>Manta elastomérica autoadesiva 6 mm</t>
+          <t>Tinta spray cinza claro fosco</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>1 m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>Tipo Armaflex — cantos, arestas e ao redor das passagens de cabo</t>
+          <t>Piso industrial (epóxi)</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr"/>
       <c r="F92" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/manta-elastomerica-autoadesiva-6-mm","🔎 manta elastomerica autoadesi")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tinta-spray-cinza-claro-fosco","🔎 tinta spray cinza claro fosc")</f>
         <v/>
       </c>
       <c r="G92" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=manta+elastomerica+autoadesiva+6+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tinta+spray+cinza+claro+fosco","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H92" s="8" t="inlineStr"/>
@@ -3677,11 +3614,11 @@
     </row>
     <row r="93">
       <c r="A93" s="10" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>Espuma expansiva PU (mini)</t>
+          <t>Tinta spray preto fosco</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
@@ -3691,16 +3628,16 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>Selagem das passagens de cabo</t>
+          <t>Estruturas e acabamento</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr"/>
       <c r="F93" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/espuma-expansiva-pu","🔎 espuma expansiva pu")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tinta-spray-preto-fosco","🔎 tinta spray preto fosco")</f>
         <v/>
       </c>
       <c r="G93" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=espuma+expansiva+pu","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tinta+spray+preto+fosco","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H93" s="13" t="inlineStr"/>
@@ -3711,11 +3648,40 @@
         <v/>
       </c>
     </row>
-    <row r="94" ht="22" customHeight="1">
-      <c r="A94" s="4" t="inlineStr">
-        <is>
-          <t>C.3 — Vedação, porta e condensado</t>
-        </is>
+    <row r="94">
+      <c r="A94" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>Verniz fosco spray</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>Proteção final do piso pintado</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr"/>
+      <c r="F94" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/verniz-fosco-spray","🔎 verniz fosco spray")</f>
+        <v/>
+      </c>
+      <c r="G94" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=verniz+fosco+spray","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H94" s="8" t="inlineStr"/>
+      <c r="I94" s="8" t="inlineStr"/>
+      <c r="J94" s="9" t="inlineStr"/>
+      <c r="K94" s="9">
+        <f>IF(C94*J94=0,"",C94*J94)</f>
+        <v/>
       </c>
     </row>
     <row r="95">
@@ -3724,26 +3690,26 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>Perfil EPDM tubular autoadesivo 9 × 6 mm</t>
+          <t>Fita adesiva amarela 10 mm</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>2 m</t>
+          <t>1 rolo</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>Vedação da porta — perfil tubular comprime muito melhor que o chato de 5 mm</t>
+          <t>Demarcação de corredores e áreas</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr"/>
       <c r="F95" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/perfil-epdm-tubular-autoadesivo-9-6-mm","🔎 perfil epdm tubular autoades")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-adesiva-amarela-10-mm","🔎 fita adesiva amarela 10 mm")</f>
         <v/>
       </c>
       <c r="G95" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=perfil+epdm+tubular+autoadesivo+9+6+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+adesiva+amarela+10+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H95" s="13" t="inlineStr"/>
@@ -3760,26 +3726,26 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>Dobradiça piano de alumínio</t>
+          <t>Fita zebrada amarelo/preto 20 mm</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 rolo</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>250 mm (cortar de uma barra de 75 cm)</t>
+          <t>Faixa de segurança em frente ao painel (exigência NR-10 — zona de trabalho)</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr"/>
       <c r="F96" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/dobradica-piano-aluminio","🔎 dobradica piano aluminio")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-zebrada-amarelo-preto-20-mm","🔎 fita zebrada amarelo preto 2")</f>
         <v/>
       </c>
       <c r="G96" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=dobradica+piano+aluminio","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+zebrada+amarelo+preto+20+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H96" s="8" t="inlineStr"/>
@@ -3796,26 +3762,26 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>Fecho de pressão (borboleta) inox</t>
+          <t>Fita adesiva verde 10 mm</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 rolo</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>Comprime a vedação — tipo fecho de baú</t>
+          <t>Rota de fuga</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr"/>
       <c r="F97" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fecho-pressao-inox","🔎 fecho pressao inox")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-adesiva-verde-10-mm","🔎 fita adesiva verde 10 mm")</f>
         <v/>
       </c>
       <c r="G97" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fecho+pressao+inox","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+adesiva+verde+10+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H97" s="13" t="inlineStr"/>
@@ -3832,26 +3798,26 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>Puxador de câmara fria (miniatura)</t>
+          <t>Figuras de maquete escala 1:50</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>Estética — pode ser um puxador de móvel pequeno</t>
+          <t>(4 na fábrica, 3 na rua, 3 reservas) Pessoas com EPI (loja de maquetaria/arquitetura)</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr"/>
       <c r="F98" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/puxador-camara-fria","🔎 puxador camara fria")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/figuras-maquete-escala-1-50","🔎 figuras maquete escala 1 50")</f>
         <v/>
       </c>
       <c r="G98" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=puxador+camara+fria","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=figuras+maquete+escala+1+50","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H98" s="8" t="inlineStr"/>
@@ -3868,26 +3834,26 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>Cola S-320 Sinteglas</t>
+          <t>Miniaturas: empilhadeira, pallets, tambores</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>250 ml</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>Colagem de acrílico por capilaridade</t>
+          <t>Ambientação do chão de fábrica</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr"/>
       <c r="F99" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/cola-s-320-sinteglas","🔎 cola s 320 sinteglas")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/miniaturas-empilhadeira-pallets-tambores","🔎 miniaturas empilhadeira, pal")</f>
         <v/>
       </c>
       <c r="G99" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=cola+s+320+sinteglas","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=miniaturas+empilhadeira%2C+pallets%2C+tambores","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H99" s="13" t="inlineStr"/>
@@ -3904,26 +3870,26 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>Silicone neutro transparente</t>
+          <t>Extintor miniatura + placa</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>1 tubo</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>Vedação de juntas (⚠️ neutro, o acético ataca o acrílico)</t>
+          <t>Sinalização de segurança</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr"/>
       <c r="F100" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/silicone-neutro-transparente","🔎 silicone neutro transparente")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/extintor-miniatura-placa","🔎 extintor miniatura placa")</f>
         <v/>
       </c>
       <c r="G100" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=silicone+neutro+transparente","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=extintor+miniatura+placa","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H100" s="8" t="inlineStr"/>
@@ -3940,26 +3906,26 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>⭐ Bandeja de alumínio REMOVÍVEL</t>
+          <t>Placas de sinalização impressas</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 folha</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>~190 × 90 mm, sem furo — desliza para fora para esvaziar. 🔧 Era fixa e inclinada, com dreno</t>
+          <t>"RISCO ELÉTRICO", "USO OBRIGATÓRIO DE EPI", "SAÍDA" — papel adesivo</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr"/>
       <c r="F101" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/bandeja-aluminio-removivel","🔎 bandeja aluminio removivel")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/placas-sinalizacao-impressas","🔎 placas sinalizacao impressas")</f>
         <v/>
       </c>
       <c r="G101" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=bandeja+aluminio+removivel","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=placas+sinalizacao+impressas","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H101" s="13" t="inlineStr"/>
@@ -3976,26 +3942,26 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>⭐ Tubo de silicone Ø 4 mm</t>
+          <t>Eletrocalha / perfilado aéreo</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>40 cm</t>
+          <t>60 cm</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>RESPIRO, enrolado em espiral dentro da câmara. ⚠️ Não é opcional: resfriar de 25 para 5 °C contrai o ar 6,7 % e, numa câmara bem vedada, isso dá 34 kgf puxando a porta para dentro. O caminho longo e estreito equaliza a pressão e quase não deixa vapor passar</t>
+          <t>Canaleta de acrílico ou perfil U de alumínio — leva os cabos do painel à câmara por cima, como na indústria</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr"/>
       <c r="F102" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/tubo-silicone-4-mm","🔎 tubo silicone 4 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/eletrocalha-perfilado-aereo","🔎 eletrocalha perfilado aereo")</f>
         <v/>
       </c>
       <c r="G102" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=tubo+silicone+4+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=eletrocalha+perfilado+aereo","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H102" s="8" t="inlineStr"/>
@@ -4012,26 +3978,26 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>⭐ Sílica gel indicadora</t>
+          <t>Suportes/mãos-francesas da eletrocalha</t>
         </is>
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>4 sachês</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>3 na câmara + 1 dentro da câmara de ar da porta dupla. Azul → rosa = trocar. Regenera no forno a 120 °C por 2 h</t>
+          <t>Cantoneira de alumínio</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr"/>
       <c r="F103" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/silica-gel-indicadora","🔎 silica gel indicadora")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/suportes-maos-francesas-eletrocalha","🔎 suportes maos francesas elet")</f>
         <v/>
       </c>
       <c r="G103" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=silica+gel+indicadora","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=suportes+maos+francesas+eletrocalha","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H103" s="13" t="inlineStr"/>
@@ -4042,47 +4008,47 @@
         <v/>
       </c>
     </row>
-    <row r="104" ht="22" customHeight="1">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t>⚡ CAMADA 2 — PAINEL DE COMANDO</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="10" t="n">
+    <row r="104">
+      <c r="A104" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="B105" s="11" t="inlineStr">
-        <is>
-          <t>Caixa de comando ou MDF</t>
-        </is>
-      </c>
-      <c r="C105" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D105" s="11" t="inlineStr">
-        <is>
-          <t>500 x 500 x 200 mm — dimensao exigida pelo layout React</t>
-        </is>
-      </c>
-      <c r="E105" s="11" t="inlineStr"/>
-      <c r="F105" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/caixa-comando-mdf","🔎 caixa comando mdf")</f>
-        <v/>
-      </c>
-      <c r="G105" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=caixa+comando+mdf","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H105" s="13" t="inlineStr"/>
-      <c r="I105" s="13" t="inlineStr"/>
-      <c r="J105" s="14" t="inlineStr"/>
-      <c r="K105" s="14">
-        <f>IF(C105*J105=0,"",C105*J105)</f>
-        <v/>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>EVA ou MDF 6 mm</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>Bases de máquinas fictícias e plataformas</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr"/>
+      <c r="F104" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/eva-mdf-6-mm","🔎 eva mdf 6 mm")</f>
+        <v/>
+      </c>
+      <c r="G104" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=eva+mdf+6+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H104" s="8" t="inlineStr"/>
+      <c r="I104" s="8" t="inlineStr"/>
+      <c r="J104" s="9" t="inlineStr"/>
+      <c r="K104" s="9">
+        <f>IF(C104*J104=0,"",C104*J104)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105" ht="22" customHeight="1">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>C.2 — Isolamento térmico</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -4091,26 +4057,26 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>Porta do painel</t>
+          <t>⭐ Fita adesiva de alumínio 50 mm</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3 rolos</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>MDF 12 mm ou acrílico fumê 5 mm (fica bonito ver os LEDs)</t>
+          <t>🔧 Virou o isolamento E a superfície externa da câmara. Reveste toda a caixa por fora e sela todas as juntas coladas do acrílico. Com ε ≈ 0,05 ela mais que dobra a resistência de superfície (0,13 → 0,31 m²·K/W). ⚠️ Barreira de vapor é a função mais importante dela — quanto menos vapor entra, mais a sílica dura e menos gelo se forma</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr"/>
       <c r="F106" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/porta-painel","🔎 porta painel")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fita-adesiva-aluminio-50-mm","🔎 fita adesiva aluminio 50 mm")</f>
         <v/>
       </c>
       <c r="G106" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=porta+painel","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fita+adesiva+aluminio+50+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H106" s="8" t="inlineStr"/>
@@ -4127,26 +4093,26 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>Trilho DIN 35 mm</t>
+          <t>Manta elastomérica autoadesiva 6 mm</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>1,5 m</t>
+          <t>1 m²</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>Aço galvanizado — 3 trilhos de ~360 mm</t>
+          <t>Tipo Armaflex — cantos, arestas e ao redor das passagens de cabo</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr"/>
       <c r="F107" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/trilho-din-35-mm","🔎 trilho din 35 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/manta-elastomerica-autoadesiva-6-mm","🔎 manta elastomerica autoadesi")</f>
         <v/>
       </c>
       <c r="G107" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=trilho+din+35+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=manta+elastomerica+autoadesiva+6+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H107" s="13" t="inlineStr"/>
@@ -4163,26 +4129,26 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>Canaleta perfurada 30 × 30 mm</t>
+          <t>Espuma expansiva PU (mini)</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>3 m</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>Com tampa. Placa de montagem: 4 horizontais + 2 verticais ≈ 2,8 m</t>
+          <t>Selagem das passagens de cabo</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr"/>
       <c r="F108" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/canaleta-perfurada-30-30-mm","🔎 canaleta perfurada 30 30 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/espuma-expansiva-pu","🔎 espuma expansiva pu")</f>
         <v/>
       </c>
       <c r="G108" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=canaleta+perfurada+30+30+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=espuma+expansiva+pu","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H108" s="8" t="inlineStr"/>
@@ -4193,68 +4159,39 @@
         <v/>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="10" t="n">
-        <v>94</v>
-      </c>
-      <c r="B109" s="11" t="inlineStr">
-        <is>
-          <t>⭐ Canaleta perfurada 25 × 25 mm</t>
-        </is>
-      </c>
-      <c r="C109" s="10" t="inlineStr">
-        <is>
-          <t>2 m</t>
-        </is>
-      </c>
-      <c r="D109" s="11" t="inlineStr">
-        <is>
-          <t>PORTA — 5 horizontais + 1 vertical na dobradiça ≈ 1,5 m. Mais estreita que a da placa porque a porta tem menos fio e não pode ficar pesada</t>
-        </is>
-      </c>
-      <c r="E109" s="11" t="inlineStr"/>
-      <c r="F109" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/canaleta-perfurada-25-25-mm","🔎 canaleta perfurada 25 25 mm")</f>
-        <v/>
-      </c>
-      <c r="G109" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=canaleta+perfurada+25+25+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H109" s="13" t="inlineStr"/>
-      <c r="I109" s="13" t="inlineStr"/>
-      <c r="J109" s="14" t="inlineStr"/>
-      <c r="K109" s="14">
-        <f>IF(C109*J109=0,"",C109*J109)</f>
-        <v/>
+    <row r="109" ht="22" customHeight="1">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>C.3 — Vedação, porta e condensado</t>
+        </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>⭐ Espiral organizador Ø 12 mm</t>
+          <t>Perfil EPDM tubular autoadesivo 9 × 6 mm</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>40 cm</t>
+          <t>2 m</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>A passagem flexível entre a placa e a porta. Protege o chicote nos ciclos de abertura</t>
+          <t>Vedação da porta — perfil tubular comprime muito melhor que o chato de 5 mm</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr"/>
       <c r="F110" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/espiral-organizador-12-mm","🔎 espiral organizador 12 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/perfil-epdm-tubular-autoadesivo-9-6-mm","🔎 perfil epdm tubular autoades")</f>
         <v/>
       </c>
       <c r="G110" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=espiral+organizador+12+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=perfil+epdm+tubular+autoadesivo+9+6+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H110" s="8" t="inlineStr"/>
@@ -4267,11 +4204,11 @@
     </row>
     <row r="111">
       <c r="A111" s="10" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>Bloco de distribuição DIN — 1 entrada 4 mm² + 4 saídas</t>
+          <t>Dobradiça piano de alumínio</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
@@ -4281,16 +4218,16 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>BD-POT — 24 V de potência comutados pelo KA2 → BTS #1, BTS #2, medição do D25 e 1 reserva. ⚠️ Cai com a emergência</t>
+          <t>250 mm (cortar de uma barra de 75 cm)</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr"/>
       <c r="F111" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/bloco-distribuicao-din","🔎 bloco distribuicao din")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/dobradica-piano-aluminio","🔎 dobradica piano aluminio")</f>
         <v/>
       </c>
       <c r="G111" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=bloco+distribuicao+din","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=dobradica+piano+aluminio","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H111" s="13" t="inlineStr"/>
@@ -4303,30 +4240,30 @@
     </row>
     <row r="112">
       <c r="A112" s="5" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>Bloco de distribuição DIN — 1 entrada 2,5 mm² + 4 saídas</t>
+          <t>Fecho de pressão (borboleta) inox</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>BD-AUX — 12 V auxiliar (do T3): cooler dos BTS + 2 coolers das Peltier + 1 reserva</t>
+          <t>Comprime a vedação — tipo fecho de baú</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr"/>
       <c r="F112" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/bloco-distribuicao-din","🔎 bloco distribuicao din")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/fecho-pressao-inox","🔎 fecho pressao inox")</f>
         <v/>
       </c>
       <c r="G112" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=bloco+distribuicao+din","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=fecho+pressao+inox","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H112" s="8" t="inlineStr"/>
@@ -4339,11 +4276,11 @@
     </row>
     <row r="113">
       <c r="A113" s="10" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>Bloco de distribuição DIN — 1 entrada 2,5 mm² + 6 saídas ⬆</t>
+          <t>Puxador de câmara fria (miniatura)</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
@@ -4353,16 +4290,16 @@
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>BD-24V — 24 V permanentes. ⚠️ Subiu de 4 para 6: são 5 cargas (DNLCB30/ESP32, cadeia de comando, positivo comum dos sinaleiros, COM do ULN2803 na PI-1, e a alimentação das 2 posições de ensaio) + 1 reserva. Não confundir com o BD-POT — este não cai com a emergência</t>
+          <t>Estética — pode ser um puxador de móvel pequeno</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr"/>
       <c r="F113" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/bloco-distribuicao-din","🔎 bloco distribuicao din")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/puxador-camara-fria","🔎 puxador camara fria")</f>
         <v/>
       </c>
       <c r="G113" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=bloco+distribuicao+din","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=puxador+camara+fria","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H113" s="13" t="inlineStr"/>
@@ -4375,30 +4312,30 @@
     </row>
     <row r="114">
       <c r="A114" s="5" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>Bloco de distribuição DIN — 1 entrada 2,5 mm² + 8 saídas ⬆</t>
+          <t>Cola S-320 Sinteglas</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>250 ml</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>BD-5V — ⚠️ Subiu de 6 para 8: são 7 cargas (Arduino, tela ES3C28P, RTC, lógica do BTS #1, lógica do BTS #2, placa PI-1 e os LEDs da maquete) + 1 reserva</t>
+          <t>Colagem de acrílico por capilaridade</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr"/>
       <c r="F114" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/bloco-distribuicao-din","🔎 bloco distribuicao din")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cola-s-320-sinteglas","🔎 cola s 320 sinteglas")</f>
         <v/>
       </c>
       <c r="G114" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=bloco+distribuicao+din","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cola+s+320+sinteglas","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H114" s="8" t="inlineStr"/>
@@ -4411,30 +4348,30 @@
     </row>
     <row r="115">
       <c r="A115" s="10" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>⭐ Barra de distribuição / régua com pente — mín. 20 pontos ⬆⬆</t>
+          <t>Silicone neutro transparente</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 tubo</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>BD-0V — o star ground do projeto. ⚠️ Um bloco de 8 saídas NÃO serve: aqui convergem 4 entradas + ~16 retornos. Use uma barra de neutro/terra de 16–20 furos em suporte DIN, ou dois blocos de 1×8 interligados por ponte de 4 mm². Entrada de 10 mm²</t>
+          <t>Vedação de juntas (⚠️ neutro, o acético ataca o acrílico)</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr"/>
       <c r="F115" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/barra-distribuicao-regua-pente","🔎 barra distribuicao regua pen")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/silicone-neutro-transparente","🔎 silicone neutro transparente")</f>
         <v/>
       </c>
       <c r="G115" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=barra+distribuicao+regua+pente","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=silicone+neutro+transparente","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H115" s="13" t="inlineStr"/>
@@ -4445,11 +4382,40 @@
         <v/>
       </c>
     </row>
-    <row r="116" ht="22" customHeight="1">
-      <c r="A116" s="4" t="inlineStr">
-        <is>
-          <t>L.1 — Controle e interface</t>
-        </is>
+    <row r="116">
+      <c r="A116" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>⭐ Bandeja de alumínio REMOVÍVEL</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>~190 × 90 mm, sem furo — desliza para fora para esvaziar. 🔧 Era fixa e inclinada, com dreno</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr"/>
+      <c r="F116" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/bandeja-aluminio-removivel","🔎 bandeja aluminio removivel")</f>
+        <v/>
+      </c>
+      <c r="G116" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=bandeja+aluminio+removivel","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H116" s="8" t="inlineStr"/>
+      <c r="I116" s="8" t="inlineStr"/>
+      <c r="J116" s="9" t="inlineStr"/>
+      <c r="K116" s="9">
+        <f>IF(C116*J116=0,"",C116*J116)</f>
+        <v/>
       </c>
     </row>
     <row r="117">
@@ -4458,32 +4424,29 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>Arduino Mega 2560 R3</t>
+          <t>⭐ Tubo de silicone Ø 4 mm</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40 cm</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>1 controlador em uso; reserva opcional</t>
+          <t>RESPIRO, enrolado em espiral dentro da câmara. ⚠️ Não é opcional: resfriar de 25 para 5 °C contrai o ar 6,7 % e, numa câmara bem vedada, isso dá 34 kgf puxando a porta para dentro. O caminho longo e estreito equaliza a pressão e quase não deixa vapor passar</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr"/>
       <c r="F117" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/arduino-mega-2560-r3","🔎 arduino mega 2560 r3")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/tubo-silicone-4-mm","🔎 tubo silicone 4 mm")</f>
         <v/>
       </c>
       <c r="G117" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=arduino+mega+2560+r3","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H117" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-arduino-mega-2560-r3.html","🌏 Arduino Mega 2560 R3")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=tubo+silicone+4+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H117" s="13" t="inlineStr"/>
       <c r="I117" s="13" t="inlineStr"/>
       <c r="J117" s="14" t="inlineStr"/>
       <c r="K117" s="14">
@@ -4497,26 +4460,26 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Shield de expansão Mega (bornes parafuso)</t>
+          <t>⭐ Sílica gel indicadora</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4 sachês</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>Sensor Shield V2.0</t>
+          <t>3 na câmara + 1 dentro da câmara de ar da porta dupla. Azul → rosa = trocar. Regenera no forno a 120 °C por 2 h</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr"/>
       <c r="F118" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/shield-expansao-mega","🔎 shield expansao mega")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/silica-gel-indicadora","🔎 silica gel indicadora")</f>
         <v/>
       </c>
       <c r="G118" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=shield+expansao+mega","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=silica+gel+indicadora","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H118" s="8" t="inlineStr"/>
@@ -4527,49 +4490,20 @@
         <v/>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="10" t="n">
-        <v>103</v>
-      </c>
-      <c r="B119" s="11" t="inlineStr">
-        <is>
-          <t>Suporte DIN para Arduino Mega</t>
-        </is>
-      </c>
-      <c r="C119" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D119" s="11" t="inlineStr">
-        <is>
-          <t>Ou SPCI4/adaptador</t>
-        </is>
-      </c>
-      <c r="E119" s="11" t="inlineStr"/>
-      <c r="F119" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/suporte-din-arduino-mega","🔎 suporte din arduino mega")</f>
-        <v/>
-      </c>
-      <c r="G119" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=suporte+din+arduino+mega","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H119" s="13" t="inlineStr"/>
-      <c r="I119" s="13" t="inlineStr"/>
-      <c r="J119" s="14" t="inlineStr"/>
-      <c r="K119" s="14">
-        <f>IF(C119*J119=0,"",C119*J119)</f>
-        <v/>
+    <row r="119" ht="22" customHeight="1">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>⚡ CAMADA 2 — PAINEL DE COMANDO</t>
+        </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>⭐ ES3C28P — ESP32-S3 2,8" toque capacitivo, microSD, microfone (LCDWIKI)</t>
+          <t>Caixa de comando ou MDF</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
@@ -4579,16 +4513,16 @@
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>A IHM do projeto. Substitui a tela Nextion e o módulo de cartão SD. 8 MB de PSRAM → a Xiaozhi roda. ILI9341V 240×320, toque capacitivo FT6336G, 5 V / 140 mA, −30 a 80 °C. Vem com alto-falante. ⚠️ Comprar a versão ES3C28P (com toque) — a ES3N28P é sem toque</t>
+          <t>500 x 500 x 200 mm — dimensao exigida pelo layout React</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr"/>
       <c r="F120" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/es3c28p-esp32-s3-2-8-toque-capacitivo-microsd","🔎 es3c28p esp32 s3 2,8 toque c")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/caixa-comando-mdf","🔎 caixa comando mdf")</f>
         <v/>
       </c>
       <c r="G120" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=es3c28p+esp32+s3+2%2C8+toque+capacitivo%2C+microsd%2C","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=caixa+comando+mdf","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H120" s="8" t="inlineStr"/>
@@ -4599,11 +4533,40 @@
         <v/>
       </c>
     </row>
-    <row r="121" ht="22" customHeight="1">
-      <c r="A121" s="4" t="inlineStr">
-        <is>
-          <t>L.2 — Potência e acionamento</t>
-        </is>
+    <row r="121">
+      <c r="A121" s="10" t="n">
+        <v>104</v>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>Porta do painel</t>
+        </is>
+      </c>
+      <c r="C121" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>MDF 12 mm ou acrílico fumê 5 mm (fica bonito ver os LEDs)</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr"/>
+      <c r="F121" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/porta-painel","🔎 porta painel")</f>
+        <v/>
+      </c>
+      <c r="G121" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=porta+painel","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H121" s="13" t="inlineStr"/>
+      <c r="I121" s="13" t="inlineStr"/>
+      <c r="J121" s="14" t="inlineStr"/>
+      <c r="K121" s="14">
+        <f>IF(C121*J121=0,"",C121*J121)</f>
+        <v/>
       </c>
     </row>
     <row r="122">
@@ -4612,32 +4575,29 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>Driver ponte-H BTS7960</t>
+          <t>Trilho DIN 35 mm</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1,5 m</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>43 A, pino IS de diagnóstico</t>
+          <t>Aço galvanizado — 3 trilhos de ~360 mm</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr"/>
       <c r="F122" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/driver-ponte-h-bts7960","🔎 driver ponte h bts7960")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/trilho-din-35-mm","🔎 trilho din 35 mm")</f>
         <v/>
       </c>
       <c r="G122" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=driver+ponte+h+bts7960","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H122" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-bts7960-43a-motor-driver-module.html","🌏 BTS7960 43A motor driver m")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=trilho+din+35+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H122" s="8" t="inlineStr"/>
       <c r="I122" s="8" t="inlineStr"/>
       <c r="J122" s="9" t="inlineStr"/>
       <c r="K122" s="9">
@@ -4651,26 +4611,26 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>Suporte SPCI4 trilho DIN</t>
+          <t>Canaleta perfurada 30 × 30 mm</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3 m</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>Fixa PCI 100 × 79 mm</t>
+          <t>Com tampa. Placa de montagem: 4 horizontais + 2 verticais ≈ 2,8 m</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr"/>
       <c r="F123" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/suporte-spci4-trilho-din","🔎 suporte spci4 trilho din")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/canaleta-perfurada-30-30-mm","🔎 canaleta perfurada 30 30 mm")</f>
         <v/>
       </c>
       <c r="G123" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=suporte+spci4+trilho+din","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=canaleta+perfurada+30+30+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H123" s="13" t="inlineStr"/>
@@ -4687,32 +4647,29 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>Cooler 40 mm 12 V</t>
+          <t>⭐ Canaleta perfurada 25 × 25 mm</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2 m</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>Refrigeração dos BTS</t>
+          <t>PORTA — 5 horizontais + 1 vertical na dobradiça ≈ 1,5 m. Mais estreita que a da placa porque a porta tem menos fio e não pode ficar pesada</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr"/>
       <c r="F124" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/cooler-40-mm-12-v","🔎 cooler 40 mm 12 v")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/canaleta-perfurada-25-25-mm","🔎 canaleta perfurada 25 25 mm")</f>
         <v/>
       </c>
       <c r="G124" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=cooler+40+mm+12+v","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H124" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-40mm-fan-12v-dc.html","🌏 40mm fan 12V DC")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=canaleta+perfurada+25+25+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H124" s="8" t="inlineStr"/>
       <c r="I124" s="8" t="inlineStr"/>
       <c r="J124" s="9" t="inlineStr"/>
       <c r="K124" s="9">
@@ -4726,32 +4683,29 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>KA1 e KA2 — Relé 8 pinos 24 Vcc + base DIN</t>
+          <t>⭐ Espiral organizador Ø 12 mm</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40 cm</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>2 conjuntos em uso; 24 Vcc, 2 contatos reversiveis, KA2 com 10 A em CC</t>
+          <t>A passagem flexível entre a placa e a porta. Protege o chicote nos ciclos de abertura</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr"/>
       <c r="F125" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/ka1-ka2","🔎 ka1 ka2")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/espiral-organizador-12-mm","🔎 espiral organizador 12 mm")</f>
         <v/>
       </c>
       <c r="G125" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=ka1+ka2","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H125" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-jqx-13f-ly2n-24vdc-relay-8-pin-2co-with-socket.html","🌏 JQX-13F LY2N 24VDC relay 8")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=espiral+organizador+12+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H125" s="13" t="inlineStr"/>
       <c r="I125" s="13" t="inlineStr"/>
       <c r="J125" s="14" t="inlineStr"/>
       <c r="K125" s="14">
@@ -4765,26 +4719,26 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>*Alternativa premium (só se sobrar orçamento)*</t>
+          <t>Bloco de distribuição DIN — 1 entrada 4 mm² + 4 saídas</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>Finder 46.61 24VDC (1 reversível 16 A) + base 95.05 para o KA2, ~R$ 80–110. Vale se você quiser folga grande sobre os 6,0 A e datasheet publicado</t>
+          <t>BD-POT — 24 V de potência comutados pelo KM1 → BTS #1, BTS #2, medição do D25 e 1 reserva. ⚠️ Cai com a emergência</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr"/>
       <c r="F126" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/alternativa-premium","🔎 alternativa premium")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/bloco-distribuicao-din","🔎 bloco distribuicao din")</f>
         <v/>
       </c>
       <c r="G126" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=alternativa+premium","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=bloco+distribuicao+din","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H126" s="8" t="inlineStr"/>
@@ -4801,32 +4755,29 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>Resistor 10 kΩ 1/4 W</t>
+          <t>Bloco de distribuição DIN — 1 entrada 2,5 mm² + 4 saídas</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>Pull-down em cada R_EN dos BTS7960 (2) + reservas. ⚠️ Garante que pino solto = driver desligado — ficou ainda mais crítico com os 24 V permanentes na entrada dos BTS</t>
+          <t>BD-AUX — 12 V auxiliar (do T3): cooler dos BTS + 2 coolers das Peltier + 1 reserva</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr"/>
       <c r="F127" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-10-k-1-4-w","🔎 resistor 10 k 1 4 w")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/bloco-distribuicao-din","🔎 bloco distribuicao din")</f>
         <v/>
       </c>
       <c r="G127" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+10+k+1+4+w","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H127" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=bloco+distribuicao+din","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H127" s="13" t="inlineStr"/>
       <c r="I127" s="13" t="inlineStr"/>
       <c r="J127" s="14" t="inlineStr"/>
       <c r="K127" s="14">
@@ -4840,32 +4791,29 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>Resistor 22 kΩ 1/4 W ⬆</t>
+          <t>Bloco de distribuição DIN — 1 entrada 2,5 mm² + 6 saídas</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>Braço superior do divisor de realimentação de tensão para o pino D25</t>
+          <t>BD-24V — 24 V permanentes. São 3 cargas (DNLCB30/ESP32, cadeia de comando e a alimentação das 2 posições de ensaio) + 3 reservas. ⭐ Duas saídas ficaram livres quando os sinaleiros passaram para 5 V: elas levavam o positivo comum das lâmpadas e o COM do o driver dos sinaleiros, que saiu. Não confundir com o BD-POT — este não cai com a emergência</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr"/>
       <c r="F128" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-22-k-1-4-w","🔎 resistor 22 k 1 4 w")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/bloco-distribuicao-din","🔎 bloco distribuicao din")</f>
         <v/>
       </c>
       <c r="G128" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+22+k+1+4+w","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H128" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=bloco+distribuicao+din","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H128" s="8" t="inlineStr"/>
       <c r="I128" s="8" t="inlineStr"/>
       <c r="J128" s="9" t="inlineStr"/>
       <c r="K128" s="9">
@@ -4879,32 +4827,29 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>Resistor 4,7 kΩ 1/4 W</t>
+          <t>Bloco de distribuição DIN — 1 entrada 2,5 mm² + 8 saídas ⬆</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>Braço inferior do mesmo divisor</t>
+          <t>BD-5V — ⚠️ Subiu de 6 para 8: são 7 cargas (Arduino, tela ES3C28P, RTC, lógica do BTS #1, lógica do BTS #2, placa PI-1 e os LEDs da maquete) + 1 reserva</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr"/>
       <c r="F129" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-4-7-k-1-4-w","🔎 resistor 4,7 k 1 4 w")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/bloco-distribuicao-din","🔎 bloco distribuicao din")</f>
         <v/>
       </c>
       <c r="G129" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+4%2C7+k+1+4+w","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H129" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=bloco+distribuicao+din","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H129" s="13" t="inlineStr"/>
       <c r="I129" s="13" t="inlineStr"/>
       <c r="J129" s="14" t="inlineStr"/>
       <c r="K129" s="14">
@@ -4912,50 +4857,47 @@
         <v/>
       </c>
     </row>
-    <row r="130" ht="22" customHeight="1">
-      <c r="A130" s="4" t="inlineStr">
-        <is>
-          <t>L.3 — Atuadores térmicos e ventilação</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="10" t="n">
+    <row r="130">
+      <c r="A130" s="5" t="n">
         <v>113</v>
       </c>
-      <c r="B131" s="11" t="inlineStr">
-        <is>
-          <t>⭐ Kit duplo de refrigeração Peltier (2× TEC1-12706)</t>
-        </is>
-      </c>
-      <c r="C131" s="10" t="inlineStr">
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>⭐ Barra de distribuição / régua com pente — mín. 20 pontos ⬆⬆</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D131" s="11" t="inlineStr">
-        <is>
-          <t>Adotado — kit já conferido por foto (imagens/peltir.avif): 2 conjuntos lado a lado, cada pastilha com seu par de fios e cada ventoinha com cabo próprio, o que viabiliza as modificações 1 e 2 sem cortar nada. Traz 2 pastilhas + radiador + 2 blocos frios + ventoinhas + montagem térmica pronta. Anunciado como 12 V / 15 A, ou seja, vem ligado em PARALELO — ⚠️ religar em SÉRIE para 24 V / 6,0 A (ver as 3 modificações abaixo). ~200 × 115 × 85 mm. Buscar kit peltier duplo TEC1-12706 refrigeração</t>
-        </is>
-      </c>
-      <c r="E131" s="11" t="inlineStr"/>
-      <c r="F131" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/kit-duplo-refrigeracao-peltier","🔎 kit duplo refrigeracao pelti")</f>
-        <v/>
-      </c>
-      <c r="G131" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=kit+duplo+refrigeracao+peltier","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H131" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-dual-tec1-12706-peltier-cooler-kit-12v.html","🌏 dual TEC1-12706 peltier co")</f>
-        <v/>
-      </c>
-      <c r="I131" s="13" t="inlineStr"/>
-      <c r="J131" s="14" t="inlineStr"/>
-      <c r="K131" s="14">
-        <f>IF(C131*J131=0,"",C131*J131)</f>
-        <v/>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>BD-0V — o star ground do projeto. ⚠️ Um bloco de 8 saídas NÃO serve: aqui convergem 4 entradas + ~16 retornos. Use uma barra de neutro/terra de 16–20 furos em suporte DIN, ou dois blocos de 1×8 interligados por ponte de 4 mm². Entrada de 10 mm²</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr"/>
+      <c r="F130" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/barra-distribuicao-regua-pente","🔎 barra distribuicao regua pen")</f>
+        <v/>
+      </c>
+      <c r="G130" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=barra+distribuicao+regua+pente","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H130" s="8" t="inlineStr"/>
+      <c r="I130" s="8" t="inlineStr"/>
+      <c r="J130" s="9" t="inlineStr"/>
+      <c r="K130" s="9">
+        <f>IF(C130*J130=0,"",C130*J130)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131" ht="22" customHeight="1">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>L.1 — Controle e interface</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -4964,7 +4906,7 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>Pastilha Peltier TEC1-12706 avulsa</t>
+          <t>Arduino Mega 2560 R3</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
@@ -4974,20 +4916,20 @@
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>Reserva. ⚠️ Trocar uma pastilha do kit exige desmontar a junta térmica — tenha a peça, mas conte com o trabalho</t>
+          <t>1 controlador em uso; reserva opcional</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr"/>
       <c r="F132" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/pastilha-peltier-tec1-12706-avulsa","🔎 pastilha peltier tec1 12706 ")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/arduino-mega-2560-r3","🔎 arduino mega 2560 r3")</f>
         <v/>
       </c>
       <c r="G132" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=pastilha+peltier+tec1+12706+avulsa","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=arduino+mega+2560+r3","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H132" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-tec1-12706-peltier-module.html","🌏 TEC1-12706 peltier module")</f>
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-arduino-mega-2560-r3.html","🌏 Arduino Mega 2560 R3")</f>
         <v/>
       </c>
       <c r="I132" s="8" t="inlineStr"/>
@@ -5003,7 +4945,7 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>⭐ Módulo MOSFET 4 canais isolado — LR7843 (MV-1)</t>
+          <t>Shield de expansão Mega (bornes parafuso)</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
@@ -5013,16 +4955,16 @@
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>66 × 50,5 mm, optoacoplador por canal, jumper H/L por canal, 60 W por canal. Comanda os 3 grupos de ventoinha e sobra 1 canal. Buscar modulo mosfet 4 canais optoacoplador LR7843</t>
+          <t>Sensor Shield V2.0</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr"/>
       <c r="F133" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/modulo-mosfet-4-canais-isolado","🔎 modulo mosfet 4 canais isola")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/shield-expansao-mega","🔎 shield expansao mega")</f>
         <v/>
       </c>
       <c r="G133" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=modulo+mosfet+4+canais+isolado","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=shield+expansao+mega","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H133" s="13" t="inlineStr"/>
@@ -5033,20 +4975,49 @@
         <v/>
       </c>
     </row>
-    <row r="134" ht="22" customHeight="1">
-      <c r="A134" s="4" t="inlineStr">
-        <is>
-          <t>L.4 — Sensores</t>
-        </is>
+    <row r="134">
+      <c r="A134" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>Suporte DIN para Arduino Mega</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>Ou SPCI4/adaptador</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr"/>
+      <c r="F134" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/suporte-din-arduino-mega","🔎 suporte din arduino mega")</f>
+        <v/>
+      </c>
+      <c r="G134" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=suporte+din+arduino+mega","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H134" s="8" t="inlineStr"/>
+      <c r="I134" s="8" t="inlineStr"/>
+      <c r="J134" s="9" t="inlineStr"/>
+      <c r="K134" s="9">
+        <f>IF(C134*J134=0,"",C134*J134)</f>
+        <v/>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="10" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>Sensor DS18B20 à prova d'água</t>
+          <t>⭐ ES3C28P — ESP32-S3 2,8" toque capacitivo, microSD, microfone (LCDWIKI)</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
@@ -5056,22 +5027,19 @@
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>1-Wire, 3 fios, colado no dissipador quente; nao fica no centro da camara</t>
+          <t>A IHM do projeto. Substitui a tela Nextion e o módulo de cartão SD. 8 MB de PSRAM → a Xiaozhi roda. ILI9341V 240×320, toque capacitivo FT6336G, 5 V / 140 mA, −30 a 80 °C. Vem com alto-falante. ⚠️ Comprar a versão ES3C28P (com toque) — a ES3N28P é sem toque</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr"/>
       <c r="F135" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/sensor-ds18b20-prova-d-agua","🔎 sensor ds18b20 prova d agua")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/es3c28p-esp32-s3-2-8-toque-capacitivo-microsd","🔎 es3c28p esp32 s3 2,8 toque c")</f>
         <v/>
       </c>
       <c r="G135" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=sensor+ds18b20+prova+d+agua","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H135" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-ds18b20-waterproof-temperature-sensor.html","🌏 DS18B20 waterproof tempera")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=es3c28p+esp32+s3+2%2C8+toque+capacitivo%2C+microsd%2C","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H135" s="13" t="inlineStr"/>
       <c r="I135" s="13" t="inlineStr"/>
       <c r="J135" s="14" t="inlineStr"/>
       <c r="K135" s="14">
@@ -5079,43 +5047,11 @@
         <v/>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="5" t="n">
-        <v>117</v>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>Resistor 4,7 kΩ 1/4 W</t>
-        </is>
-      </c>
-      <c r="C136" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>Pull-up do barramento 1-Wire</t>
-        </is>
-      </c>
-      <c r="E136" s="6" t="inlineStr"/>
-      <c r="F136" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-4-7-k-1-4-w","🔎 resistor 4,7 k 1 4 w")</f>
-        <v/>
-      </c>
-      <c r="G136" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+4%2C7+k+1+4+w","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H136" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
-        <v/>
-      </c>
-      <c r="I136" s="8" t="inlineStr"/>
-      <c r="J136" s="9" t="inlineStr"/>
-      <c r="K136" s="9">
-        <f>IF(C136*J136=0,"",C136*J136)</f>
-        <v/>
+    <row r="136" ht="22" customHeight="1">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>L.2 — Potência e acionamento</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -5124,30 +5060,30 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>Sensor AM2315C</t>
+          <t>Driver ponte-H BTS7960</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>I²C, umidade + temperatura, carcaça selada</t>
+          <t>43 A, pino IS de diagnóstico</t>
         </is>
       </c>
       <c r="E137" s="11" t="inlineStr"/>
       <c r="F137" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/sensor-am2315c","🔎 sensor am2315c")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/driver-ponte-h-bts7960","🔎 driver ponte h bts7960")</f>
         <v/>
       </c>
       <c r="G137" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=sensor+am2315c","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=driver+ponte+h+bts7960","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H137" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-am2315c-temperature-humidity-sensor.html","🌏 AM2315C temperature humidi")</f>
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-bts7960-43a-motor-driver-module.html","🌏 BTS7960 43A motor driver m")</f>
         <v/>
       </c>
       <c r="I137" s="13" t="inlineStr"/>
@@ -5163,32 +5099,29 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>Capacitor cerâmico 100 nF</t>
+          <t>Suporte SPCI4 trilho DIN</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>Filtro dos pinos IS dos BTS (2) + filtro do divisor D25 (1) + reservas</t>
+          <t>Fixa PCI 100 × 79 mm</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr"/>
       <c r="F138" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/capacitor-ceramico-100-nf","🔎 capacitor ceramico 100 nf")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/suporte-spci4-trilho-din","🔎 suporte spci4 trilho din")</f>
         <v/>
       </c>
       <c r="G138" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=capacitor+ceramico+100+nf","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H138" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-100nf-ceramic-capacitor.html","🌏 100nF ceramic capacitor")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=suporte+spci4+trilho+din","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H138" s="8" t="inlineStr"/>
       <c r="I138" s="8" t="inlineStr"/>
       <c r="J138" s="9" t="inlineStr"/>
       <c r="K138" s="9">
@@ -5202,30 +5135,30 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>Resistor 220 Ω 1/4 W</t>
+          <t>Cooler 40 mm 12 V</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>4 usos + 2 reservas — série dos LEDs brancos da iluminação da maquete (5 V). ⚠️ Não são mais dos sinaleiros do painel, que agora são de 24 V</t>
+          <t>Refrigeração dos BTS</t>
         </is>
       </c>
       <c r="E139" s="11" t="inlineStr"/>
       <c r="F139" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-220-1-4-w","🔎 resistor 220 1 4 w")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/cooler-40-mm-12-v","🔎 cooler 40 mm 12 v")</f>
         <v/>
       </c>
       <c r="G139" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+220+1+4+w","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=cooler+40+mm+12+v","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H139" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-40mm-fan-12v-dc.html","🌏 40mm fan 12V DC")</f>
         <v/>
       </c>
       <c r="I139" s="13" t="inlineStr"/>
@@ -5235,39 +5168,71 @@
         <v/>
       </c>
     </row>
-    <row r="140" ht="22" customHeight="1">
-      <c r="A140" s="4" t="inlineStr">
-        <is>
-          <t>L.4b — Posições de ensaio (dispositivos sob teste)</t>
-        </is>
+    <row r="140">
+      <c r="A140" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>KM1 — Relé 8 pinos 24 Vcc + base DIN</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>1 conjunto em uso + 1 reserva; 24 Vcc, 2 contatos reversiveis de 10 A em CC</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr"/>
+      <c r="F140" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/rele-8-pinos-24-vcc-base-din","🔎 rele 8 pinos 24 vcc base din")</f>
+        <v/>
+      </c>
+      <c r="G140" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=rele+8+pinos+24+vcc+base+din","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H140" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-jqx-13f-ly2n-24vdc-relay-10a-8-pin-ptf08a-socket.html","🌏 JQX-13F LY2N 24VDC relay 1")</f>
+        <v/>
+      </c>
+      <c r="I140" s="8" t="inlineStr"/>
+      <c r="J140" s="9" t="inlineStr"/>
+      <c r="K140" s="9">
+        <f>IF(C140*J140=0,"",C140*J140)</f>
+        <v/>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="10" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>⭐ Módulo multiplexador 16 canais CD74HC4067 — ⚠️ a versão em PLACA, com pinos</t>
+          <t>*Alternativa premium (só se sobrar orçamento)*</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>1 (vem em pacote de 5)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>O coração da detecção de falha. Varre até 16 posições com uma única entrada analógica do Arduino. Buscar modulo multiplexador analogico 16 canais CD74HC4067</t>
+          <t>Finder 46.61 24VDC (1 reversível 16 A) + base 95.05 para o KM1, ~R$ 80–110. Vale se você quiser folga grande sobre os 6,0 A e datasheet publicado</t>
         </is>
       </c>
       <c r="E141" s="11" t="inlineStr"/>
       <c r="F141" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/modulo-multiplexador-16-canais-cd74hc4067","🔎 modulo multiplexador 16 cana")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/alternativa-premium","🔎 alternativa premium")</f>
         <v/>
       </c>
       <c r="G141" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=modulo+multiplexador+16+canais+cd74hc4067","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=alternativa+premium","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H141" s="13" t="inlineStr"/>
@@ -5278,43 +5243,75 @@
         <v/>
       </c>
     </row>
-    <row r="142" ht="22" customHeight="1">
-      <c r="A142" s="4" t="inlineStr">
-        <is>
-          <t>L.5 — Placa de Interface PI-1 (onde os componentes discretos moram)</t>
-        </is>
+    <row r="142">
+      <c r="A142" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>Resistor 10 kΩ 1/4 W</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>Pull-down em cada R_EN dos BTS7960 (2) + reservas. ⚠️ Garante que pino solto = driver desligado — ficou ainda mais crítico com os 24 V permanentes na entrada dos BTS</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr"/>
+      <c r="F142" s="7">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-10-k-1-4-w","🔎 resistor 10 k 1 4 w")</f>
+        <v/>
+      </c>
+      <c r="G142" s="7">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+10+k+1+4+w","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H142" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
+        <v/>
+      </c>
+      <c r="I142" s="8" t="inlineStr"/>
+      <c r="J142" s="9" t="inlineStr"/>
+      <c r="K142" s="9">
+        <f>IF(C142*J142=0,"",C142*J142)</f>
+        <v/>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="10" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>Placa ilhada 9 x 15 cm para PI-1 + PI-2</t>
+          <t>Resistor 22 kΩ 1/4 W ⬆</t>
         </is>
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>1 placa de 34 x 58 furos, cortada ao meio para formar as duas placas</t>
+          <t>Braço superior do divisor de realimentação de tensão para o pino D25</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr"/>
       <c r="F143" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/placa-ilhada","🔎 placa ilhada")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-22-k-1-4-w","🔎 resistor 22 k 1 4 w")</f>
         <v/>
       </c>
       <c r="G143" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=placa+ilhada","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+22+k+1+4+w","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H143" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-perfboard-prototype-pcb.html","🌏 perfboard prototype PCB")</f>
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
         <v/>
       </c>
       <c r="I143" s="13" t="inlineStr"/>
@@ -5326,11 +5323,11 @@
     </row>
     <row r="144">
       <c r="A144" s="5" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>⭐ Caixa modular para trilho DIN — 6 módulos (105 mm)</t>
+          <t>Resistor 4,7 kΩ 1/4 W</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
@@ -5340,19 +5337,22 @@
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>Invólucros da PI-1 e da PI-2, no trilho 3. ⚠️ 6 módulos, não 4: as placas passaram a 86,4 mm de largura, e uma caixa de 4M só comporta 61 mm. A largura extra é o que permite rotear os fios em canais separados por baixo. Buscar caixa para trilho din 6m modular</t>
+          <t>Braço inferior do mesmo divisor</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr"/>
       <c r="F144" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/caixa-modular-trilho-din","🔎 caixa modular trilho din")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-4-7-k-1-4-w","🔎 resistor 4,7 k 1 4 w")</f>
         <v/>
       </c>
       <c r="G144" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=caixa+modular+trilho+din","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H144" s="8" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+4%2C7+k+1+4+w","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H144" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
+        <v/>
+      </c>
       <c r="I144" s="8" t="inlineStr"/>
       <c r="J144" s="9" t="inlineStr"/>
       <c r="K144" s="9">
@@ -5360,71 +5360,45 @@
         <v/>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="10" t="n">
-        <v>124</v>
-      </c>
-      <c r="B145" s="11" t="inlineStr">
-        <is>
-          <t>⭐ Borne KF301 / KRE passo 5,08 mm — 3 vias</t>
-        </is>
-      </c>
-      <c r="C145" s="10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D145" s="11" t="inlineStr">
-        <is>
-          <t>6 em uso + 4 reserva. Encaixam lado a lado — não se compra bloco de 11 vias, montam-se 3+3+3+2</t>
-        </is>
-      </c>
-      <c r="E145" s="11" t="inlineStr"/>
-      <c r="F145" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/borne-kf301-kre-passo-5-08-mm","🔎 borne kf301 kre passo 5,08 m")</f>
-        <v/>
-      </c>
-      <c r="G145" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=borne+kf301+kre+passo+5%2C08+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H145" s="13" t="inlineStr"/>
-      <c r="I145" s="13" t="inlineStr"/>
-      <c r="J145" s="14" t="inlineStr"/>
-      <c r="K145" s="14">
-        <f>IF(C145*J145=0,"",C145*J145)</f>
-        <v/>
+    <row r="145" ht="22" customHeight="1">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>L.3 — Atuadores térmicos e ventilação</t>
+        </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>⭐ Borne KF301 / KRE passo 5,08 mm — 2 vias</t>
+          <t>⭐ Kit duplo de refrigeração Peltier (2× TEC1-12706)</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
         <is>
-          <t>7 em uso + 5 reserva. Junto com os de 3 vias formam as 32 vias das duas placas</t>
+          <t>Adotado — kit já conferido por foto (imagens/peltir.avif): 2 conjuntos lado a lado, cada pastilha com seu par de fios e cada ventoinha com cabo próprio, o que viabiliza as modificações 1 e 2 sem cortar nada. Traz 2 pastilhas + radiador + 2 blocos frios + ventoinhas + montagem térmica pronta. Anunciado como 12 V / 15 A, ou seja, vem ligado em PARALELO — ⚠️ religar em SÉRIE para 24 V / 6,0 A (ver as 3 modificações abaixo). ~200 × 115 × 85 mm. Buscar kit peltier duplo TEC1-12706 refrigeração</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr"/>
       <c r="F146" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/borne-kf301-kre-passo-5-08-mm","🔎 borne kf301 kre passo 5,08 m")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/kit-duplo-refrigeracao-peltier","🔎 kit duplo refrigeracao pelti")</f>
         <v/>
       </c>
       <c r="G146" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=borne+kf301+kre+passo+5%2C08+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H146" s="8" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=kit+duplo+refrigeracao+peltier","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H146" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-dual-tec1-12706-peltier-cooler-kit-12v.html","🌏 dual TEC1-12706 peltier co")</f>
+        <v/>
+      </c>
       <c r="I146" s="8" t="inlineStr"/>
       <c r="J146" s="9" t="inlineStr"/>
       <c r="K146" s="9">
@@ -5434,11 +5408,11 @@
     </row>
     <row r="147">
       <c r="A147" s="10" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>CI ULN2803A (DIP 18 pinos)</t>
+          <t>Pastilha Peltier TEC1-12706 avulsa</t>
         </is>
       </c>
       <c r="C147" s="10" t="inlineStr">
@@ -5448,20 +5422,20 @@
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>Driver dos 4 sinaleiros de 24 V — 8 canais Darlington, 500 mA/50 V, com diodos de proteção internos. 1 uso + 1 reserva (o CI é barato e é o único ponto onde 24 V encosta na lógica)</t>
+          <t>Reserva. ⚠️ Trocar uma pastilha do kit exige desmontar a junta térmica — tenha a peça, mas conte com o trabalho</t>
         </is>
       </c>
       <c r="E147" s="11" t="inlineStr"/>
       <c r="F147" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/ci-uln2803a","🔎 ci uln2803a")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/pastilha-peltier-tec1-12706-avulsa","🔎 pastilha peltier tec1 12706 ")</f>
         <v/>
       </c>
       <c r="G147" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=ci+uln2803a","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=pastilha+peltier+tec1+12706+avulsa","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H147" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-uln2803a-dip18-darlington.html","🌏 ULN2803A DIP18 darlington")</f>
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-tec1-12706-peltier-module.html","🌏 TEC1-12706 peltier module")</f>
         <v/>
       </c>
       <c r="I147" s="13" t="inlineStr"/>
@@ -5471,43 +5445,11 @@
         <v/>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="5" t="n">
-        <v>127</v>
-      </c>
-      <c r="B148" s="6" t="inlineStr">
-        <is>
-          <t>Soquete DIP 18 pinos</t>
-        </is>
-      </c>
-      <c r="C148" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D148" s="6" t="inlineStr">
-        <is>
-          <t>⚠️ Solde o soquete, não o CI. Permite trocar o chip sem dessoldar nada</t>
-        </is>
-      </c>
-      <c r="E148" s="6" t="inlineStr"/>
-      <c r="F148" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/soquete-dip-18-pinos","🔎 soquete dip 18 pinos")</f>
-        <v/>
-      </c>
-      <c r="G148" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=soquete+dip+18+pinos","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H148" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-dip18-ic-socket.html","🌏 DIP18 IC socket")</f>
-        <v/>
-      </c>
-      <c r="I148" s="8" t="inlineStr"/>
-      <c r="J148" s="9" t="inlineStr"/>
-      <c r="K148" s="9">
-        <f>IF(C148*J148=0,"",C148*J148)</f>
-        <v/>
+    <row r="148" ht="22" customHeight="1">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>L.4 — Sensores</t>
+        </is>
       </c>
     </row>
     <row r="149">
@@ -5516,29 +5458,32 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>⭐ Módulo relé 1 canal 5 V, optoacoplado</t>
+          <t>Sensor DS18B20 à prova d'água</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>KA3 (NO) e KA4 (NC), optoacoplados; reservas opcionais</t>
+          <t>1-Wire, 3 fios, colado no dissipador quente; nao fica no centro da camara</t>
         </is>
       </c>
       <c r="E149" s="11" t="inlineStr"/>
       <c r="F149" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/modulo-rele-1-canal-5-v-optoacoplado","🔎 modulo rele 1 canal 5 v, opt")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/sensor-ds18b20-prova-d-agua","🔎 sensor ds18b20 prova d agua")</f>
         <v/>
       </c>
       <c r="G149" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=modulo+rele+1+canal+5+v%2C+optoacoplado","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H149" s="13" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=sensor+ds18b20+prova+d+agua","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H149" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-ds18b20-waterproof-temperature-sensor.html","🌏 DS18B20 waterproof tempera")</f>
+        <v/>
+      </c>
       <c r="I149" s="13" t="inlineStr"/>
       <c r="J149" s="14" t="inlineStr"/>
       <c r="K149" s="14">
@@ -5552,29 +5497,32 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>⭐ Caixa modular DIN 4 módulos (70 mm)</t>
+          <t>Resistor 4,7 kΩ 1/4 W</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>Abriga os dois módulos de relé empilhados, no trilho 2. Buscar caixa para trilho din 4m modular</t>
+          <t>Pull-up do barramento 1-Wire</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr"/>
       <c r="F150" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/caixa-modular-din-4-modulos","🔎 caixa modular din 4 modulos")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-4-7-k-1-4-w","🔎 resistor 4,7 k 1 4 w")</f>
         <v/>
       </c>
       <c r="G150" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=caixa+modular+din+4+modulos","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H150" s="8" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+4%2C7+k+1+4+w","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H150" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
+        <v/>
+      </c>
       <c r="I150" s="8" t="inlineStr"/>
       <c r="J150" s="9" t="inlineStr"/>
       <c r="K150" s="9">
@@ -5588,30 +5536,30 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>⭐ Resistor 10 kΩ · ¼ W</t>
+          <t>Sensor AM2315C</t>
         </is>
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>R10 e R11 — pull-down do IN de cada módulo para o 0 V. 2 em uso + 2 reserva. ⚠️ É o que torna o fail-safe medível: Arduino ausente ou fio rompido → IN em 0 V → relé aberto → potência cortada e ventoinha parada</t>
+          <t>I²C, umidade + temperatura, carcaça selada</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr"/>
       <c r="F151" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-10-k","🔎 resistor 10 k")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/sensor-am2315c","🔎 sensor am2315c")</f>
         <v/>
       </c>
       <c r="G151" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+10+k","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=sensor+am2315c","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H151" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-am2315c-temperature-humidity-sensor.html","🌏 AM2315C temperature humidi")</f>
         <v/>
       </c>
       <c r="I151" s="13" t="inlineStr"/>
@@ -5627,30 +5575,30 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>⭐ Diodo 1N4007</t>
+          <t>Capacitor cerâmico 100 nF</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>D1 (bobina do KA2) e D2 (ventoinhas do radiador). ⭐ Não compre de novo: já estão na lista L.2, com 2 reservas. 🔥 Ficaram MAIS importantes com os módulos de relé: um contato seco abrindo uma bobina forma arco no contato do KA3, e um contato que pita acaba soldando — o veto do firmware perdido em silêncio. 🔎 O D1 pode ser dispensável: teste o KA2 em *teste de diodo* entre A1 e A2; se conduzir num sentido só, ele já tem diodo interno. ⚠️ O D2 é obrigatório — o motor é indutivo e nada o grampeia. Catodo no +12 V</t>
+          <t>Filtro dos pinos IS dos BTS (2) + filtro do divisor D25 (1) + reservas</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr"/>
       <c r="F152" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/diodo-1n4007","🔎 diodo 1n4007")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/capacitor-ceramico-100-nf","🔎 capacitor ceramico 100 nf")</f>
         <v/>
       </c>
       <c r="G152" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=diodo+1n4007","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=capacitor+ceramico+100+nf","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H152" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1n4007-diode.html","🌏 1N4007 diode")</f>
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-100nf-ceramic-capacitor.html","🌏 100nF ceramic capacitor")</f>
         <v/>
       </c>
       <c r="I152" s="8" t="inlineStr"/>
@@ -5666,29 +5614,32 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>Fio rígido 0,25 mm² para interligação</t>
+          <t>Resistor 220 Ω 1/4 W</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>1 m</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>Ligações por baixo da placa. ⚠️ Não usar "sobra de perna" de componente em trecho longo — oxida e não é isolada</t>
+          <t>4 usos + 2 reservas — série dos LEDs brancos da iluminação da maquete (5 V). ⚠️ Não são mais dos sinaleiros do painel, que agora são de 24 V</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr"/>
       <c r="F153" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/fio-rigido-0-25-mm-interligacao","🔎 fio rigido 0,25 mm interliga")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-220-1-4-w","🔎 resistor 220 1 4 w")</f>
         <v/>
       </c>
       <c r="G153" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=fio+rigido+0%2C25+mm+interligacao","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H153" s="13" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+220+1+4+w","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H153" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
+        <v/>
+      </c>
       <c r="I153" s="13" t="inlineStr"/>
       <c r="J153" s="14" t="inlineStr"/>
       <c r="K153" s="14">
@@ -5696,74 +5647,46 @@
         <v/>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="5" t="n">
-        <v>133</v>
-      </c>
-      <c r="B154" s="6" t="inlineStr">
-        <is>
-          <t>Verniz spray para PCI (ou esmalte incolor)</t>
-        </is>
-      </c>
-      <c r="C154" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D154" s="6" t="inlineStr">
-        <is>
-          <t>Proteção do lado da solda contra umidade e oxidação</t>
-        </is>
-      </c>
-      <c r="E154" s="6" t="inlineStr"/>
-      <c r="F154" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/verniz-spray-pci","🔎 verniz spray pci")</f>
-        <v/>
-      </c>
-      <c r="G154" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=verniz+spray+pci","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H154" s="8" t="inlineStr"/>
-      <c r="I154" s="8" t="inlineStr"/>
-      <c r="J154" s="9" t="inlineStr"/>
-      <c r="K154" s="9">
-        <f>IF(C154*J154=0,"",C154*J154)</f>
-        <v/>
+    <row r="154" ht="22" customHeight="1">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>L.5 — Módulos de interface e componentes em borne</t>
+        </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="10" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>Termorretrátil Ø 2 mm</t>
+          <t>⭐ Módulo sensor de tensão 0–25 V</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>30 cm</t>
+          <t>1 (pacote de 5)</t>
         </is>
       </c>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>Isolação dos 2 resistores de 10 kΩ soldados nos BTS7960</t>
-        </is>
-      </c>
-      <c r="E155" s="11" t="inlineStr"/>
+          <t>SV-1 — substituiu o divisor R1 + R2 + C3. Divisor 30 kΩ / 7,5 kΩ com borne de parafuso. ⚠️ Divide por 5 (24 V → 4,8 V), e o soldado dividia por 5,68 (4,22 V): meça a saída antes de ligar no D25</t>
+        </is>
+      </c>
+      <c r="E155" s="11" t="inlineStr">
+        <is>
+          <t>16,07</t>
+        </is>
+      </c>
       <c r="F155" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/termorretratil-2-mm","🔎 termorretratil 2 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/modulo-sensor-tensao-0-25-v","🔎 modulo sensor tensao 0 25 v")</f>
         <v/>
       </c>
       <c r="G155" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=termorretratil+2+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H155" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-heat-shrink-tubing-kit.html","🌏 heat shrink tubing kit")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=modulo+sensor+tensao+0+25+v","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H155" s="13" t="inlineStr"/>
       <c r="I155" s="13" t="inlineStr"/>
       <c r="J155" s="14" t="inlineStr"/>
       <c r="K155" s="14">
@@ -5773,33 +5696,40 @@
     </row>
     <row r="156">
       <c r="A156" s="5" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>Etiqueta impressa em papel adesivo</t>
+          <t>⭐ DS18B20 à prova d'água + adaptador com pull-up</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr">
         <is>
-          <t>Identificação das 20 vias na frente da caixa — é o que torna a placa auditável</t>
-        </is>
-      </c>
-      <c r="E156" s="6" t="inlineStr"/>
+          <t>AD-1 — substituiu o R3. ⚠️ O pull-up de 4,7 kΩ está no ADAPTADOR, não na sonda. Se comprar só a sonda, compre também 1 resistor de 4,7 kΩ. Meça ao receber: ~4,7 kΩ entre DAT e VCC</t>
+        </is>
+      </c>
+      <c r="E156" s="6" t="inlineStr">
+        <is>
+          <t>6,90</t>
+        </is>
+      </c>
       <c r="F156" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/etiqueta-impressa-papel-adesivo","🔎 etiqueta impressa papel ades")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/ds18b20-prova-d-agua-adaptador-pull-up","🔎 ds18b20 prova d agua adaptad")</f>
         <v/>
       </c>
       <c r="G156" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=etiqueta+impressa+papel+adesivo","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H156" s="8" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=ds18b20+prova+d+agua+adaptador+pull+up","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H156" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-ds18b20-waterproof-temperature-sensor.html","🌏 DS18B20 waterproof tempera")</f>
+        <v/>
+      </c>
       <c r="I156" s="8" t="inlineStr"/>
       <c r="J156" s="9" t="inlineStr"/>
       <c r="K156" s="9">
@@ -5807,11 +5737,44 @@
         <v/>
       </c>
     </row>
-    <row r="157" ht="22" customHeight="1">
-      <c r="A157" s="4" t="inlineStr">
-        <is>
-          <t>🔧 CAMADA 3 — CABOS E ACESSÓRIOS</t>
-        </is>
+    <row r="157">
+      <c r="A157" s="10" t="n">
+        <v>135</v>
+      </c>
+      <c r="B157" s="11" t="inlineStr">
+        <is>
+          <t>⭐ Borne de passagem DIN 2,5 mm²</t>
+        </is>
+      </c>
+      <c r="C157" s="10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D157" s="11" t="inlineStr">
+        <is>
+          <t>BS-1 — 3 em uso (A0, A1, 0V) + 3 reserva. ⚠️ 2,5 mm², não 1,5: em dois deles entram três condutores (fio do BTS, fio do Arduino e perna do capacitor)</t>
+        </is>
+      </c>
+      <c r="E157" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F157" s="12">
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/borne-passagem-din-2-5-mm","🔎 borne passagem din 2,5 mm")</f>
+        <v/>
+      </c>
+      <c r="G157" s="12">
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=borne+passagem+din+2%2C5+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H157" s="13" t="inlineStr"/>
+      <c r="I157" s="13" t="inlineStr"/>
+      <c r="J157" s="14" t="inlineStr"/>
+      <c r="K157" s="14">
+        <f>IF(C157*J157=0,"",C157*J157)</f>
+        <v/>
       </c>
     </row>
     <row r="158">
@@ -5820,33 +5783,36 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>Cabo flexivel 1,5 mm² azul escuro</t>
+          <t>Capacitor cerâmico 100 nF</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>3 m</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
         <is>
-          <t>750 V; 0 V comum conforme a codificacao do React</t>
+          <t>C1 e C2 + reservas — parafusados no BS-1, sem solda</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
         <is>
-          <t>Retorno geral 0 V (6,9 A — soma dos 3 ramais)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F158" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-flexivel-1-5-mm-preto","🔎 cabo flexivel 1,5 mm preto")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/capacitor-ceramico-100-nf","🔎 capacitor ceramico 100 nf")</f>
         <v/>
       </c>
       <c r="G158" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+flexivel+1%2C5+mm+preto","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H158" s="8" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=capacitor+ceramico+100+nf","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H158" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-100nf-ceramic-capacitor.html","🌏 100nF ceramic capacitor")</f>
+        <v/>
+      </c>
       <c r="I158" s="8" t="inlineStr"/>
       <c r="J158" s="9" t="inlineStr"/>
       <c r="K158" s="9">
@@ -5860,30 +5826,30 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>Cabo flexível 1,5 mm² vermelho</t>
+          <t>⭐ Módulo relé 1 canal 5 V, optoacoplado</t>
         </is>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>2 m</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>750 V</t>
+          <t>KA1 (NO), KA2 (NC) e KA3 (NO), optoacoplados, caixa DIN 6M; reservas opcionais</t>
         </is>
       </c>
       <c r="E159" s="11" t="inlineStr">
         <is>
-          <t>24 V de potência — P1 → painel → BTS (6,0 A)</t>
+          <t>6,79</t>
         </is>
       </c>
       <c r="F159" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-flexivel-1-5-mm-vermelho","🔎 cabo flexivel 1,5 mm vermelh")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/modulo-rele-1-canal-5-v-optoacoplado","🔎 modulo rele 1 canal 5 v, opt")</f>
         <v/>
       </c>
       <c r="G159" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+flexivel+1%2C5+mm+vermelho","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=modulo+rele+1+canal+5+v%2C+optoacoplado","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H159" s="13" t="inlineStr"/>
@@ -5900,30 +5866,30 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>Cabo flexível 0,75 mm² vermelho/preto</t>
+          <t>⭐ Caixa modular DIN 6 módulos (105 mm)</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>3 m</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>750 V</t>
+          <t>Abriga os três módulos de relé empilhados, no trilho 2. ⚠️ NÃO a de 4M: 3 × 25,5 mm = 76,5 mm e a de 4M tem 70 mm. Mesmo assim o trilho 2 ficou mais folgado — o MV-1, que saiu, media 66 mm</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
         <is>
-          <t>Barramento 24 V (trechos internos) e saída de 12 V do T3 (1,0 A)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F160" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-flexivel-0-75-mm-vermelho-preto","🔎 cabo flexivel 0,75 mm vermel")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/caixa-modular-din-6-modulos","🔎 caixa modular din 6 modulos")</f>
         <v/>
       </c>
       <c r="G160" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+flexivel+0%2C75+mm+vermelho+preto","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=caixa+modular+din+6+modulos","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H160" s="8" t="inlineStr"/>
@@ -5940,33 +5906,36 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>Cabo flexível 0,5 mm² (5 cores)</t>
+          <t>⭐ Resistor 10 kΩ · ¼ W</t>
         </is>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>10 m</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>750 V</t>
+          <t>R10, R11 e ⭐ R12 (pull-down dos IN dos três módulos) + R8 e R9 (soldados nos BTS7960). ⚠️ É o que torna o fail-safe medível: Arduino ausente ou fio rompido → IN em 0 V → potência cortada e ventoinha girando</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr">
         <is>
-          <t>5 V e derivações do 12 V auxiliar</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F161" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-flexivel-0-5-mm","🔎 cabo flexivel 0,5 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-10-k","🔎 resistor 10 k")</f>
         <v/>
       </c>
       <c r="G161" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+flexivel+0%2C5+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H161" s="13" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+10+k","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H161" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
+        <v/>
+      </c>
       <c r="I161" s="13" t="inlineStr"/>
       <c r="J161" s="14" t="inlineStr"/>
       <c r="K161" s="14">
@@ -5980,33 +5949,36 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>Cabo flexível 0,25 mm² (8 cores)</t>
+          <t>⭐ Diodo 1N4007</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>15 m</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>Sinais</t>
+          <t>D1 (bobina do KM1), D2 (ventoinhas do radiador) e ⭐ D3 (as 5 internas) + 1 reserva. 🔎 O D1 pode ser dispensável: teste o KM1 em *teste de diodo* entre A1 e A2 — se conduzir num sentido só, ele já tem diodo interno. ⚠️ O D2 e o D3 são obrigatórios — o D3 entrou quando o MV-1 saiu: o módulo MOSFET trazia o roda-livre dentro da placa, o contato do KA3 não traz nada</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
         <is>
-          <t>Sensores, botões, comunicação</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F162" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-flexivel-0-25-mm","🔎 cabo flexivel 0,25 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/diodo-1n4007","🔎 diodo 1n4007")</f>
         <v/>
       </c>
       <c r="G162" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+flexivel+0%2C25+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H162" s="8" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=diodo+1n4007","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H162" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1n4007-diode.html","🌏 1N4007 diode")</f>
+        <v/>
+      </c>
       <c r="I162" s="8" t="inlineStr"/>
       <c r="J162" s="9" t="inlineStr"/>
       <c r="K162" s="9">
@@ -6020,33 +5992,36 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>Cabo par trançado blindado 2×0,25 mm²</t>
+          <t>Termorretrátil Ø 2 mm</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>2 m</t>
+          <t>30 cm</t>
         </is>
       </c>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>Blindado, malha aterrada em um ponto</t>
+          <t>Isolação dos 10 kΩ soldados nos BTS7960 e das emendas nos postes</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr">
         <is>
-          <t>I²C e 1-Wire (trecho câmara → painel)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F163" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/cabo-par-trancado-blindado-2-0-25-mm","🔎 cabo par trancado blindado 2")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/termorretratil-2-mm","🔎 termorretratil 2 mm")</f>
         <v/>
       </c>
       <c r="G163" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=cabo+par+trancado+blindado+2+0%2C25+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H163" s="13" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=termorretratil+2+mm","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H163" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-heat-shrink-tubing-kit.html","🌏 heat shrink tubing kit")</f>
+        <v/>
+      </c>
       <c r="I163" s="13" t="inlineStr"/>
       <c r="J163" s="14" t="inlineStr"/>
       <c r="K163" s="14">
@@ -6060,30 +6035,30 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>Terminal tubular (ilhós) 0,25 / 0,5 / 1,5 mm²</t>
+          <t>Etiqueta impressa em papel adesivo</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>1 kit</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>Com colarinho colorido</t>
+          <t>Identificação dos bornes — é o que torna a montagem auditável</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
         <is>
-          <t>Obrigatório em todo borne parafuso</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F164" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/terminal-tubular-0-25-0-5-1-5-mm","🔎 terminal tubular 0,25 0,5 1,")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/etiqueta-impressa-papel-adesivo","🔎 etiqueta impressa papel ades")</f>
         <v/>
       </c>
       <c r="G164" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=terminal+tubular+0%2C25+0%2C5+1%2C5+mm","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=etiqueta+impressa+papel+adesivo","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H164" s="8" t="inlineStr"/>
@@ -6094,78 +6069,39 @@
         <v/>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="10" t="n">
-        <v>143</v>
-      </c>
-      <c r="B165" s="11" t="inlineStr">
-        <is>
-          <t>Alicate de crimpar terminal tubular</t>
-        </is>
-      </c>
-      <c r="C165" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D165" s="11" t="inlineStr">
-        <is>
-          <t>Tipo quadrado/hexagonal</t>
-        </is>
-      </c>
-      <c r="E165" s="11" t="inlineStr">
-        <is>
-          <t>Ferramenta</t>
-        </is>
-      </c>
-      <c r="F165" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/alicate-crimpar-terminal-tubular","🔎 alicate crimpar terminal tub")</f>
-        <v/>
-      </c>
-      <c r="G165" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=alicate+crimpar+terminal+tubular","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H165" s="13" t="inlineStr"/>
-      <c r="I165" s="13" t="inlineStr"/>
-      <c r="J165" s="14" t="inlineStr"/>
-      <c r="K165" s="14">
-        <f>IF(C165*J165=0,"",C165*J165)</f>
-        <v/>
+    <row r="165" ht="22" customHeight="1">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>L.3 — Atuadores térmicos e ventilação</t>
+        </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>Terminal olhal M4</t>
+          <t>Ventoinha interna 12 V — grupo React</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>Amarelo/vermelho</t>
+          <t>Cinco unidades compatíveis com a geometria atual: 2 frias, 2 dos dutos e 1 do PTC; ligadas em paralelo</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
         <is>
-          <t>Aterramento</t>
-        </is>
-      </c>
-      <c r="F166" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/terminal-olhal-m4","🔎 terminal olhal m4")</f>
-        <v/>
-      </c>
-      <c r="G166" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=terminal+olhal+m4","🔎 Amazon")</f>
-        <v/>
-      </c>
+          <t>Confirmar dimensao fisica antes da compra</t>
+        </is>
+      </c>
+      <c r="F166" s="8" t="inlineStr"/>
+      <c r="G166" s="8" t="inlineStr"/>
       <c r="H166" s="8" t="inlineStr"/>
       <c r="I166" s="8" t="inlineStr"/>
       <c r="J166" s="9" t="inlineStr"/>
@@ -6174,245 +6110,41 @@
         <v/>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="10" t="n">
-        <v>145</v>
-      </c>
-      <c r="B167" s="11" t="inlineStr">
-        <is>
-          <t>Espaguete termorretrátil (kit)</t>
-        </is>
-      </c>
-      <c r="C167" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D167" s="11" t="inlineStr">
-        <is>
-          <t>Diversas bitolas</t>
-        </is>
-      </c>
-      <c r="E167" s="11" t="inlineStr">
-        <is>
-          <t>Isolação de emendas</t>
-        </is>
-      </c>
-      <c r="F167" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/espaguete-termorretratil","🔎 espaguete termorretratil")</f>
-        <v/>
-      </c>
-      <c r="G167" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=espaguete+termorretratil","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H167" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-heat-shrink-tubing-kit.html","🌏 heat shrink tubing kit")</f>
-        <v/>
-      </c>
-      <c r="I167" s="13" t="inlineStr"/>
-      <c r="J167" s="14" t="inlineStr"/>
-      <c r="K167" s="14">
-        <f>IF(C167*J167=0,"",C167*J167)</f>
-        <v/>
-      </c>
-    </row>
     <row r="168">
-      <c r="A168" s="5" t="n">
-        <v>146</v>
-      </c>
-      <c r="B168" s="6" t="inlineStr">
-        <is>
-          <t>Abraçadeiras de nylon 100 mm</t>
-        </is>
-      </c>
-      <c r="C168" s="5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="D168" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E168" s="6" t="inlineStr">
-        <is>
-          <t>Amarração</t>
-        </is>
-      </c>
-      <c r="F168" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/abracadeiras-nylon-100-mm","🔎 abracadeiras nylon 100 mm")</f>
-        <v/>
-      </c>
-      <c r="G168" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=abracadeiras+nylon+100+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H168" s="8" t="inlineStr"/>
-      <c r="I168" s="8" t="inlineStr"/>
-      <c r="J168" s="9" t="inlineStr"/>
-      <c r="K168" s="9">
-        <f>IF(C168*J168=0,"",C168*J168)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="10" t="n">
-        <v>147</v>
-      </c>
-      <c r="B169" s="11" t="inlineStr">
-        <is>
-          <t>Anilhas de identificação de cabo</t>
-        </is>
-      </c>
-      <c r="C169" s="10" t="inlineStr">
-        <is>
-          <t>1 kit</t>
-        </is>
-      </c>
-      <c r="D169" s="11" t="inlineStr">
-        <is>
-          <t>Numeradas 0–9</t>
-        </is>
-      </c>
-      <c r="E169" s="11" t="inlineStr">
-        <is>
-          <t>Identificação (norma de painel)</t>
-        </is>
-      </c>
-      <c r="F169" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/anilhas-identificacao-cabo","🔎 anilhas identificacao cabo")</f>
-        <v/>
-      </c>
-      <c r="G169" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=anilhas+identificacao+cabo","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H169" s="13" t="inlineStr"/>
-      <c r="I169" s="13" t="inlineStr"/>
-      <c r="J169" s="14" t="inlineStr"/>
-      <c r="K169" s="14">
-        <f>IF(C169*J169=0,"",C169*J169)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="5" t="n">
-        <v>148</v>
-      </c>
-      <c r="B170" s="6" t="inlineStr">
-        <is>
-          <t>Espiral organizador Ø 8 mm</t>
-        </is>
-      </c>
-      <c r="C170" s="5" t="inlineStr">
-        <is>
-          <t>2 m</t>
-        </is>
-      </c>
-      <c r="D170" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E170" s="6" t="inlineStr">
-        <is>
-          <t>Chicote painel → câmara</t>
-        </is>
-      </c>
-      <c r="F170" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/espiral-organizador-8-mm","🔎 espiral organizador 8 mm")</f>
-        <v/>
-      </c>
-      <c r="G170" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=espiral+organizador+8+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H170" s="8" t="inlineStr"/>
-      <c r="I170" s="8" t="inlineStr"/>
-      <c r="J170" s="9" t="inlineStr"/>
-      <c r="K170" s="9">
-        <f>IF(C170*J170=0,"",C170*J170)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="171" ht="22" customHeight="1">
-      <c r="A171" s="4" t="inlineStr">
-        <is>
-          <t>L.3 — Atuadores térmicos e ventilação</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="5" t="n">
-        <v>149</v>
-      </c>
-      <c r="B172" s="6" t="inlineStr">
-        <is>
-          <t>Ventoinha interna 12 V — grupo React</t>
-        </is>
-      </c>
-      <c r="C172" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D172" s="6" t="inlineStr">
-        <is>
-          <t>Cinco unidades compatíveis com a geometria atual: 2 frias, 2 dos dutos e 1 do PTC; ligadas em paralelo</t>
-        </is>
-      </c>
-      <c r="E172" s="6" t="inlineStr">
-        <is>
-          <t>Confirmar dimensao fisica antes da compra</t>
-        </is>
-      </c>
-      <c r="F172" s="8" t="inlineStr"/>
-      <c r="G172" s="8" t="inlineStr"/>
-      <c r="H172" s="8" t="inlineStr"/>
-      <c r="I172" s="8" t="inlineStr"/>
-      <c r="J172" s="9" t="inlineStr"/>
-      <c r="K172" s="9">
-        <f>IF(C172*J172=0,"",C172*J172)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="174">
-      <c r="I174" s="17" t="inlineStr">
+      <c r="I168" s="17" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="K174" s="18">
-        <f>SUM(K5:K172)</f>
+      <c r="K168" s="18">
+        <f>SUM(K5:K166)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K172"/>
+  <autoFilter ref="A4:K166"/>
   <mergeCells count="21">
-    <mergeCell ref="A130:K130"/>
-    <mergeCell ref="A157:K157"/>
-    <mergeCell ref="A142:K142"/>
-    <mergeCell ref="A60:K60"/>
-    <mergeCell ref="A94:K94"/>
+    <mergeCell ref="A148:K148"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A46:K46"/>
-    <mergeCell ref="A90:K90"/>
-    <mergeCell ref="A104:K104"/>
+    <mergeCell ref="A61:K61"/>
+    <mergeCell ref="A119:K119"/>
+    <mergeCell ref="A37:K37"/>
+    <mergeCell ref="A75:K75"/>
+    <mergeCell ref="A136:K136"/>
+    <mergeCell ref="A105:K105"/>
+    <mergeCell ref="A145:K145"/>
+    <mergeCell ref="A154:K154"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A76:K76"/>
-    <mergeCell ref="A116:K116"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A22:K22"/>
-    <mergeCell ref="A140:K140"/>
-    <mergeCell ref="A171:K171"/>
-    <mergeCell ref="A134:K134"/>
-    <mergeCell ref="A38:K38"/>
-    <mergeCell ref="A121:K121"/>
+    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="A53:K53"/>
+    <mergeCell ref="A91:K91"/>
+    <mergeCell ref="A131:K131"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="A109:K109"/>
+    <mergeCell ref="A165:K165"/>
+    <mergeCell ref="A43:K43"/>
     <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A13:K13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6652,7 +6384,7 @@
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>KA1 e KA2, bobina 24 Vcc; KA2 com contato 10 A em CC</t>
+          <t>KM1 (1 em uso + 1 reserva), bobina 24 Vcc, contato 10 A em CC</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -6673,11 +6405,11 @@
         </is>
       </c>
       <c r="C10" s="19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>KA3 NO e KA4 NC, optoacoplados</t>
+          <t>KA1 NO, KA2 NC e KA3 NO, optoacoplados; caixa DIN 6M</t>
         </is>
       </c>
       <c r="E10" s="19" t="inlineStr">
@@ -6873,11 +6605,11 @@
         </is>
       </c>
       <c r="C18" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" s="19" t="inlineStr">
         <is>
-          <t>Emergencia, START, STOP e REARME</t>
+          <t>Emergencia (cogumelo), LIGAR verde e STOP preto</t>
         </is>
       </c>
       <c r="E18" s="19" t="inlineStr">
@@ -7230,7 +6962,7 @@
       </c>
       <c r="D3" s="20" t="inlineStr">
         <is>
-          <t>P1/painel -&gt; KA2 -&gt; BD-POT -&gt; BTS</t>
+          <t>P1/painel -&gt; KM1 -&gt; BD-POT -&gt; BTS</t>
         </is>
       </c>
       <c r="E3" s="20" t="inlineStr">

--- a/BOM_Projeto_Integrador.xlsx
+++ b/BOM_Projeto_Integrador.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Dados do Projeto" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lista de Compras'!$A$4:$K$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lista de Compras'!$A$4:$K$165</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Inventario React'!$A$1:$E$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Fiacao React'!$A$1:$E$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Divergencias'!$A$1:$E$8</definedName>
@@ -582,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K168"/>
+  <dimension ref="A1:K167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -608,7 +608,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Lista de materiais · gerada de 03_lista_materiais.md em 20/08/2026 16:42 · arquitetura 127 V CA → 24 V CC → 12 / 5 / 3,3 V</t>
+          <t>Lista de materiais · gerada de 03_lista_materiais.md em 21/08/2026 15:11 · arquitetura 127 V CA → 24 V CC → 12 / 5 / 3,3 V</t>
         </is>
       </c>
     </row>
@@ -5743,17 +5743,17 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>⭐ Borne de passagem DIN 2,5 mm²</t>
+          <t>Capacitor cerâmico 100 nF</t>
         </is>
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>BS-1 — 3 em uso (A0, A1, 0V) + 3 reserva. ⚠️ 2,5 mm², não 1,5: em dois deles entram três condutores (fio do BTS, fio do Arduino e perna do capacitor)</t>
+          <t>C1 e C2 + reservas — parafusados nos bornes do Mega (A0–GND2 e A1–GND2), sem solda</t>
         </is>
       </c>
       <c r="E157" s="11" t="inlineStr">
@@ -5762,14 +5762,17 @@
         </is>
       </c>
       <c r="F157" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/borne-passagem-din-2-5-mm","🔎 borne passagem din 2,5 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/capacitor-ceramico-100-nf","🔎 capacitor ceramico 100 nf")</f>
         <v/>
       </c>
       <c r="G157" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=borne+passagem+din+2%2C5+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H157" s="13" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=capacitor+ceramico+100+nf","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H157" s="15">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-100nf-ceramic-capacitor.html","🌏 100nF ceramic capacitor")</f>
+        <v/>
+      </c>
       <c r="I157" s="13" t="inlineStr"/>
       <c r="J157" s="14" t="inlineStr"/>
       <c r="K157" s="14">
@@ -5783,36 +5786,33 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>Capacitor cerâmico 100 nF</t>
+          <t>⭐ Módulo relé 1 canal 5 V, optoacoplado</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
         <is>
-          <t>C1 e C2 + reservas — parafusados no BS-1, sem solda</t>
+          <t>KA1 (NO), KA2 (NC) e KA3 (NO), optoacoplados, caixa DIN 6M; reservas opcionais</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6,79</t>
         </is>
       </c>
       <c r="F158" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/capacitor-ceramico-100-nf","🔎 capacitor ceramico 100 nf")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/modulo-rele-1-canal-5-v-optoacoplado","🔎 modulo rele 1 canal 5 v, opt")</f>
         <v/>
       </c>
       <c r="G158" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=capacitor+ceramico+100+nf","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H158" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-100nf-ceramic-capacitor.html","🌏 100nF ceramic capacitor")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=modulo+rele+1+canal+5+v%2C+optoacoplado","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H158" s="8" t="inlineStr"/>
       <c r="I158" s="8" t="inlineStr"/>
       <c r="J158" s="9" t="inlineStr"/>
       <c r="K158" s="9">
@@ -5826,30 +5826,30 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>⭐ Módulo relé 1 canal 5 V, optoacoplado</t>
+          <t>⭐ Caixa modular DIN 6 módulos (105 mm)</t>
         </is>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>KA1 (NO), KA2 (NC) e KA3 (NO), optoacoplados, caixa DIN 6M; reservas opcionais</t>
+          <t>Abriga os três módulos de relé empilhados, no trilho 2. ⚠️ NÃO a de 4M: 3 × 25,5 mm = 76,5 mm e a de 4M tem 70 mm. Mesmo assim o trilho 2 ficou mais folgado — o MV-1, que saiu, media 66 mm</t>
         </is>
       </c>
       <c r="E159" s="11" t="inlineStr">
         <is>
-          <t>6,79</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F159" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/modulo-rele-1-canal-5-v-optoacoplado","🔎 modulo rele 1 canal 5 v, opt")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/caixa-modular-din-6-modulos","🔎 caixa modular din 6 modulos")</f>
         <v/>
       </c>
       <c r="G159" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=modulo+rele+1+canal+5+v%2C+optoacoplado","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=caixa+modular+din+6+modulos","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H159" s="13" t="inlineStr"/>
@@ -5866,17 +5866,17 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>⭐ Caixa modular DIN 6 módulos (105 mm)</t>
+          <t>⭐ Resistor 10 kΩ · ¼ W</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>Abriga os três módulos de relé empilhados, no trilho 2. ⚠️ NÃO a de 4M: 3 × 25,5 mm = 76,5 mm e a de 4M tem 70 mm. Mesmo assim o trilho 2 ficou mais folgado — o MV-1, que saiu, media 66 mm</t>
+          <t>R10, R11 e ⭐ R12 (pull-down dos IN dos três módulos) + R8 e R9 (soldados nos BTS7960). ⚠️ É o que torna o fail-safe medível: Arduino ausente ou fio rompido → IN em 0 V → potência cortada e ventoinha girando</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
@@ -5885,14 +5885,17 @@
         </is>
       </c>
       <c r="F160" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/caixa-modular-din-6-modulos","🔎 caixa modular din 6 modulos")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-10-k","🔎 resistor 10 k")</f>
         <v/>
       </c>
       <c r="G160" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=caixa+modular+din+6+modulos","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H160" s="8" t="inlineStr"/>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+10+k","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H160" s="16">
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
+        <v/>
+      </c>
       <c r="I160" s="8" t="inlineStr"/>
       <c r="J160" s="9" t="inlineStr"/>
       <c r="K160" s="9">
@@ -5906,17 +5909,17 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>⭐ Resistor 10 kΩ · ¼ W</t>
+          <t>⭐ Diodo 1N4007</t>
         </is>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>R10, R11 e ⭐ R12 (pull-down dos IN dos três módulos) + R8 e R9 (soldados nos BTS7960). ⚠️ É o que torna o fail-safe medível: Arduino ausente ou fio rompido → IN em 0 V → potência cortada e ventoinha girando</t>
+          <t>D1 (bobina do KM1), D2 (ventoinhas do radiador) e ⭐ D3 (as 5 internas) + 1 reserva. 🔎 O D1 pode ser dispensável: teste o KM1 em *teste de diodo* entre A1 e A2 — se conduzir num sentido só, ele já tem diodo interno. ⚠️ O D2 e o D3 são obrigatórios — o D3 entrou quando o MV-1 saiu: o módulo MOSFET trazia o roda-livre dentro da placa, o contato do KA3 não traz nada</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr">
@@ -5925,15 +5928,15 @@
         </is>
       </c>
       <c r="F161" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/resistor-10-k","🔎 resistor 10 k")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/diodo-1n4007","🔎 diodo 1n4007")</f>
         <v/>
       </c>
       <c r="G161" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=resistor+10+k","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=diodo+1n4007","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H161" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1-4w-resistor-kit-assorted.html","🌏 1/4W resistor kit assorted")</f>
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1n4007-diode.html","🌏 1N4007 diode")</f>
         <v/>
       </c>
       <c r="I161" s="13" t="inlineStr"/>
@@ -5949,17 +5952,17 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>⭐ Diodo 1N4007</t>
+          <t>Termorretrátil Ø 2 mm</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30 cm</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>D1 (bobina do KM1), D2 (ventoinhas do radiador) e ⭐ D3 (as 5 internas) + 1 reserva. 🔎 O D1 pode ser dispensável: teste o KM1 em *teste de diodo* entre A1 e A2 — se conduzir num sentido só, ele já tem diodo interno. ⚠️ O D2 e o D3 são obrigatórios — o D3 entrou quando o MV-1 saiu: o módulo MOSFET trazia o roda-livre dentro da placa, o contato do KA3 não traz nada</t>
+          <t>Isolação dos 10 kΩ soldados nos BTS7960 e das emendas nos postes</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
@@ -5968,15 +5971,15 @@
         </is>
       </c>
       <c r="F162" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/diodo-1n4007","🔎 diodo 1n4007")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/termorretratil-2-mm","🔎 termorretratil 2 mm")</f>
         <v/>
       </c>
       <c r="G162" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=diodo+1n4007","🔎 Amazon")</f>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=termorretratil+2+mm","🔎 Amazon")</f>
         <v/>
       </c>
       <c r="H162" s="16">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-1n4007-diode.html","🌏 1N4007 diode")</f>
+        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-heat-shrink-tubing-kit.html","🌏 heat shrink tubing kit")</f>
         <v/>
       </c>
       <c r="I162" s="8" t="inlineStr"/>
@@ -5992,17 +5995,17 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>Termorretrátil Ø 2 mm</t>
+          <t>Etiqueta impressa em papel adesivo</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>30 cm</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>Isolação dos 10 kΩ soldados nos BTS7960 e das emendas nos postes</t>
+          <t>Identificação dos bornes — é o que torna a montagem auditável</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr">
@@ -6011,17 +6014,14 @@
         </is>
       </c>
       <c r="F163" s="12">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/termorretratil-2-mm","🔎 termorretratil 2 mm")</f>
+        <f>HYPERLINK("https://lista.mercadolivre.com.br/etiqueta-impressa-papel-adesivo","🔎 etiqueta impressa papel ades")</f>
         <v/>
       </c>
       <c r="G163" s="12">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=termorretratil+2+mm","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H163" s="15">
-        <f>HYPERLINK("https://pt.aliexpress.com/w/wholesale-heat-shrink-tubing-kit.html","🌏 heat shrink tubing kit")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK("https://www.amazon.com.br/s?k=etiqueta+impressa+papel+adesivo","🔎 Amazon")</f>
+        <v/>
+      </c>
+      <c r="H163" s="13" t="inlineStr"/>
       <c r="I163" s="13" t="inlineStr"/>
       <c r="J163" s="14" t="inlineStr"/>
       <c r="K163" s="14">
@@ -6029,105 +6029,66 @@
         <v/>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="5" t="n">
+    <row r="164" ht="22" customHeight="1">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>L.3 — Atuadores térmicos e ventilação</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="10" t="n">
         <v>142</v>
       </c>
-      <c r="B164" s="6" t="inlineStr">
-        <is>
-          <t>Etiqueta impressa em papel adesivo</t>
-        </is>
-      </c>
-      <c r="C164" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D164" s="6" t="inlineStr">
-        <is>
-          <t>Identificação dos bornes — é o que torna a montagem auditável</t>
-        </is>
-      </c>
-      <c r="E164" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F164" s="7">
-        <f>HYPERLINK("https://lista.mercadolivre.com.br/etiqueta-impressa-papel-adesivo","🔎 etiqueta impressa papel ades")</f>
-        <v/>
-      </c>
-      <c r="G164" s="7">
-        <f>HYPERLINK("https://www.amazon.com.br/s?k=etiqueta+impressa+papel+adesivo","🔎 Amazon")</f>
-        <v/>
-      </c>
-      <c r="H164" s="8" t="inlineStr"/>
-      <c r="I164" s="8" t="inlineStr"/>
-      <c r="J164" s="9" t="inlineStr"/>
-      <c r="K164" s="9">
-        <f>IF(C164*J164=0,"",C164*J164)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="165" ht="22" customHeight="1">
-      <c r="A165" s="4" t="inlineStr">
-        <is>
-          <t>L.3 — Atuadores térmicos e ventilação</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="5" t="n">
-        <v>143</v>
-      </c>
-      <c r="B166" s="6" t="inlineStr">
+      <c r="B165" s="11" t="inlineStr">
         <is>
           <t>Ventoinha interna 12 V — grupo React</t>
         </is>
       </c>
-      <c r="C166" s="5" t="inlineStr">
+      <c r="C165" s="10" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D166" s="6" t="inlineStr">
+      <c r="D165" s="11" t="inlineStr">
         <is>
           <t>Cinco unidades compatíveis com a geometria atual: 2 frias, 2 dos dutos e 1 do PTC; ligadas em paralelo</t>
         </is>
       </c>
-      <c r="E166" s="6" t="inlineStr">
+      <c r="E165" s="11" t="inlineStr">
         <is>
           <t>Confirmar dimensao fisica antes da compra</t>
         </is>
       </c>
-      <c r="F166" s="8" t="inlineStr"/>
-      <c r="G166" s="8" t="inlineStr"/>
-      <c r="H166" s="8" t="inlineStr"/>
-      <c r="I166" s="8" t="inlineStr"/>
-      <c r="J166" s="9" t="inlineStr"/>
-      <c r="K166" s="9">
-        <f>IF(C166*J166=0,"",C166*J166)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="168">
-      <c r="I168" s="17" t="inlineStr">
+      <c r="F165" s="13" t="inlineStr"/>
+      <c r="G165" s="13" t="inlineStr"/>
+      <c r="H165" s="13" t="inlineStr"/>
+      <c r="I165" s="13" t="inlineStr"/>
+      <c r="J165" s="14" t="inlineStr"/>
+      <c r="K165" s="14">
+        <f>IF(C165*J165=0,"",C165*J165)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="I167" s="17" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="K168" s="18">
-        <f>SUM(K5:K166)</f>
+      <c r="K167" s="18">
+        <f>SUM(K5:K165)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K166"/>
+  <autoFilter ref="A4:K165"/>
   <mergeCells count="21">
     <mergeCell ref="A148:K148"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A61:K61"/>
     <mergeCell ref="A119:K119"/>
+    <mergeCell ref="A164:K164"/>
     <mergeCell ref="A37:K37"/>
     <mergeCell ref="A75:K75"/>
     <mergeCell ref="A136:K136"/>
@@ -6142,7 +6103,6 @@
     <mergeCell ref="A131:K131"/>
     <mergeCell ref="A20:K20"/>
     <mergeCell ref="A109:K109"/>
-    <mergeCell ref="A165:K165"/>
     <mergeCell ref="A43:K43"/>
     <mergeCell ref="A28:K28"/>
   </mergeCells>
